--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -30,6 +30,12 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Valor Despesa Empenhada</t>
+  </si>
+  <si>
+    <t>Valor Despesa Liquidada</t>
+  </si>
+  <si>
     <t>Valor Pago Financeiro</t>
   </si>
   <si>
@@ -207,6 +213,15 @@
     <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
   </si>
   <si>
+    <t>DEPARTAMENTO ESTADUAL DE TRANSITO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
     <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
   </si>
   <si>
@@ -244,9 +259,6 @@
   </si>
   <si>
     <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
   </si>
   <si>
     <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
@@ -275,7 +287,6 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -628,20 +639,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="4" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -654,17 +665,23 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>2026</v>
       </c>
@@ -672,22 +689,28 @@
         <v>1071</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="6">
-        <v>16295779.970000001</v>
+        <v>47296961.18</v>
       </c>
       <c r="E2" s="6">
+        <v>17762704.210000001</v>
+      </c>
+      <c r="F2" s="6">
+        <v>16468944.359999999</v>
+      </c>
+      <c r="G2" s="6">
         <v>1803218.12</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>7164940.5</v>
       </c>
-      <c r="G2" s="7">
+      <c r="I2" s="7">
         <v>8968158.6199999992</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2026</v>
       </c>
@@ -695,22 +718,28 @@
         <v>1081</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
-        <v>287474854.24000001</v>
+        <v>475166200.5</v>
       </c>
       <c r="E3" s="6">
-        <v>185260611.18000001</v>
+        <v>323260734.91000003</v>
       </c>
       <c r="F3" s="6">
-        <v>2288513.56</v>
-      </c>
-      <c r="G3" s="7">
-        <v>187549124.74000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>300881053.19</v>
+      </c>
+      <c r="G3" s="6">
+        <v>185261438.00999999</v>
+      </c>
+      <c r="H3" s="6">
+        <v>2330328.19</v>
+      </c>
+      <c r="I3" s="7">
+        <v>187591766.19999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>2026</v>
       </c>
@@ -718,22 +747,28 @@
         <v>1101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6">
-        <v>6064048.7300000004</v>
+        <v>6456220.3499999996</v>
       </c>
       <c r="E4" s="6">
-        <v>0</v>
+        <v>6132346.29</v>
       </c>
       <c r="F4" s="6">
+        <v>6097151.2300000004</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
         <v>93457.72</v>
       </c>
-      <c r="G4" s="7">
+      <c r="I4" s="7">
         <v>93457.72</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2026</v>
       </c>
@@ -741,22 +776,28 @@
         <v>1191</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
-        <v>538626026.98000002</v>
+        <v>634243573.63999999</v>
       </c>
       <c r="E5" s="6">
+        <v>548217152.97000003</v>
+      </c>
+      <c r="F5" s="6">
+        <v>540816039.25999999</v>
+      </c>
+      <c r="G5" s="6">
         <v>7665444.21</v>
       </c>
-      <c r="F5" s="6">
-        <v>47235212.030000001</v>
-      </c>
-      <c r="G5" s="7">
-        <v>54900656.240000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H5" s="6">
+        <v>47259141.600000001</v>
+      </c>
+      <c r="I5" s="7">
+        <v>54924585.810000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2026</v>
       </c>
@@ -764,22 +805,28 @@
         <v>1221</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6">
-        <v>15226799.949999999</v>
+        <v>35956687.219999999</v>
       </c>
       <c r="E6" s="6">
-        <v>0</v>
+        <v>16189796.859999999</v>
       </c>
       <c r="F6" s="6">
-        <v>11788720.34</v>
-      </c>
-      <c r="G6" s="7">
-        <v>11788720.34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15677126.189999999</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>18511927.670000002</v>
+      </c>
+      <c r="I6" s="7">
+        <v>18511927.670000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2026</v>
       </c>
@@ -787,22 +834,28 @@
         <v>1231</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6">
-        <v>24537278.699999999</v>
+        <v>52711036.75</v>
       </c>
       <c r="E7" s="6">
+        <v>25505408.899999999</v>
+      </c>
+      <c r="F7" s="6">
+        <v>24898693.030000001</v>
+      </c>
+      <c r="G7" s="6">
         <v>5876518.1600000001</v>
       </c>
-      <c r="F7" s="6">
-        <v>14063571.890000001</v>
-      </c>
-      <c r="G7" s="7">
-        <v>19940090.050000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H7" s="6">
+        <v>14113229.130000001</v>
+      </c>
+      <c r="I7" s="7">
+        <v>19989747.289999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
@@ -810,22 +863,28 @@
         <v>1251</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
-        <v>5558550889.1300001</v>
+        <v>5737870712.0100002</v>
       </c>
       <c r="E8" s="6">
+        <v>5580080641.2200003</v>
+      </c>
+      <c r="F8" s="6">
+        <v>5561312916.3299999</v>
+      </c>
+      <c r="G8" s="6">
         <v>18529479.850000001</v>
       </c>
-      <c r="F8" s="6">
-        <v>121684680.26000001</v>
-      </c>
-      <c r="G8" s="7">
-        <v>140214160.11000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H8" s="6">
+        <v>124290111.84999999</v>
+      </c>
+      <c r="I8" s="7">
+        <v>142819591.69999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2026</v>
       </c>
@@ -833,22 +892,28 @@
         <v>1261</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6">
-        <v>5820816218.1800003</v>
+        <v>6166912492.6400003</v>
       </c>
       <c r="E9" s="6">
-        <v>195131022.58000001</v>
+        <v>5911919418.1899996</v>
       </c>
       <c r="F9" s="6">
-        <v>111400935.27</v>
-      </c>
-      <c r="G9" s="7">
-        <v>306531957.85000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>5867772743.0200005</v>
+      </c>
+      <c r="G9" s="6">
+        <v>195886022.58000001</v>
+      </c>
+      <c r="H9" s="6">
+        <v>117179182.12</v>
+      </c>
+      <c r="I9" s="7">
+        <v>313065204.69999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2026</v>
       </c>
@@ -856,22 +921,28 @@
         <v>1271</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6">
-        <v>19544037.949999999</v>
+        <v>33497399.16</v>
       </c>
       <c r="E10" s="6">
+        <v>22869000.129999999</v>
+      </c>
+      <c r="F10" s="6">
+        <v>22206092.890000001</v>
+      </c>
+      <c r="G10" s="6">
         <v>319615.87</v>
       </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>619454.23</v>
       </c>
-      <c r="G10" s="7">
+      <c r="I10" s="7">
         <v>939070.1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>2026</v>
       </c>
@@ -879,22 +950,28 @@
         <v>1301</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="6">
-        <v>32993697.5</v>
+        <v>63327544.759999998</v>
       </c>
       <c r="E11" s="6">
+        <v>53499338.670000002</v>
+      </c>
+      <c r="F11" s="6">
+        <v>36085029.530000001</v>
+      </c>
+      <c r="G11" s="6">
         <v>15843807.77</v>
       </c>
-      <c r="F11" s="6">
-        <v>18922440.350000001</v>
-      </c>
-      <c r="G11" s="7">
-        <v>34766248.119999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H11" s="6">
+        <v>19738535.940000001</v>
+      </c>
+      <c r="I11" s="7">
+        <v>35582343.710000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2026</v>
       </c>
@@ -902,22 +979,28 @@
         <v>1371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6">
-        <v>68403276.239999995</v>
+        <v>75778333.530000001</v>
       </c>
       <c r="E12" s="6">
+        <v>71100779.090000004</v>
+      </c>
+      <c r="F12" s="6">
+        <v>68681775.329999998</v>
+      </c>
+      <c r="G12" s="6">
         <v>3823909.86</v>
       </c>
-      <c r="F12" s="6">
+      <c r="H12" s="6">
         <v>4333968.6100000003</v>
       </c>
-      <c r="G12" s="7">
+      <c r="I12" s="7">
         <v>8157878.4699999997</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>2026</v>
       </c>
@@ -925,22 +1008,28 @@
         <v>1401</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6">
-        <v>653450793.72000003</v>
+        <v>687905256.80999994</v>
       </c>
       <c r="E13" s="6">
+        <v>663871176.23000002</v>
+      </c>
+      <c r="F13" s="6">
+        <v>660799554.26999998</v>
+      </c>
+      <c r="G13" s="6">
         <v>6046803.8799999999</v>
       </c>
-      <c r="F13" s="6">
-        <v>25059331.129999999</v>
-      </c>
-      <c r="G13" s="7">
-        <v>31106135.010000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H13" s="6">
+        <v>25820867.629999999</v>
+      </c>
+      <c r="I13" s="7">
+        <v>31867671.510000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2026</v>
       </c>
@@ -948,22 +1037,28 @@
         <v>1451</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6">
-        <v>1381530348</v>
+        <v>1765951109.97</v>
       </c>
       <c r="E14" s="6">
-        <v>10020496.199999999</v>
+        <v>1439818522</v>
       </c>
       <c r="F14" s="6">
-        <v>108865524</v>
-      </c>
-      <c r="G14" s="7">
-        <v>118886020.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1407876726.23</v>
+      </c>
+      <c r="G14" s="6">
+        <v>14179981.15</v>
+      </c>
+      <c r="H14" s="6">
+        <v>110019564.72</v>
+      </c>
+      <c r="I14" s="7">
+        <v>124199545.87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2026</v>
       </c>
@@ -971,22 +1066,28 @@
         <v>1481</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6">
-        <v>36588551.729999997</v>
+        <v>41339288.020000003</v>
       </c>
       <c r="E15" s="6">
+        <v>37824839.219999999</v>
+      </c>
+      <c r="F15" s="6">
+        <v>37061535.469999999</v>
+      </c>
+      <c r="G15" s="6">
         <v>10843996.220000001</v>
       </c>
-      <c r="F15" s="6">
-        <v>9383797.3300000001</v>
-      </c>
-      <c r="G15" s="7">
-        <v>20227793.550000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H15" s="6">
+        <v>9740189.9100000001</v>
+      </c>
+      <c r="I15" s="7">
+        <v>20584186.129999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2026</v>
       </c>
@@ -994,22 +1095,28 @@
         <v>1491</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6">
-        <v>21287438.800000001</v>
+        <v>48000443.009999998</v>
       </c>
       <c r="E16" s="6">
-        <v>11104200.970000001</v>
+        <v>42840007.640000001</v>
       </c>
       <c r="F16" s="6">
+        <v>21316072.600000001</v>
+      </c>
+      <c r="G16" s="6">
+        <v>11104724.689999999</v>
+      </c>
+      <c r="H16" s="6">
         <v>2787214.53</v>
       </c>
-      <c r="G16" s="7">
-        <v>13891415.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I16" s="7">
+        <v>13891939.220000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>2026</v>
       </c>
@@ -1017,22 +1124,28 @@
         <v>1501</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
-        <v>162269444.46000001</v>
+        <v>290892001.44</v>
       </c>
       <c r="E17" s="6">
+        <v>195866521.90000001</v>
+      </c>
+      <c r="F17" s="6">
+        <v>164840594.19</v>
+      </c>
+      <c r="G17" s="6">
         <v>28627234.710000001</v>
       </c>
-      <c r="F17" s="6">
-        <v>61178194.159999996</v>
-      </c>
-      <c r="G17" s="7">
-        <v>89805428.870000005</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="6">
+        <v>61849177.25</v>
+      </c>
+      <c r="I17" s="7">
+        <v>90476411.959999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2026</v>
       </c>
@@ -1040,22 +1153,28 @@
         <v>1511</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
-        <v>1000081662.99</v>
+        <v>1082875309.95</v>
       </c>
       <c r="E18" s="6">
-        <v>6902879.3300000001</v>
+        <v>1014232057.02</v>
       </c>
       <c r="F18" s="6">
-        <v>27017055.920000002</v>
-      </c>
-      <c r="G18" s="7">
-        <v>33919935.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1002467372.65</v>
+      </c>
+      <c r="G18" s="6">
+        <v>6917250.9299999997</v>
+      </c>
+      <c r="H18" s="6">
+        <v>27582493.739999998</v>
+      </c>
+      <c r="I18" s="7">
+        <v>34499744.670000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>2026</v>
       </c>
@@ -1063,22 +1182,28 @@
         <v>1521</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="6">
-        <v>22232158.850000001</v>
+        <v>23271506.07</v>
       </c>
       <c r="E19" s="6">
+        <v>22896428.489999998</v>
+      </c>
+      <c r="F19" s="6">
+        <v>22237870.350000001</v>
+      </c>
+      <c r="G19" s="6">
         <v>5062</v>
       </c>
-      <c r="F19" s="6">
+      <c r="H19" s="6">
         <v>1303921.8600000001</v>
       </c>
-      <c r="G19" s="7">
+      <c r="I19" s="7">
         <v>1308983.8600000001</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>2026</v>
       </c>
@@ -1086,22 +1211,28 @@
         <v>1541</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6">
-        <v>6856552.1200000001</v>
+        <v>8451407.9000000004</v>
       </c>
       <c r="E20" s="6">
+        <v>7185645.0800000001</v>
+      </c>
+      <c r="F20" s="6">
+        <v>7031312.1600000001</v>
+      </c>
+      <c r="G20" s="6">
         <v>211093.49</v>
       </c>
-      <c r="F20" s="6">
+      <c r="H20" s="6">
         <v>912131.83</v>
       </c>
-      <c r="G20" s="7">
+      <c r="I20" s="7">
         <v>1123225.32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>2026</v>
       </c>
@@ -1109,22 +1240,28 @@
         <v>1631</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
-        <v>3750808.11</v>
+        <v>4197797.3499999996</v>
       </c>
       <c r="E21" s="6">
-        <v>0</v>
+        <v>3919473.04</v>
       </c>
       <c r="F21" s="6">
+        <v>3860536.43</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
         <v>34378.25</v>
       </c>
-      <c r="G21" s="7">
+      <c r="I21" s="7">
         <v>34378.25</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>2026</v>
       </c>
@@ -1132,22 +1269,28 @@
         <v>1711</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
-        <v>11629480.93</v>
+        <v>72559654.200000003</v>
       </c>
       <c r="E22" s="6">
+        <v>15978116.050000001</v>
+      </c>
+      <c r="F22" s="6">
+        <v>13850567.07</v>
+      </c>
+      <c r="G22" s="6">
         <v>60000.1</v>
       </c>
-      <c r="F22" s="6">
-        <v>40243843.719999999</v>
-      </c>
-      <c r="G22" s="7">
-        <v>40303843.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H22" s="6">
+        <v>43286985.07</v>
+      </c>
+      <c r="I22" s="7">
+        <v>43346985.170000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>2026</v>
       </c>
@@ -1155,22 +1298,28 @@
         <v>1721</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
-        <v>3082688.34</v>
+        <v>3596883.39</v>
       </c>
       <c r="E23" s="6">
+        <v>3264097.83</v>
+      </c>
+      <c r="F23" s="6">
+        <v>3194498.71</v>
+      </c>
+      <c r="G23" s="6">
         <v>122407.67</v>
       </c>
-      <c r="F23" s="6">
-        <v>102945.51</v>
-      </c>
-      <c r="G23" s="7">
-        <v>225353.18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H23" s="6">
+        <v>190745.3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>313152.96999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>2026</v>
       </c>
@@ -1178,22 +1327,28 @@
         <v>1911</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6">
-        <v>263817094.19999999</v>
+        <v>500800000</v>
       </c>
       <c r="E24" s="6">
-        <v>0</v>
+        <v>267538449.13</v>
       </c>
       <c r="F24" s="6">
+        <v>267538449.13</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
         <v>73808566.599999994</v>
       </c>
-      <c r="G24" s="7">
+      <c r="I24" s="7">
         <v>73808566.599999994</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>2026</v>
       </c>
@@ -1201,16 +1356,22 @@
         <v>1915</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
         <v>7172133.3600000003</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="6">
+        <v>7172133.3600000003</v>
+      </c>
+      <c r="F25" s="6">
+        <v>7172133.3600000003</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7"/>
+    </row>
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>2026</v>
       </c>
@@ -1218,22 +1379,28 @@
         <v>1916</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="6">
-        <v>2144268567.24</v>
+        <v>3576955016.79</v>
       </c>
       <c r="E26" s="6">
-        <v>0</v>
+        <v>2292274874.1399999</v>
       </c>
       <c r="F26" s="6">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2257151412.25</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>2026</v>
       </c>
@@ -1241,22 +1408,28 @@
         <v>1941</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6">
-        <v>56809133.600000001</v>
+        <v>59674219.560000002</v>
       </c>
       <c r="E27" s="6">
-        <v>0</v>
+        <v>58238503.140000001</v>
       </c>
       <c r="F27" s="6">
+        <v>58238141.240000002</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
         <v>874849.53</v>
       </c>
-      <c r="G27" s="7">
+      <c r="I27" s="7">
         <v>874849.53</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>2026</v>
       </c>
@@ -1264,22 +1437,28 @@
         <v>2011</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D28" s="6">
-        <v>400016617.33999997</v>
+        <v>949315008.29999995</v>
       </c>
       <c r="E28" s="6">
+        <v>464549757.69</v>
+      </c>
+      <c r="F28" s="6">
+        <v>439561051.69</v>
+      </c>
+      <c r="G28" s="6">
         <v>94822.57</v>
       </c>
-      <c r="F28" s="6">
-        <v>186372004.46000001</v>
-      </c>
-      <c r="G28" s="7">
-        <v>186466827.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H28" s="6">
+        <v>187574350.50999999</v>
+      </c>
+      <c r="I28" s="7">
+        <v>187669173.08000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>2026</v>
       </c>
@@ -1287,22 +1466,28 @@
         <v>2041</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6">
-        <v>940981.13</v>
+        <v>1156855.81</v>
       </c>
       <c r="E29" s="6">
+        <v>951635.5</v>
+      </c>
+      <c r="F29" s="6">
+        <v>944239.66</v>
+      </c>
+      <c r="G29" s="6">
         <v>1692.39</v>
       </c>
-      <c r="F29" s="6">
+      <c r="H29" s="6">
         <v>32310.94</v>
       </c>
-      <c r="G29" s="7">
+      <c r="I29" s="7">
         <v>34003.33</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>2026</v>
       </c>
@@ -1310,22 +1495,28 @@
         <v>2061</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6">
-        <v>19581893.43</v>
+        <v>24180971.109999999</v>
       </c>
       <c r="E30" s="6">
+        <v>21226298.149999999</v>
+      </c>
+      <c r="F30" s="6">
+        <v>20171643.030000001</v>
+      </c>
+      <c r="G30" s="6">
         <v>27688.16</v>
       </c>
-      <c r="F30" s="6">
-        <v>1607919.84</v>
-      </c>
-      <c r="G30" s="7">
-        <v>1635608</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H30" s="6">
+        <v>1609342.68</v>
+      </c>
+      <c r="I30" s="7">
+        <v>1637030.84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2026</v>
       </c>
@@ -1333,22 +1524,28 @@
         <v>2071</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="6">
-        <v>143069964.80000001</v>
+        <v>216009218.40000001</v>
       </c>
       <c r="E31" s="6">
-        <v>3249104.27</v>
+        <v>164768656.49000001</v>
       </c>
       <c r="F31" s="6">
+        <v>158940876.25</v>
+      </c>
+      <c r="G31" s="6">
+        <v>3290143.43</v>
+      </c>
+      <c r="H31" s="6">
         <v>1687592.31</v>
       </c>
-      <c r="G31" s="7">
-        <v>4936696.58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I31" s="7">
+        <v>4977735.74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>2026</v>
       </c>
@@ -1356,22 +1553,28 @@
         <v>2091</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" s="6">
-        <v>19389687.75</v>
+        <v>20935102</v>
       </c>
       <c r="E32" s="6">
-        <v>0</v>
+        <v>20340714.289999999</v>
       </c>
       <c r="F32" s="6">
-        <v>1005602.11</v>
-      </c>
-      <c r="G32" s="7">
-        <v>1005602.11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>19517092.48</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6">
+        <v>1008879.61</v>
+      </c>
+      <c r="I32" s="7">
+        <v>1008879.61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>2026</v>
       </c>
@@ -1379,22 +1582,28 @@
         <v>2101</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6">
-        <v>59415428.259999998</v>
+        <v>68683326.209999993</v>
       </c>
       <c r="E33" s="6">
+        <v>65614600.07</v>
+      </c>
+      <c r="F33" s="6">
+        <v>61894933.130000003</v>
+      </c>
+      <c r="G33" s="6">
         <v>486532.65</v>
       </c>
-      <c r="F33" s="6">
-        <v>6080076.4500000002</v>
-      </c>
-      <c r="G33" s="7">
-        <v>6566609.0999999996</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H33" s="6">
+        <v>6594004.2699999996</v>
+      </c>
+      <c r="I33" s="7">
+        <v>7080536.9199999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>2026</v>
       </c>
@@ -1402,22 +1611,28 @@
         <v>2121</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6">
-        <v>1002707765.5</v>
+        <v>1037970788.45</v>
       </c>
       <c r="E34" s="6">
-        <v>19255569.109999999</v>
+        <v>1028850188.5</v>
       </c>
       <c r="F34" s="6">
-        <v>33680114.390000001</v>
-      </c>
-      <c r="G34" s="7">
-        <v>52935683.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1012522386.79</v>
+      </c>
+      <c r="G34" s="6">
+        <v>19255214.109999999</v>
+      </c>
+      <c r="H34" s="6">
+        <v>33681484.509999998</v>
+      </c>
+      <c r="I34" s="7">
+        <v>52936698.619999997</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2026</v>
       </c>
@@ -1425,22 +1640,28 @@
         <v>2151</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="6">
-        <v>17519928.789999999</v>
+        <v>20371977.489999998</v>
       </c>
       <c r="E35" s="6">
+        <v>18192249.879999999</v>
+      </c>
+      <c r="F35" s="6">
+        <v>17537921.43</v>
+      </c>
+      <c r="G35" s="6">
         <v>218.93</v>
       </c>
-      <c r="F35" s="6">
+      <c r="H35" s="6">
         <v>1759293.28</v>
       </c>
-      <c r="G35" s="7">
+      <c r="I35" s="7">
         <v>1759512.21</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>2026</v>
       </c>
@@ -1448,22 +1669,28 @@
         <v>2161</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D36" s="6">
-        <v>1635373.5</v>
+        <v>1948493.74</v>
       </c>
       <c r="E36" s="6">
+        <v>1726778.34</v>
+      </c>
+      <c r="F36" s="6">
+        <v>1690995.12</v>
+      </c>
+      <c r="G36" s="6">
         <v>23147.54</v>
       </c>
-      <c r="F36" s="6">
+      <c r="H36" s="6">
         <v>154559.29999999999</v>
       </c>
-      <c r="G36" s="7">
+      <c r="I36" s="7">
         <v>177706.84</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>2026</v>
       </c>
@@ -1471,22 +1698,28 @@
         <v>2171</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D37" s="6">
-        <v>1352729.62</v>
+        <v>1516625.71</v>
       </c>
       <c r="E37" s="6">
+        <v>1470109.4</v>
+      </c>
+      <c r="F37" s="6">
+        <v>1410521.41</v>
+      </c>
+      <c r="G37" s="6">
         <v>46386.19</v>
       </c>
-      <c r="F37" s="6">
+      <c r="H37" s="6">
         <v>61424.34</v>
       </c>
-      <c r="G37" s="7">
+      <c r="I37" s="7">
         <v>107810.53</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>2026</v>
       </c>
@@ -1494,22 +1727,28 @@
         <v>2181</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6">
-        <v>15199772.810000001</v>
+        <v>25290736.920000002</v>
       </c>
       <c r="E38" s="6">
+        <v>18689578.66</v>
+      </c>
+      <c r="F38" s="6">
+        <v>18305226.5</v>
+      </c>
+      <c r="G38" s="6">
         <v>866933.31</v>
       </c>
-      <c r="F38" s="6">
-        <v>1542751.92</v>
-      </c>
-      <c r="G38" s="7">
-        <v>2409685.23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H38" s="6">
+        <v>1570988.02</v>
+      </c>
+      <c r="I38" s="7">
+        <v>2437921.33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>2026</v>
       </c>
@@ -1517,22 +1756,28 @@
         <v>2201</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="6">
-        <v>5009615.25</v>
+        <v>9559397.6300000008</v>
       </c>
       <c r="E39" s="6">
+        <v>5486559.5899999999</v>
+      </c>
+      <c r="F39" s="6">
+        <v>5144751.49</v>
+      </c>
+      <c r="G39" s="6">
         <v>702452.89</v>
       </c>
-      <c r="F39" s="6">
+      <c r="H39" s="6">
         <v>171438.62</v>
       </c>
-      <c r="G39" s="7">
+      <c r="I39" s="7">
         <v>873891.51</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>2026</v>
       </c>
@@ -1540,22 +1785,28 @@
         <v>2211</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D40" s="6">
-        <v>3707883.18</v>
+        <v>5355866.43</v>
       </c>
       <c r="E40" s="6">
+        <v>4628249.3</v>
+      </c>
+      <c r="F40" s="6">
+        <v>3777513.36</v>
+      </c>
+      <c r="G40" s="6">
         <v>32410.16</v>
       </c>
-      <c r="F40" s="6">
+      <c r="H40" s="6">
         <v>528322.15</v>
       </c>
-      <c r="G40" s="7">
+      <c r="I40" s="7">
         <v>560732.31000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>2026</v>
       </c>
@@ -1563,22 +1814,28 @@
         <v>2241</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="6">
-        <v>15078688.08</v>
+        <v>16896938.399999999</v>
       </c>
       <c r="E41" s="6">
+        <v>16648250.1</v>
+      </c>
+      <c r="F41" s="6">
+        <v>15113567.859999999</v>
+      </c>
+      <c r="G41" s="6">
         <v>3494961.12</v>
       </c>
-      <c r="F41" s="6">
-        <v>10970856.23</v>
-      </c>
-      <c r="G41" s="7">
-        <v>14465817.35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H41" s="6">
+        <v>10971227.93</v>
+      </c>
+      <c r="I41" s="7">
+        <v>14466189.050000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>2026</v>
       </c>
@@ -1586,22 +1843,28 @@
         <v>2251</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6">
-        <v>11352212.310000001</v>
+        <v>16721416.470000001</v>
       </c>
       <c r="E42" s="6">
+        <v>11908821.4</v>
+      </c>
+      <c r="F42" s="6">
+        <v>11481949.59</v>
+      </c>
+      <c r="G42" s="6">
         <v>1119472.81</v>
       </c>
-      <c r="F42" s="6">
-        <v>1859591.11</v>
-      </c>
-      <c r="G42" s="7">
-        <v>2979063.92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H42" s="6">
+        <v>1859710.27</v>
+      </c>
+      <c r="I42" s="7">
+        <v>2979183.08</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>2026</v>
       </c>
@@ -1609,22 +1872,28 @@
         <v>2261</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
-        <v>54949129.700000003</v>
+        <v>180778052.05000001</v>
       </c>
       <c r="E43" s="6">
+        <v>106295658.56999999</v>
+      </c>
+      <c r="F43" s="6">
+        <v>59080755.57</v>
+      </c>
+      <c r="G43" s="6">
         <v>7187273.0700000003</v>
       </c>
-      <c r="F43" s="6">
-        <v>132524929.45999999</v>
-      </c>
-      <c r="G43" s="7">
-        <v>139712202.53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" s="6">
+        <v>132728906.18000001</v>
+      </c>
+      <c r="I43" s="7">
+        <v>139916179.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2026</v>
       </c>
@@ -1632,22 +1901,28 @@
         <v>2271</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D44" s="6">
-        <v>578211848.49000001</v>
+        <v>843081731.38</v>
       </c>
       <c r="E44" s="6">
+        <v>746324513.37</v>
+      </c>
+      <c r="F44" s="6">
+        <v>705585579.46000004</v>
+      </c>
+      <c r="G44" s="6">
         <v>6041131.1100000003</v>
       </c>
-      <c r="F44" s="6">
-        <v>84614687.780000001</v>
-      </c>
-      <c r="G44" s="7">
-        <v>90655818.890000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H44" s="6">
+        <v>86617453.730000004</v>
+      </c>
+      <c r="I44" s="7">
+        <v>92658584.840000004</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>2026</v>
       </c>
@@ -1655,22 +1930,28 @@
         <v>2281</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" s="6">
-        <v>1600452.53</v>
+        <v>2523284.88</v>
       </c>
       <c r="E45" s="6">
-        <v>0</v>
+        <v>2026144.68</v>
       </c>
       <c r="F45" s="6">
+        <v>1850775.05</v>
+      </c>
+      <c r="G45" s="6">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6">
         <v>263905.44</v>
       </c>
-      <c r="G45" s="7">
+      <c r="I45" s="7">
         <v>263905.44</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>2026</v>
       </c>
@@ -1678,22 +1959,28 @@
         <v>2301</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D46" s="6">
-        <v>193764125.31999999</v>
+        <v>689625578.38</v>
       </c>
       <c r="E46" s="6">
+        <v>237266334.03999999</v>
+      </c>
+      <c r="F46" s="6">
+        <v>216072010.84</v>
+      </c>
+      <c r="G46" s="6">
         <v>13431647.550000001</v>
       </c>
-      <c r="F46" s="6">
-        <v>180175241.63999999</v>
-      </c>
-      <c r="G46" s="7">
-        <v>193606889.19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H46" s="6">
+        <v>196109389.86000001</v>
+      </c>
+      <c r="I46" s="7">
+        <v>209541037.41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>2026</v>
       </c>
@@ -1701,22 +1988,28 @@
         <v>2311</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="6">
-        <v>137102764.08000001</v>
+        <v>158978150.13999999</v>
       </c>
       <c r="E47" s="6">
+        <v>141658060.38</v>
+      </c>
+      <c r="F47" s="6">
+        <v>139316185.75</v>
+      </c>
+      <c r="G47" s="6">
         <v>130453.78</v>
       </c>
-      <c r="F47" s="6">
-        <v>19217422.649999999</v>
-      </c>
-      <c r="G47" s="7">
-        <v>19347876.43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H47" s="6">
+        <v>20343140.899999999</v>
+      </c>
+      <c r="I47" s="7">
+        <v>20473594.68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>2026</v>
       </c>
@@ -1724,22 +2017,28 @@
         <v>2321</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D48" s="6">
-        <v>92626505.590000004</v>
+        <v>138145210.63</v>
       </c>
       <c r="E48" s="6">
+        <v>110988348.52</v>
+      </c>
+      <c r="F48" s="6">
+        <v>95866569.849999994</v>
+      </c>
+      <c r="G48" s="6">
         <v>3348075.28</v>
       </c>
-      <c r="F48" s="6">
-        <v>22344553.66</v>
-      </c>
-      <c r="G48" s="7">
-        <v>25692628.940000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H48" s="6">
+        <v>22677237.469999999</v>
+      </c>
+      <c r="I48" s="7">
+        <v>26025312.75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>2026</v>
       </c>
@@ -1747,22 +2046,28 @@
         <v>2331</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D49" s="6">
-        <v>10337102.27</v>
+        <v>11990138.84</v>
       </c>
       <c r="E49" s="6">
+        <v>11376371.01</v>
+      </c>
+      <c r="F49" s="6">
+        <v>10723240.09</v>
+      </c>
+      <c r="G49" s="6">
         <v>6330.51</v>
       </c>
-      <c r="F49" s="6">
+      <c r="H49" s="6">
         <v>1187624.3999999999</v>
       </c>
-      <c r="G49" s="7">
+      <c r="I49" s="7">
         <v>1193954.9099999999</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>2026</v>
       </c>
@@ -1770,22 +2075,28 @@
         <v>2351</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D50" s="6">
-        <v>116098959.02</v>
+        <v>140786513.16</v>
       </c>
       <c r="E50" s="6">
+        <v>121531292.38</v>
+      </c>
+      <c r="F50" s="6">
+        <v>119406929.73999999</v>
+      </c>
+      <c r="G50" s="6">
         <v>212410.94</v>
       </c>
-      <c r="F50" s="6">
-        <v>14427404.300000001</v>
-      </c>
-      <c r="G50" s="7">
-        <v>14639815.24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H50" s="6">
+        <v>15188861.85</v>
+      </c>
+      <c r="I50" s="7">
+        <v>15401272.789999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>2026</v>
       </c>
@@ -1793,22 +2104,28 @@
         <v>2371</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D51" s="6">
-        <v>92460916.620000005</v>
+        <v>100237548.39</v>
       </c>
       <c r="E51" s="6">
+        <v>94236338.920000002</v>
+      </c>
+      <c r="F51" s="6">
+        <v>93669365.950000003</v>
+      </c>
+      <c r="G51" s="6">
         <v>509913.92</v>
       </c>
-      <c r="F51" s="6">
-        <v>4195143.7300000004</v>
-      </c>
-      <c r="G51" s="7">
-        <v>4705057.6500000004</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H51" s="6">
+        <v>4348357.1399999997</v>
+      </c>
+      <c r="I51" s="7">
+        <v>4858271.0599999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>2026</v>
       </c>
@@ -1816,22 +2133,28 @@
         <v>2421</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="6">
-        <v>8087079.46</v>
+        <v>15125385.529999999</v>
       </c>
       <c r="E52" s="6">
+        <v>8624801.8000000007</v>
+      </c>
+      <c r="F52" s="6">
+        <v>8399639.6899999995</v>
+      </c>
+      <c r="G52" s="6">
         <v>1021786.93</v>
       </c>
-      <c r="F52" s="6">
-        <v>14884665.92</v>
-      </c>
-      <c r="G52" s="7">
-        <v>15906452.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H52" s="6">
+        <v>15170846.789999999</v>
+      </c>
+      <c r="I52" s="7">
+        <v>16192633.720000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2026</v>
       </c>
@@ -1839,22 +2162,28 @@
         <v>2431</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="6">
-        <v>2111644.96</v>
+        <v>2411669.2999999998</v>
       </c>
       <c r="E53" s="6">
+        <v>2215907.9300000002</v>
+      </c>
+      <c r="F53" s="6">
+        <v>2120383.35</v>
+      </c>
+      <c r="G53" s="6">
         <v>167935.23</v>
       </c>
-      <c r="F53" s="6">
+      <c r="H53" s="6">
         <v>59221.61</v>
       </c>
-      <c r="G53" s="7">
+      <c r="I53" s="7">
         <v>227156.84</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>2026</v>
       </c>
@@ -1862,22 +2191,28 @@
         <v>2441</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D54" s="6">
-        <v>6479985.29</v>
+        <v>7774139.46</v>
       </c>
       <c r="E54" s="6">
+        <v>6533896.4699999997</v>
+      </c>
+      <c r="F54" s="6">
+        <v>6482519.8399999999</v>
+      </c>
+      <c r="G54" s="6">
         <v>8281.7999999999993</v>
       </c>
-      <c r="F54" s="6">
+      <c r="H54" s="6">
         <v>127844.74</v>
       </c>
-      <c r="G54" s="7">
+      <c r="I54" s="7">
         <v>136126.54</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>2026</v>
       </c>
@@ -1885,22 +2220,28 @@
         <v>2461</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D55" s="6">
-        <v>1080556.24</v>
+        <v>1643347.9</v>
       </c>
       <c r="E55" s="6">
+        <v>1291377.56</v>
+      </c>
+      <c r="F55" s="6">
+        <v>1196505.19</v>
+      </c>
+      <c r="G55" s="6">
         <v>17304.09</v>
       </c>
-      <c r="F55" s="6">
+      <c r="H55" s="6">
         <v>667892.4</v>
       </c>
-      <c r="G55" s="7">
+      <c r="I55" s="7">
         <v>685196.49</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>2026</v>
       </c>
@@ -1908,405 +2249,543 @@
         <v>2471</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D56" s="6">
-        <v>8146643.4900000002</v>
+        <v>18699664.32</v>
       </c>
       <c r="E56" s="6">
-        <v>0</v>
+        <v>10612503.33</v>
       </c>
       <c r="F56" s="6">
+        <v>9617499.4100000001</v>
+      </c>
+      <c r="G56" s="6">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6">
         <v>2159796.8199999998</v>
       </c>
-      <c r="G56" s="7">
+      <c r="I56" s="7">
         <v>2159796.8199999998</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>2026</v>
       </c>
       <c r="B57" s="4">
+        <v>2481</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="6">
+        <v>10531480.77</v>
+      </c>
+      <c r="E57" s="6">
+        <v>10387159.42</v>
+      </c>
+      <c r="F57" s="6">
+        <v>9363687.6300000008</v>
+      </c>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="7"/>
+    </row>
+    <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="4">
+        <v>3041</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>79326076.849999994</v>
+      </c>
+      <c r="E58" s="6">
+        <v>79326076.849999994</v>
+      </c>
+      <c r="F58" s="6">
+        <v>79326076.849999994</v>
+      </c>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="7"/>
+    </row>
+    <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="4">
+        <v>3051</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="6">
+        <v>33188492.190000001</v>
+      </c>
+      <c r="E59" s="6">
+        <v>33188492.190000001</v>
+      </c>
+      <c r="F59" s="6">
+        <v>33188492.190000001</v>
+      </c>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="7"/>
+    </row>
+    <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="4">
         <v>4091</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6">
-        <v>0</v>
-      </c>
-      <c r="F57" s="6">
-        <v>0</v>
-      </c>
-      <c r="G57" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B58" s="4">
+      <c r="C60" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6">
+        <v>0</v>
+      </c>
+      <c r="I60" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="4">
         <v>4101</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C61" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="6">
         <v>3899649.54</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E61" s="6">
+        <v>3899649.54</v>
+      </c>
+      <c r="F61" s="6">
+        <v>3899649.54</v>
+      </c>
+      <c r="G61" s="6">
         <v>360498.89</v>
       </c>
-      <c r="F58" s="6">
-        <v>0</v>
-      </c>
-      <c r="G58" s="7">
+      <c r="H61" s="6">
+        <v>0</v>
+      </c>
+      <c r="I61" s="7">
         <v>360498.89</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B59" s="4">
+    <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B62" s="4">
         <v>4141</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6">
-        <v>0</v>
-      </c>
-      <c r="F59" s="6">
+      <c r="C62" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6">
         <v>89208.58</v>
       </c>
-      <c r="G59" s="7">
+      <c r="I62" s="7">
         <v>89208.58</v>
       </c>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B60" s="4">
+    <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B63" s="4">
         <v>4251</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="6">
-        <v>24776650.050000001</v>
-      </c>
-      <c r="E60" s="6">
+      <c r="C63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="6">
+        <v>63817452.659999996</v>
+      </c>
+      <c r="E63" s="6">
+        <v>37176308.030000001</v>
+      </c>
+      <c r="F63" s="6">
+        <v>27783091.120000001</v>
+      </c>
+      <c r="G63" s="6">
         <v>522774.46</v>
       </c>
-      <c r="F60" s="6">
+      <c r="H63" s="6">
         <v>942023.07</v>
       </c>
-      <c r="G60" s="7">
+      <c r="I63" s="7">
         <v>1464797.53</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B61" s="4">
+    <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B64" s="4">
         <v>4291</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="6">
-        <v>2258512512.0100002</v>
-      </c>
-      <c r="E61" s="6">
-        <v>246291495.09999999</v>
-      </c>
-      <c r="F61" s="6">
-        <v>379766580.81</v>
-      </c>
-      <c r="G61" s="7">
-        <v>626058075.90999997</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B62" s="4">
+      <c r="C64" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="6">
+        <v>5778621422.4099998</v>
+      </c>
+      <c r="E64" s="6">
+        <v>2862909991.98</v>
+      </c>
+      <c r="F64" s="6">
+        <v>2770360701.0999999</v>
+      </c>
+      <c r="G64" s="6">
+        <v>254899668.30000001</v>
+      </c>
+      <c r="H64" s="6">
+        <v>390199014.63</v>
+      </c>
+      <c r="I64" s="7">
+        <v>645098682.92999995</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B65" s="4">
         <v>4331</v>
       </c>
-      <c r="C62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6">
-        <v>0</v>
-      </c>
-      <c r="F62" s="6">
+      <c r="C65" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="6">
+        <v>2643527.87</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6">
         <v>57465.29</v>
       </c>
-      <c r="G62" s="7">
+      <c r="I65" s="7">
         <v>57465.29</v>
       </c>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B63" s="4">
+    <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B66" s="4">
         <v>4341</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="6">
-        <v>178805.39</v>
-      </c>
-      <c r="E63" s="6">
+      <c r="C66" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>232496.52</v>
+      </c>
+      <c r="E66" s="6">
+        <v>225811.20000000001</v>
+      </c>
+      <c r="F66" s="6">
+        <v>188108.59</v>
+      </c>
+      <c r="G66" s="6">
         <v>65790.19</v>
       </c>
-      <c r="F63" s="6">
+      <c r="H66" s="6">
         <v>284844.95</v>
       </c>
-      <c r="G63" s="7">
+      <c r="I66" s="7">
         <v>350635.14</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B64" s="4">
+    <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B67" s="4">
         <v>4381</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="6">
-        <v>13919203.439999999</v>
-      </c>
-      <c r="E64" s="6">
-        <v>0</v>
-      </c>
-      <c r="F64" s="6">
-        <v>14224769.710000001</v>
-      </c>
-      <c r="G64" s="7">
-        <v>14224769.710000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B65" s="4">
+      <c r="C67" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="6">
+        <v>31274047.960000001</v>
+      </c>
+      <c r="E67" s="6">
+        <v>16840672.530000001</v>
+      </c>
+      <c r="F67" s="6">
+        <v>15656454.539999999</v>
+      </c>
+      <c r="G67" s="6">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6">
+        <v>15396977.369999999</v>
+      </c>
+      <c r="I67" s="7">
+        <v>15396977.369999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B68" s="4">
         <v>4451</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="6">
-        <v>14083555.73</v>
-      </c>
-      <c r="E65" s="6">
+      <c r="C68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="6">
+        <v>25665365.199999999</v>
+      </c>
+      <c r="E68" s="6">
+        <v>14816751.380000001</v>
+      </c>
+      <c r="F68" s="6">
+        <v>14589201.189999999</v>
+      </c>
+      <c r="G68" s="6">
         <v>28530.55</v>
       </c>
-      <c r="F65" s="6">
-        <v>4296316.33</v>
-      </c>
-      <c r="G65" s="7">
-        <v>4324846.88</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B66" s="4">
+      <c r="H68" s="6">
+        <v>4369025.57</v>
+      </c>
+      <c r="I68" s="7">
+        <v>4397556.12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B69" s="4">
         <v>4491</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="6">
+      <c r="C69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="6">
         <v>11214.34</v>
       </c>
-      <c r="E66" s="6">
-        <v>0</v>
-      </c>
-      <c r="F66" s="6">
+      <c r="E69" s="6">
+        <v>11214.34</v>
+      </c>
+      <c r="F69" s="6">
+        <v>11214.34</v>
+      </c>
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6">
         <v>134615.38</v>
       </c>
-      <c r="G66" s="7">
+      <c r="I69" s="7">
         <v>134615.38</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B67" s="4">
+    <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B70" s="4">
         <v>4541</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="6">
-        <v>85803.94</v>
-      </c>
-      <c r="E67" s="6">
-        <v>0</v>
-      </c>
-      <c r="F67" s="6">
+      <c r="C70" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D70" s="6">
+        <v>238804</v>
+      </c>
+      <c r="E70" s="6">
+        <v>101816.83</v>
+      </c>
+      <c r="F70" s="6">
+        <v>96834.97</v>
+      </c>
+      <c r="G70" s="6">
+        <v>0</v>
+      </c>
+      <c r="H70" s="6">
         <v>28664.16</v>
       </c>
-      <c r="G67" s="7">
+      <c r="I70" s="7">
         <v>28664.16</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B68" s="4">
+    <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B71" s="4">
         <v>4551</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D68" s="6">
-        <v>46118489.729999997</v>
-      </c>
-      <c r="E68" s="6">
-        <v>0</v>
-      </c>
-      <c r="F68" s="6">
+      <c r="C71" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="6">
+        <v>63142211.219999999</v>
+      </c>
+      <c r="E71" s="6">
+        <v>46218088.340000004</v>
+      </c>
+      <c r="F71" s="6">
+        <v>46206417.460000001</v>
+      </c>
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6">
         <v>486647</v>
       </c>
-      <c r="G68" s="7">
+      <c r="I71" s="7">
         <v>486647</v>
       </c>
     </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B69" s="4">
+    <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B72" s="4">
         <v>4601</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
-        <v>0</v>
-      </c>
-      <c r="G69" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B70" s="4">
-        <v>4631</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="6">
-        <v>82161177.069999993</v>
-      </c>
-      <c r="E70" s="6">
-        <v>53631506.450000003</v>
-      </c>
-      <c r="F70" s="6">
-        <v>27502772.460000001</v>
-      </c>
-      <c r="G70" s="7">
-        <v>81134278.909999996</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B71" s="4">
+      <c r="C72" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6">
+        <v>0</v>
+      </c>
+      <c r="I72" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B73" s="4">
         <v>4691</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" s="6">
-        <v>0</v>
-      </c>
-      <c r="E71" s="6">
+      <c r="C73" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" s="6">
+        <v>10842975.01</v>
+      </c>
+      <c r="E73" s="6">
+        <v>1623326.84</v>
+      </c>
+      <c r="F73" s="6">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6">
         <v>4586769.4800000004</v>
       </c>
-      <c r="F71" s="6">
-        <v>11421045.34</v>
-      </c>
-      <c r="G71" s="7">
-        <v>16007814.82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B72" s="4">
+      <c r="H73" s="6">
+        <v>15239385.1</v>
+      </c>
+      <c r="I73" s="7">
+        <v>19826154.579999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B74" s="4">
         <v>4701</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D72" s="6">
-        <v>65788.509999999995</v>
-      </c>
-      <c r="E72" s="6">
-        <v>0</v>
-      </c>
-      <c r="F72" s="6">
+      <c r="C74" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D74" s="6">
+        <v>125496.7</v>
+      </c>
+      <c r="E74" s="6">
+        <v>80760.28</v>
+      </c>
+      <c r="F74" s="6">
+        <v>79270.17</v>
+      </c>
+      <c r="G74" s="6">
+        <v>0</v>
+      </c>
+      <c r="H74" s="6">
         <v>1235436.6200000001</v>
       </c>
-      <c r="G72" s="7">
+      <c r="I74" s="7">
         <v>1235436.6200000001</v>
       </c>
     </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B73" s="4">
+    <row r="75" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B75" s="4">
         <v>4711</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" s="6">
-        <v>5136392138.0100002</v>
-      </c>
-      <c r="E73" s="6">
+      <c r="C75" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="6">
+        <v>5744037674.1800003</v>
+      </c>
+      <c r="E75" s="6">
+        <v>5740738697.2600002</v>
+      </c>
+      <c r="F75" s="6">
+        <v>5740649847.3500004</v>
+      </c>
+      <c r="G75" s="6">
         <v>57945.89</v>
       </c>
-      <c r="F73" s="6">
+      <c r="H75" s="6">
         <v>759396.57</v>
       </c>
-      <c r="G73" s="7">
+      <c r="I75" s="7">
         <v>817342.46</v>
       </c>
     </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -692,22 +692,22 @@
         <v>9</v>
       </c>
       <c r="D2" s="6">
-        <v>47296961.18</v>
+        <v>48303979.340000004</v>
       </c>
       <c r="E2" s="6">
-        <v>17762704.210000001</v>
+        <v>19547144.91</v>
       </c>
       <c r="F2" s="6">
-        <v>16468944.359999999</v>
+        <v>16817148.879999999</v>
       </c>
       <c r="G2" s="6">
         <v>1803218.12</v>
       </c>
       <c r="H2" s="6">
-        <v>7164940.5</v>
+        <v>7533532.0800000001</v>
       </c>
       <c r="I2" s="7">
-        <v>8968158.6199999992</v>
+        <v>9336750.1999999993</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -721,22 +721,22 @@
         <v>10</v>
       </c>
       <c r="D3" s="6">
-        <v>475166200.5</v>
+        <v>480126201.70999998</v>
       </c>
       <c r="E3" s="6">
-        <v>323260734.91000003</v>
+        <v>328459535.10000002</v>
       </c>
       <c r="F3" s="6">
-        <v>300881053.19</v>
+        <v>311953509.73000002</v>
       </c>
       <c r="G3" s="6">
         <v>185261438.00999999</v>
       </c>
       <c r="H3" s="6">
-        <v>2330328.19</v>
+        <v>2334143.0299999998</v>
       </c>
       <c r="I3" s="7">
-        <v>187591766.19999999</v>
+        <v>187595581.03999999</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -750,13 +750,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="6">
-        <v>6456220.3499999996</v>
+        <v>6459312.7999999998</v>
       </c>
       <c r="E4" s="6">
-        <v>6132346.29</v>
+        <v>6219350.1200000001</v>
       </c>
       <c r="F4" s="6">
-        <v>6097151.2300000004</v>
+        <v>6172119.25</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -779,22 +779,22 @@
         <v>12</v>
       </c>
       <c r="D5" s="6">
-        <v>634243573.63999999</v>
+        <v>642181449.57000005</v>
       </c>
       <c r="E5" s="6">
-        <v>548217152.97000003</v>
+        <v>560193445.82000005</v>
       </c>
       <c r="F5" s="6">
-        <v>540816039.25999999</v>
+        <v>547506548.13</v>
       </c>
       <c r="G5" s="6">
         <v>7665444.21</v>
       </c>
       <c r="H5" s="6">
-        <v>47259141.600000001</v>
+        <v>48366475.520000003</v>
       </c>
       <c r="I5" s="7">
-        <v>54924585.810000002</v>
+        <v>56031919.729999997</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -808,22 +808,22 @@
         <v>13</v>
       </c>
       <c r="D6" s="6">
-        <v>35956687.219999999</v>
+        <v>37874746.909999996</v>
       </c>
       <c r="E6" s="6">
-        <v>16189796.859999999</v>
+        <v>18362373.73</v>
       </c>
       <c r="F6" s="6">
-        <v>15677126.189999999</v>
+        <v>17716805.109999999</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>18511927.670000002</v>
+        <v>18898548.84</v>
       </c>
       <c r="I6" s="7">
-        <v>18511927.670000002</v>
+        <v>18898548.84</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -837,22 +837,22 @@
         <v>14</v>
       </c>
       <c r="D7" s="6">
-        <v>52711036.75</v>
+        <v>66209463.310000002</v>
       </c>
       <c r="E7" s="6">
-        <v>25505408.899999999</v>
+        <v>37557847.460000001</v>
       </c>
       <c r="F7" s="6">
-        <v>24898693.030000001</v>
+        <v>36918042.859999999</v>
       </c>
       <c r="G7" s="6">
         <v>5876518.1600000001</v>
       </c>
       <c r="H7" s="6">
-        <v>14113229.130000001</v>
+        <v>14224513.609999999</v>
       </c>
       <c r="I7" s="7">
-        <v>19989747.289999999</v>
+        <v>20101031.77</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -866,22 +866,22 @@
         <v>15</v>
       </c>
       <c r="D8" s="6">
-        <v>5737870712.0100002</v>
+        <v>5770809089.5299997</v>
       </c>
       <c r="E8" s="6">
-        <v>5580080641.2200003</v>
+        <v>5585846253.7299995</v>
       </c>
       <c r="F8" s="6">
-        <v>5561312916.3299999</v>
+        <v>5570780117.3100004</v>
       </c>
       <c r="G8" s="6">
         <v>18529479.850000001</v>
       </c>
       <c r="H8" s="6">
-        <v>124290111.84999999</v>
+        <v>127393248.06999999</v>
       </c>
       <c r="I8" s="7">
-        <v>142819591.69999999</v>
+        <v>145922727.91999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -895,22 +895,22 @@
         <v>16</v>
       </c>
       <c r="D9" s="6">
-        <v>6166912492.6400003</v>
+        <v>6303882782.54</v>
       </c>
       <c r="E9" s="6">
-        <v>5911919418.1899996</v>
+        <v>6041439830.5600004</v>
       </c>
       <c r="F9" s="6">
-        <v>5867772743.0200005</v>
+        <v>5912292834.5900002</v>
       </c>
       <c r="G9" s="6">
         <v>195886022.58000001</v>
       </c>
       <c r="H9" s="6">
-        <v>117179182.12</v>
+        <v>118522931.77</v>
       </c>
       <c r="I9" s="7">
-        <v>313065204.69999999</v>
+        <v>314408954.35000002</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -924,13 +924,13 @@
         <v>17</v>
       </c>
       <c r="D10" s="6">
-        <v>33497399.16</v>
+        <v>33537318.93</v>
       </c>
       <c r="E10" s="6">
-        <v>22869000.129999999</v>
+        <v>23287879.82</v>
       </c>
       <c r="F10" s="6">
-        <v>22206092.890000001</v>
+        <v>22608313.969999999</v>
       </c>
       <c r="G10" s="6">
         <v>319615.87</v>
@@ -953,22 +953,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="6">
-        <v>63327544.759999998</v>
+        <v>65751839.32</v>
       </c>
       <c r="E11" s="6">
-        <v>53499338.670000002</v>
+        <v>54800762.109999999</v>
       </c>
       <c r="F11" s="6">
-        <v>36085029.530000001</v>
+        <v>49776797.159999996</v>
       </c>
       <c r="G11" s="6">
         <v>15843807.77</v>
       </c>
       <c r="H11" s="6">
-        <v>19738535.940000001</v>
+        <v>20692197.960000001</v>
       </c>
       <c r="I11" s="7">
-        <v>35582343.710000001</v>
+        <v>36536005.729999997</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -982,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="D12" s="6">
-        <v>75778333.530000001</v>
+        <v>79592215.090000004</v>
       </c>
       <c r="E12" s="6">
-        <v>71100779.090000004</v>
+        <v>72038804.650000006</v>
       </c>
       <c r="F12" s="6">
-        <v>68681775.329999998</v>
+        <v>69370266.319999993</v>
       </c>
       <c r="G12" s="6">
         <v>3823909.86</v>
@@ -1011,22 +1011,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="6">
-        <v>687905256.80999994</v>
+        <v>690298158.04999995</v>
       </c>
       <c r="E13" s="6">
-        <v>663871176.23000002</v>
+        <v>665182905.92999995</v>
       </c>
       <c r="F13" s="6">
-        <v>660799554.26999998</v>
+        <v>661954763.51999998</v>
       </c>
       <c r="G13" s="6">
         <v>6046803.8799999999</v>
       </c>
       <c r="H13" s="6">
-        <v>25820867.629999999</v>
+        <v>27117154.359999999</v>
       </c>
       <c r="I13" s="7">
-        <v>31867671.510000002</v>
+        <v>33163958.239999998</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1040,22 +1040,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="6">
-        <v>1765951109.97</v>
+        <v>1770302389.96</v>
       </c>
       <c r="E14" s="6">
-        <v>1439818522</v>
+        <v>1456848804.27</v>
       </c>
       <c r="F14" s="6">
-        <v>1407876726.23</v>
+        <v>1441770475.1800001</v>
       </c>
       <c r="G14" s="6">
         <v>14179981.15</v>
       </c>
       <c r="H14" s="6">
-        <v>110019564.72</v>
+        <v>112699829.17</v>
       </c>
       <c r="I14" s="7">
-        <v>124199545.87</v>
+        <v>126879810.31999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1069,22 +1069,22 @@
         <v>22</v>
       </c>
       <c r="D15" s="6">
-        <v>41339288.020000003</v>
+        <v>41751730.299999997</v>
       </c>
       <c r="E15" s="6">
-        <v>37824839.219999999</v>
+        <v>39486740.299999997</v>
       </c>
       <c r="F15" s="6">
-        <v>37061535.469999999</v>
+        <v>37820996.810000002</v>
       </c>
       <c r="G15" s="6">
         <v>10843996.220000001</v>
       </c>
       <c r="H15" s="6">
-        <v>9740189.9100000001</v>
+        <v>10111490.609999999</v>
       </c>
       <c r="I15" s="7">
-        <v>20584186.129999999</v>
+        <v>20955486.829999998</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1098,22 +1098,22 @@
         <v>23</v>
       </c>
       <c r="D16" s="6">
-        <v>48000443.009999998</v>
+        <v>49320169.869999997</v>
       </c>
       <c r="E16" s="6">
-        <v>42840007.640000001</v>
+        <v>44082100.460000001</v>
       </c>
       <c r="F16" s="6">
-        <v>21316072.600000001</v>
+        <v>35350539.530000001</v>
       </c>
       <c r="G16" s="6">
-        <v>11104724.689999999</v>
+        <v>11209003.039999999</v>
       </c>
       <c r="H16" s="6">
-        <v>2787214.53</v>
+        <v>3711726.53</v>
       </c>
       <c r="I16" s="7">
-        <v>13891939.220000001</v>
+        <v>14920729.57</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1127,22 +1127,22 @@
         <v>24</v>
       </c>
       <c r="D17" s="6">
-        <v>290892001.44</v>
+        <v>295149788.68000001</v>
       </c>
       <c r="E17" s="6">
-        <v>195866521.90000001</v>
+        <v>202494452.91999999</v>
       </c>
       <c r="F17" s="6">
-        <v>164840594.19</v>
+        <v>165335449.81999999</v>
       </c>
       <c r="G17" s="6">
-        <v>28627234.710000001</v>
+        <v>28757544</v>
       </c>
       <c r="H17" s="6">
-        <v>61849177.25</v>
+        <v>64889453.780000001</v>
       </c>
       <c r="I17" s="7">
-        <v>90476411.959999993</v>
+        <v>93646997.780000001</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1156,22 +1156,22 @@
         <v>25</v>
       </c>
       <c r="D18" s="6">
-        <v>1082875309.95</v>
+        <v>1096240791.8800001</v>
       </c>
       <c r="E18" s="6">
-        <v>1014232057.02</v>
+        <v>1036977854.75</v>
       </c>
       <c r="F18" s="6">
-        <v>1002467372.65</v>
+        <v>1006932254.6799999</v>
       </c>
       <c r="G18" s="6">
-        <v>6917250.9299999997</v>
+        <v>6925334.6500000004</v>
       </c>
       <c r="H18" s="6">
-        <v>27582493.739999998</v>
+        <v>28876413.780000001</v>
       </c>
       <c r="I18" s="7">
-        <v>34499744.670000002</v>
+        <v>35801748.43</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1185,22 +1185,22 @@
         <v>26</v>
       </c>
       <c r="D19" s="6">
-        <v>23271506.07</v>
+        <v>23273368.82</v>
       </c>
       <c r="E19" s="6">
-        <v>22896428.489999998</v>
+        <v>22924717.640000001</v>
       </c>
       <c r="F19" s="6">
-        <v>22237870.350000001</v>
+        <v>22401605.710000001</v>
       </c>
       <c r="G19" s="6">
         <v>5062</v>
       </c>
       <c r="H19" s="6">
-        <v>1303921.8600000001</v>
+        <v>1311388.02</v>
       </c>
       <c r="I19" s="7">
-        <v>1308983.8600000001</v>
+        <v>1316450.02</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1214,22 +1214,22 @@
         <v>27</v>
       </c>
       <c r="D20" s="6">
-        <v>8451407.9000000004</v>
+        <v>8712420.8000000007</v>
       </c>
       <c r="E20" s="6">
-        <v>7185645.0800000001</v>
+        <v>7522376.6100000003</v>
       </c>
       <c r="F20" s="6">
-        <v>7031312.1600000001</v>
+        <v>7324983.25</v>
       </c>
       <c r="G20" s="6">
         <v>211093.49</v>
       </c>
       <c r="H20" s="6">
-        <v>912131.83</v>
+        <v>958212.55</v>
       </c>
       <c r="I20" s="7">
-        <v>1123225.32</v>
+        <v>1169306.04</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1243,13 +1243,13 @@
         <v>28</v>
       </c>
       <c r="D21" s="6">
-        <v>4197797.3499999996</v>
+        <v>4248956.37</v>
       </c>
       <c r="E21" s="6">
-        <v>3919473.04</v>
+        <v>3967707.31</v>
       </c>
       <c r="F21" s="6">
-        <v>3860536.43</v>
+        <v>3905488.71</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
@@ -1272,22 +1272,22 @@
         <v>29</v>
       </c>
       <c r="D22" s="6">
-        <v>72559654.200000003</v>
+        <v>72564683.260000005</v>
       </c>
       <c r="E22" s="6">
-        <v>15978116.050000001</v>
+        <v>18748702.800000001</v>
       </c>
       <c r="F22" s="6">
-        <v>13850567.07</v>
+        <v>17828707.190000001</v>
       </c>
       <c r="G22" s="6">
         <v>60000.1</v>
       </c>
       <c r="H22" s="6">
-        <v>43286985.07</v>
+        <v>45072263.210000001</v>
       </c>
       <c r="I22" s="7">
-        <v>43346985.170000002</v>
+        <v>45132263.310000002</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1301,22 +1301,22 @@
         <v>30</v>
       </c>
       <c r="D23" s="6">
-        <v>3596883.39</v>
+        <v>3596783.39</v>
       </c>
       <c r="E23" s="6">
-        <v>3264097.83</v>
+        <v>3319181.82</v>
       </c>
       <c r="F23" s="6">
-        <v>3194498.71</v>
+        <v>3249582.7</v>
       </c>
       <c r="G23" s="6">
         <v>122407.67</v>
       </c>
       <c r="H23" s="6">
-        <v>190745.3</v>
+        <v>214364.3</v>
       </c>
       <c r="I23" s="7">
-        <v>313152.96999999997</v>
+        <v>336771.97</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1333,10 +1333,10 @@
         <v>500800000</v>
       </c>
       <c r="E24" s="6">
-        <v>267538449.13</v>
+        <v>272994715.06</v>
       </c>
       <c r="F24" s="6">
-        <v>267538449.13</v>
+        <v>272994715.06</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -1385,10 +1385,10 @@
         <v>3576955016.79</v>
       </c>
       <c r="E26" s="6">
-        <v>2292274874.1399999</v>
+        <v>2453989975.73</v>
       </c>
       <c r="F26" s="6">
-        <v>2257151412.25</v>
+        <v>2306734419.6399999</v>
       </c>
       <c r="G26" s="6">
         <v>0</v>
@@ -1440,22 +1440,22 @@
         <v>35</v>
       </c>
       <c r="D28" s="6">
-        <v>949315008.29999995</v>
+        <v>953613140.34000003</v>
       </c>
       <c r="E28" s="6">
-        <v>464549757.69</v>
+        <v>502322037.13</v>
       </c>
       <c r="F28" s="6">
-        <v>439561051.69</v>
+        <v>479927915.43000001</v>
       </c>
       <c r="G28" s="6">
         <v>94822.57</v>
       </c>
       <c r="H28" s="6">
-        <v>187574350.50999999</v>
+        <v>188033164.62</v>
       </c>
       <c r="I28" s="7">
-        <v>187669173.08000001</v>
+        <v>188127987.19</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,13 +1469,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="6">
-        <v>1156855.81</v>
+        <v>1169524.0900000001</v>
       </c>
       <c r="E29" s="6">
-        <v>951635.5</v>
+        <v>1072982.05</v>
       </c>
       <c r="F29" s="6">
-        <v>944239.66</v>
+        <v>1047678.36</v>
       </c>
       <c r="G29" s="6">
         <v>1692.39</v>
@@ -1498,22 +1498,22 @@
         <v>37</v>
       </c>
       <c r="D30" s="6">
-        <v>24180971.109999999</v>
+        <v>24337042.760000002</v>
       </c>
       <c r="E30" s="6">
-        <v>21226298.149999999</v>
+        <v>21985111.48</v>
       </c>
       <c r="F30" s="6">
-        <v>20171643.030000001</v>
+        <v>20708670.390000001</v>
       </c>
       <c r="G30" s="6">
         <v>27688.16</v>
       </c>
       <c r="H30" s="6">
-        <v>1609342.68</v>
+        <v>1625798.68</v>
       </c>
       <c r="I30" s="7">
-        <v>1637030.84</v>
+        <v>1653486.84</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1527,22 +1527,22 @@
         <v>38</v>
       </c>
       <c r="D31" s="6">
-        <v>216009218.40000001</v>
+        <v>220685546.31999999</v>
       </c>
       <c r="E31" s="6">
-        <v>164768656.49000001</v>
+        <v>169441331.56</v>
       </c>
       <c r="F31" s="6">
-        <v>158940876.25</v>
+        <v>164204779.31</v>
       </c>
       <c r="G31" s="6">
         <v>3290143.43</v>
       </c>
       <c r="H31" s="6">
-        <v>1687592.31</v>
+        <v>3171547.73</v>
       </c>
       <c r="I31" s="7">
-        <v>4977735.74</v>
+        <v>6461691.1600000001</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1556,22 +1556,22 @@
         <v>39</v>
       </c>
       <c r="D32" s="6">
-        <v>20935102</v>
+        <v>21692165.07</v>
       </c>
       <c r="E32" s="6">
-        <v>20340714.289999999</v>
+        <v>21146632.079999998</v>
       </c>
       <c r="F32" s="6">
-        <v>19517092.48</v>
+        <v>19984165.399999999</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" s="6">
-        <v>1008879.61</v>
+        <v>1010938.21</v>
       </c>
       <c r="I32" s="7">
-        <v>1008879.61</v>
+        <v>1010938.21</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1585,22 +1585,22 @@
         <v>40</v>
       </c>
       <c r="D33" s="6">
-        <v>68683326.209999993</v>
+        <v>70408960.730000004</v>
       </c>
       <c r="E33" s="6">
-        <v>65614600.07</v>
+        <v>67521762.819999993</v>
       </c>
       <c r="F33" s="6">
-        <v>61894933.130000003</v>
+        <v>63373739.07</v>
       </c>
       <c r="G33" s="6">
         <v>486532.65</v>
       </c>
       <c r="H33" s="6">
-        <v>6594004.2699999996</v>
+        <v>6658345.8700000001</v>
       </c>
       <c r="I33" s="7">
-        <v>7080536.9199999999</v>
+        <v>7144878.5199999996</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,22 +1614,22 @@
         <v>41</v>
       </c>
       <c r="D34" s="6">
-        <v>1037970788.45</v>
+        <v>1048197290.33</v>
       </c>
       <c r="E34" s="6">
-        <v>1028850188.5</v>
+        <v>1031569547.5599999</v>
       </c>
       <c r="F34" s="6">
-        <v>1012522386.79</v>
+        <v>1018072253.36</v>
       </c>
       <c r="G34" s="6">
         <v>19255214.109999999</v>
       </c>
       <c r="H34" s="6">
-        <v>33681484.509999998</v>
+        <v>33950875.049999997</v>
       </c>
       <c r="I34" s="7">
-        <v>52936698.619999997</v>
+        <v>53206089.159999996</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1643,22 +1643,22 @@
         <v>42</v>
       </c>
       <c r="D35" s="6">
-        <v>20371977.489999998</v>
+        <v>20797026.800000001</v>
       </c>
       <c r="E35" s="6">
-        <v>18192249.879999999</v>
+        <v>18266599.239999998</v>
       </c>
       <c r="F35" s="6">
-        <v>17537921.43</v>
+        <v>17874700.140000001</v>
       </c>
       <c r="G35" s="6">
         <v>218.93</v>
       </c>
       <c r="H35" s="6">
-        <v>1759293.28</v>
+        <v>1820237.73</v>
       </c>
       <c r="I35" s="7">
-        <v>1759512.21</v>
+        <v>1820456.66</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1672,13 +1672,13 @@
         <v>43</v>
       </c>
       <c r="D36" s="6">
-        <v>1948493.74</v>
+        <v>2038198.26</v>
       </c>
       <c r="E36" s="6">
-        <v>1726778.34</v>
+        <v>1773279.02</v>
       </c>
       <c r="F36" s="6">
-        <v>1690995.12</v>
+        <v>1721747.41</v>
       </c>
       <c r="G36" s="6">
         <v>23147.54</v>
@@ -1701,13 +1701,13 @@
         <v>44</v>
       </c>
       <c r="D37" s="6">
-        <v>1516625.71</v>
+        <v>1528659.91</v>
       </c>
       <c r="E37" s="6">
-        <v>1470109.4</v>
+        <v>1475863.79</v>
       </c>
       <c r="F37" s="6">
-        <v>1410521.41</v>
+        <v>1418255.75</v>
       </c>
       <c r="G37" s="6">
         <v>46386.19</v>
@@ -1730,22 +1730,22 @@
         <v>45</v>
       </c>
       <c r="D38" s="6">
-        <v>25290736.920000002</v>
+        <v>25547980.489999998</v>
       </c>
       <c r="E38" s="6">
-        <v>18689578.66</v>
+        <v>19630483.43</v>
       </c>
       <c r="F38" s="6">
-        <v>18305226.5</v>
+        <v>18365902.699999999</v>
       </c>
       <c r="G38" s="6">
         <v>866933.31</v>
       </c>
       <c r="H38" s="6">
-        <v>1570988.02</v>
+        <v>1596469.6</v>
       </c>
       <c r="I38" s="7">
-        <v>2437921.33</v>
+        <v>2463402.91</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1759,13 +1759,13 @@
         <v>46</v>
       </c>
       <c r="D39" s="6">
-        <v>9559397.6300000008</v>
+        <v>9672483.0700000003</v>
       </c>
       <c r="E39" s="6">
-        <v>5486559.5899999999</v>
+        <v>5893171.9400000004</v>
       </c>
       <c r="F39" s="6">
-        <v>5144751.49</v>
+        <v>5600551.2000000002</v>
       </c>
       <c r="G39" s="6">
         <v>702452.89</v>
@@ -1788,13 +1788,13 @@
         <v>47</v>
       </c>
       <c r="D40" s="6">
-        <v>5355866.43</v>
+        <v>5816895.4199999999</v>
       </c>
       <c r="E40" s="6">
-        <v>4628249.3</v>
+        <v>5129112.5999999996</v>
       </c>
       <c r="F40" s="6">
-        <v>3777513.36</v>
+        <v>4383117.2</v>
       </c>
       <c r="G40" s="6">
         <v>32410.16</v>
@@ -1817,22 +1817,22 @@
         <v>48</v>
       </c>
       <c r="D41" s="6">
-        <v>16896938.399999999</v>
+        <v>17192527.75</v>
       </c>
       <c r="E41" s="6">
-        <v>16648250.1</v>
+        <v>16852822.16</v>
       </c>
       <c r="F41" s="6">
-        <v>15113567.859999999</v>
+        <v>15390511.24</v>
       </c>
       <c r="G41" s="6">
-        <v>3494961.12</v>
+        <v>4364694.79</v>
       </c>
       <c r="H41" s="6">
         <v>10971227.93</v>
       </c>
       <c r="I41" s="7">
-        <v>14466189.050000001</v>
+        <v>15335922.720000001</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1846,13 +1846,13 @@
         <v>49</v>
       </c>
       <c r="D42" s="6">
-        <v>16721416.470000001</v>
+        <v>16736167.17</v>
       </c>
       <c r="E42" s="6">
-        <v>11908821.4</v>
+        <v>12059068.199999999</v>
       </c>
       <c r="F42" s="6">
-        <v>11481949.59</v>
+        <v>11581264.98</v>
       </c>
       <c r="G42" s="6">
         <v>1119472.81</v>
@@ -1875,22 +1875,22 @@
         <v>50</v>
       </c>
       <c r="D43" s="6">
-        <v>180778052.05000001</v>
+        <v>183435428.56</v>
       </c>
       <c r="E43" s="6">
-        <v>106295658.56999999</v>
+        <v>112965769.29000001</v>
       </c>
       <c r="F43" s="6">
-        <v>59080755.57</v>
+        <v>82586490.579999998</v>
       </c>
       <c r="G43" s="6">
         <v>7187273.0700000003</v>
       </c>
       <c r="H43" s="6">
-        <v>132728906.18000001</v>
+        <v>132798886.17</v>
       </c>
       <c r="I43" s="7">
-        <v>139916179.25</v>
+        <v>139986159.24000001</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1904,22 +1904,22 @@
         <v>51</v>
       </c>
       <c r="D44" s="6">
-        <v>843081731.38</v>
+        <v>882289198.39999998</v>
       </c>
       <c r="E44" s="6">
-        <v>746324513.37</v>
+        <v>768326465.59000003</v>
       </c>
       <c r="F44" s="6">
-        <v>705585579.46000004</v>
+        <v>736005338.38</v>
       </c>
       <c r="G44" s="6">
         <v>6041131.1100000003</v>
       </c>
       <c r="H44" s="6">
-        <v>86617453.730000004</v>
+        <v>87298827.409999996</v>
       </c>
       <c r="I44" s="7">
-        <v>92658584.840000004</v>
+        <v>93339958.519999996</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1933,13 +1933,13 @@
         <v>52</v>
       </c>
       <c r="D45" s="6">
-        <v>2523284.88</v>
+        <v>2509804.83</v>
       </c>
       <c r="E45" s="6">
-        <v>2026144.68</v>
+        <v>2070300.23</v>
       </c>
       <c r="F45" s="6">
-        <v>1850775.05</v>
+        <v>1923221.48</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>
@@ -1962,22 +1962,22 @@
         <v>53</v>
       </c>
       <c r="D46" s="6">
-        <v>689625578.38</v>
+        <v>748120917.36000001</v>
       </c>
       <c r="E46" s="6">
-        <v>237266334.03999999</v>
+        <v>260422693.69999999</v>
       </c>
       <c r="F46" s="6">
-        <v>216072010.84</v>
+        <v>229469171.47999999</v>
       </c>
       <c r="G46" s="6">
         <v>13431647.550000001</v>
       </c>
       <c r="H46" s="6">
-        <v>196109389.86000001</v>
+        <v>198036549.34</v>
       </c>
       <c r="I46" s="7">
-        <v>209541037.41</v>
+        <v>211468196.88999999</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1991,22 +1991,22 @@
         <v>54</v>
       </c>
       <c r="D47" s="6">
-        <v>158978150.13999999</v>
+        <v>162072686.41999999</v>
       </c>
       <c r="E47" s="6">
-        <v>141658060.38</v>
+        <v>146233242.94999999</v>
       </c>
       <c r="F47" s="6">
-        <v>139316185.75</v>
+        <v>143025270.34</v>
       </c>
       <c r="G47" s="6">
         <v>130453.78</v>
       </c>
       <c r="H47" s="6">
-        <v>20343140.899999999</v>
+        <v>20617821.059999999</v>
       </c>
       <c r="I47" s="7">
-        <v>20473594.68</v>
+        <v>20748274.84</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2020,22 +2020,22 @@
         <v>55</v>
       </c>
       <c r="D48" s="6">
-        <v>138145210.63</v>
+        <v>143771603.31999999</v>
       </c>
       <c r="E48" s="6">
-        <v>110988348.52</v>
+        <v>113134315.06999999</v>
       </c>
       <c r="F48" s="6">
-        <v>95866569.849999994</v>
+        <v>102426104.72</v>
       </c>
       <c r="G48" s="6">
         <v>3348075.28</v>
       </c>
       <c r="H48" s="6">
-        <v>22677237.469999999</v>
+        <v>22867796.5</v>
       </c>
       <c r="I48" s="7">
-        <v>26025312.75</v>
+        <v>26215871.780000001</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2049,13 +2049,13 @@
         <v>56</v>
       </c>
       <c r="D49" s="6">
-        <v>11990138.84</v>
+        <v>12013998.300000001</v>
       </c>
       <c r="E49" s="6">
-        <v>11376371.01</v>
+        <v>11434698.49</v>
       </c>
       <c r="F49" s="6">
-        <v>10723240.09</v>
+        <v>10783232.48</v>
       </c>
       <c r="G49" s="6">
         <v>6330.51</v>
@@ -2078,22 +2078,22 @@
         <v>57</v>
       </c>
       <c r="D50" s="6">
-        <v>140786513.16</v>
+        <v>141599497.34999999</v>
       </c>
       <c r="E50" s="6">
-        <v>121531292.38</v>
+        <v>124840950.11</v>
       </c>
       <c r="F50" s="6">
-        <v>119406929.73999999</v>
+        <v>122344490.83</v>
       </c>
       <c r="G50" s="6">
         <v>212410.94</v>
       </c>
       <c r="H50" s="6">
-        <v>15188861.85</v>
+        <v>15411225.58</v>
       </c>
       <c r="I50" s="7">
-        <v>15401272.789999999</v>
+        <v>15623636.52</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2107,22 +2107,22 @@
         <v>58</v>
       </c>
       <c r="D51" s="6">
-        <v>100237548.39</v>
+        <v>100811741.7</v>
       </c>
       <c r="E51" s="6">
-        <v>94236338.920000002</v>
+        <v>94908963.129999995</v>
       </c>
       <c r="F51" s="6">
-        <v>93669365.950000003</v>
+        <v>94446804.920000002</v>
       </c>
       <c r="G51" s="6">
         <v>509913.92</v>
       </c>
       <c r="H51" s="6">
-        <v>4348357.1399999997</v>
+        <v>4406376.47</v>
       </c>
       <c r="I51" s="7">
-        <v>4858271.0599999996</v>
+        <v>4916290.3899999997</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2136,22 +2136,22 @@
         <v>59</v>
       </c>
       <c r="D52" s="6">
-        <v>15125385.529999999</v>
+        <v>15477223.98</v>
       </c>
       <c r="E52" s="6">
-        <v>8624801.8000000007</v>
+        <v>8709736.2599999998</v>
       </c>
       <c r="F52" s="6">
-        <v>8399639.6899999995</v>
+        <v>8483669.3399999999</v>
       </c>
       <c r="G52" s="6">
         <v>1021786.93</v>
       </c>
       <c r="H52" s="6">
-        <v>15170846.789999999</v>
+        <v>15988440.560000001</v>
       </c>
       <c r="I52" s="7">
-        <v>16192633.720000001</v>
+        <v>17010227.489999998</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2165,13 +2165,13 @@
         <v>60</v>
       </c>
       <c r="D53" s="6">
-        <v>2411669.2999999998</v>
+        <v>2607301.87</v>
       </c>
       <c r="E53" s="6">
-        <v>2215907.9300000002</v>
+        <v>2239224.48</v>
       </c>
       <c r="F53" s="6">
-        <v>2120383.35</v>
+        <v>2143656.5299999998</v>
       </c>
       <c r="G53" s="6">
         <v>167935.23</v>
@@ -2194,13 +2194,13 @@
         <v>61</v>
       </c>
       <c r="D54" s="6">
-        <v>7774139.46</v>
+        <v>7954474.5800000001</v>
       </c>
       <c r="E54" s="6">
-        <v>6533896.4699999997</v>
+        <v>6693499.3399999999</v>
       </c>
       <c r="F54" s="6">
-        <v>6482519.8399999999</v>
+        <v>6628977.1799999997</v>
       </c>
       <c r="G54" s="6">
         <v>8281.7999999999993</v>
@@ -2223,13 +2223,13 @@
         <v>62</v>
       </c>
       <c r="D55" s="6">
-        <v>1643347.9</v>
+        <v>3030627.45</v>
       </c>
       <c r="E55" s="6">
-        <v>1291377.56</v>
+        <v>1304694.97</v>
       </c>
       <c r="F55" s="6">
-        <v>1196505.19</v>
+        <v>1209423.76</v>
       </c>
       <c r="G55" s="6">
         <v>17304.09</v>
@@ -2252,13 +2252,13 @@
         <v>63</v>
       </c>
       <c r="D56" s="6">
-        <v>18699664.32</v>
+        <v>18702893.32</v>
       </c>
       <c r="E56" s="6">
-        <v>10612503.33</v>
+        <v>10817875.369999999</v>
       </c>
       <c r="F56" s="6">
-        <v>9617499.4100000001</v>
+        <v>9910760.5999999996</v>
       </c>
       <c r="G56" s="6">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>64</v>
       </c>
       <c r="D57" s="6">
-        <v>10531480.77</v>
+        <v>11503647.800000001</v>
       </c>
       <c r="E57" s="6">
-        <v>10387159.42</v>
+        <v>11194430.9</v>
       </c>
       <c r="F57" s="6">
-        <v>9363687.6300000008</v>
+        <v>9363822.0800000001</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -2304,13 +2304,13 @@
         <v>65</v>
       </c>
       <c r="D58" s="6">
-        <v>79326076.849999994</v>
+        <v>113201966.42</v>
       </c>
       <c r="E58" s="6">
-        <v>79326076.849999994</v>
+        <v>113201966.42</v>
       </c>
       <c r="F58" s="6">
-        <v>79326076.849999994</v>
+        <v>113201966.42</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -2327,13 +2327,13 @@
         <v>66</v>
       </c>
       <c r="D59" s="6">
-        <v>33188492.190000001</v>
+        <v>45052077.520000003</v>
       </c>
       <c r="E59" s="6">
-        <v>33188492.190000001</v>
+        <v>45052077.520000003</v>
       </c>
       <c r="F59" s="6">
-        <v>33188492.190000001</v>
+        <v>45052077.520000003</v>
       </c>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -2373,13 +2373,13 @@
         <v>68</v>
       </c>
       <c r="D61" s="6">
-        <v>3899649.54</v>
+        <v>5965481.0700000003</v>
       </c>
       <c r="E61" s="6">
-        <v>3899649.54</v>
+        <v>4960280.8099999996</v>
       </c>
       <c r="F61" s="6">
-        <v>3899649.54</v>
+        <v>4960280.8099999996</v>
       </c>
       <c r="G61" s="6">
         <v>360498.89</v>
@@ -2401,9 +2401,15 @@
       <c r="C62" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
+      <c r="D62" s="6">
+        <v>23226.75</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0</v>
+      </c>
+      <c r="F62" s="6">
+        <v>0</v>
+      </c>
       <c r="G62" s="6">
         <v>0</v>
       </c>
@@ -2425,13 +2431,13 @@
         <v>70</v>
       </c>
       <c r="D63" s="6">
-        <v>63817452.659999996</v>
+        <v>66061886.119999997</v>
       </c>
       <c r="E63" s="6">
-        <v>37176308.030000001</v>
+        <v>38553030</v>
       </c>
       <c r="F63" s="6">
-        <v>27783091.120000001</v>
+        <v>28855764.219999999</v>
       </c>
       <c r="G63" s="6">
         <v>522774.46</v>
@@ -2454,22 +2460,22 @@
         <v>71</v>
       </c>
       <c r="D64" s="6">
-        <v>5778621422.4099998</v>
+        <v>6432945131.2200003</v>
       </c>
       <c r="E64" s="6">
-        <v>2862909991.98</v>
+        <v>3146070994.8600001</v>
       </c>
       <c r="F64" s="6">
-        <v>2770360701.0999999</v>
+        <v>2901354540.4099998</v>
       </c>
       <c r="G64" s="6">
-        <v>254899668.30000001</v>
+        <v>254670453.41999999</v>
       </c>
       <c r="H64" s="6">
-        <v>390199014.63</v>
+        <v>403268655.44</v>
       </c>
       <c r="I64" s="7">
-        <v>645098682.92999995</v>
+        <v>657939108.86000001</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2512,13 +2518,13 @@
         <v>73</v>
       </c>
       <c r="D66" s="6">
-        <v>232496.52</v>
+        <v>253561.99</v>
       </c>
       <c r="E66" s="6">
-        <v>225811.20000000001</v>
+        <v>248535.63</v>
       </c>
       <c r="F66" s="6">
-        <v>188108.59</v>
+        <v>231462.84</v>
       </c>
       <c r="G66" s="6">
         <v>65790.19</v>
@@ -2541,22 +2547,22 @@
         <v>74</v>
       </c>
       <c r="D67" s="6">
-        <v>31274047.960000001</v>
+        <v>32199093.260000002</v>
       </c>
       <c r="E67" s="6">
-        <v>16840672.530000001</v>
+        <v>20733009.960000001</v>
       </c>
       <c r="F67" s="6">
-        <v>15656454.539999999</v>
+        <v>18980822.289999999</v>
       </c>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>15396977.369999999</v>
+        <v>16892454.149999999</v>
       </c>
       <c r="I67" s="7">
-        <v>15396977.369999999</v>
+        <v>16892454.149999999</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2570,22 +2576,22 @@
         <v>75</v>
       </c>
       <c r="D68" s="6">
-        <v>25665365.199999999</v>
+        <v>25849993.550000001</v>
       </c>
       <c r="E68" s="6">
-        <v>14816751.380000001</v>
+        <v>22079098.399999999</v>
       </c>
       <c r="F68" s="6">
-        <v>14589201.189999999</v>
+        <v>15569057.76</v>
       </c>
       <c r="G68" s="6">
         <v>28530.55</v>
       </c>
       <c r="H68" s="6">
-        <v>4369025.57</v>
+        <v>6922960.6699999999</v>
       </c>
       <c r="I68" s="7">
-        <v>4397556.12</v>
+        <v>6951491.2199999997</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2631,10 +2637,10 @@
         <v>238804</v>
       </c>
       <c r="E70" s="6">
-        <v>101816.83</v>
+        <v>121014.71</v>
       </c>
       <c r="F70" s="6">
-        <v>96834.97</v>
+        <v>114372.23</v>
       </c>
       <c r="G70" s="6">
         <v>0</v>
@@ -2660,10 +2666,10 @@
         <v>63142211.219999999</v>
       </c>
       <c r="E71" s="6">
-        <v>46218088.340000004</v>
+        <v>53174810.909999996</v>
       </c>
       <c r="F71" s="6">
-        <v>46206417.460000001</v>
+        <v>53152004.670000002</v>
       </c>
       <c r="G71" s="6">
         <v>0</v>
@@ -2709,22 +2715,22 @@
         <v>80</v>
       </c>
       <c r="D73" s="6">
-        <v>10842975.01</v>
+        <v>11146939.67</v>
       </c>
       <c r="E73" s="6">
-        <v>1623326.84</v>
+        <v>2353416.91</v>
       </c>
       <c r="F73" s="6">
-        <v>0</v>
+        <v>1586135.48</v>
       </c>
       <c r="G73" s="6">
         <v>4586769.4800000004</v>
       </c>
       <c r="H73" s="6">
-        <v>15239385.1</v>
+        <v>23419440.469999999</v>
       </c>
       <c r="I73" s="7">
-        <v>19826154.579999998</v>
+        <v>28006209.949999999</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2738,13 +2744,13 @@
         <v>81</v>
       </c>
       <c r="D74" s="6">
-        <v>125496.7</v>
+        <v>126099.31</v>
       </c>
       <c r="E74" s="6">
-        <v>80760.28</v>
+        <v>85063.46</v>
       </c>
       <c r="F74" s="6">
-        <v>79270.17</v>
+        <v>83592.240000000005</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -2767,13 +2773,13 @@
         <v>82</v>
       </c>
       <c r="D75" s="6">
-        <v>5744037674.1800003</v>
+        <v>5744412634.9700003</v>
       </c>
       <c r="E75" s="6">
-        <v>5740738697.2600002</v>
+        <v>5741032512.5500002</v>
       </c>
       <c r="F75" s="6">
-        <v>5740649847.3500004</v>
+        <v>5740925028.6300001</v>
       </c>
       <c r="G75" s="6">
         <v>57945.89</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -692,22 +692,22 @@
         <v>9</v>
       </c>
       <c r="D2" s="6">
-        <v>48303979.340000004</v>
+        <v>48541058.689999998</v>
       </c>
       <c r="E2" s="6">
-        <v>19547144.91</v>
+        <v>19998222.75</v>
       </c>
       <c r="F2" s="6">
-        <v>16817148.879999999</v>
+        <v>16920729.699999999</v>
       </c>
       <c r="G2" s="6">
         <v>1803218.12</v>
       </c>
       <c r="H2" s="6">
-        <v>7533532.0800000001</v>
+        <v>9123946</v>
       </c>
       <c r="I2" s="7">
-        <v>9336750.1999999993</v>
+        <v>10927164.119999999</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -721,13 +721,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="6">
-        <v>480126201.70999998</v>
+        <v>482044629.67000002</v>
       </c>
       <c r="E3" s="6">
-        <v>328459535.10000002</v>
+        <v>340648226.49000001</v>
       </c>
       <c r="F3" s="6">
-        <v>311953509.73000002</v>
+        <v>318068310.60000002</v>
       </c>
       <c r="G3" s="6">
         <v>185261438.00999999</v>
@@ -750,13 +750,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="6">
-        <v>6459312.7999999998</v>
+        <v>6494533.79</v>
       </c>
       <c r="E4" s="6">
-        <v>6219350.1200000001</v>
+        <v>6256089.2300000004</v>
       </c>
       <c r="F4" s="6">
-        <v>6172119.25</v>
+        <v>6208634.1299999999</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -779,22 +779,22 @@
         <v>12</v>
       </c>
       <c r="D5" s="6">
-        <v>642181449.57000005</v>
+        <v>646898178.23000002</v>
       </c>
       <c r="E5" s="6">
-        <v>560193445.82000005</v>
+        <v>567521751.27999997</v>
       </c>
       <c r="F5" s="6">
-        <v>547506548.13</v>
+        <v>549505322.71000004</v>
       </c>
       <c r="G5" s="6">
         <v>7665444.21</v>
       </c>
       <c r="H5" s="6">
-        <v>48366475.520000003</v>
+        <v>48467480.920000002</v>
       </c>
       <c r="I5" s="7">
-        <v>56031919.729999997</v>
+        <v>56132925.130000003</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -808,13 +808,13 @@
         <v>13</v>
       </c>
       <c r="D6" s="6">
-        <v>37874746.909999996</v>
+        <v>37888385.329999998</v>
       </c>
       <c r="E6" s="6">
-        <v>18362373.73</v>
+        <v>18427647.449999999</v>
       </c>
       <c r="F6" s="6">
-        <v>17716805.109999999</v>
+        <v>17781706.469999999</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>14</v>
       </c>
       <c r="D7" s="6">
-        <v>66209463.310000002</v>
+        <v>67825743.239999995</v>
       </c>
       <c r="E7" s="6">
-        <v>37557847.460000001</v>
+        <v>39989170.670000002</v>
       </c>
       <c r="F7" s="6">
-        <v>36918042.859999999</v>
+        <v>39506776.460000001</v>
       </c>
       <c r="G7" s="6">
         <v>5876518.1600000001</v>
       </c>
       <c r="H7" s="6">
-        <v>14224513.609999999</v>
+        <v>14436883.66</v>
       </c>
       <c r="I7" s="7">
-        <v>20101031.77</v>
+        <v>20313401.82</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -866,22 +866,22 @@
         <v>15</v>
       </c>
       <c r="D8" s="6">
-        <v>5770809089.5299997</v>
+        <v>5782741333.5</v>
       </c>
       <c r="E8" s="6">
-        <v>5585846253.7299995</v>
+        <v>5598188912.3199997</v>
       </c>
       <c r="F8" s="6">
-        <v>5570780117.3100004</v>
+        <v>5582849294.1199999</v>
       </c>
       <c r="G8" s="6">
         <v>18529479.850000001</v>
       </c>
       <c r="H8" s="6">
-        <v>127393248.06999999</v>
+        <v>132039237.27</v>
       </c>
       <c r="I8" s="7">
-        <v>145922727.91999999</v>
+        <v>150568717.12</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -895,22 +895,22 @@
         <v>16</v>
       </c>
       <c r="D9" s="6">
-        <v>6303882782.54</v>
+        <v>6548492067.1400003</v>
       </c>
       <c r="E9" s="6">
-        <v>6041439830.5600004</v>
+        <v>6288241790.9300003</v>
       </c>
       <c r="F9" s="6">
-        <v>5912292834.5900002</v>
+        <v>6077544342.4499998</v>
       </c>
       <c r="G9" s="6">
         <v>195886022.58000001</v>
       </c>
       <c r="H9" s="6">
-        <v>118522931.77</v>
+        <v>119422848.89</v>
       </c>
       <c r="I9" s="7">
-        <v>314408954.35000002</v>
+        <v>315308871.47000003</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -924,13 +924,13 @@
         <v>17</v>
       </c>
       <c r="D10" s="6">
-        <v>33537318.93</v>
+        <v>33546341.780000001</v>
       </c>
       <c r="E10" s="6">
-        <v>23287879.82</v>
+        <v>23320589.710000001</v>
       </c>
       <c r="F10" s="6">
-        <v>22608313.969999999</v>
+        <v>22643200.350000001</v>
       </c>
       <c r="G10" s="6">
         <v>319615.87</v>
@@ -953,22 +953,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="6">
-        <v>65751839.32</v>
+        <v>68905686.510000005</v>
       </c>
       <c r="E11" s="6">
-        <v>54800762.109999999</v>
+        <v>58110768.850000001</v>
       </c>
       <c r="F11" s="6">
-        <v>49776797.159999996</v>
+        <v>51946823.200000003</v>
       </c>
       <c r="G11" s="6">
         <v>15843807.77</v>
       </c>
       <c r="H11" s="6">
-        <v>20692197.960000001</v>
+        <v>21025828.969999999</v>
       </c>
       <c r="I11" s="7">
-        <v>36536005.729999997</v>
+        <v>36869636.740000002</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -982,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="D12" s="6">
-        <v>79592215.090000004</v>
+        <v>80060092.079999998</v>
       </c>
       <c r="E12" s="6">
-        <v>72038804.650000006</v>
+        <v>72768414.540000007</v>
       </c>
       <c r="F12" s="6">
-        <v>69370266.319999993</v>
+        <v>71513431.640000001</v>
       </c>
       <c r="G12" s="6">
         <v>3823909.86</v>
@@ -1011,22 +1011,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="6">
-        <v>690298158.04999995</v>
+        <v>690547959.28999996</v>
       </c>
       <c r="E13" s="6">
-        <v>665182905.92999995</v>
+        <v>667076238.23000002</v>
       </c>
       <c r="F13" s="6">
-        <v>661954763.51999998</v>
+        <v>664266727.12</v>
       </c>
       <c r="G13" s="6">
         <v>6046803.8799999999</v>
       </c>
       <c r="H13" s="6">
-        <v>27117154.359999999</v>
+        <v>27623490.77</v>
       </c>
       <c r="I13" s="7">
-        <v>33163958.239999998</v>
+        <v>33670294.649999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1040,22 +1040,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="6">
-        <v>1770302389.96</v>
+        <v>1831892085.25</v>
       </c>
       <c r="E14" s="6">
-        <v>1456848804.27</v>
+        <v>1496182974.25</v>
       </c>
       <c r="F14" s="6">
-        <v>1441770475.1800001</v>
+        <v>1460816233.71</v>
       </c>
       <c r="G14" s="6">
         <v>14179981.15</v>
       </c>
       <c r="H14" s="6">
-        <v>112699829.17</v>
+        <v>113371319.05</v>
       </c>
       <c r="I14" s="7">
-        <v>126879810.31999999</v>
+        <v>127551300.2</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1069,22 +1069,22 @@
         <v>22</v>
       </c>
       <c r="D15" s="6">
-        <v>41751730.299999997</v>
+        <v>45757561.450000003</v>
       </c>
       <c r="E15" s="6">
-        <v>39486740.299999997</v>
+        <v>43358716.189999998</v>
       </c>
       <c r="F15" s="6">
-        <v>37820996.810000002</v>
+        <v>38547937.329999998</v>
       </c>
       <c r="G15" s="6">
         <v>10843996.220000001</v>
       </c>
       <c r="H15" s="6">
-        <v>10111490.609999999</v>
+        <v>10529953.6</v>
       </c>
       <c r="I15" s="7">
-        <v>20955486.829999998</v>
+        <v>21373949.82</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1098,13 +1098,13 @@
         <v>23</v>
       </c>
       <c r="D16" s="6">
-        <v>49320169.869999997</v>
+        <v>50471543.600000001</v>
       </c>
       <c r="E16" s="6">
-        <v>44082100.460000001</v>
+        <v>44574823.140000001</v>
       </c>
       <c r="F16" s="6">
-        <v>35350539.530000001</v>
+        <v>37396450.350000001</v>
       </c>
       <c r="G16" s="6">
         <v>11209003.039999999</v>
@@ -1127,13 +1127,13 @@
         <v>24</v>
       </c>
       <c r="D17" s="6">
-        <v>295149788.68000001</v>
+        <v>304264202.60000002</v>
       </c>
       <c r="E17" s="6">
-        <v>202494452.91999999</v>
+        <v>213719232.41999999</v>
       </c>
       <c r="F17" s="6">
-        <v>165335449.81999999</v>
+        <v>184721504.41</v>
       </c>
       <c r="G17" s="6">
         <v>28757544</v>
@@ -1156,22 +1156,22 @@
         <v>25</v>
       </c>
       <c r="D18" s="6">
-        <v>1096240791.8800001</v>
+        <v>1091109113.22</v>
       </c>
       <c r="E18" s="6">
-        <v>1036977854.75</v>
+        <v>1041623006.4299999</v>
       </c>
       <c r="F18" s="6">
-        <v>1006932254.6799999</v>
+        <v>1013968286.4400001</v>
       </c>
       <c r="G18" s="6">
         <v>6925334.6500000004</v>
       </c>
       <c r="H18" s="6">
-        <v>28876413.780000001</v>
+        <v>29904342.25</v>
       </c>
       <c r="I18" s="7">
-        <v>35801748.43</v>
+        <v>36829676.899999999</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1185,13 +1185,13 @@
         <v>26</v>
       </c>
       <c r="D19" s="6">
-        <v>23273368.82</v>
+        <v>23289837.949999999</v>
       </c>
       <c r="E19" s="6">
-        <v>22924717.640000001</v>
+        <v>22948926.329999998</v>
       </c>
       <c r="F19" s="6">
-        <v>22401605.710000001</v>
+        <v>22420924.789999999</v>
       </c>
       <c r="G19" s="6">
         <v>5062</v>
@@ -1214,22 +1214,22 @@
         <v>27</v>
       </c>
       <c r="D20" s="6">
-        <v>8712420.8000000007</v>
+        <v>9041642.9900000002</v>
       </c>
       <c r="E20" s="6">
-        <v>7522376.6100000003</v>
+        <v>7532917.25</v>
       </c>
       <c r="F20" s="6">
-        <v>7324983.25</v>
+        <v>7339089.9100000001</v>
       </c>
       <c r="G20" s="6">
-        <v>211093.49</v>
+        <v>211328.04</v>
       </c>
       <c r="H20" s="6">
         <v>958212.55</v>
       </c>
       <c r="I20" s="7">
-        <v>1169306.04</v>
+        <v>1169540.5900000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1243,13 +1243,13 @@
         <v>28</v>
       </c>
       <c r="D21" s="6">
-        <v>4248956.37</v>
+        <v>4286510.72</v>
       </c>
       <c r="E21" s="6">
-        <v>3967707.31</v>
+        <v>4066632.61</v>
       </c>
       <c r="F21" s="6">
-        <v>3905488.71</v>
+        <v>4002981.87</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
@@ -1272,22 +1272,22 @@
         <v>29</v>
       </c>
       <c r="D22" s="6">
-        <v>72564683.260000005</v>
+        <v>73021536.939999998</v>
       </c>
       <c r="E22" s="6">
-        <v>18748702.800000001</v>
+        <v>19144310.789999999</v>
       </c>
       <c r="F22" s="6">
-        <v>17828707.190000001</v>
+        <v>18156721.469999999</v>
       </c>
       <c r="G22" s="6">
         <v>60000.1</v>
       </c>
       <c r="H22" s="6">
-        <v>45072263.210000001</v>
+        <v>46881628.140000001</v>
       </c>
       <c r="I22" s="7">
-        <v>45132263.310000002</v>
+        <v>46941628.240000002</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1301,13 +1301,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="6">
-        <v>3596783.39</v>
+        <v>3577897.55</v>
       </c>
       <c r="E23" s="6">
-        <v>3319181.82</v>
+        <v>3325299.01</v>
       </c>
       <c r="F23" s="6">
-        <v>3249582.7</v>
+        <v>3255681.43</v>
       </c>
       <c r="G23" s="6">
         <v>122407.67</v>
@@ -1330,13 +1330,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="6">
-        <v>500800000</v>
+        <v>504400000</v>
       </c>
       <c r="E24" s="6">
-        <v>272994715.06</v>
+        <v>276987551.11000001</v>
       </c>
       <c r="F24" s="6">
-        <v>272994715.06</v>
+        <v>276987551.11000001</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -1382,13 +1382,13 @@
         <v>33</v>
       </c>
       <c r="D26" s="6">
-        <v>3576955016.79</v>
+        <v>3583402171.8200002</v>
       </c>
       <c r="E26" s="6">
-        <v>2453989975.73</v>
+        <v>2571046760.6399999</v>
       </c>
       <c r="F26" s="6">
-        <v>2306734419.6399999</v>
+        <v>2418938285.0300002</v>
       </c>
       <c r="G26" s="6">
         <v>0</v>
@@ -1414,10 +1414,10 @@
         <v>59674219.560000002</v>
       </c>
       <c r="E27" s="6">
-        <v>58238503.140000001</v>
+        <v>58393473.920000002</v>
       </c>
       <c r="F27" s="6">
-        <v>58238141.240000002</v>
+        <v>58379623.710000001</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
@@ -1440,22 +1440,22 @@
         <v>35</v>
       </c>
       <c r="D28" s="6">
-        <v>953613140.34000003</v>
+        <v>964483849.28999996</v>
       </c>
       <c r="E28" s="6">
-        <v>502322037.13</v>
+        <v>528304522.22000003</v>
       </c>
       <c r="F28" s="6">
-        <v>479927915.43000001</v>
+        <v>508764385.52999997</v>
       </c>
       <c r="G28" s="6">
         <v>94822.57</v>
       </c>
       <c r="H28" s="6">
-        <v>188033164.62</v>
+        <v>188225260.33000001</v>
       </c>
       <c r="I28" s="7">
-        <v>188127987.19</v>
+        <v>188320082.90000001</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,13 +1469,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="6">
-        <v>1169524.0900000001</v>
+        <v>1171455.3400000001</v>
       </c>
       <c r="E29" s="6">
-        <v>1072982.05</v>
+        <v>1073078.97</v>
       </c>
       <c r="F29" s="6">
-        <v>1047678.36</v>
+        <v>1047774.18</v>
       </c>
       <c r="G29" s="6">
         <v>1692.39</v>
@@ -1498,22 +1498,22 @@
         <v>37</v>
       </c>
       <c r="D30" s="6">
-        <v>24337042.760000002</v>
+        <v>24352949.23</v>
       </c>
       <c r="E30" s="6">
-        <v>21985111.48</v>
+        <v>22057242.82</v>
       </c>
       <c r="F30" s="6">
-        <v>20708670.390000001</v>
+        <v>20783538.16</v>
       </c>
       <c r="G30" s="6">
         <v>27688.16</v>
       </c>
       <c r="H30" s="6">
-        <v>1625798.68</v>
+        <v>1661700.62</v>
       </c>
       <c r="I30" s="7">
-        <v>1653486.84</v>
+        <v>1689388.78</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1527,13 +1527,13 @@
         <v>38</v>
       </c>
       <c r="D31" s="6">
-        <v>220685546.31999999</v>
+        <v>227082535.97999999</v>
       </c>
       <c r="E31" s="6">
-        <v>169441331.56</v>
+        <v>174574938.41</v>
       </c>
       <c r="F31" s="6">
-        <v>164204779.31</v>
+        <v>166795902.69</v>
       </c>
       <c r="G31" s="6">
         <v>3290143.43</v>
@@ -1556,13 +1556,13 @@
         <v>39</v>
       </c>
       <c r="D32" s="6">
-        <v>21692165.07</v>
+        <v>21897896.16</v>
       </c>
       <c r="E32" s="6">
-        <v>21146632.079999998</v>
+        <v>21464740.170000002</v>
       </c>
       <c r="F32" s="6">
-        <v>19984165.399999999</v>
+        <v>20648122.93</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
@@ -1585,22 +1585,22 @@
         <v>40</v>
       </c>
       <c r="D33" s="6">
-        <v>70408960.730000004</v>
+        <v>71186662.739999995</v>
       </c>
       <c r="E33" s="6">
-        <v>67521762.819999993</v>
+        <v>68813843.079999998</v>
       </c>
       <c r="F33" s="6">
-        <v>63373739.07</v>
+        <v>64799631.68</v>
       </c>
       <c r="G33" s="6">
         <v>486532.65</v>
       </c>
       <c r="H33" s="6">
-        <v>6658345.8700000001</v>
+        <v>6665995.5499999998</v>
       </c>
       <c r="I33" s="7">
-        <v>7144878.5199999996</v>
+        <v>7152528.2000000002</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,22 +1614,22 @@
         <v>41</v>
       </c>
       <c r="D34" s="6">
-        <v>1048197290.33</v>
+        <v>1059404577.5599999</v>
       </c>
       <c r="E34" s="6">
-        <v>1031569547.5599999</v>
+        <v>1036389045.24</v>
       </c>
       <c r="F34" s="6">
-        <v>1018072253.36</v>
+        <v>1022106447.09</v>
       </c>
       <c r="G34" s="6">
-        <v>19255214.109999999</v>
+        <v>19255569.109999999</v>
       </c>
       <c r="H34" s="6">
-        <v>33950875.049999997</v>
+        <v>34201217.229999997</v>
       </c>
       <c r="I34" s="7">
-        <v>53206089.159999996</v>
+        <v>53456786.340000004</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1643,22 +1643,22 @@
         <v>42</v>
       </c>
       <c r="D35" s="6">
-        <v>20797026.800000001</v>
+        <v>23006458.739999998</v>
       </c>
       <c r="E35" s="6">
-        <v>18266599.239999998</v>
+        <v>18476673.620000001</v>
       </c>
       <c r="F35" s="6">
-        <v>17874700.140000001</v>
+        <v>18367536.09</v>
       </c>
       <c r="G35" s="6">
         <v>218.93</v>
       </c>
       <c r="H35" s="6">
-        <v>1820237.73</v>
+        <v>1837402.18</v>
       </c>
       <c r="I35" s="7">
-        <v>1820456.66</v>
+        <v>1837621.11</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1672,13 +1672,13 @@
         <v>43</v>
       </c>
       <c r="D36" s="6">
-        <v>2038198.26</v>
+        <v>2065823.64</v>
       </c>
       <c r="E36" s="6">
-        <v>1773279.02</v>
+        <v>1821169.85</v>
       </c>
       <c r="F36" s="6">
-        <v>1721747.41</v>
+        <v>1783256.3</v>
       </c>
       <c r="G36" s="6">
         <v>23147.54</v>
@@ -1701,22 +1701,22 @@
         <v>44</v>
       </c>
       <c r="D37" s="6">
-        <v>1528659.91</v>
+        <v>1531661.61</v>
       </c>
       <c r="E37" s="6">
-        <v>1475863.79</v>
+        <v>1492551.43</v>
       </c>
       <c r="F37" s="6">
-        <v>1418255.75</v>
+        <v>1432906.63</v>
       </c>
       <c r="G37" s="6">
         <v>46386.19</v>
       </c>
       <c r="H37" s="6">
-        <v>61424.34</v>
+        <v>65411.040000000001</v>
       </c>
       <c r="I37" s="7">
-        <v>107810.53</v>
+        <v>111797.23</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1730,13 +1730,13 @@
         <v>45</v>
       </c>
       <c r="D38" s="6">
-        <v>25547980.489999998</v>
+        <v>25620205.489999998</v>
       </c>
       <c r="E38" s="6">
-        <v>19630483.43</v>
+        <v>19707977.18</v>
       </c>
       <c r="F38" s="6">
-        <v>18365902.699999999</v>
+        <v>19135439.890000001</v>
       </c>
       <c r="G38" s="6">
         <v>866933.31</v>
@@ -1759,13 +1759,13 @@
         <v>46</v>
       </c>
       <c r="D39" s="6">
-        <v>9672483.0700000003</v>
+        <v>9673373.0700000003</v>
       </c>
       <c r="E39" s="6">
-        <v>5893171.9400000004</v>
+        <v>5948647.8499999996</v>
       </c>
       <c r="F39" s="6">
-        <v>5600551.2000000002</v>
+        <v>5763833.2300000004</v>
       </c>
       <c r="G39" s="6">
         <v>702452.89</v>
@@ -1791,10 +1791,10 @@
         <v>5816895.4199999999</v>
       </c>
       <c r="E40" s="6">
-        <v>5129112.5999999996</v>
+        <v>5169375.8899999997</v>
       </c>
       <c r="F40" s="6">
-        <v>4383117.2</v>
+        <v>4502270.87</v>
       </c>
       <c r="G40" s="6">
         <v>32410.16</v>
@@ -1817,13 +1817,13 @@
         <v>48</v>
       </c>
       <c r="D41" s="6">
-        <v>17192527.75</v>
+        <v>17511213.539999999</v>
       </c>
       <c r="E41" s="6">
-        <v>16852822.16</v>
+        <v>16906216.34</v>
       </c>
       <c r="F41" s="6">
-        <v>15390511.24</v>
+        <v>15444131.939999999</v>
       </c>
       <c r="G41" s="6">
         <v>4364694.79</v>
@@ -1846,13 +1846,13 @@
         <v>49</v>
       </c>
       <c r="D42" s="6">
-        <v>16736167.17</v>
+        <v>16752882.43</v>
       </c>
       <c r="E42" s="6">
-        <v>12059068.199999999</v>
+        <v>13065384.48</v>
       </c>
       <c r="F42" s="6">
-        <v>11581264.98</v>
+        <v>12668652.91</v>
       </c>
       <c r="G42" s="6">
         <v>1119472.81</v>
@@ -1875,22 +1875,22 @@
         <v>50</v>
       </c>
       <c r="D43" s="6">
-        <v>183435428.56</v>
+        <v>189888031.84</v>
       </c>
       <c r="E43" s="6">
-        <v>112965769.29000001</v>
+        <v>113444018.38</v>
       </c>
       <c r="F43" s="6">
-        <v>82586490.579999998</v>
+        <v>83013003.150000006</v>
       </c>
       <c r="G43" s="6">
         <v>7187273.0700000003</v>
       </c>
       <c r="H43" s="6">
-        <v>132798886.17</v>
+        <v>132911425.15000001</v>
       </c>
       <c r="I43" s="7">
-        <v>139986159.24000001</v>
+        <v>140098698.22</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1904,22 +1904,22 @@
         <v>51</v>
       </c>
       <c r="D44" s="6">
-        <v>882289198.39999998</v>
+        <v>889945126.60000002</v>
       </c>
       <c r="E44" s="6">
-        <v>768326465.59000003</v>
+        <v>780925832.25</v>
       </c>
       <c r="F44" s="6">
-        <v>736005338.38</v>
+        <v>742536864.25999999</v>
       </c>
       <c r="G44" s="6">
         <v>6041131.1100000003</v>
       </c>
       <c r="H44" s="6">
-        <v>87298827.409999996</v>
+        <v>87465812.599999994</v>
       </c>
       <c r="I44" s="7">
-        <v>93339958.519999996</v>
+        <v>93506943.709999993</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1933,13 +1933,13 @@
         <v>52</v>
       </c>
       <c r="D45" s="6">
-        <v>2509804.83</v>
+        <v>2727861.46</v>
       </c>
       <c r="E45" s="6">
-        <v>2070300.23</v>
+        <v>2074349.29</v>
       </c>
       <c r="F45" s="6">
-        <v>1923221.48</v>
+        <v>1927172.93</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>
@@ -1962,22 +1962,22 @@
         <v>53</v>
       </c>
       <c r="D46" s="6">
-        <v>748120917.36000001</v>
+        <v>752692974.57000005</v>
       </c>
       <c r="E46" s="6">
-        <v>260422693.69999999</v>
+        <v>304095023.60000002</v>
       </c>
       <c r="F46" s="6">
-        <v>229469171.47999999</v>
+        <v>257572265.05000001</v>
       </c>
       <c r="G46" s="6">
         <v>13431647.550000001</v>
       </c>
       <c r="H46" s="6">
-        <v>198036549.34</v>
+        <v>208038007.97999999</v>
       </c>
       <c r="I46" s="7">
-        <v>211468196.88999999</v>
+        <v>221469655.53</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1991,22 +1991,22 @@
         <v>54</v>
       </c>
       <c r="D47" s="6">
-        <v>162072686.41999999</v>
+        <v>165417433.5</v>
       </c>
       <c r="E47" s="6">
-        <v>146233242.94999999</v>
+        <v>147689785.09999999</v>
       </c>
       <c r="F47" s="6">
-        <v>143025270.34</v>
+        <v>144505320.77000001</v>
       </c>
       <c r="G47" s="6">
         <v>130453.78</v>
       </c>
       <c r="H47" s="6">
-        <v>20617821.059999999</v>
+        <v>20747045.100000001</v>
       </c>
       <c r="I47" s="7">
-        <v>20748274.84</v>
+        <v>20877498.879999999</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2020,22 +2020,22 @@
         <v>55</v>
       </c>
       <c r="D48" s="6">
-        <v>143771603.31999999</v>
+        <v>144493381.86000001</v>
       </c>
       <c r="E48" s="6">
-        <v>113134315.06999999</v>
+        <v>115397613.66</v>
       </c>
       <c r="F48" s="6">
-        <v>102426104.72</v>
+        <v>109136392.78</v>
       </c>
       <c r="G48" s="6">
         <v>3348075.28</v>
       </c>
       <c r="H48" s="6">
-        <v>22867796.5</v>
+        <v>22911977.390000001</v>
       </c>
       <c r="I48" s="7">
-        <v>26215871.780000001</v>
+        <v>26260052.670000002</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2049,13 +2049,13 @@
         <v>56</v>
       </c>
       <c r="D49" s="6">
-        <v>12013998.300000001</v>
+        <v>12168220.48</v>
       </c>
       <c r="E49" s="6">
-        <v>11434698.49</v>
+        <v>11604226.99</v>
       </c>
       <c r="F49" s="6">
-        <v>10783232.48</v>
+        <v>11137452.93</v>
       </c>
       <c r="G49" s="6">
         <v>6330.51</v>
@@ -2078,22 +2078,22 @@
         <v>57</v>
       </c>
       <c r="D50" s="6">
-        <v>141599497.34999999</v>
+        <v>142396273.94999999</v>
       </c>
       <c r="E50" s="6">
-        <v>124840950.11</v>
+        <v>126451149.41</v>
       </c>
       <c r="F50" s="6">
-        <v>122344490.83</v>
+        <v>123542274.75</v>
       </c>
       <c r="G50" s="6">
         <v>212410.94</v>
       </c>
       <c r="H50" s="6">
-        <v>15411225.58</v>
+        <v>16077300.689999999</v>
       </c>
       <c r="I50" s="7">
-        <v>15623636.52</v>
+        <v>16289711.630000001</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2107,22 +2107,22 @@
         <v>58</v>
       </c>
       <c r="D51" s="6">
-        <v>100811741.7</v>
+        <v>101599866.06999999</v>
       </c>
       <c r="E51" s="6">
-        <v>94908963.129999995</v>
+        <v>95670025.430000007</v>
       </c>
       <c r="F51" s="6">
-        <v>94446804.920000002</v>
+        <v>95322859.430000007</v>
       </c>
       <c r="G51" s="6">
         <v>509913.92</v>
       </c>
       <c r="H51" s="6">
-        <v>4406376.47</v>
+        <v>4438581.3600000003</v>
       </c>
       <c r="I51" s="7">
-        <v>4916290.3899999997</v>
+        <v>4948495.28</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2136,22 +2136,22 @@
         <v>59</v>
       </c>
       <c r="D52" s="6">
-        <v>15477223.98</v>
+        <v>17323198.149999999</v>
       </c>
       <c r="E52" s="6">
-        <v>8709736.2599999998</v>
+        <v>8885984.8699999992</v>
       </c>
       <c r="F52" s="6">
-        <v>8483669.3399999999</v>
+        <v>8659845.6899999995</v>
       </c>
       <c r="G52" s="6">
         <v>1021786.93</v>
       </c>
       <c r="H52" s="6">
-        <v>15988440.560000001</v>
+        <v>16542946.17</v>
       </c>
       <c r="I52" s="7">
-        <v>17010227.489999998</v>
+        <v>17564733.100000001</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2165,13 +2165,13 @@
         <v>60</v>
       </c>
       <c r="D53" s="6">
-        <v>2607301.87</v>
+        <v>2607453.4900000002</v>
       </c>
       <c r="E53" s="6">
-        <v>2239224.48</v>
+        <v>2441194.7999999998</v>
       </c>
       <c r="F53" s="6">
-        <v>2143656.5299999998</v>
+        <v>2315549</v>
       </c>
       <c r="G53" s="6">
         <v>167935.23</v>
@@ -2194,13 +2194,13 @@
         <v>61</v>
       </c>
       <c r="D54" s="6">
-        <v>7954474.5800000001</v>
+        <v>7988165.04</v>
       </c>
       <c r="E54" s="6">
-        <v>6693499.3399999999</v>
+        <v>6767708.5099999998</v>
       </c>
       <c r="F54" s="6">
-        <v>6628977.1799999997</v>
+        <v>6704417.4800000004</v>
       </c>
       <c r="G54" s="6">
         <v>8281.7999999999993</v>
@@ -2223,13 +2223,13 @@
         <v>62</v>
       </c>
       <c r="D55" s="6">
-        <v>3030627.45</v>
+        <v>3045071.74</v>
       </c>
       <c r="E55" s="6">
-        <v>1304694.97</v>
+        <v>1327899.98</v>
       </c>
       <c r="F55" s="6">
-        <v>1209423.76</v>
+        <v>1230645.52</v>
       </c>
       <c r="G55" s="6">
         <v>17304.09</v>
@@ -2252,13 +2252,13 @@
         <v>63</v>
       </c>
       <c r="D56" s="6">
-        <v>18702893.32</v>
+        <v>19063893.32</v>
       </c>
       <c r="E56" s="6">
-        <v>10817875.369999999</v>
+        <v>11048619.630000001</v>
       </c>
       <c r="F56" s="6">
-        <v>9910760.5999999996</v>
+        <v>9936965.5999999996</v>
       </c>
       <c r="G56" s="6">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>64</v>
       </c>
       <c r="D57" s="6">
-        <v>11503647.800000001</v>
+        <v>15973495.289999999</v>
       </c>
       <c r="E57" s="6">
-        <v>11194430.9</v>
+        <v>15666637.560000001</v>
       </c>
       <c r="F57" s="6">
-        <v>9363822.0800000001</v>
+        <v>13604733.130000001</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -2373,13 +2373,13 @@
         <v>68</v>
       </c>
       <c r="D61" s="6">
-        <v>5965481.0700000003</v>
+        <v>5206932.43</v>
       </c>
       <c r="E61" s="6">
-        <v>4960280.8099999996</v>
+        <v>5206932.43</v>
       </c>
       <c r="F61" s="6">
-        <v>4960280.8099999996</v>
+        <v>5206932.43</v>
       </c>
       <c r="G61" s="6">
         <v>360498.89</v>
@@ -2402,7 +2402,7 @@
         <v>69</v>
       </c>
       <c r="D62" s="6">
-        <v>23226.75</v>
+        <v>123226.75</v>
       </c>
       <c r="E62" s="6">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>70</v>
       </c>
       <c r="D63" s="6">
-        <v>66061886.119999997</v>
+        <v>68231509.290000007</v>
       </c>
       <c r="E63" s="6">
-        <v>38553030</v>
+        <v>40554528.810000002</v>
       </c>
       <c r="F63" s="6">
-        <v>28855764.219999999</v>
+        <v>31016651.600000001</v>
       </c>
       <c r="G63" s="6">
         <v>522774.46</v>
@@ -2460,22 +2460,22 @@
         <v>71</v>
       </c>
       <c r="D64" s="6">
-        <v>6432945131.2200003</v>
+        <v>7096501565.7799997</v>
       </c>
       <c r="E64" s="6">
-        <v>3146070994.8600001</v>
+        <v>3251270790.9699998</v>
       </c>
       <c r="F64" s="6">
-        <v>2901354540.4099998</v>
+        <v>2986518612.96</v>
       </c>
       <c r="G64" s="6">
-        <v>254670453.41999999</v>
+        <v>255021157.40000001</v>
       </c>
       <c r="H64" s="6">
-        <v>403268655.44</v>
+        <v>406790858.24000001</v>
       </c>
       <c r="I64" s="7">
-        <v>657939108.86000001</v>
+        <v>661812015.63999999</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2518,22 +2518,22 @@
         <v>73</v>
       </c>
       <c r="D66" s="6">
-        <v>253561.99</v>
+        <v>253601.91</v>
       </c>
       <c r="E66" s="6">
-        <v>248535.63</v>
+        <v>250057.48</v>
       </c>
       <c r="F66" s="6">
-        <v>231462.84</v>
+        <v>232984.69</v>
       </c>
       <c r="G66" s="6">
-        <v>65790.19</v>
+        <v>68494.850000000006</v>
       </c>
       <c r="H66" s="6">
         <v>284844.95</v>
       </c>
       <c r="I66" s="7">
-        <v>350635.14</v>
+        <v>353339.8</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2547,22 +2547,22 @@
         <v>74</v>
       </c>
       <c r="D67" s="6">
-        <v>32199093.260000002</v>
+        <v>45937523.609999999</v>
       </c>
       <c r="E67" s="6">
-        <v>20733009.960000001</v>
+        <v>21778893.280000001</v>
       </c>
       <c r="F67" s="6">
-        <v>18980822.289999999</v>
+        <v>19663515.68</v>
       </c>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>16892454.149999999</v>
+        <v>17655143.399999999</v>
       </c>
       <c r="I67" s="7">
-        <v>16892454.149999999</v>
+        <v>17655143.399999999</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2576,13 +2576,13 @@
         <v>75</v>
       </c>
       <c r="D68" s="6">
-        <v>25849993.550000001</v>
+        <v>26233706.559999999</v>
       </c>
       <c r="E68" s="6">
-        <v>22079098.399999999</v>
+        <v>22204310.210000001</v>
       </c>
       <c r="F68" s="6">
-        <v>15569057.76</v>
+        <v>21503011.300000001</v>
       </c>
       <c r="G68" s="6">
         <v>28530.55</v>
@@ -2715,22 +2715,22 @@
         <v>80</v>
       </c>
       <c r="D73" s="6">
-        <v>11146939.67</v>
+        <v>11207617.67</v>
       </c>
       <c r="E73" s="6">
-        <v>2353416.91</v>
+        <v>2714034.91</v>
       </c>
       <c r="F73" s="6">
-        <v>1586135.48</v>
+        <v>1870532.73</v>
       </c>
       <c r="G73" s="6">
         <v>4586769.4800000004</v>
       </c>
       <c r="H73" s="6">
-        <v>23419440.469999999</v>
+        <v>26358666.129999999</v>
       </c>
       <c r="I73" s="7">
-        <v>28006209.949999999</v>
+        <v>30945435.609999999</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2747,10 +2747,10 @@
         <v>126099.31</v>
       </c>
       <c r="E74" s="6">
-        <v>85063.46</v>
+        <v>89168.26</v>
       </c>
       <c r="F74" s="6">
-        <v>83592.240000000005</v>
+        <v>87697.04</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -2773,13 +2773,13 @@
         <v>82</v>
       </c>
       <c r="D75" s="6">
-        <v>5744412634.9700003</v>
+        <v>5798977120.6999998</v>
       </c>
       <c r="E75" s="6">
-        <v>5741032512.5500002</v>
+        <v>5795596998.2799997</v>
       </c>
       <c r="F75" s="6">
-        <v>5740925028.6300001</v>
+        <v>5795489514.3599997</v>
       </c>
       <c r="G75" s="6">
         <v>57945.89</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -692,22 +692,22 @@
         <v>9</v>
       </c>
       <c r="D2" s="6">
-        <v>48541058.689999998</v>
+        <v>49413706.600000001</v>
       </c>
       <c r="E2" s="6">
-        <v>19998222.75</v>
+        <v>21270175.949999999</v>
       </c>
       <c r="F2" s="6">
-        <v>16920729.699999999</v>
+        <v>18854491.32</v>
       </c>
       <c r="G2" s="6">
         <v>1803218.12</v>
       </c>
       <c r="H2" s="6">
-        <v>9123946</v>
+        <v>9395969.3000000007</v>
       </c>
       <c r="I2" s="7">
-        <v>10927164.119999999</v>
+        <v>11199187.42</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -721,22 +721,22 @@
         <v>10</v>
       </c>
       <c r="D3" s="6">
-        <v>482044629.67000002</v>
+        <v>484376237.14999998</v>
       </c>
       <c r="E3" s="6">
-        <v>340648226.49000001</v>
+        <v>348482474.98000002</v>
       </c>
       <c r="F3" s="6">
-        <v>318068310.60000002</v>
+        <v>331321689.98000002</v>
       </c>
       <c r="G3" s="6">
         <v>185261438.00999999</v>
       </c>
       <c r="H3" s="6">
-        <v>2334143.0299999998</v>
+        <v>2413043.11</v>
       </c>
       <c r="I3" s="7">
-        <v>187595581.03999999</v>
+        <v>187674481.12</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -750,13 +750,13 @@
         <v>11</v>
       </c>
       <c r="D4" s="6">
-        <v>6494533.79</v>
+        <v>6620623.2999999998</v>
       </c>
       <c r="E4" s="6">
-        <v>6256089.2300000004</v>
+        <v>6398017.04</v>
       </c>
       <c r="F4" s="6">
-        <v>6208634.1299999999</v>
+        <v>6350639.9699999997</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -779,22 +779,22 @@
         <v>12</v>
       </c>
       <c r="D5" s="6">
-        <v>646898178.23000002</v>
+        <v>779728797.73000002</v>
       </c>
       <c r="E5" s="6">
-        <v>567521751.27999997</v>
+        <v>700407956.59000003</v>
       </c>
       <c r="F5" s="6">
-        <v>549505322.71000004</v>
+        <v>680939121.91999996</v>
       </c>
       <c r="G5" s="6">
         <v>7665444.21</v>
       </c>
       <c r="H5" s="6">
-        <v>48467480.920000002</v>
+        <v>49026978.5</v>
       </c>
       <c r="I5" s="7">
-        <v>56132925.130000003</v>
+        <v>56692422.710000001</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -808,22 +808,22 @@
         <v>13</v>
       </c>
       <c r="D6" s="6">
-        <v>37888385.329999998</v>
+        <v>38222574.100000001</v>
       </c>
       <c r="E6" s="6">
-        <v>18427647.449999999</v>
+        <v>18955096.260000002</v>
       </c>
       <c r="F6" s="6">
-        <v>17781706.469999999</v>
+        <v>18119461.190000001</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>18898548.84</v>
+        <v>19703721.510000002</v>
       </c>
       <c r="I6" s="7">
-        <v>18898548.84</v>
+        <v>19703721.510000002</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -837,22 +837,22 @@
         <v>14</v>
       </c>
       <c r="D7" s="6">
-        <v>67825743.239999995</v>
+        <v>88398162.939999998</v>
       </c>
       <c r="E7" s="6">
-        <v>39989170.670000002</v>
+        <v>54260937.939999998</v>
       </c>
       <c r="F7" s="6">
-        <v>39506776.460000001</v>
+        <v>53778401.259999998</v>
       </c>
       <c r="G7" s="6">
         <v>5876518.1600000001</v>
       </c>
       <c r="H7" s="6">
-        <v>14436883.66</v>
+        <v>15736444.300000001</v>
       </c>
       <c r="I7" s="7">
-        <v>20313401.82</v>
+        <v>21612962.460000001</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -866,22 +866,22 @@
         <v>15</v>
       </c>
       <c r="D8" s="6">
-        <v>5782741333.5</v>
+        <v>7255764736.6499996</v>
       </c>
       <c r="E8" s="6">
-        <v>5598188912.3199997</v>
+        <v>7066814219.5600004</v>
       </c>
       <c r="F8" s="6">
-        <v>5582849294.1199999</v>
+        <v>7051362392.5299997</v>
       </c>
       <c r="G8" s="6">
         <v>18529479.850000001</v>
       </c>
       <c r="H8" s="6">
-        <v>132039237.27</v>
+        <v>133357683.37</v>
       </c>
       <c r="I8" s="7">
-        <v>150568717.12</v>
+        <v>151887163.22</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -895,22 +895,22 @@
         <v>16</v>
       </c>
       <c r="D9" s="6">
-        <v>6548492067.1400003</v>
+        <v>7809715773.9200001</v>
       </c>
       <c r="E9" s="6">
-        <v>6288241790.9300003</v>
+        <v>7569386615.5799999</v>
       </c>
       <c r="F9" s="6">
-        <v>6077544342.4499998</v>
+        <v>7374931357.8199997</v>
       </c>
       <c r="G9" s="6">
         <v>195886022.58000001</v>
       </c>
       <c r="H9" s="6">
-        <v>119422848.89</v>
+        <v>120082324.41</v>
       </c>
       <c r="I9" s="7">
-        <v>315308871.47000003</v>
+        <v>315968346.99000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -924,22 +924,22 @@
         <v>17</v>
       </c>
       <c r="D10" s="6">
-        <v>33546341.780000001</v>
+        <v>35124631.18</v>
       </c>
       <c r="E10" s="6">
-        <v>23320589.710000001</v>
+        <v>24924379.52</v>
       </c>
       <c r="F10" s="6">
-        <v>22643200.350000001</v>
+        <v>23467871.5</v>
       </c>
       <c r="G10" s="6">
         <v>319615.87</v>
       </c>
       <c r="H10" s="6">
-        <v>619454.23</v>
+        <v>620274.23</v>
       </c>
       <c r="I10" s="7">
-        <v>939070.1</v>
+        <v>939890.1</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -953,22 +953,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="6">
-        <v>68905686.510000005</v>
+        <v>72870921.719999999</v>
       </c>
       <c r="E11" s="6">
-        <v>58110768.850000001</v>
+        <v>61210908.240000002</v>
       </c>
       <c r="F11" s="6">
-        <v>51946823.200000003</v>
+        <v>54026756.82</v>
       </c>
       <c r="G11" s="6">
         <v>15843807.77</v>
       </c>
       <c r="H11" s="6">
-        <v>21025828.969999999</v>
+        <v>22848293.109999999</v>
       </c>
       <c r="I11" s="7">
-        <v>36869636.740000002</v>
+        <v>38692100.880000003</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -982,13 +982,13 @@
         <v>19</v>
       </c>
       <c r="D12" s="6">
-        <v>80060092.079999998</v>
+        <v>90204665.670000002</v>
       </c>
       <c r="E12" s="6">
-        <v>72768414.540000007</v>
+        <v>83306543.75</v>
       </c>
       <c r="F12" s="6">
-        <v>71513431.640000001</v>
+        <v>81929617.040000007</v>
       </c>
       <c r="G12" s="6">
         <v>3823909.86</v>
@@ -1011,22 +1011,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="6">
-        <v>690547959.28999996</v>
+        <v>854595332.21000004</v>
       </c>
       <c r="E13" s="6">
-        <v>667076238.23000002</v>
+        <v>830243623.21000004</v>
       </c>
       <c r="F13" s="6">
-        <v>664266727.12</v>
+        <v>828280751.91999996</v>
       </c>
       <c r="G13" s="6">
         <v>6046803.8799999999</v>
       </c>
       <c r="H13" s="6">
-        <v>27623490.77</v>
+        <v>28693040.09</v>
       </c>
       <c r="I13" s="7">
-        <v>33670294.649999999</v>
+        <v>34739843.969999999</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1040,22 +1040,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="6">
-        <v>1831892085.25</v>
+        <v>1942900766.29</v>
       </c>
       <c r="E14" s="6">
-        <v>1496182974.25</v>
+        <v>1624409708.01</v>
       </c>
       <c r="F14" s="6">
-        <v>1460816233.71</v>
+        <v>1601455358.04</v>
       </c>
       <c r="G14" s="6">
-        <v>14179981.15</v>
+        <v>14409521.41</v>
       </c>
       <c r="H14" s="6">
-        <v>113371319.05</v>
+        <v>114681486.28</v>
       </c>
       <c r="I14" s="7">
-        <v>127551300.2</v>
+        <v>129091007.69</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1069,22 +1069,22 @@
         <v>22</v>
       </c>
       <c r="D15" s="6">
-        <v>45757561.450000003</v>
+        <v>48847630.140000001</v>
       </c>
       <c r="E15" s="6">
-        <v>43358716.189999998</v>
+        <v>46014739.579999998</v>
       </c>
       <c r="F15" s="6">
-        <v>38547937.329999998</v>
+        <v>45068132.219999999</v>
       </c>
       <c r="G15" s="6">
-        <v>10843996.220000001</v>
+        <v>11543150.439999999</v>
       </c>
       <c r="H15" s="6">
-        <v>10529953.6</v>
+        <v>11090758.09</v>
       </c>
       <c r="I15" s="7">
-        <v>21373949.82</v>
+        <v>22633908.530000001</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1098,22 +1098,22 @@
         <v>23</v>
       </c>
       <c r="D16" s="6">
-        <v>50471543.600000001</v>
+        <v>109174026.64</v>
       </c>
       <c r="E16" s="6">
-        <v>44574823.140000001</v>
+        <v>48907216.109999999</v>
       </c>
       <c r="F16" s="6">
-        <v>37396450.350000001</v>
+        <v>41063314.729999997</v>
       </c>
       <c r="G16" s="6">
         <v>11209003.039999999</v>
       </c>
       <c r="H16" s="6">
-        <v>3711726.53</v>
+        <v>4094313.55</v>
       </c>
       <c r="I16" s="7">
-        <v>14920729.57</v>
+        <v>15303316.59</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1127,22 +1127,22 @@
         <v>24</v>
       </c>
       <c r="D17" s="6">
-        <v>304264202.60000002</v>
+        <v>312466170</v>
       </c>
       <c r="E17" s="6">
-        <v>213719232.41999999</v>
+        <v>220481346.53</v>
       </c>
       <c r="F17" s="6">
-        <v>184721504.41</v>
+        <v>197468873.80000001</v>
       </c>
       <c r="G17" s="6">
         <v>28757544</v>
       </c>
       <c r="H17" s="6">
-        <v>64889453.780000001</v>
+        <v>65545570.299999997</v>
       </c>
       <c r="I17" s="7">
-        <v>93646997.780000001</v>
+        <v>94303114.299999997</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1156,22 +1156,22 @@
         <v>25</v>
       </c>
       <c r="D18" s="6">
-        <v>1091109113.22</v>
+        <v>1276615091.5599999</v>
       </c>
       <c r="E18" s="6">
-        <v>1041623006.4299999</v>
+        <v>1221724810.98</v>
       </c>
       <c r="F18" s="6">
-        <v>1013968286.4400001</v>
+        <v>1188726604.28</v>
       </c>
       <c r="G18" s="6">
         <v>6925334.6500000004</v>
       </c>
       <c r="H18" s="6">
-        <v>29904342.25</v>
+        <v>30018112.559999999</v>
       </c>
       <c r="I18" s="7">
-        <v>36829676.899999999</v>
+        <v>36943447.210000001</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1185,13 +1185,13 @@
         <v>26</v>
       </c>
       <c r="D19" s="6">
-        <v>23289837.949999999</v>
+        <v>23669587.420000002</v>
       </c>
       <c r="E19" s="6">
-        <v>22948926.329999998</v>
+        <v>23275782.289999999</v>
       </c>
       <c r="F19" s="6">
-        <v>22420924.789999999</v>
+        <v>22766821.149999999</v>
       </c>
       <c r="G19" s="6">
         <v>5062</v>
@@ -1214,22 +1214,22 @@
         <v>27</v>
       </c>
       <c r="D20" s="6">
-        <v>9041642.9900000002</v>
+        <v>10374710.49</v>
       </c>
       <c r="E20" s="6">
-        <v>7532917.25</v>
+        <v>9028147.9800000004</v>
       </c>
       <c r="F20" s="6">
-        <v>7339089.9100000001</v>
+        <v>8813826.4600000009</v>
       </c>
       <c r="G20" s="6">
         <v>211328.04</v>
       </c>
       <c r="H20" s="6">
-        <v>958212.55</v>
+        <v>959977.43</v>
       </c>
       <c r="I20" s="7">
-        <v>1169540.5900000001</v>
+        <v>1171305.47</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1243,13 +1243,13 @@
         <v>28</v>
       </c>
       <c r="D21" s="6">
-        <v>4286510.72</v>
+        <v>4362530.38</v>
       </c>
       <c r="E21" s="6">
-        <v>4066632.61</v>
+        <v>4158919.41</v>
       </c>
       <c r="F21" s="6">
-        <v>4002981.87</v>
+        <v>4095268.67</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
@@ -1272,22 +1272,22 @@
         <v>29</v>
       </c>
       <c r="D22" s="6">
-        <v>73021536.939999998</v>
+        <v>75766363.930000007</v>
       </c>
       <c r="E22" s="6">
-        <v>19144310.789999999</v>
+        <v>21239098.52</v>
       </c>
       <c r="F22" s="6">
-        <v>18156721.469999999</v>
+        <v>19867834.359999999</v>
       </c>
       <c r="G22" s="6">
         <v>60000.1</v>
       </c>
       <c r="H22" s="6">
-        <v>46881628.140000001</v>
+        <v>48788270.479999997</v>
       </c>
       <c r="I22" s="7">
-        <v>46941628.240000002</v>
+        <v>48848270.579999998</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1301,13 +1301,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="6">
-        <v>3577897.55</v>
+        <v>3640285.05</v>
       </c>
       <c r="E23" s="6">
-        <v>3325299.01</v>
+        <v>3386840.55</v>
       </c>
       <c r="F23" s="6">
-        <v>3255681.43</v>
+        <v>3316962.27</v>
       </c>
       <c r="G23" s="6">
         <v>122407.67</v>
@@ -1330,13 +1330,13 @@
         <v>31</v>
       </c>
       <c r="D24" s="6">
-        <v>504400000</v>
+        <v>509489748.27999997</v>
       </c>
       <c r="E24" s="6">
-        <v>276987551.11000001</v>
+        <v>352867696.62</v>
       </c>
       <c r="F24" s="6">
-        <v>276987551.11000001</v>
+        <v>352863333.85000002</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>32</v>
       </c>
       <c r="D25" s="6">
-        <v>7172133.3600000003</v>
+        <v>7173386.8099999996</v>
       </c>
       <c r="E25" s="6">
-        <v>7172133.3600000003</v>
+        <v>7173386.8099999996</v>
       </c>
       <c r="F25" s="6">
         <v>7172133.3600000003</v>
@@ -1411,22 +1411,22 @@
         <v>34</v>
       </c>
       <c r="D27" s="6">
-        <v>59674219.560000002</v>
+        <v>75440224.450000003</v>
       </c>
       <c r="E27" s="6">
-        <v>58393473.920000002</v>
+        <v>74157334.280000001</v>
       </c>
       <c r="F27" s="6">
-        <v>58379623.710000001</v>
+        <v>74152468.260000005</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" s="6">
-        <v>874849.53</v>
+        <v>886712.42</v>
       </c>
       <c r="I27" s="7">
-        <v>874849.53</v>
+        <v>886712.42</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1440,22 +1440,22 @@
         <v>35</v>
       </c>
       <c r="D28" s="6">
-        <v>964483849.28999996</v>
+        <v>972412166.30999994</v>
       </c>
       <c r="E28" s="6">
-        <v>528304522.22000003</v>
+        <v>567305249.00999999</v>
       </c>
       <c r="F28" s="6">
-        <v>508764385.52999997</v>
+        <v>550092147.48000002</v>
       </c>
       <c r="G28" s="6">
         <v>94822.57</v>
       </c>
       <c r="H28" s="6">
-        <v>188225260.33000001</v>
+        <v>188581228.80000001</v>
       </c>
       <c r="I28" s="7">
-        <v>188320082.90000001</v>
+        <v>188676051.37</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,13 +1469,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="6">
-        <v>1171455.3400000001</v>
+        <v>1180376.47</v>
       </c>
       <c r="E29" s="6">
-        <v>1073078.97</v>
+        <v>1079231.28</v>
       </c>
       <c r="F29" s="6">
-        <v>1047774.18</v>
+        <v>1052724.1000000001</v>
       </c>
       <c r="G29" s="6">
         <v>1692.39</v>
@@ -1498,22 +1498,22 @@
         <v>37</v>
       </c>
       <c r="D30" s="6">
-        <v>24352949.23</v>
+        <v>24643439.030000001</v>
       </c>
       <c r="E30" s="6">
-        <v>22057242.82</v>
+        <v>22366252.5</v>
       </c>
       <c r="F30" s="6">
-        <v>20783538.16</v>
+        <v>21436015.289999999</v>
       </c>
       <c r="G30" s="6">
         <v>27688.16</v>
       </c>
       <c r="H30" s="6">
-        <v>1661700.62</v>
+        <v>1664261.76</v>
       </c>
       <c r="I30" s="7">
-        <v>1689388.78</v>
+        <v>1691949.92</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1527,13 +1527,13 @@
         <v>38</v>
       </c>
       <c r="D31" s="6">
-        <v>227082535.97999999</v>
+        <v>244920040.12</v>
       </c>
       <c r="E31" s="6">
-        <v>174574938.41</v>
+        <v>180665502.15000001</v>
       </c>
       <c r="F31" s="6">
-        <v>166795902.69</v>
+        <v>174263893.84999999</v>
       </c>
       <c r="G31" s="6">
         <v>3290143.43</v>
@@ -1556,22 +1556,22 @@
         <v>39</v>
       </c>
       <c r="D32" s="6">
-        <v>21897896.16</v>
+        <v>22039396.73</v>
       </c>
       <c r="E32" s="6">
-        <v>21464740.170000002</v>
+        <v>21604834.690000001</v>
       </c>
       <c r="F32" s="6">
-        <v>20648122.93</v>
+        <v>20882205.66</v>
       </c>
       <c r="G32" s="6">
-        <v>0</v>
+        <v>8.36</v>
       </c>
       <c r="H32" s="6">
         <v>1010938.21</v>
       </c>
       <c r="I32" s="7">
-        <v>1010938.21</v>
+        <v>1010946.57</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1585,22 +1585,22 @@
         <v>40</v>
       </c>
       <c r="D33" s="6">
-        <v>71186662.739999995</v>
+        <v>72183057.489999995</v>
       </c>
       <c r="E33" s="6">
-        <v>68813843.079999998</v>
+        <v>69264378.560000002</v>
       </c>
       <c r="F33" s="6">
-        <v>64799631.68</v>
+        <v>65667747.060000002</v>
       </c>
       <c r="G33" s="6">
         <v>486532.65</v>
       </c>
       <c r="H33" s="6">
-        <v>6665995.5499999998</v>
+        <v>6666623.1900000004</v>
       </c>
       <c r="I33" s="7">
-        <v>7152528.2000000002</v>
+        <v>7153155.8399999999</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1614,22 +1614,22 @@
         <v>41</v>
       </c>
       <c r="D34" s="6">
-        <v>1059404577.5599999</v>
+        <v>1134082855.6900001</v>
       </c>
       <c r="E34" s="6">
-        <v>1036389045.24</v>
+        <v>1111097023.6700001</v>
       </c>
       <c r="F34" s="6">
-        <v>1022106447.09</v>
+        <v>1095465052.74</v>
       </c>
       <c r="G34" s="6">
         <v>19255569.109999999</v>
       </c>
       <c r="H34" s="6">
-        <v>34201217.229999997</v>
+        <v>34294835.789999999</v>
       </c>
       <c r="I34" s="7">
-        <v>53456786.340000004</v>
+        <v>53550404.899999999</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1643,22 +1643,22 @@
         <v>42</v>
       </c>
       <c r="D35" s="6">
-        <v>23006458.739999998</v>
+        <v>24148580.109999999</v>
       </c>
       <c r="E35" s="6">
-        <v>18476673.620000001</v>
+        <v>20520349.989999998</v>
       </c>
       <c r="F35" s="6">
-        <v>18367536.09</v>
+        <v>20371429.27</v>
       </c>
       <c r="G35" s="6">
         <v>218.93</v>
       </c>
       <c r="H35" s="6">
-        <v>1837402.18</v>
+        <v>1851249.62</v>
       </c>
       <c r="I35" s="7">
-        <v>1837621.11</v>
+        <v>1851468.55</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1672,13 +1672,13 @@
         <v>43</v>
       </c>
       <c r="D36" s="6">
-        <v>2065823.64</v>
+        <v>2107358.4500000002</v>
       </c>
       <c r="E36" s="6">
-        <v>1821169.85</v>
+        <v>1951631.47</v>
       </c>
       <c r="F36" s="6">
-        <v>1783256.3</v>
+        <v>1903450.65</v>
       </c>
       <c r="G36" s="6">
         <v>23147.54</v>
@@ -1701,13 +1701,13 @@
         <v>44</v>
       </c>
       <c r="D37" s="6">
-        <v>1531661.61</v>
+        <v>1572800.04</v>
       </c>
       <c r="E37" s="6">
-        <v>1492551.43</v>
+        <v>1535622.6</v>
       </c>
       <c r="F37" s="6">
-        <v>1432906.63</v>
+        <v>1474211.29</v>
       </c>
       <c r="G37" s="6">
         <v>46386.19</v>
@@ -1730,13 +1730,13 @@
         <v>45</v>
       </c>
       <c r="D38" s="6">
-        <v>25620205.489999998</v>
+        <v>25938971.690000001</v>
       </c>
       <c r="E38" s="6">
-        <v>19707977.18</v>
+        <v>19976184.649999999</v>
       </c>
       <c r="F38" s="6">
-        <v>19135439.890000001</v>
+        <v>19434602.949999999</v>
       </c>
       <c r="G38" s="6">
         <v>866933.31</v>
@@ -1759,13 +1759,13 @@
         <v>46</v>
       </c>
       <c r="D39" s="6">
-        <v>9673373.0700000003</v>
+        <v>9696002.3800000008</v>
       </c>
       <c r="E39" s="6">
-        <v>5948647.8499999996</v>
+        <v>6016352.6100000003</v>
       </c>
       <c r="F39" s="6">
-        <v>5763833.2300000004</v>
+        <v>5831435.1299999999</v>
       </c>
       <c r="G39" s="6">
         <v>702452.89</v>
@@ -1788,13 +1788,13 @@
         <v>47</v>
       </c>
       <c r="D40" s="6">
-        <v>5816895.4199999999</v>
+        <v>5847603.4199999999</v>
       </c>
       <c r="E40" s="6">
-        <v>5169375.8899999997</v>
+        <v>5173479.3899999997</v>
       </c>
       <c r="F40" s="6">
-        <v>4502270.87</v>
+        <v>4506374.37</v>
       </c>
       <c r="G40" s="6">
         <v>32410.16</v>
@@ -1817,13 +1817,13 @@
         <v>48</v>
       </c>
       <c r="D41" s="6">
-        <v>17511213.539999999</v>
+        <v>17910910.66</v>
       </c>
       <c r="E41" s="6">
-        <v>16906216.34</v>
+        <v>17355249.829999998</v>
       </c>
       <c r="F41" s="6">
-        <v>15444131.939999999</v>
+        <v>15965044.85</v>
       </c>
       <c r="G41" s="6">
         <v>4364694.79</v>
@@ -1846,13 +1846,13 @@
         <v>49</v>
       </c>
       <c r="D42" s="6">
-        <v>16752882.43</v>
+        <v>16767696.93</v>
       </c>
       <c r="E42" s="6">
-        <v>13065384.48</v>
+        <v>13773129.970000001</v>
       </c>
       <c r="F42" s="6">
-        <v>12668652.91</v>
+        <v>12749528.119999999</v>
       </c>
       <c r="G42" s="6">
         <v>1119472.81</v>
@@ -1875,22 +1875,22 @@
         <v>50</v>
       </c>
       <c r="D43" s="6">
-        <v>189888031.84</v>
+        <v>195505342.75</v>
       </c>
       <c r="E43" s="6">
-        <v>113444018.38</v>
+        <v>115744174.64</v>
       </c>
       <c r="F43" s="6">
-        <v>83013003.150000006</v>
+        <v>99817297.409999996</v>
       </c>
       <c r="G43" s="6">
         <v>7187273.0700000003</v>
       </c>
       <c r="H43" s="6">
-        <v>132911425.15000001</v>
+        <v>132930229.86</v>
       </c>
       <c r="I43" s="7">
-        <v>140098698.22</v>
+        <v>140117502.93000001</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1904,22 +1904,22 @@
         <v>51</v>
       </c>
       <c r="D44" s="6">
-        <v>889945126.60000002</v>
+        <v>911946197.34000003</v>
       </c>
       <c r="E44" s="6">
-        <v>780925832.25</v>
+        <v>817705828.07000005</v>
       </c>
       <c r="F44" s="6">
-        <v>742536864.25999999</v>
+        <v>782681483.01999998</v>
       </c>
       <c r="G44" s="6">
         <v>6041131.1100000003</v>
       </c>
       <c r="H44" s="6">
-        <v>87465812.599999994</v>
+        <v>87809002.459999993</v>
       </c>
       <c r="I44" s="7">
-        <v>93506943.709999993</v>
+        <v>93850133.569999993</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1933,13 +1933,13 @@
         <v>52</v>
       </c>
       <c r="D45" s="6">
-        <v>2727861.46</v>
+        <v>2787555.49</v>
       </c>
       <c r="E45" s="6">
-        <v>2074349.29</v>
+        <v>2096145.96</v>
       </c>
       <c r="F45" s="6">
-        <v>1927172.93</v>
+        <v>1947170.01</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>
@@ -1962,22 +1962,22 @@
         <v>53</v>
       </c>
       <c r="D46" s="6">
-        <v>752692974.57000005</v>
+        <v>763759929.73000002</v>
       </c>
       <c r="E46" s="6">
-        <v>304095023.60000002</v>
+        <v>346704213.30000001</v>
       </c>
       <c r="F46" s="6">
-        <v>257572265.05000001</v>
+        <v>310592871.91000003</v>
       </c>
       <c r="G46" s="6">
         <v>13431647.550000001</v>
       </c>
       <c r="H46" s="6">
-        <v>208038007.97999999</v>
+        <v>222450392.75999999</v>
       </c>
       <c r="I46" s="7">
-        <v>221469655.53</v>
+        <v>235882040.31</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -1991,22 +1991,22 @@
         <v>54</v>
       </c>
       <c r="D47" s="6">
-        <v>165417433.5</v>
+        <v>169052531.97999999</v>
       </c>
       <c r="E47" s="6">
-        <v>147689785.09999999</v>
+        <v>152360154.84</v>
       </c>
       <c r="F47" s="6">
-        <v>144505320.77000001</v>
+        <v>149048039.99000001</v>
       </c>
       <c r="G47" s="6">
         <v>130453.78</v>
       </c>
       <c r="H47" s="6">
-        <v>20747045.100000001</v>
+        <v>21168001.68</v>
       </c>
       <c r="I47" s="7">
-        <v>20877498.879999999</v>
+        <v>21298455.460000001</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2020,22 +2020,22 @@
         <v>55</v>
       </c>
       <c r="D48" s="6">
-        <v>144493381.86000001</v>
+        <v>145051647.11000001</v>
       </c>
       <c r="E48" s="6">
-        <v>115397613.66</v>
+        <v>118990162.62</v>
       </c>
       <c r="F48" s="6">
-        <v>109136392.78</v>
+        <v>112164363.84999999</v>
       </c>
       <c r="G48" s="6">
         <v>3348075.28</v>
       </c>
       <c r="H48" s="6">
-        <v>22911977.390000001</v>
+        <v>23369369.02</v>
       </c>
       <c r="I48" s="7">
-        <v>26260052.670000002</v>
+        <v>26717444.300000001</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2049,13 +2049,13 @@
         <v>56</v>
       </c>
       <c r="D49" s="6">
-        <v>12168220.48</v>
+        <v>13304080.380000001</v>
       </c>
       <c r="E49" s="6">
-        <v>11604226.99</v>
+        <v>12707145.99</v>
       </c>
       <c r="F49" s="6">
-        <v>11137452.93</v>
+        <v>12192877.619999999</v>
       </c>
       <c r="G49" s="6">
         <v>6330.51</v>
@@ -2078,22 +2078,22 @@
         <v>57</v>
       </c>
       <c r="D50" s="6">
-        <v>142396273.94999999</v>
+        <v>144861337.21000001</v>
       </c>
       <c r="E50" s="6">
-        <v>126451149.41</v>
+        <v>129070911.23999999</v>
       </c>
       <c r="F50" s="6">
-        <v>123542274.75</v>
+        <v>126557978.40000001</v>
       </c>
       <c r="G50" s="6">
         <v>212410.94</v>
       </c>
       <c r="H50" s="6">
-        <v>16077300.689999999</v>
+        <v>16113875.630000001</v>
       </c>
       <c r="I50" s="7">
-        <v>16289711.630000001</v>
+        <v>16326286.57</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2107,13 +2107,13 @@
         <v>58</v>
       </c>
       <c r="D51" s="6">
-        <v>101599866.06999999</v>
+        <v>102398045.23</v>
       </c>
       <c r="E51" s="6">
-        <v>95670025.430000007</v>
+        <v>96569244.400000006</v>
       </c>
       <c r="F51" s="6">
-        <v>95322859.430000007</v>
+        <v>95820271.790000007</v>
       </c>
       <c r="G51" s="6">
         <v>509913.92</v>
@@ -2136,22 +2136,22 @@
         <v>59</v>
       </c>
       <c r="D52" s="6">
-        <v>17323198.149999999</v>
+        <v>18227397.699999999</v>
       </c>
       <c r="E52" s="6">
-        <v>8885984.8699999992</v>
+        <v>10232562.210000001</v>
       </c>
       <c r="F52" s="6">
-        <v>8659845.6899999995</v>
+        <v>9582006.9900000002</v>
       </c>
       <c r="G52" s="6">
         <v>1021786.93</v>
       </c>
       <c r="H52" s="6">
-        <v>16542946.17</v>
+        <v>17147828.899999999</v>
       </c>
       <c r="I52" s="7">
-        <v>17564733.100000001</v>
+        <v>18169615.829999998</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2168,10 +2168,10 @@
         <v>2607453.4900000002</v>
       </c>
       <c r="E53" s="6">
-        <v>2441194.7999999998</v>
+        <v>2443354.7999999998</v>
       </c>
       <c r="F53" s="6">
-        <v>2315549</v>
+        <v>2317709</v>
       </c>
       <c r="G53" s="6">
         <v>167935.23</v>
@@ -2194,22 +2194,22 @@
         <v>61</v>
       </c>
       <c r="D54" s="6">
-        <v>7988165.04</v>
+        <v>7981855.5099999998</v>
       </c>
       <c r="E54" s="6">
-        <v>6767708.5099999998</v>
+        <v>6828648.7199999997</v>
       </c>
       <c r="F54" s="6">
-        <v>6704417.4800000004</v>
+        <v>6764666.4800000004</v>
       </c>
       <c r="G54" s="6">
         <v>8281.7999999999993</v>
       </c>
       <c r="H54" s="6">
-        <v>127844.74</v>
+        <v>127999.74</v>
       </c>
       <c r="I54" s="7">
-        <v>136126.54</v>
+        <v>136281.54</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2223,13 +2223,13 @@
         <v>62</v>
       </c>
       <c r="D55" s="6">
-        <v>3045071.74</v>
+        <v>3793405.96</v>
       </c>
       <c r="E55" s="6">
-        <v>1327899.98</v>
+        <v>1515334.62</v>
       </c>
       <c r="F55" s="6">
-        <v>1230645.52</v>
+        <v>1247967.3899999999</v>
       </c>
       <c r="G55" s="6">
         <v>17304.09</v>
@@ -2252,13 +2252,13 @@
         <v>63</v>
       </c>
       <c r="D56" s="6">
-        <v>19063893.32</v>
+        <v>20893874.93</v>
       </c>
       <c r="E56" s="6">
-        <v>11048619.630000001</v>
+        <v>12326001.869999999</v>
       </c>
       <c r="F56" s="6">
-        <v>9936965.5999999996</v>
+        <v>10759514.699999999</v>
       </c>
       <c r="G56" s="6">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>64</v>
       </c>
       <c r="D57" s="6">
-        <v>15973495.289999999</v>
+        <v>18032052.550000001</v>
       </c>
       <c r="E57" s="6">
-        <v>15666637.560000001</v>
+        <v>16079599.02</v>
       </c>
       <c r="F57" s="6">
-        <v>13604733.130000001</v>
+        <v>13620168.58</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -2414,10 +2414,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>89208.58</v>
+        <v>155231.67999999999</v>
       </c>
       <c r="I62" s="7">
-        <v>89208.58</v>
+        <v>155231.67999999999</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2431,22 +2431,22 @@
         <v>70</v>
       </c>
       <c r="D63" s="6">
-        <v>68231509.290000007</v>
+        <v>69936127.409999996</v>
       </c>
       <c r="E63" s="6">
-        <v>40554528.810000002</v>
+        <v>50268231.509999998</v>
       </c>
       <c r="F63" s="6">
-        <v>31016651.600000001</v>
+        <v>44489994.43</v>
       </c>
       <c r="G63" s="6">
-        <v>522774.46</v>
+        <v>524553.05000000005</v>
       </c>
       <c r="H63" s="6">
         <v>942023.07</v>
       </c>
       <c r="I63" s="7">
-        <v>1464797.53</v>
+        <v>1466576.12</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2460,22 +2460,22 @@
         <v>71</v>
       </c>
       <c r="D64" s="6">
-        <v>7096501565.7799997</v>
+        <v>7504254080.8900003</v>
       </c>
       <c r="E64" s="6">
-        <v>3251270790.9699998</v>
+        <v>4279401285.3400002</v>
       </c>
       <c r="F64" s="6">
-        <v>2986518612.96</v>
+        <v>3744253567.6799998</v>
       </c>
       <c r="G64" s="6">
-        <v>255021157.40000001</v>
+        <v>287531233.52999997</v>
       </c>
       <c r="H64" s="6">
-        <v>406790858.24000001</v>
+        <v>413197992.27999997</v>
       </c>
       <c r="I64" s="7">
-        <v>661812015.63999999</v>
+        <v>700729225.80999994</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>57465.29</v>
+        <v>249016.26</v>
       </c>
       <c r="I65" s="7">
-        <v>57465.29</v>
+        <v>249016.26</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2521,10 +2521,10 @@
         <v>253601.91</v>
       </c>
       <c r="E66" s="6">
-        <v>250057.48</v>
+        <v>250427.59</v>
       </c>
       <c r="F66" s="6">
-        <v>232984.69</v>
+        <v>233354.8</v>
       </c>
       <c r="G66" s="6">
         <v>68494.850000000006</v>
@@ -2547,13 +2547,13 @@
         <v>74</v>
       </c>
       <c r="D67" s="6">
-        <v>45937523.609999999</v>
+        <v>61866644.289999999</v>
       </c>
       <c r="E67" s="6">
-        <v>21778893.280000001</v>
+        <v>22109851.149999999</v>
       </c>
       <c r="F67" s="6">
-        <v>19663515.68</v>
+        <v>20858515.370000001</v>
       </c>
       <c r="G67" s="6">
         <v>0</v>
@@ -2576,22 +2576,22 @@
         <v>75</v>
       </c>
       <c r="D68" s="6">
-        <v>26233706.559999999</v>
+        <v>27225084.52</v>
       </c>
       <c r="E68" s="6">
-        <v>22204310.210000001</v>
+        <v>22657229.890000001</v>
       </c>
       <c r="F68" s="6">
-        <v>21503011.300000001</v>
+        <v>21592367.870000001</v>
       </c>
       <c r="G68" s="6">
         <v>28530.55</v>
       </c>
       <c r="H68" s="6">
-        <v>6922960.6699999999</v>
+        <v>6923391.7300000004</v>
       </c>
       <c r="I68" s="7">
-        <v>6951491.2199999997</v>
+        <v>6951922.2800000003</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2666,10 +2666,10 @@
         <v>63142211.219999999</v>
       </c>
       <c r="E71" s="6">
-        <v>53174810.909999996</v>
+        <v>53176826.32</v>
       </c>
       <c r="F71" s="6">
-        <v>53152004.670000002</v>
+        <v>53154020.079999998</v>
       </c>
       <c r="G71" s="6">
         <v>0</v>
@@ -2715,22 +2715,22 @@
         <v>80</v>
       </c>
       <c r="D73" s="6">
-        <v>11207617.67</v>
+        <v>11296547.869999999</v>
       </c>
       <c r="E73" s="6">
-        <v>2714034.91</v>
+        <v>3439041.34</v>
       </c>
       <c r="F73" s="6">
-        <v>1870532.73</v>
+        <v>2511554.62</v>
       </c>
       <c r="G73" s="6">
         <v>4586769.4800000004</v>
       </c>
       <c r="H73" s="6">
-        <v>26358666.129999999</v>
+        <v>27919467</v>
       </c>
       <c r="I73" s="7">
-        <v>30945435.609999999</v>
+        <v>32506236.48</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2744,13 +2744,13 @@
         <v>81</v>
       </c>
       <c r="D74" s="6">
-        <v>126099.31</v>
+        <v>126058</v>
       </c>
       <c r="E74" s="6">
-        <v>89168.26</v>
+        <v>90118.65</v>
       </c>
       <c r="F74" s="6">
-        <v>87697.04</v>
+        <v>88688.74</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -2773,13 +2773,13 @@
         <v>82</v>
       </c>
       <c r="D75" s="6">
-        <v>5798977120.6999998</v>
+        <v>7289086863.6400003</v>
       </c>
       <c r="E75" s="6">
-        <v>5795596998.2799997</v>
+        <v>7280614292</v>
       </c>
       <c r="F75" s="6">
-        <v>5795489514.3599997</v>
+        <v>7280506775.1300001</v>
       </c>
       <c r="G75" s="6">
         <v>57945.89</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\OneDrive\Documents\html\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DF316A-225A-47AF-83E2-928BE166FE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
+    <t>Unidade Orçamentária - Código/Nome</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Sigla</t>
   </si>
   <si>
     <t>Valor Despesa Empenhada</t>
@@ -48,232 +49,442 @@
     <t>Valor Pago RP</t>
   </si>
   <si>
-    <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>ADVOCACIA GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
-  </si>
-  <si>
-    <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
-  </si>
-  <si>
-    <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE GOVERNO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>CONTROLADORIA-GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA-GERAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
-  </si>
-  <si>
-    <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
-  </si>
-  <si>
-    <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-  </si>
-  <si>
-    <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
-  </si>
-  <si>
-    <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO JOAO PINHEIRO</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HELENA ANTIPOFF</t>
-  </si>
-  <si>
-    <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE ARTE DE OURO PRETO</t>
-  </si>
-  <si>
-    <t>FUNDACAO CLOVIS SALGADO</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
-  </si>
-  <si>
-    <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO EZEQUIEL DIAS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO ESTADUAL DE TRANSITO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE HABITACAO</t>
-  </si>
-  <si>
-    <t>FUNDO PENITENCIARIO ESTADUAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SAUDE</t>
-  </si>
-  <si>
-    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
-  </si>
-  <si>
-    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE CULTURA</t>
-  </si>
-  <si>
-    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+    <t>1071 - GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>GABINETE MILITAR</t>
+  </si>
+  <si>
+    <t>1081 - ADVOCACIA GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>1101 - OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>OGE</t>
+  </si>
+  <si>
+    <t>1191 - SECRETARIA DE ESTADO DE FAZENDA</t>
+  </si>
+  <si>
+    <t>SEF</t>
+  </si>
+  <si>
+    <t>1221 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>1231 - SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+  </si>
+  <si>
+    <t>SEAPA</t>
+  </si>
+  <si>
+    <t>1251 - POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PMMG</t>
+  </si>
+  <si>
+    <t>1261 - SECRETARIA DE ESTADO DE EDUCACAO</t>
+  </si>
+  <si>
+    <t>SEE</t>
+  </si>
+  <si>
+    <t>1271 - SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+  </si>
+  <si>
+    <t>SECULT</t>
+  </si>
+  <si>
+    <t>1301 - SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+  </si>
+  <si>
+    <t>SEINFRA</t>
+  </si>
+  <si>
+    <t>1371 - SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+  </si>
+  <si>
+    <t>SEMAD</t>
+  </si>
+  <si>
+    <t>1401 - CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>CBMMG</t>
+  </si>
+  <si>
+    <t>1451 - SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+  </si>
+  <si>
+    <t>SEJUSP</t>
+  </si>
+  <si>
+    <t>1481 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+  </si>
+  <si>
+    <t>SEDESE</t>
+  </si>
+  <si>
+    <t>1491 - SECRETARIA DE ESTADO DE GOVERNO</t>
+  </si>
+  <si>
+    <t>SEGOV</t>
+  </si>
+  <si>
+    <t>1501 - SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>SEPLAG</t>
+  </si>
+  <si>
+    <t>1511 - POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PCMG</t>
+  </si>
+  <si>
+    <t>1521 - CONTROLADORIA-GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>CGE</t>
+  </si>
+  <si>
+    <t>1541 - ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ESP MG</t>
+  </si>
+  <si>
+    <t>1631 - SECRETARIA-GERAL</t>
+  </si>
+  <si>
+    <t>SEC. GERAL</t>
+  </si>
+  <si>
+    <t>1711 - SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+  </si>
+  <si>
+    <t>SECOM</t>
+  </si>
+  <si>
+    <t>1721 - SECRETARIA DE ESTADO DA CASA CIVIL</t>
+  </si>
+  <si>
+    <t>SCC</t>
+  </si>
+  <si>
+    <t>1911 - EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+  </si>
+  <si>
+    <t>EGE - SEF</t>
+  </si>
+  <si>
+    <t>1915 - PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+  </si>
+  <si>
+    <t>PARTICIPAÇÃO EMPRESAS</t>
+  </si>
+  <si>
+    <t>1916 - GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+  </si>
+  <si>
+    <t>GDPE - SEF</t>
+  </si>
+  <si>
+    <t>1941 - EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>EGE-SEPLAG</t>
+  </si>
+  <si>
+    <t>2011 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSEMG</t>
+  </si>
+  <si>
+    <t>2041 - LOTERIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>LEMG</t>
+  </si>
+  <si>
+    <t>2061 - FUNDACAO JOAO PINHEIRO</t>
+  </si>
+  <si>
+    <t>FJP</t>
+  </si>
+  <si>
+    <t>2071 - FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAPEMIG</t>
+  </si>
+  <si>
+    <t>2091 - FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>FEAM</t>
+  </si>
+  <si>
+    <t>2101 - INSTITUTO ESTADUAL DE FLORESTAS</t>
+  </si>
+  <si>
+    <t>IEF</t>
+  </si>
+  <si>
+    <t>2121 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSM</t>
+  </si>
+  <si>
+    <t>2151 - FUNDACAO HELENA ANTIPOFF</t>
+  </si>
+  <si>
+    <t>FHA</t>
+  </si>
+  <si>
+    <t>2161 - FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+  </si>
+  <si>
+    <t>FUCAM</t>
+  </si>
+  <si>
+    <t>2171 - FUNDACAO DE ARTE DE OURO PRETO</t>
+  </si>
+  <si>
+    <t>FAOP</t>
+  </si>
+  <si>
+    <t>2181 - FUNDACAO CLOVIS SALGADO</t>
+  </si>
+  <si>
+    <t>FCS</t>
+  </si>
+  <si>
+    <t>2201 - INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IEPHA</t>
+  </si>
+  <si>
+    <t>2211 - FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+  </si>
+  <si>
+    <t>TV MINAS</t>
+  </si>
+  <si>
+    <t>2241 - INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+  </si>
+  <si>
+    <t>IGAM</t>
+  </si>
+  <si>
+    <t>2251 - JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>JUCEMG</t>
+  </si>
+  <si>
+    <t>2261 - FUNDACAO EZEQUIEL DIAS</t>
+  </si>
+  <si>
+    <t>FUNED</t>
+  </si>
+  <si>
+    <t>2271 - FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FHEMIG</t>
+  </si>
+  <si>
+    <t>2281 - FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UTRAMIG</t>
+  </si>
+  <si>
+    <t>2301 - DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>DER-MG</t>
+  </si>
+  <si>
+    <t>2311 - UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>UNIMONTES</t>
+  </si>
+  <si>
+    <t>2321 - FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>HEMOMINAS</t>
+  </si>
+  <si>
+    <t>2331 - INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPEMMG</t>
+  </si>
+  <si>
+    <t>2351 - UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UEMG</t>
+  </si>
+  <si>
+    <t>2371 - INSTITUTO MINEIRO DE AGROPECUARIA</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>2421 - INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IDENE</t>
+  </si>
+  <si>
+    <t>2431 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>AGÊNCIA RMBH</t>
+  </si>
+  <si>
+    <t>2441 - AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+  </si>
+  <si>
+    <t>ARSAE -MG</t>
+  </si>
+  <si>
+    <t>2461 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+  </si>
+  <si>
+    <t>ARMVA</t>
+  </si>
+  <si>
+    <t>2471 - AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ARTEMIG</t>
+  </si>
+  <si>
+    <t>2481 - DEPARTAMENTO ESTADUAL DE TRANSITO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>DETRAN/MG</t>
+  </si>
+  <si>
+    <t>3041 - EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMATER</t>
+  </si>
+  <si>
+    <t>3051 - EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EPAMIG</t>
+  </si>
+  <si>
+    <t>4101 - FUNDO ESTADUAL DE HABITACAO</t>
+  </si>
+  <si>
+    <t>FEH</t>
+  </si>
+  <si>
+    <t>4141 - FUNDO PENITENCIARIO ESTADUAL</t>
+  </si>
+  <si>
+    <t>FPE</t>
+  </si>
+  <si>
+    <t>4251 - FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>FEAS</t>
+  </si>
+  <si>
+    <t>4291 - FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FES</t>
+  </si>
+  <si>
+    <t>4331 - FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>FDM</t>
+  </si>
+  <si>
+    <t>4341 - FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+  </si>
+  <si>
+    <t>FHIDRO</t>
+  </si>
+  <si>
+    <t>4381 - FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FUNTRANS</t>
+  </si>
+  <si>
+    <t>4451 - FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+  </si>
+  <si>
+    <t>FEPDC</t>
+  </si>
+  <si>
+    <t>4491 - FUNDO ESTADUAL DE CULTURA</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t>4541 - FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAHMEMG</t>
+  </si>
+  <si>
+    <t>4551 - FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNAPEC</t>
+  </si>
+  <si>
+    <t>4691 - FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FESP-MG</t>
+  </si>
+  <si>
+    <t>4701 - FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FET-MG</t>
+  </si>
+  <si>
+    <t>4711 - FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FFP - MG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
@@ -387,39 +598,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -452,9 +663,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -487,6 +715,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -548,13 +793,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -563,6 +801,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -627,24 +872,44 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I76"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="119.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
     <col min="4" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="25.140625" customWidth="1"/>
@@ -652,14 +917,14 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -685,49 +950,49 @@
       <c r="A2" s="4">
         <v>2026</v>
       </c>
-      <c r="B2" s="4">
-        <v>1071</v>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="6">
-        <v>49413706.600000001</v>
+        <v>50333102.829999998</v>
       </c>
       <c r="E2" s="6">
-        <v>21270175.949999999</v>
+        <v>22039501.16</v>
       </c>
       <c r="F2" s="6">
-        <v>18854491.32</v>
+        <v>19499856.440000001</v>
       </c>
       <c r="G2" s="6">
         <v>1803218.12</v>
       </c>
       <c r="H2" s="6">
-        <v>9395969.3000000007</v>
+        <v>10471762.98</v>
       </c>
       <c r="I2" s="7">
-        <v>11199187.42</v>
+        <v>12274981.1</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2026</v>
       </c>
-      <c r="B3" s="4">
-        <v>1081</v>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6">
-        <v>484376237.14999998</v>
+        <v>513093563.66000003</v>
       </c>
       <c r="E3" s="6">
-        <v>348482474.98000002</v>
+        <v>379156790.51999998</v>
       </c>
       <c r="F3" s="6">
-        <v>331321689.98000002</v>
+        <v>361898727.75999999</v>
       </c>
       <c r="G3" s="6">
         <v>185261438.00999999</v>
@@ -743,20 +1008,20 @@
       <c r="A4" s="4">
         <v>2026</v>
       </c>
-      <c r="B4" s="4">
-        <v>1101</v>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6">
-        <v>6620623.2999999998</v>
+        <v>7960219.1200000001</v>
       </c>
       <c r="E4" s="6">
-        <v>6398017.04</v>
+        <v>7787166.8799999999</v>
       </c>
       <c r="F4" s="6">
-        <v>6350639.9699999997</v>
+        <v>7739939.8099999996</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
@@ -772,49 +1037,49 @@
       <c r="A5" s="4">
         <v>2026</v>
       </c>
-      <c r="B5" s="4">
-        <v>1191</v>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6">
-        <v>779728797.73000002</v>
+        <v>780283309.87</v>
       </c>
       <c r="E5" s="6">
-        <v>700407956.59000003</v>
+        <v>705268109.13999999</v>
       </c>
       <c r="F5" s="6">
-        <v>680939121.91999996</v>
+        <v>684402327.92999995</v>
       </c>
       <c r="G5" s="6">
         <v>7665444.21</v>
       </c>
       <c r="H5" s="6">
-        <v>49026978.5</v>
+        <v>49428303.590000004</v>
       </c>
       <c r="I5" s="7">
-        <v>56692422.710000001</v>
+        <v>57093747.799999997</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2026</v>
       </c>
-      <c r="B6" s="4">
-        <v>1221</v>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6">
-        <v>38222574.100000001</v>
+        <v>41353113.049999997</v>
       </c>
       <c r="E6" s="6">
-        <v>18955096.260000002</v>
+        <v>20770262.629999999</v>
       </c>
       <c r="F6" s="6">
-        <v>18119461.190000001</v>
+        <v>19939722.629999999</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -830,107 +1095,107 @@
       <c r="A7" s="4">
         <v>2026</v>
       </c>
-      <c r="B7" s="4">
-        <v>1231</v>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6">
-        <v>88398162.939999998</v>
+        <v>118134863.48</v>
       </c>
       <c r="E7" s="6">
-        <v>54260937.939999998</v>
+        <v>64104490.509999998</v>
       </c>
       <c r="F7" s="6">
-        <v>53778401.259999998</v>
+        <v>63623721.25</v>
       </c>
       <c r="G7" s="6">
         <v>5876518.1600000001</v>
       </c>
       <c r="H7" s="6">
-        <v>15736444.300000001</v>
+        <v>15877554.130000001</v>
       </c>
       <c r="I7" s="7">
-        <v>21612962.460000001</v>
+        <v>21754072.289999999</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
-      <c r="B8" s="4">
-        <v>1251</v>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6">
-        <v>7255764736.6499996</v>
+        <v>7256718042.5</v>
       </c>
       <c r="E8" s="6">
-        <v>7066814219.5600004</v>
+        <v>7086491883.1499996</v>
       </c>
       <c r="F8" s="6">
-        <v>7051362392.5299997</v>
+        <v>7067818065.7200003</v>
       </c>
       <c r="G8" s="6">
         <v>18529479.850000001</v>
       </c>
       <c r="H8" s="6">
-        <v>133357683.37</v>
+        <v>134066972.3</v>
       </c>
       <c r="I8" s="7">
-        <v>151887163.22</v>
+        <v>152596452.15000001</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2026</v>
       </c>
-      <c r="B9" s="4">
-        <v>1261</v>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6">
-        <v>7809715773.9200001</v>
+        <v>7817102676.5500002</v>
       </c>
       <c r="E9" s="6">
-        <v>7569386615.5799999</v>
+        <v>7577370603.1899996</v>
       </c>
       <c r="F9" s="6">
-        <v>7374931357.8199997</v>
+        <v>7381904378.8299999</v>
       </c>
       <c r="G9" s="6">
         <v>195886022.58000001</v>
       </c>
       <c r="H9" s="6">
-        <v>120082324.41</v>
+        <v>120185979.37</v>
       </c>
       <c r="I9" s="7">
-        <v>315968346.99000001</v>
+        <v>316072001.94999999</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2026</v>
       </c>
-      <c r="B10" s="4">
-        <v>1271</v>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
-        <v>35124631.18</v>
+        <v>38699570.240000002</v>
       </c>
       <c r="E10" s="6">
-        <v>24924379.52</v>
+        <v>27148738.079999998</v>
       </c>
       <c r="F10" s="6">
-        <v>23467871.5</v>
+        <v>25956490.899999999</v>
       </c>
       <c r="G10" s="6">
         <v>319615.87</v>
@@ -946,20 +1211,20 @@
       <c r="A11" s="4">
         <v>2026</v>
       </c>
-      <c r="B11" s="4">
-        <v>1301</v>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
-        <v>72870921.719999999</v>
+        <v>102453194.94</v>
       </c>
       <c r="E11" s="6">
-        <v>61210908.240000002</v>
+        <v>67172844.180000007</v>
       </c>
       <c r="F11" s="6">
-        <v>54026756.82</v>
+        <v>58228420.869999997</v>
       </c>
       <c r="G11" s="6">
         <v>15843807.77</v>
@@ -975,20 +1240,20 @@
       <c r="A12" s="4">
         <v>2026</v>
       </c>
-      <c r="B12" s="4">
-        <v>1371</v>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D12" s="6">
-        <v>90204665.670000002</v>
+        <v>90383064.430000007</v>
       </c>
       <c r="E12" s="6">
-        <v>83306543.75</v>
+        <v>83316015.329999998</v>
       </c>
       <c r="F12" s="6">
-        <v>81929617.040000007</v>
+        <v>81932938.969999999</v>
       </c>
       <c r="G12" s="6">
         <v>3823909.86</v>
@@ -1004,194 +1269,194 @@
       <c r="A13" s="4">
         <v>2026</v>
       </c>
-      <c r="B13" s="4">
-        <v>1401</v>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
-        <v>854595332.21000004</v>
+        <v>859922223.48000002</v>
       </c>
       <c r="E13" s="6">
-        <v>830243623.21000004</v>
+        <v>835678342.82000005</v>
       </c>
       <c r="F13" s="6">
-        <v>828280751.91999996</v>
+        <v>833512002.55999994</v>
       </c>
       <c r="G13" s="6">
         <v>6046803.8799999999</v>
       </c>
       <c r="H13" s="6">
-        <v>28693040.09</v>
+        <v>29213232.489999998</v>
       </c>
       <c r="I13" s="7">
-        <v>34739843.969999999</v>
+        <v>35260036.369999997</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2026</v>
       </c>
-      <c r="B14" s="4">
-        <v>1451</v>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
-        <v>1942900766.29</v>
+        <v>2078297639.8599999</v>
       </c>
       <c r="E14" s="6">
-        <v>1624409708.01</v>
+        <v>1764074108.78</v>
       </c>
       <c r="F14" s="6">
-        <v>1601455358.04</v>
+        <v>1736247897.3199999</v>
       </c>
       <c r="G14" s="6">
         <v>14409521.41</v>
       </c>
       <c r="H14" s="6">
-        <v>114681486.28</v>
+        <v>115002249.94</v>
       </c>
       <c r="I14" s="7">
-        <v>129091007.69</v>
+        <v>129411771.34999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2026</v>
       </c>
-      <c r="B15" s="4">
-        <v>1481</v>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
-        <v>48847630.140000001</v>
+        <v>54246777.049999997</v>
       </c>
       <c r="E15" s="6">
-        <v>46014739.579999998</v>
+        <v>51120182.079999998</v>
       </c>
       <c r="F15" s="6">
-        <v>45068132.219999999</v>
+        <v>49002233.009999998</v>
       </c>
       <c r="G15" s="6">
-        <v>11543150.439999999</v>
+        <v>11643019.560000001</v>
       </c>
       <c r="H15" s="6">
-        <v>11090758.09</v>
+        <v>11110952.67</v>
       </c>
       <c r="I15" s="7">
-        <v>22633908.530000001</v>
+        <v>22753972.23</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2026</v>
       </c>
-      <c r="B16" s="4">
-        <v>1491</v>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6">
-        <v>109174026.64</v>
+        <v>138417268.66999999</v>
       </c>
       <c r="E16" s="6">
-        <v>48907216.109999999</v>
+        <v>128661039.59999999</v>
       </c>
       <c r="F16" s="6">
-        <v>41063314.729999997</v>
+        <v>46001482.68</v>
       </c>
       <c r="G16" s="6">
         <v>11209003.039999999</v>
       </c>
       <c r="H16" s="6">
-        <v>4094313.55</v>
+        <v>4097302.63</v>
       </c>
       <c r="I16" s="7">
-        <v>15303316.59</v>
+        <v>15306305.67</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>2026</v>
       </c>
-      <c r="B17" s="4">
-        <v>1501</v>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6">
-        <v>312466170</v>
+        <v>327857055.98000002</v>
       </c>
       <c r="E17" s="6">
-        <v>220481346.53</v>
+        <v>239045474.21000001</v>
       </c>
       <c r="F17" s="6">
-        <v>197468873.80000001</v>
+        <v>212379476.78999999</v>
       </c>
       <c r="G17" s="6">
         <v>28757544</v>
       </c>
       <c r="H17" s="6">
-        <v>65545570.299999997</v>
+        <v>65564826.420000002</v>
       </c>
       <c r="I17" s="7">
-        <v>94303114.299999997</v>
+        <v>94322370.420000002</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2026</v>
       </c>
-      <c r="B18" s="4">
-        <v>1511</v>
+      <c r="B18" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6">
-        <v>1276615091.5599999</v>
+        <v>1348570226.99</v>
       </c>
       <c r="E18" s="6">
-        <v>1221724810.98</v>
+        <v>1293498593.9000001</v>
       </c>
       <c r="F18" s="6">
-        <v>1188726604.28</v>
+        <v>1264784716.23</v>
       </c>
       <c r="G18" s="6">
-        <v>6925334.6500000004</v>
+        <v>6933418.3700000001</v>
       </c>
       <c r="H18" s="6">
-        <v>30018112.559999999</v>
+        <v>30019348.699999999</v>
       </c>
       <c r="I18" s="7">
-        <v>36943447.210000001</v>
+        <v>36952767.07</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>2026</v>
       </c>
-      <c r="B19" s="4">
-        <v>1521</v>
+      <c r="B19" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D19" s="6">
-        <v>23669587.420000002</v>
+        <v>29046400.140000001</v>
       </c>
       <c r="E19" s="6">
-        <v>23275782.289999999</v>
+        <v>28560680.550000001</v>
       </c>
       <c r="F19" s="6">
-        <v>22766821.149999999</v>
+        <v>28516153.66</v>
       </c>
       <c r="G19" s="6">
         <v>5062</v>
@@ -1207,11 +1472,11 @@
       <c r="A20" s="4">
         <v>2026</v>
       </c>
-      <c r="B20" s="4">
-        <v>1541</v>
+      <c r="B20" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D20" s="6">
         <v>10374710.49</v>
@@ -1236,20 +1501,20 @@
       <c r="A21" s="4">
         <v>2026</v>
       </c>
-      <c r="B21" s="4">
-        <v>1631</v>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D21" s="6">
-        <v>4362530.38</v>
+        <v>5424664.3300000001</v>
       </c>
       <c r="E21" s="6">
-        <v>4158919.41</v>
+        <v>5008885.7300000004</v>
       </c>
       <c r="F21" s="6">
-        <v>4095268.67</v>
+        <v>4878402.6900000004</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
@@ -1265,49 +1530,49 @@
       <c r="A22" s="4">
         <v>2026</v>
       </c>
-      <c r="B22" s="4">
-        <v>1711</v>
+      <c r="B22" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6">
-        <v>75766363.930000007</v>
+        <v>76686953.590000004</v>
       </c>
       <c r="E22" s="6">
-        <v>21239098.52</v>
+        <v>22340816.5</v>
       </c>
       <c r="F22" s="6">
-        <v>19867834.359999999</v>
+        <v>21169850.079999998</v>
       </c>
       <c r="G22" s="6">
         <v>60000.1</v>
       </c>
       <c r="H22" s="6">
-        <v>48788270.479999997</v>
+        <v>49334843.259999998</v>
       </c>
       <c r="I22" s="7">
-        <v>48848270.579999998</v>
+        <v>49394843.359999999</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>2026</v>
       </c>
-      <c r="B23" s="4">
-        <v>1721</v>
+      <c r="B23" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D23" s="6">
-        <v>3640285.05</v>
+        <v>3966087.15</v>
       </c>
       <c r="E23" s="6">
-        <v>3386840.55</v>
+        <v>3863826.91</v>
       </c>
       <c r="F23" s="6">
-        <v>3316962.27</v>
+        <v>3793948.63</v>
       </c>
       <c r="G23" s="6">
         <v>122407.67</v>
@@ -1323,20 +1588,20 @@
       <c r="A24" s="4">
         <v>2026</v>
       </c>
-      <c r="B24" s="4">
-        <v>1911</v>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D24" s="6">
         <v>509489748.27999997</v>
       </c>
       <c r="E24" s="6">
-        <v>352867696.62</v>
+        <v>352904437.10000002</v>
       </c>
       <c r="F24" s="6">
-        <v>352863333.85000002</v>
+        <v>352900074.32999998</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -1352,20 +1617,20 @@
       <c r="A25" s="4">
         <v>2026</v>
       </c>
-      <c r="B25" s="4">
-        <v>1915</v>
+      <c r="B25" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D25" s="6">
-        <v>7173386.8099999996</v>
+        <v>12949020.939999999</v>
       </c>
       <c r="E25" s="6">
-        <v>7173386.8099999996</v>
+        <v>10390853.25</v>
       </c>
       <c r="F25" s="6">
-        <v>7172133.3600000003</v>
+        <v>10389599.800000001</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1375,11 +1640,11 @@
       <c r="A26" s="4">
         <v>2026</v>
       </c>
-      <c r="B26" s="4">
-        <v>1916</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D26" s="6">
         <v>3583402171.8200002</v>
@@ -1404,11 +1669,11 @@
       <c r="A27" s="4">
         <v>2026</v>
       </c>
-      <c r="B27" s="4">
-        <v>1941</v>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D27" s="6">
         <v>75440224.450000003</v>
@@ -1433,49 +1698,49 @@
       <c r="A28" s="4">
         <v>2026</v>
       </c>
-      <c r="B28" s="4">
-        <v>2011</v>
+      <c r="B28" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D28" s="6">
-        <v>972412166.30999994</v>
+        <v>1001553741.2</v>
       </c>
       <c r="E28" s="6">
-        <v>567305249.00999999</v>
+        <v>607244574.02999997</v>
       </c>
       <c r="F28" s="6">
-        <v>550092147.48000002</v>
+        <v>588736258.87</v>
       </c>
       <c r="G28" s="6">
-        <v>94822.57</v>
+        <v>96897.37</v>
       </c>
       <c r="H28" s="6">
-        <v>188581228.80000001</v>
+        <v>188670437.75</v>
       </c>
       <c r="I28" s="7">
-        <v>188676051.37</v>
+        <v>188767335.12</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>2026</v>
       </c>
-      <c r="B29" s="4">
-        <v>2041</v>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D29" s="6">
-        <v>1180376.47</v>
+        <v>1406717.43</v>
       </c>
       <c r="E29" s="6">
-        <v>1079231.28</v>
+        <v>1307667.6299999999</v>
       </c>
       <c r="F29" s="6">
-        <v>1052724.1000000001</v>
+        <v>1282358.1299999999</v>
       </c>
       <c r="G29" s="6">
         <v>1692.39</v>
@@ -1491,49 +1756,49 @@
       <c r="A30" s="4">
         <v>2026</v>
       </c>
-      <c r="B30" s="4">
-        <v>2061</v>
+      <c r="B30" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D30" s="6">
-        <v>24643439.030000001</v>
+        <v>29190967.77</v>
       </c>
       <c r="E30" s="6">
-        <v>22366252.5</v>
+        <v>26734603.98</v>
       </c>
       <c r="F30" s="6">
-        <v>21436015.289999999</v>
+        <v>25804146.57</v>
       </c>
       <c r="G30" s="6">
         <v>27688.16</v>
       </c>
       <c r="H30" s="6">
-        <v>1664261.76</v>
+        <v>1666488.31</v>
       </c>
       <c r="I30" s="7">
-        <v>1691949.92</v>
+        <v>1694176.47</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2026</v>
       </c>
-      <c r="B31" s="4">
-        <v>2071</v>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D31" s="6">
-        <v>244920040.12</v>
+        <v>260400573.12</v>
       </c>
       <c r="E31" s="6">
-        <v>180665502.15000001</v>
+        <v>195636352.28</v>
       </c>
       <c r="F31" s="6">
-        <v>174263893.84999999</v>
+        <v>176786888.59</v>
       </c>
       <c r="G31" s="6">
         <v>3290143.43</v>
@@ -1549,49 +1814,49 @@
       <c r="A32" s="4">
         <v>2026</v>
       </c>
-      <c r="B32" s="4">
-        <v>2091</v>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6">
-        <v>22039396.73</v>
+        <v>24194128.079999998</v>
       </c>
       <c r="E32" s="6">
-        <v>21604834.690000001</v>
+        <v>23765660.390000001</v>
       </c>
       <c r="F32" s="6">
-        <v>20882205.66</v>
+        <v>23076552.109999999</v>
       </c>
       <c r="G32" s="6">
         <v>8.36</v>
       </c>
       <c r="H32" s="6">
-        <v>1010938.21</v>
+        <v>1011787.8</v>
       </c>
       <c r="I32" s="7">
-        <v>1010946.57</v>
+        <v>1011796.16</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>2026</v>
       </c>
-      <c r="B33" s="4">
-        <v>2101</v>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6">
-        <v>72183057.489999995</v>
+        <v>90207613.730000004</v>
       </c>
       <c r="E33" s="6">
-        <v>69264378.560000002</v>
+        <v>82073368.769999996</v>
       </c>
       <c r="F33" s="6">
-        <v>65667747.060000002</v>
+        <v>78735814.680000007</v>
       </c>
       <c r="G33" s="6">
         <v>486532.65</v>
@@ -1607,78 +1872,78 @@
       <c r="A34" s="4">
         <v>2026</v>
       </c>
-      <c r="B34" s="4">
-        <v>2121</v>
+      <c r="B34" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D34" s="6">
-        <v>1134082855.6900001</v>
+        <v>1314224901.8699999</v>
       </c>
       <c r="E34" s="6">
-        <v>1111097023.6700001</v>
+        <v>1291109960</v>
       </c>
       <c r="F34" s="6">
-        <v>1095465052.74</v>
+        <v>1278570853.1400001</v>
       </c>
       <c r="G34" s="6">
         <v>19255569.109999999</v>
       </c>
       <c r="H34" s="6">
-        <v>34294835.789999999</v>
+        <v>34392390.560000002</v>
       </c>
       <c r="I34" s="7">
-        <v>53550404.899999999</v>
+        <v>53647959.670000002</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2026</v>
       </c>
-      <c r="B35" s="4">
-        <v>2151</v>
+      <c r="B35" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D35" s="6">
-        <v>24148580.109999999</v>
+        <v>26727293.120000001</v>
       </c>
       <c r="E35" s="6">
-        <v>20520349.989999998</v>
+        <v>22914417.300000001</v>
       </c>
       <c r="F35" s="6">
-        <v>20371429.27</v>
+        <v>22765496.579999998</v>
       </c>
       <c r="G35" s="6">
         <v>218.93</v>
       </c>
       <c r="H35" s="6">
-        <v>1851249.62</v>
+        <v>1853773.94</v>
       </c>
       <c r="I35" s="7">
-        <v>1851468.55</v>
+        <v>1853992.87</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>2026</v>
       </c>
-      <c r="B36" s="4">
-        <v>2161</v>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D36" s="6">
-        <v>2107358.4500000002</v>
+        <v>2379404.08</v>
       </c>
       <c r="E36" s="6">
-        <v>1951631.47</v>
+        <v>2225173.37</v>
       </c>
       <c r="F36" s="6">
-        <v>1903450.65</v>
+        <v>2177305.08</v>
       </c>
       <c r="G36" s="6">
         <v>23147.54</v>
@@ -1694,20 +1959,20 @@
       <c r="A37" s="4">
         <v>2026</v>
       </c>
-      <c r="B37" s="4">
-        <v>2171</v>
+      <c r="B37" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D37" s="6">
-        <v>1572800.04</v>
+        <v>1813281.08</v>
       </c>
       <c r="E37" s="6">
-        <v>1535622.6</v>
+        <v>1776099.64</v>
       </c>
       <c r="F37" s="6">
-        <v>1474211.29</v>
+        <v>1714688.33</v>
       </c>
       <c r="G37" s="6">
         <v>46386.19</v>
@@ -1723,20 +1988,20 @@
       <c r="A38" s="4">
         <v>2026</v>
       </c>
-      <c r="B38" s="4">
-        <v>2181</v>
+      <c r="B38" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D38" s="6">
-        <v>25938971.690000001</v>
+        <v>28243743.690000001</v>
       </c>
       <c r="E38" s="6">
-        <v>19976184.649999999</v>
+        <v>22195608.920000002</v>
       </c>
       <c r="F38" s="6">
-        <v>19434602.949999999</v>
+        <v>21680439.260000002</v>
       </c>
       <c r="G38" s="6">
         <v>866933.31</v>
@@ -1752,49 +2017,49 @@
       <c r="A39" s="4">
         <v>2026</v>
       </c>
-      <c r="B39" s="4">
-        <v>2201</v>
+      <c r="B39" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6">
-        <v>9696002.3800000008</v>
+        <v>10759581.539999999</v>
       </c>
       <c r="E39" s="6">
-        <v>6016352.6100000003</v>
+        <v>7092718.2000000002</v>
       </c>
       <c r="F39" s="6">
-        <v>5831435.1299999999</v>
+        <v>6908765.1299999999</v>
       </c>
       <c r="G39" s="6">
         <v>702452.89</v>
       </c>
       <c r="H39" s="6">
-        <v>171438.62</v>
+        <v>420931.82</v>
       </c>
       <c r="I39" s="7">
-        <v>873891.51</v>
+        <v>1123384.71</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>2026</v>
       </c>
-      <c r="B40" s="4">
-        <v>2211</v>
+      <c r="B40" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="D40" s="6">
-        <v>5847603.4199999999</v>
+        <v>6613854.96</v>
       </c>
       <c r="E40" s="6">
-        <v>5173479.3899999997</v>
+        <v>5946830.2800000003</v>
       </c>
       <c r="F40" s="6">
-        <v>4506374.37</v>
+        <v>5323848.8099999996</v>
       </c>
       <c r="G40" s="6">
         <v>32410.16</v>
@@ -1810,20 +2075,20 @@
       <c r="A41" s="4">
         <v>2026</v>
       </c>
-      <c r="B41" s="4">
-        <v>2241</v>
+      <c r="B41" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D41" s="6">
-        <v>17910910.66</v>
+        <v>20385477.039999999</v>
       </c>
       <c r="E41" s="6">
-        <v>17355249.829999998</v>
+        <v>19830311.579999998</v>
       </c>
       <c r="F41" s="6">
-        <v>15965044.85</v>
+        <v>18440106.600000001</v>
       </c>
       <c r="G41" s="6">
         <v>4364694.79</v>
@@ -1839,20 +2104,20 @@
       <c r="A42" s="4">
         <v>2026</v>
       </c>
-      <c r="B42" s="4">
-        <v>2251</v>
+      <c r="B42" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6">
-        <v>16767696.93</v>
+        <v>18576688.039999999</v>
       </c>
       <c r="E42" s="6">
-        <v>13773129.970000001</v>
+        <v>15584583.060000001</v>
       </c>
       <c r="F42" s="6">
-        <v>12749528.119999999</v>
+        <v>14586546.609999999</v>
       </c>
       <c r="G42" s="6">
         <v>1119472.81</v>
@@ -1868,78 +2133,78 @@
       <c r="A43" s="4">
         <v>2026</v>
       </c>
-      <c r="B43" s="4">
-        <v>2261</v>
+      <c r="B43" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6">
-        <v>195505342.75</v>
+        <v>207775618.49000001</v>
       </c>
       <c r="E43" s="6">
-        <v>115744174.64</v>
+        <v>124906098.41</v>
       </c>
       <c r="F43" s="6">
-        <v>99817297.409999996</v>
+        <v>115778347.31999999</v>
       </c>
       <c r="G43" s="6">
         <v>7187273.0700000003</v>
       </c>
       <c r="H43" s="6">
-        <v>132930229.86</v>
+        <v>133013791.70999999</v>
       </c>
       <c r="I43" s="7">
-        <v>140117502.93000001</v>
+        <v>140201064.78</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2026</v>
       </c>
-      <c r="B44" s="4">
-        <v>2271</v>
+      <c r="B44" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D44" s="6">
-        <v>911946197.34000003</v>
+        <v>1044335266.21</v>
       </c>
       <c r="E44" s="6">
-        <v>817705828.07000005</v>
+        <v>941728715.10000002</v>
       </c>
       <c r="F44" s="6">
-        <v>782681483.01999998</v>
+        <v>917197923.22000003</v>
       </c>
       <c r="G44" s="6">
         <v>6041131.1100000003</v>
       </c>
       <c r="H44" s="6">
-        <v>87809002.459999993</v>
+        <v>87908190.090000004</v>
       </c>
       <c r="I44" s="7">
-        <v>93850133.569999993</v>
+        <v>93949321.200000003</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>2026</v>
       </c>
-      <c r="B45" s="4">
-        <v>2281</v>
+      <c r="B45" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D45" s="6">
-        <v>2787555.49</v>
+        <v>3288395.28</v>
       </c>
       <c r="E45" s="6">
-        <v>2096145.96</v>
+        <v>2623362.2599999998</v>
       </c>
       <c r="F45" s="6">
-        <v>1947170.01</v>
+        <v>2433609.67</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>
@@ -1955,107 +2220,107 @@
       <c r="A46" s="4">
         <v>2026</v>
       </c>
-      <c r="B46" s="4">
-        <v>2301</v>
+      <c r="B46" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D46" s="6">
-        <v>763759929.73000002</v>
+        <v>793358070.67999995</v>
       </c>
       <c r="E46" s="6">
-        <v>346704213.30000001</v>
+        <v>382862605.67000002</v>
       </c>
       <c r="F46" s="6">
-        <v>310592871.91000003</v>
+        <v>356135938.11000001</v>
       </c>
       <c r="G46" s="6">
         <v>13431647.550000001</v>
       </c>
       <c r="H46" s="6">
-        <v>222450392.75999999</v>
+        <v>234921379.28</v>
       </c>
       <c r="I46" s="7">
-        <v>235882040.31</v>
+        <v>248353026.83000001</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>2026</v>
       </c>
-      <c r="B47" s="4">
-        <v>2311</v>
+      <c r="B47" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="D47" s="6">
-        <v>169052531.97999999</v>
+        <v>202572896.53999999</v>
       </c>
       <c r="E47" s="6">
-        <v>152360154.84</v>
+        <v>183993167.69</v>
       </c>
       <c r="F47" s="6">
-        <v>149048039.99000001</v>
+        <v>180646211.38999999</v>
       </c>
       <c r="G47" s="6">
         <v>130453.78</v>
       </c>
       <c r="H47" s="6">
-        <v>21168001.68</v>
+        <v>21208446.82</v>
       </c>
       <c r="I47" s="7">
-        <v>21298455.460000001</v>
+        <v>21338900.600000001</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>2026</v>
       </c>
-      <c r="B48" s="4">
-        <v>2321</v>
+      <c r="B48" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D48" s="6">
-        <v>145051647.11000001</v>
+        <v>172218517.28</v>
       </c>
       <c r="E48" s="6">
-        <v>118990162.62</v>
+        <v>136980130.88</v>
       </c>
       <c r="F48" s="6">
-        <v>112164363.84999999</v>
+        <v>128798459.62</v>
       </c>
       <c r="G48" s="6">
         <v>3348075.28</v>
       </c>
       <c r="H48" s="6">
-        <v>23369369.02</v>
+        <v>23395965.100000001</v>
       </c>
       <c r="I48" s="7">
-        <v>26717444.300000001</v>
+        <v>26744040.379999999</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>2026</v>
       </c>
-      <c r="B49" s="4">
-        <v>2331</v>
+      <c r="B49" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D49" s="6">
-        <v>13304080.380000001</v>
+        <v>14926040.699999999</v>
       </c>
       <c r="E49" s="6">
-        <v>12707145.99</v>
+        <v>14335104.300000001</v>
       </c>
       <c r="F49" s="6">
-        <v>12192877.619999999</v>
+        <v>13820458.65</v>
       </c>
       <c r="G49" s="6">
         <v>6330.51</v>
@@ -2071,49 +2336,49 @@
       <c r="A50" s="4">
         <v>2026</v>
       </c>
-      <c r="B50" s="4">
-        <v>2351</v>
+      <c r="B50" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D50" s="6">
-        <v>144861337.21000001</v>
+        <v>171632651.13</v>
       </c>
       <c r="E50" s="6">
-        <v>129070911.23999999</v>
+        <v>152988784.11000001</v>
       </c>
       <c r="F50" s="6">
-        <v>126557978.40000001</v>
+        <v>150446177.96000001</v>
       </c>
       <c r="G50" s="6">
         <v>212410.94</v>
       </c>
       <c r="H50" s="6">
-        <v>16113875.630000001</v>
+        <v>16611764.4</v>
       </c>
       <c r="I50" s="7">
-        <v>16326286.57</v>
+        <v>16824175.34</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>2026</v>
       </c>
-      <c r="B51" s="4">
-        <v>2371</v>
+      <c r="B51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D51" s="6">
-        <v>102398045.23</v>
+        <v>125954803.36</v>
       </c>
       <c r="E51" s="6">
-        <v>96569244.400000006</v>
+        <v>119863840.45</v>
       </c>
       <c r="F51" s="6">
-        <v>95820271.790000007</v>
+        <v>119115450.20999999</v>
       </c>
       <c r="G51" s="6">
         <v>509913.92</v>
@@ -2129,49 +2394,49 @@
       <c r="A52" s="4">
         <v>2026</v>
       </c>
-      <c r="B52" s="4">
-        <v>2421</v>
+      <c r="B52" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D52" s="6">
-        <v>18227397.699999999</v>
+        <v>18861236.109999999</v>
       </c>
       <c r="E52" s="6">
-        <v>10232562.210000001</v>
+        <v>11185623.48</v>
       </c>
       <c r="F52" s="6">
-        <v>9582006.9900000002</v>
+        <v>10719764.41</v>
       </c>
       <c r="G52" s="6">
         <v>1021786.93</v>
       </c>
       <c r="H52" s="6">
-        <v>17147828.899999999</v>
+        <v>17283667.5</v>
       </c>
       <c r="I52" s="7">
-        <v>18169615.829999998</v>
+        <v>18305454.43</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2026</v>
       </c>
-      <c r="B53" s="4">
-        <v>2431</v>
+      <c r="B53" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D53" s="6">
-        <v>2607453.4900000002</v>
+        <v>2948648.33</v>
       </c>
       <c r="E53" s="6">
-        <v>2443354.7999999998</v>
+        <v>2777271.64</v>
       </c>
       <c r="F53" s="6">
-        <v>2317709</v>
+        <v>2651625.84</v>
       </c>
       <c r="G53" s="6">
         <v>167935.23</v>
@@ -2187,20 +2452,20 @@
       <c r="A54" s="4">
         <v>2026</v>
       </c>
-      <c r="B54" s="4">
-        <v>2441</v>
+      <c r="B54" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D54" s="6">
-        <v>7981855.5099999998</v>
+        <v>9645729.8100000005</v>
       </c>
       <c r="E54" s="6">
-        <v>6828648.7199999997</v>
+        <v>8492523.0199999996</v>
       </c>
       <c r="F54" s="6">
-        <v>6764666.4800000004</v>
+        <v>8428771.7699999996</v>
       </c>
       <c r="G54" s="6">
         <v>8281.7999999999993</v>
@@ -2216,20 +2481,20 @@
       <c r="A55" s="4">
         <v>2026</v>
       </c>
-      <c r="B55" s="4">
-        <v>2461</v>
+      <c r="B55" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D55" s="6">
-        <v>3793405.96</v>
+        <v>3937101.41</v>
       </c>
       <c r="E55" s="6">
-        <v>1515334.62</v>
+        <v>1663227.24</v>
       </c>
       <c r="F55" s="6">
-        <v>1247967.3899999999</v>
+        <v>1395850.81</v>
       </c>
       <c r="G55" s="6">
         <v>17304.09</v>
@@ -2245,20 +2510,20 @@
       <c r="A56" s="4">
         <v>2026</v>
       </c>
-      <c r="B56" s="4">
-        <v>2471</v>
+      <c r="B56" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>63</v>
+        <v>118</v>
       </c>
       <c r="D56" s="6">
-        <v>20893874.93</v>
+        <v>21896563.969999999</v>
       </c>
       <c r="E56" s="6">
-        <v>12326001.869999999</v>
+        <v>13409038.970000001</v>
       </c>
       <c r="F56" s="6">
-        <v>10759514.699999999</v>
+        <v>12413981.08</v>
       </c>
       <c r="G56" s="6">
         <v>0</v>
@@ -2274,20 +2539,20 @@
       <c r="A57" s="4">
         <v>2026</v>
       </c>
-      <c r="B57" s="4">
-        <v>2481</v>
+      <c r="B57" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6">
-        <v>18032052.550000001</v>
+        <v>30244686.66</v>
       </c>
       <c r="E57" s="6">
-        <v>16079599.02</v>
+        <v>21873276.199999999</v>
       </c>
       <c r="F57" s="6">
-        <v>13620168.58</v>
+        <v>19413845.760000002</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -2297,11 +2562,11 @@
       <c r="A58" s="4">
         <v>2026</v>
       </c>
-      <c r="B58" s="4">
-        <v>3041</v>
+      <c r="B58" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="D58" s="6">
         <v>113201966.42</v>
@@ -2320,11 +2585,11 @@
       <c r="A59" s="4">
         <v>2026</v>
       </c>
-      <c r="B59" s="4">
-        <v>3051</v>
+      <c r="B59" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D59" s="6">
         <v>45052077.520000003</v>
@@ -2343,455 +2608,409 @@
       <c r="A60" s="4">
         <v>2026</v>
       </c>
-      <c r="B60" s="4">
-        <v>4091</v>
+      <c r="B60" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
+        <v>126</v>
+      </c>
+      <c r="D60" s="6">
+        <v>5271038.8099999996</v>
+      </c>
+      <c r="E60" s="6">
+        <v>5271038.8099999996</v>
+      </c>
+      <c r="F60" s="6">
+        <v>5271038.8099999996</v>
+      </c>
       <c r="G60" s="6">
-        <v>0</v>
+        <v>360498.89</v>
       </c>
       <c r="H60" s="6">
         <v>0</v>
       </c>
       <c r="I60" s="7">
-        <v>0</v>
+        <v>360498.89</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>2026</v>
       </c>
-      <c r="B61" s="4">
-        <v>4101</v>
+      <c r="B61" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D61" s="6">
-        <v>5206932.43</v>
+        <v>123226.75</v>
       </c>
       <c r="E61" s="6">
-        <v>5206932.43</v>
+        <v>0</v>
       </c>
       <c r="F61" s="6">
-        <v>5206932.43</v>
+        <v>0</v>
       </c>
       <c r="G61" s="6">
-        <v>360498.89</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
-        <v>0</v>
+        <v>155231.67999999999</v>
       </c>
       <c r="I61" s="7">
-        <v>360498.89</v>
+        <v>155231.67999999999</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>2026</v>
       </c>
-      <c r="B62" s="4">
-        <v>4141</v>
+      <c r="B62" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D62" s="6">
-        <v>123226.75</v>
+        <v>69949633.010000005</v>
       </c>
       <c r="E62" s="6">
-        <v>0</v>
+        <v>50340137.18</v>
       </c>
       <c r="F62" s="6">
-        <v>0</v>
+        <v>45326808.759999998</v>
       </c>
       <c r="G62" s="6">
-        <v>0</v>
+        <v>524553.05000000005</v>
       </c>
       <c r="H62" s="6">
-        <v>155231.67999999999</v>
+        <v>942023.07</v>
       </c>
       <c r="I62" s="7">
-        <v>155231.67999999999</v>
+        <v>1466576.12</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>2026</v>
       </c>
-      <c r="B63" s="4">
-        <v>4251</v>
+      <c r="B63" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D63" s="6">
-        <v>69936127.409999996</v>
+        <v>7625410696.9099998</v>
       </c>
       <c r="E63" s="6">
-        <v>50268231.509999998</v>
+        <v>4333871835.1400003</v>
       </c>
       <c r="F63" s="6">
-        <v>44489994.43</v>
+        <v>3792313228.8600001</v>
       </c>
       <c r="G63" s="6">
-        <v>524553.05000000005</v>
+        <v>314231539.63999999</v>
       </c>
       <c r="H63" s="6">
-        <v>942023.07</v>
+        <v>417443064.38</v>
       </c>
       <c r="I63" s="7">
-        <v>1466576.12</v>
+        <v>731674604.01999998</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>2026</v>
       </c>
-      <c r="B64" s="4">
-        <v>4291</v>
+      <c r="B64" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D64" s="6">
-        <v>7504254080.8900003</v>
+        <v>2643527.87</v>
       </c>
       <c r="E64" s="6">
-        <v>4279401285.3400002</v>
+        <v>0</v>
       </c>
       <c r="F64" s="6">
-        <v>3744253567.6799998</v>
+        <v>0</v>
       </c>
       <c r="G64" s="6">
-        <v>287531233.52999997</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>413197992.27999997</v>
+        <v>249016.26</v>
       </c>
       <c r="I64" s="7">
-        <v>700729225.80999994</v>
+        <v>249016.26</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>2026</v>
       </c>
-      <c r="B65" s="4">
-        <v>4331</v>
+      <c r="B65" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D65" s="6">
-        <v>2643527.87</v>
+        <v>253198.11</v>
       </c>
       <c r="E65" s="6">
-        <v>0</v>
+        <v>250023.79</v>
       </c>
       <c r="F65" s="6">
-        <v>0</v>
+        <v>233354.8</v>
       </c>
       <c r="G65" s="6">
-        <v>0</v>
+        <v>68494.850000000006</v>
       </c>
       <c r="H65" s="6">
-        <v>249016.26</v>
+        <v>284844.95</v>
       </c>
       <c r="I65" s="7">
-        <v>249016.26</v>
+        <v>353339.8</v>
       </c>
     </row>
     <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>2026</v>
       </c>
-      <c r="B66" s="4">
-        <v>4341</v>
+      <c r="B66" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="D66" s="6">
-        <v>253601.91</v>
+        <v>63825262.399999999</v>
       </c>
       <c r="E66" s="6">
-        <v>250427.59</v>
+        <v>24477904.309999999</v>
       </c>
       <c r="F66" s="6">
-        <v>233354.8</v>
+        <v>21671005.68</v>
       </c>
       <c r="G66" s="6">
-        <v>68494.850000000006</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>284844.95</v>
+        <v>17655143.399999999</v>
       </c>
       <c r="I66" s="7">
-        <v>353339.8</v>
+        <v>17655143.399999999</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>2026</v>
       </c>
-      <c r="B67" s="4">
-        <v>4381</v>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="D67" s="6">
-        <v>61866644.289999999</v>
+        <v>27225944.600000001</v>
       </c>
       <c r="E67" s="6">
-        <v>22109851.149999999</v>
+        <v>22676484.550000001</v>
       </c>
       <c r="F67" s="6">
-        <v>20858515.370000001</v>
+        <v>21895306.32</v>
       </c>
       <c r="G67" s="6">
-        <v>0</v>
+        <v>28530.55</v>
       </c>
       <c r="H67" s="6">
-        <v>17655143.399999999</v>
+        <v>6923391.7300000004</v>
       </c>
       <c r="I67" s="7">
-        <v>17655143.399999999</v>
+        <v>6951922.2800000003</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>2026</v>
       </c>
-      <c r="B68" s="4">
-        <v>4451</v>
+      <c r="B68" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D68" s="6">
-        <v>27225084.52</v>
+        <v>11214.34</v>
       </c>
       <c r="E68" s="6">
-        <v>22657229.890000001</v>
+        <v>11214.34</v>
       </c>
       <c r="F68" s="6">
-        <v>21592367.870000001</v>
+        <v>11214.34</v>
       </c>
       <c r="G68" s="6">
-        <v>28530.55</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>6923391.7300000004</v>
+        <v>134615.38</v>
       </c>
       <c r="I68" s="7">
-        <v>6951922.2800000003</v>
+        <v>134615.38</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>2026</v>
       </c>
-      <c r="B69" s="4">
-        <v>4491</v>
+      <c r="B69" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="D69" s="6">
-        <v>11214.34</v>
+        <v>238804</v>
       </c>
       <c r="E69" s="6">
-        <v>11214.34</v>
+        <v>121014.71</v>
       </c>
       <c r="F69" s="6">
-        <v>11214.34</v>
+        <v>114372.23</v>
       </c>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>134615.38</v>
+        <v>28664.16</v>
       </c>
       <c r="I69" s="7">
-        <v>134615.38</v>
+        <v>28664.16</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>2026</v>
       </c>
-      <c r="B70" s="4">
-        <v>4541</v>
+      <c r="B70" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D70" s="6">
-        <v>238804</v>
+        <v>63142211.219999999</v>
       </c>
       <c r="E70" s="6">
-        <v>121014.71</v>
+        <v>53176826.32</v>
       </c>
       <c r="F70" s="6">
-        <v>114372.23</v>
+        <v>53154020.079999998</v>
       </c>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>28664.16</v>
+        <v>486647</v>
       </c>
       <c r="I70" s="7">
-        <v>28664.16</v>
+        <v>486647</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>2026</v>
       </c>
-      <c r="B71" s="4">
-        <v>4551</v>
+      <c r="B71" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D71" s="6">
-        <v>63142211.219999999</v>
+        <v>12355199.539999999</v>
       </c>
       <c r="E71" s="6">
-        <v>53176826.32</v>
+        <v>3439041.34</v>
       </c>
       <c r="F71" s="6">
-        <v>53154020.079999998</v>
+        <v>2511554.62</v>
       </c>
       <c r="G71" s="6">
-        <v>0</v>
+        <v>4586769.4800000004</v>
       </c>
       <c r="H71" s="6">
-        <v>486647</v>
+        <v>28598578.190000001</v>
       </c>
       <c r="I71" s="7">
-        <v>486647</v>
+        <v>33185347.670000002</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>2026</v>
       </c>
-      <c r="B72" s="4">
-        <v>4601</v>
+      <c r="B72" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
+        <v>150</v>
+      </c>
+      <c r="D72" s="6">
+        <v>126208</v>
+      </c>
+      <c r="E72" s="6">
+        <v>90757.35</v>
+      </c>
+      <c r="F72" s="6">
+        <v>89327.44</v>
+      </c>
       <c r="G72" s="6">
         <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>0</v>
+        <v>1235436.6200000001</v>
       </c>
       <c r="I72" s="7">
-        <v>0</v>
+        <v>1235436.6200000001</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>2026</v>
       </c>
-      <c r="B73" s="4">
-        <v>4691</v>
+      <c r="B73" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="D73" s="6">
-        <v>11296547.869999999</v>
+        <v>7337765892.8599997</v>
       </c>
       <c r="E73" s="6">
-        <v>3439041.34</v>
+        <v>7329278321.2200003</v>
       </c>
       <c r="F73" s="6">
-        <v>2511554.62</v>
+        <v>7329170804.3500004</v>
       </c>
       <c r="G73" s="6">
-        <v>4586769.4800000004</v>
+        <v>57945.89</v>
       </c>
       <c r="H73" s="6">
-        <v>27919467</v>
+        <v>759396.57</v>
       </c>
       <c r="I73" s="7">
-        <v>32506236.48</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B74" s="4">
-        <v>4701</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="6">
-        <v>126058</v>
-      </c>
-      <c r="E74" s="6">
-        <v>90118.65</v>
-      </c>
-      <c r="F74" s="6">
-        <v>88688.74</v>
-      </c>
-      <c r="G74" s="6">
-        <v>0</v>
-      </c>
-      <c r="H74" s="6">
-        <v>1235436.6200000001</v>
-      </c>
-      <c r="I74" s="7">
-        <v>1235436.6200000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B75" s="4">
-        <v>4711</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D75" s="6">
-        <v>7289086863.6400003</v>
-      </c>
-      <c r="E75" s="6">
-        <v>7280614292</v>
-      </c>
-      <c r="F75" s="6">
-        <v>7280506775.1300001</v>
-      </c>
-      <c r="G75" s="6">
-        <v>57945.89</v>
-      </c>
-      <c r="H75" s="6">
-        <v>759396.57</v>
-      </c>
-      <c r="I75" s="7">
         <v>817342.46</v>
       </c>
     </row>
-    <row r="76" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>513653805.21</v>
+        <v>514070266.27</v>
       </c>
       <c r="F2" t="n">
-        <v>380026618.16</v>
+        <v>382058890.66</v>
       </c>
       <c r="G2" t="n">
-        <v>362677336.62</v>
+        <v>364595456.07</v>
       </c>
       <c r="H2" t="n">
         <v>185261438.01</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2948648.33</v>
+        <v>2951648.33</v>
       </c>
       <c r="F3" t="n">
-        <v>2777271.64</v>
+        <v>2794398.09</v>
       </c>
       <c r="G3" t="n">
-        <v>2651625.84</v>
+        <v>2668752.29</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -573,10 +573,10 @@
         <v>3937101.41</v>
       </c>
       <c r="F4" t="n">
-        <v>1673380.9</v>
+        <v>1683364.47</v>
       </c>
       <c r="G4" t="n">
-        <v>1535785.05</v>
+        <v>1554216.32</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9645729.810000001</v>
+        <v>9923254.4</v>
       </c>
       <c r="F5" t="n">
-        <v>8492858.42</v>
+        <v>8494608.880000001</v>
       </c>
       <c r="G5" t="n">
-        <v>8429107.17</v>
+        <v>8430857.630000001</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>127999.74</v>
+        <v>136822.38</v>
       </c>
       <c r="J5" t="n">
-        <v>136281.54</v>
+        <v>145104.18</v>
       </c>
     </row>
     <row r="6">
@@ -645,10 +645,10 @@
         <v>25504063.97</v>
       </c>
       <c r="F6" t="n">
-        <v>13409038.97</v>
+        <v>13537339.42</v>
       </c>
       <c r="G6" t="n">
-        <v>12413981.08</v>
+        <v>12532915.5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>861716990.33</v>
+        <v>862097291.8200001</v>
       </c>
       <c r="F7" t="n">
-        <v>835863693.95</v>
+        <v>836270598.9400001</v>
       </c>
       <c r="G7" t="n">
-        <v>833674242.54</v>
+        <v>833878886.58</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>29800493.71</v>
+        <v>30083148.62</v>
       </c>
       <c r="J7" t="n">
-        <v>35847297.59</v>
+        <v>36129952.5</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29046400.14</v>
+        <v>29046548.13</v>
       </c>
       <c r="F8" t="n">
-        <v>28560680.55</v>
+        <v>28659281.68</v>
       </c>
       <c r="G8" t="n">
-        <v>28518481.66</v>
+        <v>28518667.66</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>806315610.91</v>
+        <v>774324428.66</v>
       </c>
       <c r="F9" t="n">
-        <v>387219464.23</v>
+        <v>391359168.28</v>
       </c>
       <c r="G9" t="n">
-        <v>360985147.74</v>
+        <v>368046580.97</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>240931409.29</v>
+        <v>241242494.06</v>
       </c>
       <c r="J9" t="n">
-        <v>254363056.84</v>
+        <v>254674141.61</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30244686.66</v>
+        <v>30411058.3</v>
       </c>
       <c r="F10" t="n">
-        <v>21873276.2</v>
+        <v>28486969.61</v>
       </c>
       <c r="G10" t="n">
-        <v>19413845.76</v>
+        <v>19440111.49</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -855,10 +855,10 @@
         <v>75440224.45</v>
       </c>
       <c r="F12" t="n">
-        <v>74157334.28</v>
+        <v>74159478.81</v>
       </c>
       <c r="G12" t="n">
-        <v>74152468.26000001</v>
+        <v>74154612.79000001</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10403210.49</v>
+        <v>10408620.49</v>
       </c>
       <c r="F15" t="n">
-        <v>9052429.98</v>
+        <v>9071623.48</v>
       </c>
       <c r="G15" t="n">
-        <v>8829077.529999999</v>
+        <v>8855700.800000001</v>
       </c>
       <c r="H15" t="n">
         <v>211328.04</v>
@@ -987,10 +987,10 @@
         <v>238804</v>
       </c>
       <c r="F16" t="n">
-        <v>121014.71</v>
+        <v>132007.37</v>
       </c>
       <c r="G16" t="n">
-        <v>114372.23</v>
+        <v>125364.89</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1908793.03</v>
+        <v>1916818.73</v>
       </c>
       <c r="F17" t="n">
-        <v>1776269.96</v>
+        <v>1778945.66</v>
       </c>
       <c r="G17" t="n">
-        <v>1714853.84</v>
+        <v>1717401.11</v>
       </c>
       <c r="H17" t="n">
         <v>46386.19</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>260400573.12</v>
+        <v>264344947.52</v>
       </c>
       <c r="F18" t="n">
-        <v>196199531.61</v>
+        <v>201580726.02</v>
       </c>
       <c r="G18" t="n">
-        <v>176786888.59</v>
+        <v>194902692.47</v>
       </c>
       <c r="H18" t="n">
-        <v>3290143.43</v>
+        <v>3369052.62</v>
       </c>
       <c r="I18" t="n">
         <v>3171547.73</v>
       </c>
       <c r="J18" t="n">
-        <v>6461691.16</v>
+        <v>6540600.35</v>
       </c>
     </row>
     <row r="19">
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>28330604.43</v>
+        <v>29517582.69</v>
       </c>
       <c r="F19" t="n">
-        <v>22283110.45</v>
+        <v>22341650.91</v>
       </c>
       <c r="G19" t="n">
-        <v>21686256.88</v>
+        <v>21812994.44</v>
       </c>
       <c r="H19" t="n">
         <v>866933.3100000001</v>
@@ -1164,22 +1164,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>24341803.02</v>
+        <v>27876420.84</v>
       </c>
       <c r="F21" t="n">
-        <v>23769444.08</v>
+        <v>27310705.34</v>
       </c>
       <c r="G21" t="n">
-        <v>23077302.91</v>
+        <v>26575784.3</v>
       </c>
       <c r="H21" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1011787.8</v>
+        <v>1012555.92</v>
       </c>
       <c r="J21" t="n">
-        <v>1011796.16</v>
+        <v>1012564.28</v>
       </c>
     </row>
     <row r="22">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>69939930.88</v>
+        <v>70137245.29000001</v>
       </c>
       <c r="F22" t="n">
-        <v>50344034.96</v>
+        <v>50375152.06</v>
       </c>
       <c r="G22" t="n">
-        <v>45612436.07</v>
+        <v>45684675.24</v>
       </c>
       <c r="H22" t="n">
         <v>524553.05</v>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>27505944.6</v>
+        <v>27507961.25</v>
       </c>
       <c r="F25" t="n">
-        <v>22676484.55</v>
+        <v>22713027.51</v>
       </c>
       <c r="G25" t="n">
-        <v>21895306.32</v>
+        <v>21933373.28</v>
       </c>
       <c r="H25" t="n">
         <v>28530.55</v>
@@ -1344,22 +1344,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7660182298.74</v>
+        <v>7790766674.1</v>
       </c>
       <c r="F26" t="n">
-        <v>4340659895.11</v>
+        <v>4661156723.57</v>
       </c>
       <c r="G26" t="n">
-        <v>3872548047.97</v>
+        <v>4169200368.67</v>
       </c>
       <c r="H26" t="n">
-        <v>327902584.31</v>
+        <v>328021594.31</v>
       </c>
       <c r="I26" t="n">
-        <v>420400565.09</v>
+        <v>420582157</v>
       </c>
       <c r="J26" t="n">
-        <v>748303149.4</v>
+        <v>748603751.3099999</v>
       </c>
     </row>
     <row r="27">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15817655.54</v>
+        <v>15929545.64</v>
       </c>
       <c r="F27" t="n">
-        <v>3610199.52</v>
+        <v>3873125.58</v>
       </c>
       <c r="G27" t="n">
-        <v>2511554.62</v>
+        <v>2663637.63</v>
       </c>
       <c r="H27" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I27" t="n">
-        <v>28613791.41</v>
+        <v>28734440.05</v>
       </c>
       <c r="J27" t="n">
-        <v>33200560.89</v>
+        <v>33321209.53</v>
       </c>
     </row>
     <row r="28">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>126709.03</v>
+        <v>136709.03</v>
       </c>
       <c r="F28" t="n">
         <v>97422.83</v>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7337822491.04</v>
+        <v>7338117340.34</v>
       </c>
       <c r="F29" t="n">
-        <v>7329331330.66</v>
+        <v>7333990297.6</v>
       </c>
       <c r="G29" t="n">
-        <v>7329223813.79</v>
+        <v>7333882780.73</v>
       </c>
       <c r="H29" t="n">
         <v>57945.89</v>
@@ -1488,22 +1488,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>26731244.06</v>
+        <v>26757959.8</v>
       </c>
       <c r="F30" t="n">
-        <v>22942201.96</v>
+        <v>23318410.88</v>
       </c>
       <c r="G30" t="n">
-        <v>22762349.63</v>
+        <v>23135771.29</v>
       </c>
       <c r="H30" t="n">
         <v>218.93</v>
       </c>
       <c r="I30" t="n">
-        <v>1853888.34</v>
+        <v>1858404.49</v>
       </c>
       <c r="J30" t="n">
-        <v>1854107.27</v>
+        <v>1858623.42</v>
       </c>
     </row>
     <row r="31">
@@ -1524,22 +1524,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049172567.23</v>
+        <v>1062043662.4</v>
       </c>
       <c r="F31" t="n">
-        <v>943501447.13</v>
+        <v>962220701.35</v>
       </c>
       <c r="G31" t="n">
-        <v>920027689.34</v>
+        <v>923273159.1799999</v>
       </c>
       <c r="H31" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I31" t="n">
-        <v>87909504.84</v>
+        <v>88092813.40000001</v>
       </c>
       <c r="J31" t="n">
-        <v>93950635.95</v>
+        <v>94133944.51000001</v>
       </c>
     </row>
     <row r="32">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>253198.11</v>
+        <v>265198.11</v>
       </c>
       <c r="F32" t="n">
-        <v>250023.79</v>
+        <v>253902.69</v>
       </c>
       <c r="G32" t="n">
-        <v>233354.8</v>
+        <v>237233.7</v>
       </c>
       <c r="H32" t="n">
         <v>68494.85000000001</v>
@@ -1596,13 +1596,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29461641.71</v>
+        <v>29481394.65</v>
       </c>
       <c r="F33" t="n">
-        <v>26973338.85</v>
+        <v>26976729.92</v>
       </c>
       <c r="G33" t="n">
-        <v>26307066.62</v>
+        <v>26313057.93</v>
       </c>
       <c r="H33" t="n">
         <v>27688.16</v>
@@ -1671,10 +1671,10 @@
         <v>2379404.08</v>
       </c>
       <c r="F35" t="n">
-        <v>2225173.37</v>
+        <v>2225935.97</v>
       </c>
       <c r="G35" t="n">
-        <v>2177305.08</v>
+        <v>2176937.82</v>
       </c>
       <c r="H35" t="n">
         <v>23147.54</v>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63142211.22</v>
+        <v>63080228.54</v>
       </c>
       <c r="F36" t="n">
         <v>53176826.32</v>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208333430.08</v>
+        <v>215216264.13</v>
       </c>
       <c r="F37" t="n">
-        <v>125340475.4</v>
+        <v>125917514.76</v>
       </c>
       <c r="G37" t="n">
-        <v>115831958.34</v>
+        <v>117322899.76</v>
       </c>
       <c r="H37" t="n">
         <v>7187273.07</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63825262.4</v>
+        <v>64033251.48</v>
       </c>
       <c r="F38" t="n">
-        <v>24477904.31</v>
+        <v>24746538.94</v>
       </c>
       <c r="G38" t="n">
-        <v>22931026.83</v>
+        <v>23236103.01</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>50651353.34</v>
+        <v>50810309.27</v>
       </c>
       <c r="F39" t="n">
-        <v>22090605.02</v>
+        <v>22650570.02</v>
       </c>
       <c r="G39" t="n">
-        <v>19605621.96</v>
+        <v>19870797.98</v>
       </c>
       <c r="H39" t="n">
         <v>1803218.12</v>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3583402171.82</v>
+        <v>3583448472.29</v>
       </c>
       <c r="F40" t="n">
-        <v>2643451363.99</v>
+        <v>2645309163.76</v>
       </c>
       <c r="G40" t="n">
         <v>2601873354.88</v>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>172681886.42</v>
+        <v>178948555.58</v>
       </c>
       <c r="F41" t="n">
-        <v>137762356.75</v>
+        <v>142389040.73</v>
       </c>
       <c r="G41" t="n">
-        <v>128833235.74</v>
+        <v>129835404.74</v>
       </c>
       <c r="H41" t="n">
         <v>3348075.28</v>
@@ -1920,22 +1920,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>18861236.11</v>
+        <v>17399121.26</v>
       </c>
       <c r="F42" t="n">
-        <v>11303774.17</v>
+        <v>11419836.57</v>
       </c>
       <c r="G42" t="n">
-        <v>11058187.46</v>
+        <v>11161441.7</v>
       </c>
       <c r="H42" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I42" t="n">
-        <v>17827544.54</v>
+        <v>18011040.84</v>
       </c>
       <c r="J42" t="n">
-        <v>18849331.47</v>
+        <v>19032827.77</v>
       </c>
     </row>
     <row r="43">
@@ -1956,22 +1956,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>90216485.51000001</v>
+        <v>92319334.70999999</v>
       </c>
       <c r="F43" t="n">
-        <v>82264986.3</v>
+        <v>83540486.84999999</v>
       </c>
       <c r="G43" t="n">
-        <v>79165777.45</v>
+        <v>79447535.27</v>
       </c>
       <c r="H43" t="n">
         <v>486532.65</v>
       </c>
       <c r="I43" t="n">
-        <v>6666623.19</v>
+        <v>6742366.4</v>
       </c>
       <c r="J43" t="n">
-        <v>7153155.84</v>
+        <v>7228899.05</v>
       </c>
     </row>
     <row r="44">
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10769581.54</v>
+        <v>10822613.94</v>
       </c>
       <c r="F44" t="n">
-        <v>7093430.59</v>
+        <v>7482862.09</v>
       </c>
       <c r="G44" t="n">
-        <v>6909475.74</v>
+        <v>6952009.54</v>
       </c>
       <c r="H44" t="n">
         <v>702452.89</v>
@@ -2028,13 +2028,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>20386150.27</v>
+        <v>23115195.59</v>
       </c>
       <c r="F45" t="n">
-        <v>19830984.81</v>
+        <v>19850957.94</v>
       </c>
       <c r="G45" t="n">
-        <v>18440779.83</v>
+        <v>18460805.31</v>
       </c>
       <c r="H45" t="n">
         <v>4364694.79</v>
@@ -2064,22 +2064,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>126048468.14</v>
+        <v>126603509.9</v>
       </c>
       <c r="F46" t="n">
-        <v>120047640.9</v>
+        <v>120943998.16</v>
       </c>
       <c r="G46" t="n">
-        <v>119308610.75</v>
+        <v>119877895.35</v>
       </c>
       <c r="H46" t="n">
         <v>509913.92</v>
       </c>
       <c r="I46" t="n">
-        <v>4438581.36</v>
+        <v>4484845.2</v>
       </c>
       <c r="J46" t="n">
-        <v>4948495.28</v>
+        <v>4994759.12</v>
       </c>
     </row>
     <row r="47">
@@ -2100,13 +2100,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14926055.7</v>
+        <v>15099349.78</v>
       </c>
       <c r="F47" t="n">
-        <v>14335254.5</v>
+        <v>14385527.18</v>
       </c>
       <c r="G47" t="n">
-        <v>13820608.85</v>
+        <v>13846719.15</v>
       </c>
       <c r="H47" t="n">
         <v>6330.51</v>
@@ -2136,22 +2136,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1002227953.17</v>
+        <v>1010594151.8</v>
       </c>
       <c r="F48" t="n">
-        <v>608123577.3099999</v>
+        <v>621822705.8099999</v>
       </c>
       <c r="G48" t="n">
-        <v>588559607.76</v>
+        <v>603259863.13</v>
       </c>
       <c r="H48" t="n">
         <v>96897.37</v>
       </c>
       <c r="I48" t="n">
-        <v>188670437.75</v>
+        <v>188836076.17</v>
       </c>
       <c r="J48" t="n">
-        <v>188767335.12</v>
+        <v>188932973.54</v>
       </c>
     </row>
     <row r="49">
@@ -2172,22 +2172,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1319037100.57</v>
+        <v>1324804675.2</v>
       </c>
       <c r="F49" t="n">
-        <v>1295018763.41</v>
+        <v>1302079049.63</v>
       </c>
       <c r="G49" t="n">
-        <v>1279047066.49</v>
+        <v>1281515101.39</v>
       </c>
       <c r="H49" t="n">
         <v>19255569.11</v>
       </c>
       <c r="I49" t="n">
-        <v>34393761.44</v>
+        <v>34428481.86</v>
       </c>
       <c r="J49" t="n">
-        <v>53649330.55</v>
+        <v>53684050.97</v>
       </c>
     </row>
     <row r="50">
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18576688.04</v>
+        <v>18576838.04</v>
       </c>
       <c r="F50" t="n">
         <v>15585217.56</v>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1406807.69</v>
+        <v>1407629.61</v>
       </c>
       <c r="F51" t="n">
-        <v>1307757.89</v>
+        <v>1310007.83</v>
       </c>
       <c r="G51" t="n">
-        <v>1282358.13</v>
+        <v>1284163.7</v>
       </c>
       <c r="H51" t="n">
         <v>1692.39</v>
@@ -2283,10 +2283,10 @@
         <v>8400551.970000001</v>
       </c>
       <c r="F52" t="n">
-        <v>7787166.88</v>
+        <v>7801096.67</v>
       </c>
       <c r="G52" t="n">
-        <v>7739939.81</v>
+        <v>7753869.6</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1348900910.49</v>
+        <v>1350100182.24</v>
       </c>
       <c r="F54" t="n">
-        <v>1293814105.45</v>
+        <v>1294460609.67</v>
       </c>
       <c r="G54" t="n">
-        <v>1271208196.58</v>
+        <v>1271530443.54</v>
       </c>
       <c r="H54" t="n">
         <v>6933418.37</v>
       </c>
       <c r="I54" t="n">
-        <v>30091723.02</v>
+        <v>30204480.99</v>
       </c>
       <c r="J54" t="n">
-        <v>37025141.39</v>
+        <v>37137899.36</v>
       </c>
     </row>
     <row r="55">
@@ -2382,22 +2382,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7258167360.95</v>
+        <v>7262276359.39</v>
       </c>
       <c r="F55" t="n">
-        <v>7087076648.9</v>
+        <v>7089115398.38</v>
       </c>
       <c r="G55" t="n">
-        <v>7067991324.28</v>
+        <v>7069201650.27</v>
       </c>
       <c r="H55" t="n">
         <v>18529479.85</v>
       </c>
       <c r="I55" t="n">
-        <v>134077234.95</v>
+        <v>135744038.98</v>
       </c>
       <c r="J55" t="n">
-        <v>152606714.8</v>
+        <v>154273518.83</v>
       </c>
     </row>
     <row r="56">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3968782.74</v>
+        <v>4106200.56</v>
       </c>
       <c r="F56" t="n">
-        <v>3864690.1</v>
+        <v>3874327.07</v>
       </c>
       <c r="G56" t="n">
-        <v>3794811.82</v>
+        <v>3804448.79</v>
       </c>
       <c r="H56" t="n">
         <v>122407.67</v>
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>128739212.24</v>
+        <v>128918818.05</v>
       </c>
       <c r="F57" t="n">
-        <v>64623419.42</v>
+        <v>66288650.86</v>
       </c>
       <c r="G57" t="n">
-        <v>63959748.02</v>
+        <v>65585154.58</v>
       </c>
       <c r="H57" t="n">
         <v>5876518.16</v>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5425287.33</v>
+        <v>5435087.33</v>
       </c>
       <c r="F58" t="n">
-        <v>5008885.73</v>
+        <v>5226859.94</v>
       </c>
       <c r="G58" t="n">
-        <v>4878402.69</v>
+        <v>4960806.78</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>77086953.59</v>
+        <v>77127690.19</v>
       </c>
       <c r="F59" t="n">
-        <v>22483716.1</v>
+        <v>23364535.75</v>
       </c>
       <c r="G59" t="n">
-        <v>21192960.75</v>
+        <v>21473227.64</v>
       </c>
       <c r="H59" t="n">
         <v>60000.1</v>
       </c>
       <c r="I59" t="n">
-        <v>49334843.26</v>
+        <v>50018579.51</v>
       </c>
       <c r="J59" t="n">
-        <v>49394843.36</v>
+        <v>50078579.61</v>
       </c>
     </row>
     <row r="60">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>39300407.96</v>
+        <v>39862207.96</v>
       </c>
       <c r="F60" t="n">
-        <v>28099075.4</v>
+        <v>31382947.16</v>
       </c>
       <c r="G60" t="n">
-        <v>26670807.95</v>
+        <v>29605249.06</v>
       </c>
       <c r="H60" t="n">
         <v>319615.87</v>
@@ -2598,13 +2598,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>41353113.05</v>
+        <v>41404903.36</v>
       </c>
       <c r="F61" t="n">
-        <v>20770718.93</v>
+        <v>20850889.7</v>
       </c>
       <c r="G61" t="n">
-        <v>20111349.07</v>
+        <v>20159206.89</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2634,22 +2634,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>54320053.46</v>
+        <v>55976159.7</v>
       </c>
       <c r="F62" t="n">
-        <v>51487026.05</v>
+        <v>53193429.96</v>
       </c>
       <c r="G62" t="n">
-        <v>49003517.11</v>
+        <v>49104203.97</v>
       </c>
       <c r="H62" t="n">
         <v>11643019.56</v>
       </c>
       <c r="I62" t="n">
-        <v>12755310.13</v>
+        <v>12960666.33</v>
       </c>
       <c r="J62" t="n">
-        <v>24398329.69</v>
+        <v>24603685.89</v>
       </c>
     </row>
     <row r="63">
@@ -2670,22 +2670,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7902568097.09</v>
+        <v>8024335554.95</v>
       </c>
       <c r="F63" t="n">
-        <v>7623982863.99</v>
+        <v>7746936049</v>
       </c>
       <c r="G63" t="n">
-        <v>7480716506.86</v>
+        <v>7590619128.28</v>
       </c>
       <c r="H63" t="n">
         <v>195886022.58</v>
       </c>
       <c r="I63" t="n">
-        <v>120241546.82</v>
+        <v>120883076.33</v>
       </c>
       <c r="J63" t="n">
-        <v>316127569.4</v>
+        <v>316769098.91</v>
       </c>
     </row>
     <row r="64">
@@ -2706,22 +2706,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>780657922.35</v>
+        <v>781783945.47</v>
       </c>
       <c r="F64" t="n">
-        <v>707366466.8099999</v>
+        <v>707951632.4</v>
       </c>
       <c r="G64" t="n">
-        <v>684768369.58</v>
+        <v>689766450.0599999</v>
       </c>
       <c r="H64" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I64" t="n">
-        <v>49428303.59</v>
+        <v>52705172.01</v>
       </c>
       <c r="J64" t="n">
-        <v>57093747.8</v>
+        <v>60370616.22</v>
       </c>
     </row>
     <row r="65">
@@ -2742,13 +2742,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>139368230.28</v>
+        <v>158759828.15</v>
       </c>
       <c r="F65" t="n">
-        <v>128671513.6</v>
+        <v>128679147.6</v>
       </c>
       <c r="G65" t="n">
-        <v>46427120.61</v>
+        <v>46432158.61</v>
       </c>
       <c r="H65" t="n">
         <v>11209003.04</v>
@@ -2778,22 +2778,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>181412321.24</v>
+        <v>261441207.6</v>
       </c>
       <c r="F66" t="n">
-        <v>71943129.77</v>
+        <v>241617823.02</v>
       </c>
       <c r="G66" t="n">
-        <v>58232531.84</v>
+        <v>59811443.25</v>
       </c>
       <c r="H66" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I66" t="n">
-        <v>22916457.16</v>
+        <v>23223711.09</v>
       </c>
       <c r="J66" t="n">
-        <v>38760264.93</v>
+        <v>39067518.86</v>
       </c>
     </row>
     <row r="67">
@@ -2814,22 +2814,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2078223522.57</v>
+        <v>2086419052.77</v>
       </c>
       <c r="F67" t="n">
-        <v>1768444613.55</v>
+        <v>1777181085.73</v>
       </c>
       <c r="G67" t="n">
-        <v>1739162715.17</v>
+        <v>1740889581.07</v>
       </c>
       <c r="H67" t="n">
         <v>14409521.41</v>
       </c>
       <c r="I67" t="n">
-        <v>115155971.18</v>
+        <v>118156942.9</v>
       </c>
       <c r="J67" t="n">
-        <v>129565492.59</v>
+        <v>132566464.31</v>
       </c>
     </row>
     <row r="68">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>92196721.67</v>
+        <v>92383806.69</v>
       </c>
       <c r="F68" t="n">
-        <v>83359990.23999999</v>
+        <v>85378052.56</v>
       </c>
       <c r="G68" t="n">
-        <v>81943323.59</v>
+        <v>82433466.44</v>
       </c>
       <c r="H68" t="n">
         <v>3823909.86</v>
@@ -2886,22 +2886,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>329240899.8</v>
+        <v>330091502.74</v>
       </c>
       <c r="F69" t="n">
-        <v>240976267.14</v>
+        <v>245271727.12</v>
       </c>
       <c r="G69" t="n">
-        <v>212535235.52</v>
+        <v>212496050.12</v>
       </c>
       <c r="H69" t="n">
         <v>28757544</v>
       </c>
       <c r="I69" t="n">
-        <v>65564826.42</v>
+        <v>65723942.79</v>
       </c>
       <c r="J69" t="n">
-        <v>94322370.42</v>
+        <v>94481486.79000001</v>
       </c>
     </row>
     <row r="70">
@@ -2922,13 +2922,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6613854.96</v>
+        <v>6613242.68</v>
       </c>
       <c r="F70" t="n">
-        <v>5946830.28</v>
+        <v>6013476.48</v>
       </c>
       <c r="G70" t="n">
-        <v>5323848.81</v>
+        <v>5331183.62</v>
       </c>
       <c r="H70" t="n">
         <v>32410.16</v>
@@ -2958,22 +2958,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>172411987.68</v>
+        <v>175845892.82</v>
       </c>
       <c r="F71" t="n">
-        <v>153141400.02</v>
+        <v>154454255.92</v>
       </c>
       <c r="G71" t="n">
-        <v>150632001.98</v>
+        <v>151889453.26</v>
       </c>
       <c r="H71" t="n">
         <v>212410.94</v>
       </c>
       <c r="I71" t="n">
-        <v>16611764.4</v>
+        <v>16643609.16</v>
       </c>
       <c r="J71" t="n">
-        <v>16824175.34</v>
+        <v>16856020.1</v>
       </c>
     </row>
     <row r="72">
@@ -2994,22 +2994,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>202832265.24</v>
+        <v>203143430.29</v>
       </c>
       <c r="F72" t="n">
-        <v>184399390.38</v>
+        <v>185092145.77</v>
       </c>
       <c r="G72" t="n">
-        <v>181059044.35</v>
+        <v>181340299.89</v>
       </c>
       <c r="H72" t="n">
         <v>130453.78</v>
       </c>
       <c r="I72" t="n">
-        <v>21271942.04</v>
+        <v>21347975.9</v>
       </c>
       <c r="J72" t="n">
-        <v>21402395.82</v>
+        <v>21478429.68</v>
       </c>
     </row>
     <row r="73">
@@ -3030,13 +3030,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3288395.28</v>
+        <v>3344499.29</v>
       </c>
       <c r="F73" t="n">
-        <v>2623473.3</v>
+        <v>2687352</v>
       </c>
       <c r="G73" t="n">
-        <v>2433720.71</v>
+        <v>2491353.06</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>514070266.27</v>
+        <v>543936175.24</v>
       </c>
       <c r="F2" t="n">
-        <v>382058890.66</v>
+        <v>411126783.45</v>
       </c>
       <c r="G2" t="n">
-        <v>364595456.07</v>
+        <v>370000767.56</v>
       </c>
       <c r="H2" t="n">
         <v>185261438.01</v>
       </c>
       <c r="I2" t="n">
-        <v>2413043.11</v>
+        <v>2432931.84</v>
       </c>
       <c r="J2" t="n">
-        <v>187674481.12</v>
+        <v>187694369.85</v>
       </c>
     </row>
     <row r="3">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3937101.41</v>
+        <v>3941334.41</v>
       </c>
       <c r="F4" t="n">
-        <v>1683364.47</v>
+        <v>1699871.29</v>
       </c>
       <c r="G4" t="n">
-        <v>1554216.32</v>
+        <v>1570416.09</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9923254.4</v>
+        <v>9926653.26</v>
       </c>
       <c r="F5" t="n">
-        <v>8494608.880000001</v>
+        <v>8598730.630000001</v>
       </c>
       <c r="G5" t="n">
-        <v>8430857.630000001</v>
+        <v>8442900.289999999</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25504063.97</v>
+        <v>25128623.15</v>
       </c>
       <c r="F6" t="n">
-        <v>13537339.42</v>
+        <v>14468921.58</v>
       </c>
       <c r="G6" t="n">
-        <v>12532915.5</v>
+        <v>12548609.83</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>862097291.8200001</v>
+        <v>863404587.34</v>
       </c>
       <c r="F7" t="n">
-        <v>836270598.9400001</v>
+        <v>838537064.55</v>
       </c>
       <c r="G7" t="n">
-        <v>833878886.58</v>
+        <v>836394422.36</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>30083148.62</v>
+        <v>30216259.25</v>
       </c>
       <c r="J7" t="n">
-        <v>36129952.5</v>
+        <v>36263063.13</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29046548.13</v>
+        <v>29046728.49</v>
       </c>
       <c r="F8" t="n">
-        <v>28659281.68</v>
+        <v>28683938.62</v>
       </c>
       <c r="G8" t="n">
-        <v>28518667.66</v>
+        <v>28534285.87</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>774324428.66</v>
+        <v>850318343.86</v>
       </c>
       <c r="F9" t="n">
-        <v>391359168.28</v>
+        <v>414085822.26</v>
       </c>
       <c r="G9" t="n">
-        <v>368046580.97</v>
+        <v>377691597.11</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>241242494.06</v>
+        <v>242701527.09</v>
       </c>
       <c r="J9" t="n">
-        <v>254674141.61</v>
+        <v>256133174.64</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30411058.3</v>
+        <v>35614805.9</v>
       </c>
       <c r="F10" t="n">
-        <v>28486969.61</v>
+        <v>29713848.51</v>
       </c>
       <c r="G10" t="n">
-        <v>19440111.49</v>
+        <v>19442488.55</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>509489748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>356769713.06</v>
+        <v>361457254.74</v>
       </c>
       <c r="G11" t="n">
-        <v>356765350.29</v>
+        <v>361452891.97</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -855,10 +855,10 @@
         <v>75440224.45</v>
       </c>
       <c r="F12" t="n">
-        <v>74159478.81</v>
+        <v>74314095.13</v>
       </c>
       <c r="G12" t="n">
-        <v>74154612.79000001</v>
+        <v>74300547.36</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>113201966.42</v>
+        <v>145843538.13</v>
       </c>
       <c r="F13" t="n">
-        <v>113201966.42</v>
+        <v>145843538.13</v>
       </c>
       <c r="G13" t="n">
-        <v>113201966.42</v>
+        <v>145843538.13</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -906,25 +906,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3051</v>
+        <v>3151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>45052077.52</v>
+        <v>12769086.04</v>
       </c>
       <c r="F14" t="n">
-        <v>45052077.52</v>
+        <v>12769086.04</v>
       </c>
       <c r="G14" t="n">
-        <v>45052077.52</v>
+        <v>12769086.04</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -936,35 +936,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10408620.49</v>
+        <v>57931533.11</v>
       </c>
       <c r="F15" t="n">
-        <v>9071623.48</v>
+        <v>57931533.11</v>
       </c>
       <c r="G15" t="n">
-        <v>8855700.800000001</v>
-      </c>
-      <c r="H15" t="n">
-        <v>211328.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>959977.4300000001</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1171305.47</v>
-      </c>
+        <v>57931533.11</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,34 +966,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>238804</v>
+        <v>11192884.41</v>
       </c>
       <c r="F16" t="n">
-        <v>132007.37</v>
+        <v>9139544.08</v>
       </c>
       <c r="G16" t="n">
-        <v>125364.89</v>
+        <v>8883564.42</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>211328.04</v>
       </c>
       <c r="I16" t="n">
-        <v>28664.16</v>
+        <v>959977.4300000001</v>
       </c>
       <c r="J16" t="n">
-        <v>28664.16</v>
+        <v>1171305.47</v>
       </c>
     </row>
     <row r="17">
@@ -1008,34 +1002,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1916818.73</v>
+        <v>238804</v>
       </c>
       <c r="F17" t="n">
-        <v>1778945.66</v>
+        <v>151205.25</v>
       </c>
       <c r="G17" t="n">
-        <v>1717401.11</v>
+        <v>142902.15</v>
       </c>
       <c r="H17" t="n">
-        <v>46386.19</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>65411.04</v>
+        <v>28664.16</v>
       </c>
       <c r="J17" t="n">
-        <v>111797.23</v>
+        <v>28664.16</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +1038,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>264344947.52</v>
+        <v>1984640.82</v>
       </c>
       <c r="F18" t="n">
-        <v>201580726.02</v>
+        <v>1916307.54</v>
       </c>
       <c r="G18" t="n">
-        <v>194902692.47</v>
+        <v>1832242.43</v>
       </c>
       <c r="H18" t="n">
-        <v>3369052.62</v>
+        <v>46386.19</v>
       </c>
       <c r="I18" t="n">
-        <v>3171547.73</v>
+        <v>65411.04</v>
       </c>
       <c r="J18" t="n">
-        <v>6540600.35</v>
+        <v>111797.23</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1074,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>29517582.69</v>
+        <v>264680925.16</v>
       </c>
       <c r="F19" t="n">
-        <v>22341650.91</v>
+        <v>203456363.57</v>
       </c>
       <c r="G19" t="n">
-        <v>21812994.44</v>
+        <v>196822499.94</v>
       </c>
       <c r="H19" t="n">
-        <v>866933.3100000001</v>
+        <v>3369052.62</v>
       </c>
       <c r="I19" t="n">
-        <v>1596469.6</v>
+        <v>3173797.73</v>
       </c>
       <c r="J19" t="n">
-        <v>2463402.91</v>
+        <v>6542850.35</v>
       </c>
     </row>
     <row r="20">
@@ -1116,34 +1110,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2643527.87</v>
+        <v>30762420.5</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>22347482.8</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>21822313.67</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>866933.3100000001</v>
       </c>
       <c r="I20" t="n">
-        <v>249016.26</v>
+        <v>1596469.6</v>
       </c>
       <c r="J20" t="n">
-        <v>249016.26</v>
+        <v>2463402.91</v>
       </c>
     </row>
     <row r="21">
@@ -1152,34 +1146,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>27876420.84</v>
+        <v>2643527.87</v>
       </c>
       <c r="F21" t="n">
-        <v>27310705.34</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>26575784.3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8.359999999999999</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1012555.92</v>
+        <v>249016.26</v>
       </c>
       <c r="J21" t="n">
-        <v>1012564.28</v>
+        <v>249016.26</v>
       </c>
     </row>
     <row r="22">
@@ -1188,35 +1182,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAGE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4251</v>
+        <v>4751</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDO ESPECIAL DA ADVOCACIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>70137245.29000001</v>
+        <v>5135321.57</v>
       </c>
       <c r="F22" t="n">
-        <v>50375152.06</v>
+        <v>2088569.45</v>
       </c>
       <c r="G22" t="n">
-        <v>45684675.24</v>
-      </c>
-      <c r="H22" t="n">
-        <v>524553.05</v>
-      </c>
-      <c r="I22" t="n">
-        <v>942023.0699999999</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1466576.12</v>
-      </c>
+        <v>875597.37</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1224,34 +1212,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4491</v>
+        <v>2091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11214.34</v>
+        <v>31688798.89</v>
       </c>
       <c r="F23" t="n">
-        <v>11214.34</v>
+        <v>30834010.05</v>
       </c>
       <c r="G23" t="n">
-        <v>11214.34</v>
+        <v>29721690.65</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>134615.38</v>
+        <v>1012611.59</v>
       </c>
       <c r="J23" t="n">
-        <v>134615.38</v>
+        <v>1012619.95</v>
       </c>
     </row>
     <row r="24">
@@ -1260,34 +1248,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4101</v>
+        <v>4251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5271038.81</v>
+        <v>71175843.08</v>
       </c>
       <c r="F24" t="n">
-        <v>5271038.81</v>
+        <v>56557268.83</v>
       </c>
       <c r="G24" t="n">
-        <v>5271038.81</v>
+        <v>45815973.5</v>
       </c>
       <c r="H24" t="n">
-        <v>360498.89</v>
+        <v>594553.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>942023.0699999999</v>
       </c>
       <c r="J24" t="n">
-        <v>360498.89</v>
+        <v>1536576.12</v>
       </c>
     </row>
     <row r="25">
@@ -1296,34 +1284,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4451</v>
+        <v>4491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>27507961.25</v>
+        <v>11214.34</v>
       </c>
       <c r="F25" t="n">
-        <v>22713027.51</v>
+        <v>11214.34</v>
       </c>
       <c r="G25" t="n">
-        <v>21933373.28</v>
+        <v>11214.34</v>
       </c>
       <c r="H25" t="n">
-        <v>28530.55</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>6923391.73</v>
+        <v>134615.38</v>
       </c>
       <c r="J25" t="n">
-        <v>6951922.28</v>
+        <v>134615.38</v>
       </c>
     </row>
     <row r="26">
@@ -1332,34 +1320,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4291</v>
+        <v>4101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7790766674.1</v>
+        <v>5271038.81</v>
       </c>
       <c r="F26" t="n">
-        <v>4661156723.57</v>
+        <v>5271038.81</v>
       </c>
       <c r="G26" t="n">
-        <v>4169200368.67</v>
+        <v>5271038.81</v>
       </c>
       <c r="H26" t="n">
-        <v>328021594.31</v>
+        <v>360498.89</v>
       </c>
       <c r="I26" t="n">
-        <v>420582157</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>748603751.3099999</v>
+        <v>360498.89</v>
       </c>
     </row>
     <row r="27">
@@ -1368,34 +1356,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4691</v>
+        <v>4291</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15929545.64</v>
+        <v>7943663927.91</v>
       </c>
       <c r="F27" t="n">
-        <v>3873125.58</v>
+        <v>5336308950.18</v>
       </c>
       <c r="G27" t="n">
-        <v>2663637.63</v>
+        <v>4390220616.73</v>
       </c>
       <c r="H27" t="n">
-        <v>4586769.48</v>
+        <v>328021594.31</v>
       </c>
       <c r="I27" t="n">
-        <v>28734440.05</v>
+        <v>422422570.55</v>
       </c>
       <c r="J27" t="n">
-        <v>33321209.53</v>
+        <v>750444164.86</v>
       </c>
     </row>
     <row r="28">
@@ -1404,34 +1392,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4701</v>
+        <v>4691</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>136709.03</v>
+        <v>17448191.64</v>
       </c>
       <c r="F28" t="n">
-        <v>97422.83</v>
+        <v>4456867.6</v>
       </c>
       <c r="G28" t="n">
-        <v>95697.03</v>
+        <v>2822568.13</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>1235436.62</v>
+        <v>28765446.66</v>
       </c>
       <c r="J28" t="n">
-        <v>1235436.62</v>
+        <v>33352216.14</v>
       </c>
     </row>
     <row r="29">
@@ -1440,34 +1428,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4711</v>
+        <v>4701</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7338117340.34</v>
+        <v>357313.03</v>
       </c>
       <c r="F29" t="n">
-        <v>7333990297.6</v>
+        <v>105364.73</v>
       </c>
       <c r="G29" t="n">
-        <v>7333882780.73</v>
+        <v>103638.93</v>
       </c>
       <c r="H29" t="n">
-        <v>57945.89</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>759396.5699999999</v>
+        <v>1235436.62</v>
       </c>
       <c r="J29" t="n">
-        <v>817342.46</v>
+        <v>1235436.62</v>
       </c>
     </row>
     <row r="30">
@@ -1476,34 +1464,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2151</v>
+        <v>4711</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>26757959.8</v>
+        <v>7340427651.1</v>
       </c>
       <c r="F30" t="n">
-        <v>23318410.88</v>
+        <v>7336306353.96</v>
       </c>
       <c r="G30" t="n">
-        <v>23135771.29</v>
+        <v>7336197060.8</v>
       </c>
       <c r="H30" t="n">
-        <v>218.93</v>
+        <v>57945.89</v>
       </c>
       <c r="I30" t="n">
-        <v>1858404.49</v>
+        <v>759396.5699999999</v>
       </c>
       <c r="J30" t="n">
-        <v>1858623.42</v>
+        <v>817342.46</v>
       </c>
     </row>
     <row r="31">
@@ -1512,34 +1500,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2271</v>
+        <v>2151</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1062043662.4</v>
+        <v>26689236.44</v>
       </c>
       <c r="F31" t="n">
-        <v>962220701.35</v>
+        <v>23463054.54</v>
       </c>
       <c r="G31" t="n">
-        <v>923273159.1799999</v>
+        <v>23274240.8</v>
       </c>
       <c r="H31" t="n">
-        <v>6041131.11</v>
+        <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>88092813.40000001</v>
+        <v>1864236.06</v>
       </c>
       <c r="J31" t="n">
-        <v>94133944.51000001</v>
+        <v>1864454.99</v>
       </c>
     </row>
     <row r="32">
@@ -1548,34 +1536,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4341</v>
+        <v>2271</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>265198.11</v>
+        <v>1094377468.03</v>
       </c>
       <c r="F32" t="n">
-        <v>253902.69</v>
+        <v>979618444.21</v>
       </c>
       <c r="G32" t="n">
-        <v>237233.7</v>
+        <v>941582245.51</v>
       </c>
       <c r="H32" t="n">
-        <v>68494.85000000001</v>
+        <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>284844.95</v>
+        <v>88230551.12</v>
       </c>
       <c r="J32" t="n">
-        <v>353339.8</v>
+        <v>94271682.23</v>
       </c>
     </row>
     <row r="33">
@@ -1584,34 +1572,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2061</v>
+        <v>4341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29481394.65</v>
+        <v>301848.61</v>
       </c>
       <c r="F33" t="n">
-        <v>26976729.92</v>
+        <v>290553.19</v>
       </c>
       <c r="G33" t="n">
-        <v>26313057.93</v>
+        <v>267566.06</v>
       </c>
       <c r="H33" t="n">
-        <v>27688.16</v>
+        <v>68494.85000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>1666488.31</v>
+        <v>284844.95</v>
       </c>
       <c r="J33" t="n">
-        <v>1694176.47</v>
+        <v>353339.8</v>
       </c>
     </row>
     <row r="34">
@@ -1620,34 +1608,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4141</v>
+        <v>2061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>123226.75</v>
+        <v>29482961.15</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>27017981.78</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>26345951.35</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>27688.16</v>
       </c>
       <c r="I34" t="n">
-        <v>155231.68</v>
+        <v>1666488.31</v>
       </c>
       <c r="J34" t="n">
-        <v>155231.68</v>
+        <v>1694176.47</v>
       </c>
     </row>
     <row r="35">
@@ -1656,34 +1644,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2161</v>
+        <v>4141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2379404.08</v>
+        <v>123226.75</v>
       </c>
       <c r="F35" t="n">
-        <v>2225935.97</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>2176937.82</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>23147.54</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>154559.3</v>
+        <v>155231.68</v>
       </c>
       <c r="J35" t="n">
-        <v>177706.84</v>
+        <v>155231.68</v>
       </c>
     </row>
     <row r="36">
@@ -1692,34 +1680,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4551</v>
+        <v>4631</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>63080228.54</v>
+        <v>432646942.18</v>
       </c>
       <c r="F36" t="n">
-        <v>53176826.32</v>
+        <v>133548550.97</v>
       </c>
       <c r="G36" t="n">
-        <v>53154020.08</v>
+        <v>123177705.83</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>53631506.45</v>
       </c>
       <c r="I36" t="n">
-        <v>486647</v>
+        <v>35431658.61</v>
       </c>
       <c r="J36" t="n">
-        <v>486647</v>
+        <v>89063165.06</v>
       </c>
     </row>
     <row r="37">
@@ -1728,34 +1716,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2261</v>
+        <v>2161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>215216264.13</v>
+        <v>2379404.08</v>
       </c>
       <c r="F37" t="n">
-        <v>125917514.76</v>
+        <v>2244486.72</v>
       </c>
       <c r="G37" t="n">
-        <v>117322899.76</v>
+        <v>2196094.87</v>
       </c>
       <c r="H37" t="n">
-        <v>7187273.07</v>
+        <v>23147.54</v>
       </c>
       <c r="I37" t="n">
-        <v>133013791.71</v>
+        <v>154559.3</v>
       </c>
       <c r="J37" t="n">
-        <v>140201064.78</v>
+        <v>177706.84</v>
       </c>
     </row>
     <row r="38">
@@ -1764,34 +1752,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4381</v>
+        <v>4551</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>64033251.48</v>
+        <v>63097212.7</v>
       </c>
       <c r="F38" t="n">
-        <v>24746538.94</v>
+        <v>59701195.81</v>
       </c>
       <c r="G38" t="n">
-        <v>23236103.01</v>
+        <v>59652829.72</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>17655143.4</v>
+        <v>486647</v>
       </c>
       <c r="J38" t="n">
-        <v>17655143.4</v>
+        <v>486647</v>
       </c>
     </row>
     <row r="39">
@@ -1800,34 +1788,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1071</v>
+        <v>2261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>50810309.27</v>
+        <v>218080512.28</v>
       </c>
       <c r="F39" t="n">
-        <v>22650570.02</v>
+        <v>142772683.83</v>
       </c>
       <c r="G39" t="n">
-        <v>19870797.98</v>
+        <v>120245718.71</v>
       </c>
       <c r="H39" t="n">
-        <v>1803218.12</v>
+        <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>10471762.98</v>
+        <v>133179787.1</v>
       </c>
       <c r="J39" t="n">
-        <v>12274981.1</v>
+        <v>140367060.17</v>
       </c>
     </row>
     <row r="40">
@@ -1836,34 +1824,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1916</v>
+        <v>4381</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3583448472.29</v>
+        <v>64034288.66</v>
       </c>
       <c r="F40" t="n">
-        <v>2645309163.76</v>
+        <v>25839182.66</v>
       </c>
       <c r="G40" t="n">
-        <v>2601873354.88</v>
+        <v>24115766.59</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>17655143.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>17655143.4</v>
       </c>
     </row>
     <row r="41">
@@ -1872,34 +1860,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2321</v>
+        <v>1071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>178948555.58</v>
+        <v>51388425.52</v>
       </c>
       <c r="F41" t="n">
-        <v>142389040.73</v>
+        <v>22952678.41</v>
       </c>
       <c r="G41" t="n">
-        <v>129835404.74</v>
+        <v>20511954.49</v>
       </c>
       <c r="H41" t="n">
-        <v>3348075.28</v>
+        <v>1803218.12</v>
       </c>
       <c r="I41" t="n">
-        <v>23395965.1</v>
+        <v>11190518.07</v>
       </c>
       <c r="J41" t="n">
-        <v>26744040.38</v>
+        <v>12993736.19</v>
       </c>
     </row>
     <row r="42">
@@ -1908,34 +1896,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2421</v>
+        <v>1916</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17399121.26</v>
+        <v>3586260740.28</v>
       </c>
       <c r="F42" t="n">
-        <v>11419836.57</v>
+        <v>2762004780.42</v>
       </c>
       <c r="G42" t="n">
-        <v>11161441.7</v>
+        <v>2603731154.65</v>
       </c>
       <c r="H42" t="n">
-        <v>1021786.93</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>18011040.84</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>19032827.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1944,34 +1932,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2101</v>
+        <v>2321</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>92319334.70999999</v>
+        <v>183608642.4</v>
       </c>
       <c r="F43" t="n">
-        <v>83540486.84999999</v>
+        <v>146133759.01</v>
       </c>
       <c r="G43" t="n">
-        <v>79447535.27</v>
+        <v>138341327.2</v>
       </c>
       <c r="H43" t="n">
-        <v>486532.65</v>
+        <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>6742366.4</v>
+        <v>23401545.3</v>
       </c>
       <c r="J43" t="n">
-        <v>7228899.05</v>
+        <v>26749620.58</v>
       </c>
     </row>
     <row r="44">
@@ -1980,34 +1968,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2201</v>
+        <v>2421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10822613.94</v>
+        <v>23910729.4</v>
       </c>
       <c r="F44" t="n">
-        <v>7482862.09</v>
+        <v>12515389.94</v>
       </c>
       <c r="G44" t="n">
-        <v>6952009.54</v>
+        <v>11681905.38</v>
       </c>
       <c r="H44" t="n">
-        <v>702452.89</v>
+        <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>420931.82</v>
+        <v>18182757.84</v>
       </c>
       <c r="J44" t="n">
-        <v>1123384.71</v>
+        <v>19204544.77</v>
       </c>
     </row>
     <row r="45">
@@ -2016,34 +2004,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>23115195.59</v>
+        <v>96163980.14</v>
       </c>
       <c r="F45" t="n">
-        <v>19850957.94</v>
+        <v>86925532.31</v>
       </c>
       <c r="G45" t="n">
-        <v>18460805.31</v>
+        <v>80603237.66</v>
       </c>
       <c r="H45" t="n">
-        <v>4364694.79</v>
+        <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>10971227.93</v>
+        <v>6742366.4</v>
       </c>
       <c r="J45" t="n">
-        <v>15335922.72</v>
+        <v>7228899.05</v>
       </c>
     </row>
     <row r="46">
@@ -2052,34 +2040,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2371</v>
+        <v>2201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>126603509.9</v>
+        <v>10906815.13</v>
       </c>
       <c r="F46" t="n">
-        <v>120943998.16</v>
+        <v>7549395.24</v>
       </c>
       <c r="G46" t="n">
-        <v>119877895.35</v>
+        <v>6987704.34</v>
       </c>
       <c r="H46" t="n">
-        <v>509913.92</v>
+        <v>702452.89</v>
       </c>
       <c r="I46" t="n">
-        <v>4484845.2</v>
+        <v>420931.82</v>
       </c>
       <c r="J46" t="n">
-        <v>4994759.12</v>
+        <v>1123384.71</v>
       </c>
     </row>
     <row r="47">
@@ -2088,34 +2076,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2331</v>
+        <v>2241</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15099349.78</v>
+        <v>23673396.74</v>
       </c>
       <c r="F47" t="n">
-        <v>14385527.18</v>
+        <v>20054387.49</v>
       </c>
       <c r="G47" t="n">
-        <v>13846719.15</v>
+        <v>18504394.55</v>
       </c>
       <c r="H47" t="n">
-        <v>6330.51</v>
+        <v>4364694.79</v>
       </c>
       <c r="I47" t="n">
-        <v>1187624.4</v>
+        <v>10971227.93</v>
       </c>
       <c r="J47" t="n">
-        <v>1193954.91</v>
+        <v>15335922.72</v>
       </c>
     </row>
     <row r="48">
@@ -2124,34 +2112,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2011</v>
+        <v>2371</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1010594151.8</v>
+        <v>127225754.01</v>
       </c>
       <c r="F48" t="n">
-        <v>621822705.8099999</v>
+        <v>122392980.5</v>
       </c>
       <c r="G48" t="n">
-        <v>603259863.13</v>
+        <v>120497686.09</v>
       </c>
       <c r="H48" t="n">
-        <v>96897.37</v>
+        <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>188836076.17</v>
+        <v>4663494.02</v>
       </c>
       <c r="J48" t="n">
-        <v>188932973.54</v>
+        <v>5173407.94</v>
       </c>
     </row>
     <row r="49">
@@ -2160,34 +2148,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2121</v>
+        <v>2331</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1324804675.2</v>
+        <v>15096393.38</v>
       </c>
       <c r="F49" t="n">
-        <v>1302079049.63</v>
+        <v>14417784.78</v>
       </c>
       <c r="G49" t="n">
-        <v>1281515101.39</v>
+        <v>13890498.88</v>
       </c>
       <c r="H49" t="n">
-        <v>19255569.11</v>
+        <v>6330.51</v>
       </c>
       <c r="I49" t="n">
-        <v>34428481.86</v>
+        <v>1187624.4</v>
       </c>
       <c r="J49" t="n">
-        <v>53684050.97</v>
+        <v>1193954.91</v>
       </c>
     </row>
     <row r="50">
@@ -2196,34 +2184,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2251</v>
+        <v>2011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>18576838.04</v>
+        <v>1024157150.07</v>
       </c>
       <c r="F50" t="n">
-        <v>15585217.56</v>
+        <v>641243856.11</v>
       </c>
       <c r="G50" t="n">
-        <v>14587181.11</v>
+        <v>626162267.08</v>
       </c>
       <c r="H50" t="n">
-        <v>1119472.81</v>
+        <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>1859710.27</v>
+        <v>191802246.14</v>
       </c>
       <c r="J50" t="n">
-        <v>2979183.08</v>
+        <v>191899143.51</v>
       </c>
     </row>
     <row r="51">
@@ -2232,34 +2220,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2041</v>
+        <v>2121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1407629.61</v>
+        <v>1328550473.85</v>
       </c>
       <c r="F51" t="n">
-        <v>1310007.83</v>
+        <v>1308477295.61</v>
       </c>
       <c r="G51" t="n">
-        <v>1284163.7</v>
+        <v>1292874353.4</v>
       </c>
       <c r="H51" t="n">
-        <v>1692.39</v>
+        <v>19255569.11</v>
       </c>
       <c r="I51" t="n">
-        <v>32310.94</v>
+        <v>34442130.88</v>
       </c>
       <c r="J51" t="n">
-        <v>34003.33</v>
+        <v>53697699.99</v>
       </c>
     </row>
     <row r="52">
@@ -2268,34 +2256,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1101</v>
+        <v>2251</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8400551.970000001</v>
+        <v>18226032.52</v>
       </c>
       <c r="F52" t="n">
-        <v>7801096.67</v>
+        <v>15623696.23</v>
       </c>
       <c r="G52" t="n">
-        <v>7753869.6</v>
+        <v>15079559.95</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1119472.81</v>
       </c>
       <c r="I52" t="n">
-        <v>93457.72</v>
+        <v>1859710.27</v>
       </c>
       <c r="J52" t="n">
-        <v>93457.72</v>
+        <v>2979183.08</v>
       </c>
     </row>
     <row r="53">
@@ -2304,29 +2292,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1915</v>
+        <v>2041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>12949020.94</v>
+        <v>1421219.12</v>
       </c>
       <c r="F53" t="n">
-        <v>10390853.25</v>
+        <v>1314597.34</v>
       </c>
       <c r="G53" t="n">
-        <v>10390853.25</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+        <v>1289253.21</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1692.39</v>
+      </c>
+      <c r="I53" t="n">
+        <v>32310.94</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34003.33</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2334,34 +2328,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1511</v>
+        <v>1101</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1350100182.24</v>
+        <v>8419594.25</v>
       </c>
       <c r="F54" t="n">
-        <v>1294460609.67</v>
+        <v>7812145.67</v>
       </c>
       <c r="G54" t="n">
-        <v>1271530443.54</v>
+        <v>7764918.6</v>
       </c>
       <c r="H54" t="n">
-        <v>6933418.37</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>30204480.99</v>
+        <v>93457.72</v>
       </c>
       <c r="J54" t="n">
-        <v>37137899.36</v>
+        <v>93457.72</v>
       </c>
     </row>
     <row r="55">
@@ -2370,35 +2364,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1251</v>
+        <v>1915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>7262276359.39</v>
+        <v>12949020.94</v>
       </c>
       <c r="F55" t="n">
-        <v>7089115398.38</v>
+        <v>10390853.25</v>
       </c>
       <c r="G55" t="n">
-        <v>7069201650.27</v>
-      </c>
-      <c r="H55" t="n">
-        <v>18529479.85</v>
-      </c>
-      <c r="I55" t="n">
-        <v>135744038.98</v>
-      </c>
-      <c r="J55" t="n">
-        <v>154273518.83</v>
-      </c>
+        <v>10390853.25</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2406,34 +2394,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1721</v>
+        <v>1511</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4106200.56</v>
+        <v>1376034808.3</v>
       </c>
       <c r="F56" t="n">
-        <v>3874327.07</v>
+        <v>1307116183.63</v>
       </c>
       <c r="G56" t="n">
-        <v>3804448.79</v>
+        <v>1272102113.72</v>
       </c>
       <c r="H56" t="n">
-        <v>122407.67</v>
+        <v>6938153.34</v>
       </c>
       <c r="I56" t="n">
-        <v>214364.3</v>
+        <v>30206880.91</v>
       </c>
       <c r="J56" t="n">
-        <v>336771.97</v>
+        <v>37145034.25</v>
       </c>
     </row>
     <row r="57">
@@ -2442,34 +2430,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1231</v>
+        <v>1251</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>128918818.05</v>
+        <v>7278349249.64</v>
       </c>
       <c r="F57" t="n">
-        <v>66288650.86</v>
+        <v>7094610899.95</v>
       </c>
       <c r="G57" t="n">
-        <v>65585154.58</v>
+        <v>7071966281.12</v>
       </c>
       <c r="H57" t="n">
-        <v>5876518.16</v>
+        <v>18529479.85</v>
       </c>
       <c r="I57" t="n">
-        <v>15877554.13</v>
+        <v>136157945.57</v>
       </c>
       <c r="J57" t="n">
-        <v>21754072.29</v>
+        <v>154687425.42</v>
       </c>
     </row>
     <row r="58">
@@ -2478,34 +2466,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1631</v>
+        <v>1721</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5435087.33</v>
+        <v>4112200.56</v>
       </c>
       <c r="F58" t="n">
-        <v>5226859.94</v>
+        <v>4054091.4</v>
       </c>
       <c r="G58" t="n">
-        <v>4960806.78</v>
+        <v>3961398.24</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>122407.67</v>
       </c>
       <c r="I58" t="n">
-        <v>34378.25</v>
+        <v>214364.3</v>
       </c>
       <c r="J58" t="n">
-        <v>34378.25</v>
+        <v>336771.97</v>
       </c>
     </row>
     <row r="59">
@@ -2514,34 +2502,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1711</v>
+        <v>1231</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>77127690.19</v>
+        <v>162142608.03</v>
       </c>
       <c r="F59" t="n">
-        <v>23364535.75</v>
+        <v>66781023.87</v>
       </c>
       <c r="G59" t="n">
-        <v>21473227.64</v>
+        <v>66068652.88</v>
       </c>
       <c r="H59" t="n">
-        <v>60000.1</v>
+        <v>5876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>50018579.51</v>
+        <v>16274575.81</v>
       </c>
       <c r="J59" t="n">
-        <v>50078579.61</v>
+        <v>22151093.97</v>
       </c>
     </row>
     <row r="60">
@@ -2550,34 +2538,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1271</v>
+        <v>1631</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>39862207.96</v>
+        <v>5442922.91</v>
       </c>
       <c r="F60" t="n">
-        <v>31382947.16</v>
+        <v>5245799.41</v>
       </c>
       <c r="G60" t="n">
-        <v>29605249.06</v>
+        <v>5151032.13</v>
       </c>
       <c r="H60" t="n">
-        <v>319615.87</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>620274.23</v>
+        <v>34378.25</v>
       </c>
       <c r="J60" t="n">
-        <v>939890.1</v>
+        <v>34378.25</v>
       </c>
     </row>
     <row r="61">
@@ -2586,34 +2574,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1221</v>
+        <v>1711</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>41404903.36</v>
+        <v>84134445.2</v>
       </c>
       <c r="F61" t="n">
-        <v>20850889.7</v>
+        <v>23960016.35</v>
       </c>
       <c r="G61" t="n">
-        <v>20159206.89</v>
+        <v>21921141.96</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>22666016.68</v>
+        <v>50018579.51</v>
       </c>
       <c r="J61" t="n">
-        <v>22666016.68</v>
+        <v>50078579.61</v>
       </c>
     </row>
     <row r="62">
@@ -2622,34 +2610,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1481</v>
+        <v>1271</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>55976159.7</v>
+        <v>40879742.58</v>
       </c>
       <c r="F62" t="n">
-        <v>53193429.96</v>
+        <v>32863264.55</v>
       </c>
       <c r="G62" t="n">
-        <v>49104203.97</v>
+        <v>30934152.7</v>
       </c>
       <c r="H62" t="n">
-        <v>11643019.56</v>
+        <v>319615.87</v>
       </c>
       <c r="I62" t="n">
-        <v>12960666.33</v>
+        <v>620274.23</v>
       </c>
       <c r="J62" t="n">
-        <v>24603685.89</v>
+        <v>939890.1</v>
       </c>
     </row>
     <row r="63">
@@ -2658,34 +2646,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8024335554.95</v>
+        <v>41573098.03</v>
       </c>
       <c r="F63" t="n">
-        <v>7746936049</v>
+        <v>20952374.13</v>
       </c>
       <c r="G63" t="n">
-        <v>7590619128.28</v>
+        <v>20286751.54</v>
       </c>
       <c r="H63" t="n">
-        <v>195886022.58</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>120883076.33</v>
+        <v>23205532.54</v>
       </c>
       <c r="J63" t="n">
-        <v>316769098.91</v>
+        <v>23205532.54</v>
       </c>
     </row>
     <row r="64">
@@ -2694,34 +2682,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1191</v>
+        <v>1481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>781783945.47</v>
+        <v>58207777.37</v>
       </c>
       <c r="F64" t="n">
-        <v>707951632.4</v>
+        <v>55027346.75</v>
       </c>
       <c r="G64" t="n">
-        <v>689766450.0599999</v>
+        <v>49824816.44</v>
       </c>
       <c r="H64" t="n">
-        <v>7665444.21</v>
+        <v>11841578.76</v>
       </c>
       <c r="I64" t="n">
-        <v>52705172.01</v>
+        <v>13121241.52</v>
       </c>
       <c r="J64" t="n">
-        <v>60370616.22</v>
+        <v>24962820.28</v>
       </c>
     </row>
     <row r="65">
@@ -2730,34 +2718,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1491</v>
+        <v>1261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>158759828.15</v>
+        <v>8199882136.34</v>
       </c>
       <c r="F65" t="n">
-        <v>128679147.6</v>
+        <v>7895284034.95</v>
       </c>
       <c r="G65" t="n">
-        <v>46432158.61</v>
+        <v>7740330207.98</v>
       </c>
       <c r="H65" t="n">
-        <v>11209003.04</v>
+        <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>4291386.34</v>
+        <v>121971369.87</v>
       </c>
       <c r="J65" t="n">
-        <v>15500389.38</v>
+        <v>317878796.34</v>
       </c>
     </row>
     <row r="66">
@@ -2766,34 +2754,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>261441207.6</v>
+        <v>796391273.97</v>
       </c>
       <c r="F66" t="n">
-        <v>241617823.02</v>
+        <v>710965649.33</v>
       </c>
       <c r="G66" t="n">
-        <v>59811443.25</v>
+        <v>694211517.77</v>
       </c>
       <c r="H66" t="n">
-        <v>15843807.77</v>
+        <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>23223711.09</v>
+        <v>53658725.35</v>
       </c>
       <c r="J66" t="n">
-        <v>39067518.86</v>
+        <v>61324169.56</v>
       </c>
     </row>
     <row r="67">
@@ -2802,34 +2790,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1451</v>
+        <v>1491</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2086419052.77</v>
+        <v>182792954.67</v>
       </c>
       <c r="F67" t="n">
-        <v>1777181085.73</v>
+        <v>171096164.8</v>
       </c>
       <c r="G67" t="n">
-        <v>1740889581.07</v>
+        <v>100017172.01</v>
       </c>
       <c r="H67" t="n">
-        <v>14409521.41</v>
+        <v>11209003.04</v>
       </c>
       <c r="I67" t="n">
-        <v>118156942.9</v>
+        <v>4958053</v>
       </c>
       <c r="J67" t="n">
-        <v>132566464.31</v>
+        <v>16167056.04</v>
       </c>
     </row>
     <row r="68">
@@ -2838,34 +2826,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1371</v>
+        <v>1301</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>92383806.69</v>
+        <v>432925915.27</v>
       </c>
       <c r="F68" t="n">
-        <v>85378052.56</v>
+        <v>416316423.01</v>
       </c>
       <c r="G68" t="n">
-        <v>82433466.44</v>
+        <v>264256708.79</v>
       </c>
       <c r="H68" t="n">
-        <v>3823909.86</v>
+        <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>4333968.61</v>
+        <v>23609683.4</v>
       </c>
       <c r="J68" t="n">
-        <v>8157878.47</v>
+        <v>39453491.17</v>
       </c>
     </row>
     <row r="69">
@@ -2874,34 +2862,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1501</v>
+        <v>1451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>330091502.74</v>
+        <v>2177937757.47</v>
       </c>
       <c r="F69" t="n">
-        <v>245271727.12</v>
+        <v>1874929269.64</v>
       </c>
       <c r="G69" t="n">
-        <v>212496050.12</v>
+        <v>1833320035.09</v>
       </c>
       <c r="H69" t="n">
-        <v>28757544</v>
+        <v>14512845.39</v>
       </c>
       <c r="I69" t="n">
-        <v>65723942.79</v>
+        <v>119269170.01</v>
       </c>
       <c r="J69" t="n">
-        <v>94481486.79000001</v>
+        <v>133782015.4</v>
       </c>
     </row>
     <row r="70">
@@ -2910,34 +2898,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2211</v>
+        <v>1371</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6613242.68</v>
+        <v>95159911.92</v>
       </c>
       <c r="F70" t="n">
-        <v>6013476.48</v>
+        <v>87193925.27</v>
       </c>
       <c r="G70" t="n">
-        <v>5331183.62</v>
+        <v>85444488.81</v>
       </c>
       <c r="H70" t="n">
-        <v>32410.16</v>
+        <v>3823909.86</v>
       </c>
       <c r="I70" t="n">
-        <v>528322.15</v>
+        <v>4333968.61</v>
       </c>
       <c r="J70" t="n">
-        <v>560732.3100000001</v>
+        <v>8157878.47</v>
       </c>
     </row>
     <row r="71">
@@ -2946,34 +2934,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2351</v>
+        <v>1501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>175845892.82</v>
+        <v>342003098.39</v>
       </c>
       <c r="F71" t="n">
-        <v>154454255.92</v>
+        <v>257663321.15</v>
       </c>
       <c r="G71" t="n">
-        <v>151889453.26</v>
+        <v>217209608.59</v>
       </c>
       <c r="H71" t="n">
-        <v>212410.94</v>
+        <v>28757544</v>
       </c>
       <c r="I71" t="n">
-        <v>16643609.16</v>
+        <v>65743924.29</v>
       </c>
       <c r="J71" t="n">
-        <v>16856020.1</v>
+        <v>94501468.29000001</v>
       </c>
     </row>
     <row r="72">
@@ -2982,34 +2970,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2311</v>
+        <v>2211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>203143430.29</v>
+        <v>7173612.89</v>
       </c>
       <c r="F72" t="n">
-        <v>185092145.77</v>
+        <v>6260918.39</v>
       </c>
       <c r="G72" t="n">
-        <v>181340299.89</v>
+        <v>5803286.04</v>
       </c>
       <c r="H72" t="n">
-        <v>130453.78</v>
+        <v>32410.16</v>
       </c>
       <c r="I72" t="n">
-        <v>21347975.9</v>
+        <v>528322.15</v>
       </c>
       <c r="J72" t="n">
-        <v>21478429.68</v>
+        <v>560732.3100000001</v>
       </c>
     </row>
     <row r="73">
@@ -3018,33 +3006,105 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>176999709.79</v>
+      </c>
+      <c r="F73" t="n">
+        <v>157889787.31</v>
+      </c>
+      <c r="G73" t="n">
+        <v>154831837.43</v>
+      </c>
+      <c r="H73" t="n">
+        <v>212410.94</v>
+      </c>
+      <c r="I73" t="n">
+        <v>16669029.31</v>
+      </c>
+      <c r="J73" t="n">
+        <v>16881440.25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>206939945.62</v>
+      </c>
+      <c r="F74" t="n">
+        <v>186951138.81</v>
+      </c>
+      <c r="G74" t="n">
+        <v>183532314.13</v>
+      </c>
+      <c r="H74" t="n">
+        <v>130453.78</v>
+      </c>
+      <c r="I74" t="n">
+        <v>21425330.3</v>
+      </c>
+      <c r="J74" t="n">
+        <v>21555784.08</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C75" t="n">
         <v>2281</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E73" t="n">
-        <v>3344499.29</v>
-      </c>
-      <c r="F73" t="n">
-        <v>2687352</v>
-      </c>
-      <c r="G73" t="n">
-        <v>2491353.06</v>
-      </c>
-      <c r="H73" t="n">
+      <c r="E75" t="n">
+        <v>3803197.08</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2756915.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2557434.76</v>
+      </c>
+      <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I75" t="n">
         <v>263905.44</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J75" t="n">
         <v>263905.44</v>
       </c>
     </row>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>543936175.24</v>
+        <v>546138672.5</v>
       </c>
       <c r="F2" t="n">
-        <v>411126783.45</v>
+        <v>456308702.99</v>
       </c>
       <c r="G2" t="n">
-        <v>370000767.56</v>
+        <v>394707422.07</v>
       </c>
       <c r="H2" t="n">
-        <v>185261438.01</v>
+        <v>214279372.77</v>
       </c>
       <c r="I2" t="n">
         <v>2432931.84</v>
       </c>
       <c r="J2" t="n">
-        <v>187694369.85</v>
+        <v>216712304.61</v>
       </c>
     </row>
     <row r="3">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2951648.33</v>
+        <v>3200427.23</v>
       </c>
       <c r="F3" t="n">
-        <v>2794398.09</v>
+        <v>3053000.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2668752.29</v>
+        <v>2829391.05</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3941334.41</v>
+        <v>3924226.74</v>
       </c>
       <c r="F4" t="n">
-        <v>1699871.29</v>
+        <v>1717945.15</v>
       </c>
       <c r="G4" t="n">
-        <v>1570416.09</v>
+        <v>1588301.39</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9926653.26</v>
+        <v>9984237.949999999</v>
       </c>
       <c r="F5" t="n">
-        <v>8598730.630000001</v>
+        <v>8694331.949999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8442900.289999999</v>
+        <v>8538576.73</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>136822.38</v>
+        <v>138222.38</v>
       </c>
       <c r="J5" t="n">
-        <v>145104.18</v>
+        <v>146504.18</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25128623.15</v>
+        <v>19853468.47</v>
       </c>
       <c r="F6" t="n">
-        <v>14468921.58</v>
+        <v>14510995.56</v>
       </c>
       <c r="G6" t="n">
-        <v>12548609.83</v>
+        <v>13083081.27</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>863404587.34</v>
+        <v>864580454.79</v>
       </c>
       <c r="F7" t="n">
-        <v>838537064.55</v>
+        <v>840080192.84</v>
       </c>
       <c r="G7" t="n">
-        <v>836394422.36</v>
+        <v>837761172.45</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>30216259.25</v>
+        <v>32148306.23</v>
       </c>
       <c r="J7" t="n">
-        <v>36263063.13</v>
+        <v>38195110.11</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29046728.49</v>
+        <v>29047163.41</v>
       </c>
       <c r="F8" t="n">
-        <v>28683938.62</v>
+        <v>28937853.69</v>
       </c>
       <c r="G8" t="n">
-        <v>28534285.87</v>
+        <v>28634203.1</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>850318343.86</v>
+        <v>916463080.77</v>
       </c>
       <c r="F9" t="n">
-        <v>414085822.26</v>
+        <v>447411719.14</v>
       </c>
       <c r="G9" t="n">
-        <v>377691597.11</v>
+        <v>383047722.4</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>242701527.09</v>
+        <v>248924289.71</v>
       </c>
       <c r="J9" t="n">
-        <v>256133174.64</v>
+        <v>262355937.26</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>35614805.9</v>
+        <v>38592034.27</v>
       </c>
       <c r="F10" t="n">
-        <v>29713848.51</v>
+        <v>33094015.24</v>
       </c>
       <c r="G10" t="n">
-        <v>19442488.55</v>
+        <v>19453414.91</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -816,13 +816,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>509489748.28</v>
+        <v>509509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>361457254.74</v>
+        <v>361922980.24</v>
       </c>
       <c r="G11" t="n">
-        <v>361452891.97</v>
+        <v>361918617.47</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -858,16 +858,16 @@
         <v>74314095.13</v>
       </c>
       <c r="G12" t="n">
-        <v>74300547.36</v>
+        <v>74303745.93000001</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>886712.42</v>
+        <v>893022.58</v>
       </c>
       <c r="J12" t="n">
-        <v>886712.42</v>
+        <v>893022.58</v>
       </c>
     </row>
     <row r="13">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11192884.41</v>
+        <v>11257892.63</v>
       </c>
       <c r="F16" t="n">
-        <v>9139544.08</v>
+        <v>9428172.470000001</v>
       </c>
       <c r="G16" t="n">
-        <v>8883564.42</v>
+        <v>9165928.07</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1984640.82</v>
+        <v>1985195.17</v>
       </c>
       <c r="F18" t="n">
-        <v>1916307.54</v>
+        <v>1919444.74</v>
       </c>
       <c r="G18" t="n">
-        <v>1832242.43</v>
+        <v>1835286.91</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
       </c>
       <c r="I18" t="n">
-        <v>65411.04</v>
+        <v>67312.25999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>111797.23</v>
+        <v>113698.45</v>
       </c>
     </row>
     <row r="19">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>264680925.16</v>
+        <v>267600908.85</v>
       </c>
       <c r="F19" t="n">
-        <v>203456363.57</v>
+        <v>207842846.5</v>
       </c>
       <c r="G19" t="n">
-        <v>196822499.94</v>
+        <v>201257759.21</v>
       </c>
       <c r="H19" t="n">
         <v>3369052.62</v>
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30762420.5</v>
+        <v>30797003.7</v>
       </c>
       <c r="F20" t="n">
-        <v>22347482.8</v>
+        <v>22366933.64</v>
       </c>
       <c r="G20" t="n">
-        <v>21822313.67</v>
+        <v>21843861.73</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1596469.6</v>
+        <v>1598585.9</v>
       </c>
       <c r="J20" t="n">
-        <v>2463402.91</v>
+        <v>2465519.21</v>
       </c>
     </row>
     <row r="21">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5135321.57</v>
+        <v>5173831.57</v>
       </c>
       <c r="F22" t="n">
-        <v>2088569.45</v>
+        <v>2092581.35</v>
       </c>
       <c r="G22" t="n">
-        <v>875597.37</v>
+        <v>2080797.85</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31688798.89</v>
+        <v>32291159.69</v>
       </c>
       <c r="F23" t="n">
-        <v>30834010.05</v>
+        <v>31634416.1</v>
       </c>
       <c r="G23" t="n">
-        <v>29721690.65</v>
+        <v>30128701.61</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>71175843.08</v>
+        <v>72424271.42</v>
       </c>
       <c r="F24" t="n">
-        <v>56557268.83</v>
+        <v>57538853.85</v>
       </c>
       <c r="G24" t="n">
-        <v>45815973.5</v>
+        <v>56806406.37</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5271038.81</v>
+        <v>6496388.19</v>
       </c>
       <c r="F26" t="n">
-        <v>5271038.81</v>
+        <v>6496388.19</v>
       </c>
       <c r="G26" t="n">
-        <v>5271038.81</v>
+        <v>6496388.19</v>
       </c>
       <c r="H26" t="n">
         <v>360498.89</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7943663927.91</v>
+        <v>8267954316.3</v>
       </c>
       <c r="F27" t="n">
-        <v>5336308950.18</v>
+        <v>5968518675.77</v>
       </c>
       <c r="G27" t="n">
-        <v>4390220616.73</v>
+        <v>5682782918.46</v>
       </c>
       <c r="H27" t="n">
         <v>328021594.31</v>
       </c>
       <c r="I27" t="n">
-        <v>422422570.55</v>
+        <v>425822333.34</v>
       </c>
       <c r="J27" t="n">
-        <v>750444164.86</v>
+        <v>753843927.65</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>17448191.64</v>
+        <v>18422304.66</v>
       </c>
       <c r="F28" t="n">
-        <v>4456867.6</v>
+        <v>4478309.34</v>
       </c>
       <c r="G28" t="n">
-        <v>2822568.13</v>
+        <v>3351991.9</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>28765446.66</v>
+        <v>29870819.08</v>
       </c>
       <c r="J28" t="n">
-        <v>33352216.14</v>
+        <v>34457588.56</v>
       </c>
     </row>
     <row r="29">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>357313.03</v>
+        <v>377313.03</v>
       </c>
       <c r="F29" t="n">
-        <v>105364.73</v>
+        <v>108091.8</v>
       </c>
       <c r="G29" t="n">
-        <v>103638.93</v>
+        <v>106344.36</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7340427651.1</v>
+        <v>7341602168.67</v>
       </c>
       <c r="F30" t="n">
-        <v>7336306353.96</v>
+        <v>7337489874.58</v>
       </c>
       <c r="G30" t="n">
-        <v>7336197060.8</v>
+        <v>7337371244.56</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>26689236.44</v>
+        <v>26689241.97</v>
       </c>
       <c r="F31" t="n">
-        <v>23463054.54</v>
+        <v>23943741.12</v>
       </c>
       <c r="G31" t="n">
-        <v>23274240.8</v>
+        <v>23729778.35</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>1864236.06</v>
+        <v>1890806.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1864454.99</v>
+        <v>1891025.63</v>
       </c>
     </row>
     <row r="32">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1094377468.03</v>
+        <v>1124454027.11</v>
       </c>
       <c r="F32" t="n">
-        <v>979618444.21</v>
+        <v>992345991.76</v>
       </c>
       <c r="G32" t="n">
-        <v>941582245.51</v>
+        <v>957147629.27</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>88230551.12</v>
+        <v>91179119.90000001</v>
       </c>
       <c r="J32" t="n">
-        <v>94271682.23</v>
+        <v>97220251.01000001</v>
       </c>
     </row>
     <row r="33">
@@ -1587,10 +1587,10 @@
         <v>301848.61</v>
       </c>
       <c r="F33" t="n">
-        <v>290553.19</v>
+        <v>291131.29</v>
       </c>
       <c r="G33" t="n">
-        <v>267566.06</v>
+        <v>268167.76</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>29482961.15</v>
+        <v>29539266.42</v>
       </c>
       <c r="F34" t="n">
-        <v>27017981.78</v>
+        <v>27983182.41</v>
       </c>
       <c r="G34" t="n">
-        <v>26345951.35</v>
+        <v>26373887.96</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
       </c>
       <c r="I34" t="n">
-        <v>1666488.31</v>
+        <v>1674828.31</v>
       </c>
       <c r="J34" t="n">
-        <v>1694176.47</v>
+        <v>1702516.47</v>
       </c>
     </row>
     <row r="35">
@@ -1695,10 +1695,10 @@
         <v>432646942.18</v>
       </c>
       <c r="F36" t="n">
-        <v>133548550.97</v>
+        <v>145955807.46</v>
       </c>
       <c r="G36" t="n">
-        <v>123177705.83</v>
+        <v>135055006.14</v>
       </c>
       <c r="H36" t="n">
         <v>53631506.45</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2379404.08</v>
+        <v>2379612.34</v>
       </c>
       <c r="F37" t="n">
-        <v>2244486.72</v>
+        <v>2244694.98</v>
       </c>
       <c r="G37" t="n">
-        <v>2196094.87</v>
+        <v>2196303.13</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1770,7 +1770,7 @@
         <v>59701195.81</v>
       </c>
       <c r="G38" t="n">
-        <v>59652829.72</v>
+        <v>59678389.57</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>218080512.28</v>
+        <v>218111470.56</v>
       </c>
       <c r="F39" t="n">
-        <v>142772683.83</v>
+        <v>144002575.84</v>
       </c>
       <c r="G39" t="n">
-        <v>120245718.71</v>
+        <v>123146390.5</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>133179787.1</v>
+        <v>133310361.18</v>
       </c>
       <c r="J39" t="n">
-        <v>140367060.17</v>
+        <v>140497634.25</v>
       </c>
     </row>
     <row r="40">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>64034288.66</v>
+        <v>64042195.83</v>
       </c>
       <c r="F40" t="n">
-        <v>25839182.66</v>
+        <v>28996537.12</v>
       </c>
       <c r="G40" t="n">
-        <v>24115766.59</v>
+        <v>26481184.88</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,22 +1872,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>51388425.52</v>
+        <v>53382913.65</v>
       </c>
       <c r="F41" t="n">
-        <v>22952678.41</v>
+        <v>23456615.76</v>
       </c>
       <c r="G41" t="n">
-        <v>20511954.49</v>
+        <v>21697815.01</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
       </c>
       <c r="I41" t="n">
-        <v>11190518.07</v>
+        <v>11291437.22</v>
       </c>
       <c r="J41" t="n">
-        <v>12993736.19</v>
+        <v>13094655.34</v>
       </c>
     </row>
     <row r="42">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3586260740.28</v>
+        <v>3587463350.96</v>
       </c>
       <c r="F42" t="n">
-        <v>2762004780.42</v>
+        <v>2788947268.49</v>
       </c>
       <c r="G42" t="n">
-        <v>2603731154.65</v>
+        <v>2634805575.37</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>183608642.4</v>
+        <v>184244061.28</v>
       </c>
       <c r="F43" t="n">
-        <v>146133759.01</v>
+        <v>149592723.08</v>
       </c>
       <c r="G43" t="n">
-        <v>138341327.2</v>
+        <v>142132644.66</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>23401545.3</v>
+        <v>23413795.3</v>
       </c>
       <c r="J43" t="n">
-        <v>26749620.58</v>
+        <v>26761870.58</v>
       </c>
     </row>
     <row r="44">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>23910729.4</v>
+        <v>25081009.4</v>
       </c>
       <c r="F44" t="n">
-        <v>12515389.94</v>
+        <v>13054615.56</v>
       </c>
       <c r="G44" t="n">
-        <v>11681905.38</v>
+        <v>12727213.1</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>96163980.14</v>
+        <v>96821326.23999999</v>
       </c>
       <c r="F45" t="n">
-        <v>86925532.31</v>
+        <v>88071432.44</v>
       </c>
       <c r="G45" t="n">
-        <v>80603237.66</v>
+        <v>81908172.42</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>6742366.4</v>
+        <v>7106445.14</v>
       </c>
       <c r="J45" t="n">
-        <v>7228899.05</v>
+        <v>7592977.79</v>
       </c>
     </row>
     <row r="46">
@@ -2052,22 +2052,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>10906815.13</v>
+        <v>11112659.41</v>
       </c>
       <c r="F46" t="n">
-        <v>7549395.24</v>
+        <v>7773616.89</v>
       </c>
       <c r="G46" t="n">
-        <v>6987704.34</v>
+        <v>7131111.02</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
       </c>
       <c r="I46" t="n">
-        <v>420931.82</v>
+        <v>447256.9</v>
       </c>
       <c r="J46" t="n">
-        <v>1123384.71</v>
+        <v>1149709.79</v>
       </c>
     </row>
     <row r="47">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23673396.74</v>
+        <v>23873955.56</v>
       </c>
       <c r="F47" t="n">
-        <v>20054387.49</v>
+        <v>21536503.41</v>
       </c>
       <c r="G47" t="n">
-        <v>18504394.55</v>
+        <v>20098348.01</v>
       </c>
       <c r="H47" t="n">
-        <v>4364694.79</v>
+        <v>5234428.46</v>
       </c>
       <c r="I47" t="n">
         <v>10971227.93</v>
       </c>
       <c r="J47" t="n">
-        <v>15335922.72</v>
+        <v>16205656.39</v>
       </c>
     </row>
     <row r="48">
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>127225754.01</v>
+        <v>127435637.12</v>
       </c>
       <c r="F48" t="n">
-        <v>122392980.5</v>
+        <v>122862735.49</v>
       </c>
       <c r="G48" t="n">
-        <v>120497686.09</v>
+        <v>122210963.18</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4663494.02</v>
+        <v>4668361.04</v>
       </c>
       <c r="J48" t="n">
-        <v>5173407.94</v>
+        <v>5178274.96</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15096393.38</v>
+        <v>15184514.47</v>
       </c>
       <c r="F49" t="n">
-        <v>14417784.78</v>
+        <v>14585569.05</v>
       </c>
       <c r="G49" t="n">
-        <v>13890498.88</v>
+        <v>13962804.12</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1024157150.07</v>
+        <v>1029524757.75</v>
       </c>
       <c r="F50" t="n">
-        <v>641243856.11</v>
+        <v>670460371.92</v>
       </c>
       <c r="G50" t="n">
-        <v>626162267.08</v>
+        <v>651484826.34</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>191802246.14</v>
+        <v>192003440.36</v>
       </c>
       <c r="J50" t="n">
-        <v>191899143.51</v>
+        <v>192100337.73</v>
       </c>
     </row>
     <row r="51">
@@ -2232,13 +2232,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1328550473.85</v>
+        <v>1342560808.36</v>
       </c>
       <c r="F51" t="n">
-        <v>1308477295.61</v>
+        <v>1319237866.01</v>
       </c>
       <c r="G51" t="n">
-        <v>1292874353.4</v>
+        <v>1296682980.11</v>
       </c>
       <c r="H51" t="n">
         <v>19255569.11</v>
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18226032.52</v>
+        <v>18594472.27</v>
       </c>
       <c r="F52" t="n">
-        <v>15623696.23</v>
+        <v>15744989.54</v>
       </c>
       <c r="G52" t="n">
-        <v>15079559.95</v>
+        <v>15213889.98</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1421219.12</v>
+        <v>1464301.66</v>
       </c>
       <c r="F53" t="n">
-        <v>1314597.34</v>
+        <v>1409414.14</v>
       </c>
       <c r="G53" t="n">
-        <v>1289253.21</v>
+        <v>1301310.34</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8419594.25</v>
+        <v>8428044.25</v>
       </c>
       <c r="F54" t="n">
-        <v>7812145.67</v>
+        <v>7922996.52</v>
       </c>
       <c r="G54" t="n">
-        <v>7764918.6</v>
+        <v>7860760</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1376034808.3</v>
+        <v>1377763187.21</v>
       </c>
       <c r="F56" t="n">
-        <v>1307116183.63</v>
+        <v>1317606556.11</v>
       </c>
       <c r="G56" t="n">
-        <v>1272102113.72</v>
+        <v>1285025265.96</v>
       </c>
       <c r="H56" t="n">
-        <v>6938153.34</v>
+        <v>6938464.44</v>
       </c>
       <c r="I56" t="n">
-        <v>30206880.91</v>
+        <v>30235885.26</v>
       </c>
       <c r="J56" t="n">
-        <v>37145034.25</v>
+        <v>37174349.7</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>7278349249.64</v>
+        <v>7289699336.16</v>
       </c>
       <c r="F57" t="n">
-        <v>7094610899.95</v>
+        <v>7101841640.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7071966281.12</v>
+        <v>7083067964.58</v>
       </c>
       <c r="H57" t="n">
         <v>18529479.85</v>
       </c>
       <c r="I57" t="n">
-        <v>136157945.57</v>
+        <v>139388763.12</v>
       </c>
       <c r="J57" t="n">
-        <v>154687425.42</v>
+        <v>157918242.97</v>
       </c>
     </row>
     <row r="58">
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4112200.56</v>
+        <v>4112416.63</v>
       </c>
       <c r="F58" t="n">
         <v>4054091.4</v>
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>162142608.03</v>
+        <v>178314076.96</v>
       </c>
       <c r="F59" t="n">
-        <v>66781023.87</v>
+        <v>118378654.98</v>
       </c>
       <c r="G59" t="n">
-        <v>66068652.88</v>
+        <v>117660127.2</v>
       </c>
       <c r="H59" t="n">
         <v>5876518.16</v>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442922.91</v>
+        <v>5499636.91</v>
       </c>
       <c r="F60" t="n">
-        <v>5245799.41</v>
+        <v>5320513.38</v>
       </c>
       <c r="G60" t="n">
-        <v>5151032.13</v>
+        <v>5234344.02</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>84134445.2</v>
+        <v>82266587.05</v>
       </c>
       <c r="F61" t="n">
-        <v>23960016.35</v>
+        <v>24646944.34</v>
       </c>
       <c r="G61" t="n">
-        <v>21921141.96</v>
+        <v>23012886.94</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>50018579.51</v>
+        <v>54336522.18</v>
       </c>
       <c r="J61" t="n">
-        <v>50078579.61</v>
+        <v>54396522.28</v>
       </c>
     </row>
     <row r="62">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>40879742.58</v>
+        <v>54014804.36</v>
       </c>
       <c r="F62" t="n">
-        <v>32863264.55</v>
+        <v>39771812.83</v>
       </c>
       <c r="G62" t="n">
-        <v>30934152.7</v>
+        <v>36630635.68</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>41573098.03</v>
+        <v>57619188.75</v>
       </c>
       <c r="F63" t="n">
-        <v>20952374.13</v>
+        <v>22333476.41</v>
       </c>
       <c r="G63" t="n">
-        <v>20286751.54</v>
+        <v>21460092.93</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>58207777.37</v>
+        <v>61794761.22</v>
       </c>
       <c r="F64" t="n">
-        <v>55027346.75</v>
+        <v>57800156.21</v>
       </c>
       <c r="G64" t="n">
-        <v>49824816.44</v>
+        <v>51958426</v>
       </c>
       <c r="H64" t="n">
         <v>11841578.76</v>
       </c>
       <c r="I64" t="n">
-        <v>13121241.52</v>
+        <v>13472883.85</v>
       </c>
       <c r="J64" t="n">
-        <v>24962820.28</v>
+        <v>25314462.61</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8199882136.34</v>
+        <v>8507344769.88</v>
       </c>
       <c r="F65" t="n">
-        <v>7895284034.95</v>
+        <v>8154987590.7</v>
       </c>
       <c r="G65" t="n">
-        <v>7740330207.98</v>
+        <v>8072300999.19</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>121971369.87</v>
+        <v>122874578.26</v>
       </c>
       <c r="J65" t="n">
-        <v>317878796.34</v>
+        <v>318782004.73</v>
       </c>
     </row>
     <row r="66">
@@ -2766,13 +2766,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>796391273.97</v>
+        <v>801223284.51</v>
       </c>
       <c r="F66" t="n">
-        <v>710965649.33</v>
+        <v>716649393.64</v>
       </c>
       <c r="G66" t="n">
-        <v>694211517.77</v>
+        <v>699763534.55</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>182792954.67</v>
+        <v>230616253.02</v>
       </c>
       <c r="F67" t="n">
-        <v>171096164.8</v>
+        <v>209613635.64</v>
       </c>
       <c r="G67" t="n">
-        <v>100017172.01</v>
+        <v>166706258.01</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>432925915.27</v>
+        <v>546834208.88</v>
       </c>
       <c r="F68" t="n">
-        <v>416316423.01</v>
+        <v>515595352.73</v>
       </c>
       <c r="G68" t="n">
-        <v>264256708.79</v>
+        <v>413827494.97</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2177937757.47</v>
+        <v>2181840214.99</v>
       </c>
       <c r="F69" t="n">
-        <v>1874929269.64</v>
+        <v>1889247943.4</v>
       </c>
       <c r="G69" t="n">
-        <v>1833320035.09</v>
+        <v>1856647406.11</v>
       </c>
       <c r="H69" t="n">
         <v>14512845.39</v>
       </c>
       <c r="I69" t="n">
-        <v>119269170.01</v>
+        <v>120417237.34</v>
       </c>
       <c r="J69" t="n">
-        <v>133782015.4</v>
+        <v>134930082.73</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>95159911.92</v>
+        <v>96286008.34</v>
       </c>
       <c r="F70" t="n">
-        <v>87193925.27</v>
+        <v>89035904.91</v>
       </c>
       <c r="G70" t="n">
-        <v>85444488.81</v>
+        <v>87056176.14</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>342003098.39</v>
+        <v>342987694.47</v>
       </c>
       <c r="F71" t="n">
-        <v>257663321.15</v>
+        <v>265828669.7</v>
       </c>
       <c r="G71" t="n">
-        <v>217209608.59</v>
+        <v>228391898.43</v>
       </c>
       <c r="H71" t="n">
         <v>28757544</v>
       </c>
       <c r="I71" t="n">
-        <v>65743924.29</v>
+        <v>66176285.25</v>
       </c>
       <c r="J71" t="n">
-        <v>94501468.29000001</v>
+        <v>94933829.25</v>
       </c>
     </row>
     <row r="72">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>7173612.89</v>
+        <v>7239832.1</v>
       </c>
       <c r="F72" t="n">
-        <v>6260918.39</v>
+        <v>6769921.99</v>
       </c>
       <c r="G72" t="n">
-        <v>5803286.04</v>
+        <v>5818100.34</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>176999709.79</v>
+        <v>177427207.4</v>
       </c>
       <c r="F73" t="n">
-        <v>157889787.31</v>
+        <v>160755052.2</v>
       </c>
       <c r="G73" t="n">
-        <v>154831837.43</v>
+        <v>157424415.06</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
       </c>
       <c r="I73" t="n">
-        <v>16669029.31</v>
+        <v>18431088.77</v>
       </c>
       <c r="J73" t="n">
-        <v>16881440.25</v>
+        <v>18643499.71</v>
       </c>
     </row>
     <row r="74">
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>206939945.62</v>
+        <v>208646211.11</v>
       </c>
       <c r="F74" t="n">
-        <v>186951138.81</v>
+        <v>191291258.58</v>
       </c>
       <c r="G74" t="n">
-        <v>183532314.13</v>
+        <v>187325307.49</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>21425330.3</v>
+        <v>21491872.15</v>
       </c>
       <c r="J74" t="n">
-        <v>21555784.08</v>
+        <v>21622325.93</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3803197.08</v>
+        <v>3812554.78</v>
       </c>
       <c r="F75" t="n">
-        <v>2756915.05</v>
+        <v>2782570.48</v>
       </c>
       <c r="G75" t="n">
-        <v>2557434.76</v>
+        <v>2579400.16</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>546138672.5</v>
+        <v>567543007.35</v>
       </c>
       <c r="F2" t="n">
-        <v>456308702.99</v>
+        <v>529251892.91</v>
       </c>
       <c r="G2" t="n">
-        <v>394707422.07</v>
+        <v>437311826.64</v>
       </c>
       <c r="H2" t="n">
-        <v>214279372.77</v>
+        <v>214250064.35</v>
       </c>
       <c r="I2" t="n">
-        <v>2432931.84</v>
+        <v>2470511.47</v>
       </c>
       <c r="J2" t="n">
-        <v>216712304.61</v>
+        <v>216720575.82</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>3053000.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2829391.05</v>
+        <v>2890186.24</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3924226.74</v>
+        <v>3959037.53</v>
       </c>
       <c r="F4" t="n">
-        <v>1717945.15</v>
+        <v>1771150.82</v>
       </c>
       <c r="G4" t="n">
-        <v>1588301.39</v>
+        <v>1635175.99</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9984237.949999999</v>
+        <v>10015612.8</v>
       </c>
       <c r="F5" t="n">
-        <v>8694331.949999999</v>
+        <v>8722592.23</v>
       </c>
       <c r="G5" t="n">
-        <v>8538576.73</v>
+        <v>8641847.58</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19853468.47</v>
+        <v>26480608.61</v>
       </c>
       <c r="F6" t="n">
-        <v>14510995.56</v>
+        <v>16712661.44</v>
       </c>
       <c r="G6" t="n">
-        <v>13083081.27</v>
+        <v>15355876.91</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864580454.79</v>
+        <v>873359758.36</v>
       </c>
       <c r="F7" t="n">
-        <v>840080192.84</v>
+        <v>841727563.51</v>
       </c>
       <c r="G7" t="n">
-        <v>837761172.45</v>
+        <v>838595952.9400001</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>32148306.23</v>
+        <v>32153940</v>
       </c>
       <c r="J7" t="n">
-        <v>38195110.11</v>
+        <v>38200743.88</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29047163.41</v>
+        <v>29122346.86</v>
       </c>
       <c r="F8" t="n">
-        <v>28937853.69</v>
+        <v>28950554.65</v>
       </c>
       <c r="G8" t="n">
-        <v>28634203.1</v>
+        <v>28882572.93</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>916463080.77</v>
+        <v>1053590902.04</v>
       </c>
       <c r="F9" t="n">
-        <v>447411719.14</v>
+        <v>534051414.58</v>
       </c>
       <c r="G9" t="n">
-        <v>383047722.4</v>
+        <v>388996180.45</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>248924289.71</v>
+        <v>255490033.6</v>
       </c>
       <c r="J9" t="n">
-        <v>262355937.26</v>
+        <v>268921681.15</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38592034.27</v>
+        <v>38724582.13</v>
       </c>
       <c r="F10" t="n">
-        <v>33094015.24</v>
+        <v>33501422.42</v>
       </c>
       <c r="G10" t="n">
-        <v>19453414.91</v>
+        <v>28554320.15</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>509509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>361922980.24</v>
+        <v>436560170.93</v>
       </c>
       <c r="G11" t="n">
-        <v>361918617.47</v>
+        <v>365189828.84</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>75440224.45</v>
       </c>
       <c r="F12" t="n">
-        <v>74314095.13</v>
+        <v>74496088.67</v>
       </c>
       <c r="G12" t="n">
         <v>74303745.93000001</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11257892.63</v>
+        <v>11309381.03</v>
       </c>
       <c r="F16" t="n">
-        <v>9428172.470000001</v>
+        <v>9579734.02</v>
       </c>
       <c r="G16" t="n">
-        <v>9165928.07</v>
+        <v>9214988.880000001</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1985195.17</v>
+        <v>1985990.62</v>
       </c>
       <c r="F18" t="n">
-        <v>1919444.74</v>
+        <v>1925204.18</v>
       </c>
       <c r="G18" t="n">
-        <v>1835286.91</v>
+        <v>1840976.67</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>267600908.85</v>
+        <v>271342892.54</v>
       </c>
       <c r="F19" t="n">
-        <v>207842846.5</v>
+        <v>210579895.99</v>
       </c>
       <c r="G19" t="n">
-        <v>201257759.21</v>
+        <v>203147711.32</v>
       </c>
       <c r="H19" t="n">
         <v>3369052.62</v>
       </c>
       <c r="I19" t="n">
-        <v>3173797.73</v>
+        <v>3674484.75</v>
       </c>
       <c r="J19" t="n">
-        <v>6542850.35</v>
+        <v>7043537.37</v>
       </c>
     </row>
     <row r="20">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30797003.7</v>
+        <v>30801228.69</v>
       </c>
       <c r="F20" t="n">
-        <v>22366933.64</v>
+        <v>23388123.36</v>
       </c>
       <c r="G20" t="n">
-        <v>21843861.73</v>
+        <v>22646930.57</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
@@ -1197,10 +1197,10 @@
         <v>5173831.57</v>
       </c>
       <c r="F22" t="n">
-        <v>2092581.35</v>
+        <v>2157612.25</v>
       </c>
       <c r="G22" t="n">
-        <v>2080797.85</v>
+        <v>2086183.75</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>32291159.69</v>
+        <v>32334136.98</v>
       </c>
       <c r="F23" t="n">
-        <v>31634416.1</v>
+        <v>31982170.73</v>
       </c>
       <c r="G23" t="n">
-        <v>30128701.61</v>
+        <v>30948887.6</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>72424271.42</v>
+        <v>73577264.63</v>
       </c>
       <c r="F24" t="n">
-        <v>57538853.85</v>
+        <v>59314256.03</v>
       </c>
       <c r="G24" t="n">
-        <v>56806406.37</v>
+        <v>58181169.43</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6496388.19</v>
+        <v>6534927.36</v>
       </c>
       <c r="F26" t="n">
-        <v>6496388.19</v>
+        <v>6499021.15</v>
       </c>
       <c r="G26" t="n">
-        <v>6496388.19</v>
+        <v>6499021.15</v>
       </c>
       <c r="H26" t="n">
         <v>360498.89</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8267954316.3</v>
+        <v>8324091279.58</v>
       </c>
       <c r="F27" t="n">
-        <v>5968518675.77</v>
+        <v>6187310992.66</v>
       </c>
       <c r="G27" t="n">
-        <v>5682782918.46</v>
+        <v>5823423530.47</v>
       </c>
       <c r="H27" t="n">
-        <v>328021594.31</v>
+        <v>337639370.08</v>
       </c>
       <c r="I27" t="n">
-        <v>425822333.34</v>
+        <v>433901629.01</v>
       </c>
       <c r="J27" t="n">
-        <v>753843927.65</v>
+        <v>771540999.09</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>18422304.66</v>
+        <v>20918207.67</v>
       </c>
       <c r="F28" t="n">
-        <v>4478309.34</v>
+        <v>6030068.12</v>
       </c>
       <c r="G28" t="n">
-        <v>3351991.9</v>
+        <v>4240430.78</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>29870819.08</v>
+        <v>30571739.86</v>
       </c>
       <c r="J28" t="n">
-        <v>34457588.56</v>
+        <v>35158509.34</v>
       </c>
     </row>
     <row r="29">
@@ -1443,10 +1443,10 @@
         <v>377313.03</v>
       </c>
       <c r="F29" t="n">
-        <v>108091.8</v>
+        <v>112539.5</v>
       </c>
       <c r="G29" t="n">
-        <v>106344.36</v>
+        <v>110792.06</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7341602168.67</v>
+        <v>7349684527.54</v>
       </c>
       <c r="F30" t="n">
-        <v>7337489874.58</v>
+        <v>7340006868.97</v>
       </c>
       <c r="G30" t="n">
-        <v>7337371244.56</v>
+        <v>7339879826.73</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>26689241.97</v>
+        <v>28034461.35</v>
       </c>
       <c r="F31" t="n">
-        <v>23943741.12</v>
+        <v>24762074.23</v>
       </c>
       <c r="G31" t="n">
-        <v>23729778.35</v>
+        <v>24501695.76</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1124454027.11</v>
+        <v>1145288025.9</v>
       </c>
       <c r="F32" t="n">
-        <v>992345991.76</v>
+        <v>1007150356.84</v>
       </c>
       <c r="G32" t="n">
-        <v>957147629.27</v>
+        <v>973388422.97</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>91179119.90000001</v>
+        <v>91510279.09</v>
       </c>
       <c r="J32" t="n">
-        <v>97220251.01000001</v>
+        <v>97551410.2</v>
       </c>
     </row>
     <row r="33">
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>301848.61</v>
+        <v>304155.02</v>
       </c>
       <c r="F33" t="n">
-        <v>291131.29</v>
+        <v>293437.71</v>
       </c>
       <c r="G33" t="n">
-        <v>268167.76</v>
+        <v>270420.09</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,13 +1620,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>29539266.42</v>
+        <v>29595866.88</v>
       </c>
       <c r="F34" t="n">
-        <v>27983182.41</v>
+        <v>28084611.42</v>
       </c>
       <c r="G34" t="n">
-        <v>26373887.96</v>
+        <v>27288671.41</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>123226.75</v>
+        <v>1272418.75</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1149192</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>155231.68</v>
+        <v>330494.88</v>
       </c>
       <c r="J35" t="n">
-        <v>155231.68</v>
+        <v>330494.88</v>
       </c>
     </row>
     <row r="36">
@@ -1695,10 +1695,10 @@
         <v>432646942.18</v>
       </c>
       <c r="F36" t="n">
-        <v>145955807.46</v>
+        <v>158944934.25</v>
       </c>
       <c r="G36" t="n">
-        <v>135055006.14</v>
+        <v>145507480.92</v>
       </c>
       <c r="H36" t="n">
         <v>53631506.45</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2379612.34</v>
+        <v>2394612.34</v>
       </c>
       <c r="F37" t="n">
-        <v>2244694.98</v>
+        <v>2251695.48</v>
       </c>
       <c r="G37" t="n">
-        <v>2196303.13</v>
+        <v>2203095.37</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1767,10 +1767,10 @@
         <v>63097212.7</v>
       </c>
       <c r="F38" t="n">
-        <v>59701195.81</v>
+        <v>59757125.84</v>
       </c>
       <c r="G38" t="n">
-        <v>59678389.57</v>
+        <v>59734319.6</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>218111470.56</v>
+        <v>220457458.26</v>
       </c>
       <c r="F39" t="n">
-        <v>144002575.84</v>
+        <v>159330668.83</v>
       </c>
       <c r="G39" t="n">
-        <v>123146390.5</v>
+        <v>124523224.48</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>133310361.18</v>
+        <v>133334792.31</v>
       </c>
       <c r="J39" t="n">
-        <v>140497634.25</v>
+        <v>140522065.38</v>
       </c>
     </row>
     <row r="40">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>64042195.83</v>
+        <v>63680777.79</v>
       </c>
       <c r="F40" t="n">
-        <v>28996537.12</v>
+        <v>30258592.25</v>
       </c>
       <c r="G40" t="n">
-        <v>26481184.88</v>
+        <v>28087036.73</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53382913.65</v>
+        <v>54479019.4</v>
       </c>
       <c r="F41" t="n">
-        <v>23456615.76</v>
+        <v>23962433.01</v>
       </c>
       <c r="G41" t="n">
-        <v>21697815.01</v>
+        <v>22296843.74</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3587463350.96</v>
+        <v>3587463351.05</v>
       </c>
       <c r="F42" t="n">
-        <v>2788947268.49</v>
+        <v>3370156381.14</v>
       </c>
       <c r="G42" t="n">
-        <v>2634805575.37</v>
+        <v>3107590425.12</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>184244061.28</v>
+        <v>185088909.18</v>
       </c>
       <c r="F43" t="n">
-        <v>149592723.08</v>
+        <v>153430024.78</v>
       </c>
       <c r="G43" t="n">
-        <v>142132644.66</v>
+        <v>148496639.8</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>23413795.3</v>
+        <v>23532405.38</v>
       </c>
       <c r="J43" t="n">
-        <v>26761870.58</v>
+        <v>26880480.66</v>
       </c>
     </row>
     <row r="44">
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25081009.4</v>
+        <v>25633243.89</v>
       </c>
       <c r="F44" t="n">
-        <v>13054615.56</v>
+        <v>13557129</v>
       </c>
       <c r="G44" t="n">
-        <v>12727213.1</v>
+        <v>12992939.42</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>18182757.84</v>
+        <v>18376867.37</v>
       </c>
       <c r="J44" t="n">
-        <v>19204544.77</v>
+        <v>19398654.3</v>
       </c>
     </row>
     <row r="45">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>96821326.23999999</v>
+        <v>97269212.77</v>
       </c>
       <c r="F45" t="n">
-        <v>88071432.44</v>
+        <v>88914728.12</v>
       </c>
       <c r="G45" t="n">
-        <v>81908172.42</v>
+        <v>83462180.54000001</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>7106445.14</v>
+        <v>7244971.19</v>
       </c>
       <c r="J45" t="n">
-        <v>7592977.79</v>
+        <v>7731503.84</v>
       </c>
     </row>
     <row r="46">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>11112659.41</v>
+        <v>11129530.59</v>
       </c>
       <c r="F46" t="n">
-        <v>7773616.89</v>
+        <v>8499645.289999999</v>
       </c>
       <c r="G46" t="n">
-        <v>7131111.02</v>
+        <v>8027701.49</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23873955.56</v>
+        <v>23897982.9</v>
       </c>
       <c r="F47" t="n">
-        <v>21536503.41</v>
+        <v>21640038.19</v>
       </c>
       <c r="G47" t="n">
-        <v>20098348.01</v>
+        <v>20200947.25</v>
       </c>
       <c r="H47" t="n">
         <v>5234428.46</v>
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>127435637.12</v>
+        <v>128487296.4</v>
       </c>
       <c r="F48" t="n">
-        <v>122862735.49</v>
+        <v>123301513.8</v>
       </c>
       <c r="G48" t="n">
-        <v>122210963.18</v>
+        <v>122490595.06</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4668361.04</v>
+        <v>4718709.47</v>
       </c>
       <c r="J48" t="n">
-        <v>5178274.96</v>
+        <v>5228623.39</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15184514.47</v>
+        <v>16613890.91</v>
       </c>
       <c r="F49" t="n">
-        <v>14585569.05</v>
+        <v>15785883.87</v>
       </c>
       <c r="G49" t="n">
-        <v>13962804.12</v>
+        <v>15113267.01</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1029524757.75</v>
+        <v>1040476951.19</v>
       </c>
       <c r="F50" t="n">
-        <v>670460371.92</v>
+        <v>723599820.1900001</v>
       </c>
       <c r="G50" t="n">
-        <v>651484826.34</v>
+        <v>704446179.71</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>192003440.36</v>
+        <v>192157498.6</v>
       </c>
       <c r="J50" t="n">
-        <v>192100337.73</v>
+        <v>192254395.97</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1342560808.36</v>
+        <v>1388414457.92</v>
       </c>
       <c r="F51" t="n">
-        <v>1319237866.01</v>
+        <v>1373603272.88</v>
       </c>
       <c r="G51" t="n">
-        <v>1296682980.11</v>
+        <v>1349889895.07</v>
       </c>
       <c r="H51" t="n">
-        <v>19255569.11</v>
+        <v>19281961</v>
       </c>
       <c r="I51" t="n">
-        <v>34442130.88</v>
+        <v>34443501.76</v>
       </c>
       <c r="J51" t="n">
-        <v>53697699.99</v>
+        <v>53725462.76</v>
       </c>
     </row>
     <row r="52">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18594472.27</v>
+        <v>18354626.58</v>
       </c>
       <c r="F52" t="n">
-        <v>15744989.54</v>
+        <v>16395825.67</v>
       </c>
       <c r="G52" t="n">
-        <v>15213889.98</v>
+        <v>15457996.49</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
@@ -2307,10 +2307,10 @@
         <v>1464301.66</v>
       </c>
       <c r="F53" t="n">
-        <v>1409414.14</v>
+        <v>1413308.51</v>
       </c>
       <c r="G53" t="n">
-        <v>1301310.34</v>
+        <v>1374125.67</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8428044.25</v>
+        <v>8506542.25</v>
       </c>
       <c r="F54" t="n">
-        <v>7922996.52</v>
+        <v>8001213.25</v>
       </c>
       <c r="G54" t="n">
-        <v>7860760</v>
+        <v>7938346.35</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12949020.94</v>
+        <v>12961302.85</v>
       </c>
       <c r="F55" t="n">
-        <v>10390853.25</v>
+        <v>10403135.16</v>
       </c>
       <c r="G55" t="n">
         <v>10390853.25</v>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1377763187.21</v>
+        <v>1385530752.05</v>
       </c>
       <c r="F56" t="n">
-        <v>1317606556.11</v>
+        <v>1324699618.87</v>
       </c>
       <c r="G56" t="n">
-        <v>1285025265.96</v>
+        <v>1309703145.14</v>
       </c>
       <c r="H56" t="n">
         <v>6938464.44</v>
       </c>
       <c r="I56" t="n">
-        <v>30235885.26</v>
+        <v>30377299.29</v>
       </c>
       <c r="J56" t="n">
-        <v>37174349.7</v>
+        <v>37315763.73</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>7289699336.16</v>
+        <v>7309418515.18</v>
       </c>
       <c r="F57" t="n">
-        <v>7101841640.25</v>
+        <v>7116651535.61</v>
       </c>
       <c r="G57" t="n">
-        <v>7083067964.58</v>
+        <v>7097075559.41</v>
       </c>
       <c r="H57" t="n">
         <v>18529479.85</v>
       </c>
       <c r="I57" t="n">
-        <v>139388763.12</v>
+        <v>139998246.63</v>
       </c>
       <c r="J57" t="n">
-        <v>157918242.97</v>
+        <v>158527726.48</v>
       </c>
     </row>
     <row r="58">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4112416.63</v>
+        <v>4112809.7</v>
       </c>
       <c r="F58" t="n">
-        <v>4054091.4</v>
+        <v>4054484.47</v>
       </c>
       <c r="G58" t="n">
-        <v>3961398.24</v>
+        <v>3961791.31</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>178314076.96</v>
+        <v>248507880.41</v>
       </c>
       <c r="F59" t="n">
-        <v>118378654.98</v>
+        <v>194043370.19</v>
       </c>
       <c r="G59" t="n">
-        <v>117660127.2</v>
+        <v>192953153.07</v>
       </c>
       <c r="H59" t="n">
-        <v>5876518.16</v>
+        <v>6876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>16274575.81</v>
+        <v>16392015.92</v>
       </c>
       <c r="J59" t="n">
-        <v>22151093.97</v>
+        <v>23268534.08</v>
       </c>
     </row>
     <row r="60">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5499636.91</v>
+        <v>5518280.7</v>
       </c>
       <c r="F60" t="n">
-        <v>5320513.38</v>
+        <v>5339696.41</v>
       </c>
       <c r="G60" t="n">
-        <v>5234344.02</v>
+        <v>5253527.05</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>82266587.05</v>
+        <v>82865181.3</v>
       </c>
       <c r="F61" t="n">
-        <v>24646944.34</v>
+        <v>36368431.49</v>
       </c>
       <c r="G61" t="n">
-        <v>23012886.94</v>
+        <v>34538568.93</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>54336522.18</v>
+        <v>56779446.78</v>
       </c>
       <c r="J61" t="n">
-        <v>54396522.28</v>
+        <v>56839446.88</v>
       </c>
     </row>
     <row r="62">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>54014804.36</v>
+        <v>103843078.63</v>
       </c>
       <c r="F62" t="n">
-        <v>39771812.83</v>
+        <v>93683920.23</v>
       </c>
       <c r="G62" t="n">
-        <v>36630635.68</v>
+        <v>65553661.76</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>57619188.75</v>
+        <v>59439299.8</v>
       </c>
       <c r="F63" t="n">
-        <v>22333476.41</v>
+        <v>23889261.09</v>
       </c>
       <c r="G63" t="n">
-        <v>21460092.93</v>
+        <v>22612315.81</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>61794761.22</v>
+        <v>79760646.64</v>
       </c>
       <c r="F64" t="n">
-        <v>57800156.21</v>
+        <v>76531903.53</v>
       </c>
       <c r="G64" t="n">
-        <v>51958426</v>
+        <v>64806500.18</v>
       </c>
       <c r="H64" t="n">
-        <v>11841578.76</v>
+        <v>11842578.76</v>
       </c>
       <c r="I64" t="n">
-        <v>13472883.85</v>
+        <v>14102752.39</v>
       </c>
       <c r="J64" t="n">
-        <v>25314462.61</v>
+        <v>25945331.15</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8507344769.88</v>
+        <v>8664018022.610001</v>
       </c>
       <c r="F65" t="n">
-        <v>8154987590.7</v>
+        <v>8322194732.45</v>
       </c>
       <c r="G65" t="n">
-        <v>8072300999.19</v>
+        <v>8239564659.31</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>122874578.26</v>
+        <v>132456860.67</v>
       </c>
       <c r="J65" t="n">
-        <v>318782004.73</v>
+        <v>328364287.14</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>801223284.51</v>
+        <v>805041968.35</v>
       </c>
       <c r="F66" t="n">
-        <v>716649393.64</v>
+        <v>725780634.59</v>
       </c>
       <c r="G66" t="n">
-        <v>699763534.55</v>
+        <v>708195519.15</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>53658725.35</v>
+        <v>53836568.43</v>
       </c>
       <c r="J66" t="n">
-        <v>61324169.56</v>
+        <v>61502012.64</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230616253.02</v>
+        <v>297637267.84</v>
       </c>
       <c r="F67" t="n">
-        <v>209613635.64</v>
+        <v>286218181.32</v>
       </c>
       <c r="G67" t="n">
-        <v>166706258.01</v>
+        <v>243379380.24</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>546834208.88</v>
+        <v>595320093.95</v>
       </c>
       <c r="F68" t="n">
-        <v>515595352.73</v>
+        <v>575373025.97</v>
       </c>
       <c r="G68" t="n">
-        <v>413827494.97</v>
+        <v>501647281.47</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>23609683.4</v>
+        <v>24497708.44</v>
       </c>
       <c r="J68" t="n">
-        <v>39453491.17</v>
+        <v>40341516.21</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2181840214.99</v>
+        <v>2198972195.57</v>
       </c>
       <c r="F69" t="n">
-        <v>1889247943.4</v>
+        <v>1939524868.42</v>
       </c>
       <c r="G69" t="n">
-        <v>1856647406.11</v>
+        <v>1912787373.06</v>
       </c>
       <c r="H69" t="n">
-        <v>14512845.39</v>
+        <v>14513945.66</v>
       </c>
       <c r="I69" t="n">
-        <v>120417237.34</v>
+        <v>123227122.58</v>
       </c>
       <c r="J69" t="n">
-        <v>134930082.73</v>
+        <v>137741068.24</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>96286008.34</v>
+        <v>98201227.43000001</v>
       </c>
       <c r="F70" t="n">
-        <v>89035904.91</v>
+        <v>90223934.06</v>
       </c>
       <c r="G70" t="n">
-        <v>87056176.14</v>
+        <v>87531113.01000001</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>342987694.47</v>
+        <v>347898507.16</v>
       </c>
       <c r="F71" t="n">
-        <v>265828669.7</v>
+        <v>273870857.62</v>
       </c>
       <c r="G71" t="n">
-        <v>228391898.43</v>
+        <v>237837918.39</v>
       </c>
       <c r="H71" t="n">
-        <v>28757544</v>
+        <v>28757634.3</v>
       </c>
       <c r="I71" t="n">
-        <v>66176285.25</v>
+        <v>66276910.43</v>
       </c>
       <c r="J71" t="n">
-        <v>94933829.25</v>
+        <v>95034544.73</v>
       </c>
     </row>
     <row r="72">
@@ -2982,22 +2982,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>7239832.1</v>
+        <v>7248002.09</v>
       </c>
       <c r="F72" t="n">
-        <v>6769921.99</v>
+        <v>6783613.16</v>
       </c>
       <c r="G72" t="n">
-        <v>5818100.34</v>
+        <v>5878301.7</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
       </c>
       <c r="I72" t="n">
-        <v>528322.15</v>
+        <v>560777.9399999999</v>
       </c>
       <c r="J72" t="n">
-        <v>560732.3100000001</v>
+        <v>593188.1</v>
       </c>
     </row>
     <row r="73">
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>177427207.4</v>
+        <v>179150781.22</v>
       </c>
       <c r="F73" t="n">
-        <v>160755052.2</v>
+        <v>163123253.36</v>
       </c>
       <c r="G73" t="n">
-        <v>157424415.06</v>
+        <v>159757200.72</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
       </c>
       <c r="I73" t="n">
-        <v>18431088.77</v>
+        <v>18466096.57</v>
       </c>
       <c r="J73" t="n">
-        <v>18643499.71</v>
+        <v>18678507.51</v>
       </c>
     </row>
     <row r="74">
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>208646211.11</v>
+        <v>210294308.69</v>
       </c>
       <c r="F74" t="n">
-        <v>191291258.58</v>
+        <v>195066164.82</v>
       </c>
       <c r="G74" t="n">
-        <v>187325307.49</v>
+        <v>190215982.12</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>21491872.15</v>
+        <v>21692603.48</v>
       </c>
       <c r="J74" t="n">
-        <v>21622325.93</v>
+        <v>21823057.26</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3812554.78</v>
+        <v>3852271.18</v>
       </c>
       <c r="F75" t="n">
-        <v>2782570.48</v>
+        <v>2783906.47</v>
       </c>
       <c r="G75" t="n">
-        <v>2579400.16</v>
+        <v>2584163.88</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>567543007.35</v>
+        <v>617806106.28</v>
       </c>
       <c r="F2" t="n">
-        <v>529251892.91</v>
+        <v>592945182.22</v>
       </c>
       <c r="G2" t="n">
-        <v>437311826.64</v>
+        <v>502096123.26</v>
       </c>
       <c r="H2" t="n">
         <v>214250064.35</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3200427.23</v>
+        <v>3551203.43</v>
       </c>
       <c r="F3" t="n">
-        <v>3053000.24</v>
+        <v>3409454.44</v>
       </c>
       <c r="G3" t="n">
-        <v>2890186.24</v>
+        <v>3240962.44</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3959037.53</v>
+        <v>4104662.83</v>
       </c>
       <c r="F4" t="n">
-        <v>1771150.82</v>
+        <v>2110495.29</v>
       </c>
       <c r="G4" t="n">
-        <v>1635175.99</v>
+        <v>1797202.17</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10015612.8</v>
+        <v>11612415.15</v>
       </c>
       <c r="F5" t="n">
-        <v>8722592.23</v>
+        <v>10322467.96</v>
       </c>
       <c r="G5" t="n">
-        <v>8641847.58</v>
+        <v>10245394.62</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>26480608.61</v>
+        <v>27794225.72</v>
       </c>
       <c r="F6" t="n">
-        <v>16712661.44</v>
+        <v>18053785.27</v>
       </c>
       <c r="G6" t="n">
-        <v>15355876.91</v>
+        <v>16508612.73</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>873359758.36</v>
+        <v>1040966458.63</v>
       </c>
       <c r="F7" t="n">
-        <v>841727563.51</v>
+        <v>1006441325.88</v>
       </c>
       <c r="G7" t="n">
-        <v>838595952.9400001</v>
+        <v>1004878559.2</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>32153940</v>
+        <v>32552462.46</v>
       </c>
       <c r="J7" t="n">
-        <v>38200743.88</v>
+        <v>38599266.34</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29122346.86</v>
+        <v>34787350.53</v>
       </c>
       <c r="F8" t="n">
-        <v>28950554.65</v>
+        <v>34621511.95</v>
       </c>
       <c r="G8" t="n">
-        <v>28882572.93</v>
+        <v>34547507.17</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1053590902.04</v>
+        <v>1083963872.32</v>
       </c>
       <c r="F9" t="n">
-        <v>534051414.58</v>
+        <v>582499745.65</v>
       </c>
       <c r="G9" t="n">
-        <v>388996180.45</v>
+        <v>556409451.3</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>255490033.6</v>
+        <v>270507894.5</v>
       </c>
       <c r="J9" t="n">
-        <v>268921681.15</v>
+        <v>283939542.05</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>38724582.13</v>
+        <v>48450358.23</v>
       </c>
       <c r="F10" t="n">
-        <v>33501422.42</v>
+        <v>43255573.74</v>
       </c>
       <c r="G10" t="n">
-        <v>28554320.15</v>
+        <v>35221082.21</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>509509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>436560170.93</v>
+        <v>444147454.03</v>
       </c>
       <c r="G11" t="n">
-        <v>365189828.84</v>
+        <v>444143091.26</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>75440224.45</v>
+        <v>90894782.2</v>
       </c>
       <c r="F12" t="n">
-        <v>74496088.67</v>
+        <v>89950646.42</v>
       </c>
       <c r="G12" t="n">
-        <v>74303745.93000001</v>
+        <v>89758303.68000001</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>11309381.03</v>
+        <v>12812866.45</v>
       </c>
       <c r="F16" t="n">
-        <v>9579734.02</v>
+        <v>11168321.81</v>
       </c>
       <c r="G16" t="n">
-        <v>9214988.880000001</v>
+        <v>10869424.55</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1985990.62</v>
+        <v>2275080.17</v>
       </c>
       <c r="F18" t="n">
-        <v>1925204.18</v>
+        <v>2215164.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1840976.67</v>
+        <v>2134468.54</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>271342892.54</v>
+        <v>306172748.78</v>
       </c>
       <c r="F19" t="n">
-        <v>210579895.99</v>
+        <v>245877095.59</v>
       </c>
       <c r="G19" t="n">
-        <v>203147711.32</v>
+        <v>225832606.4</v>
       </c>
       <c r="H19" t="n">
         <v>3369052.62</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30801228.69</v>
+        <v>32017496.6</v>
       </c>
       <c r="F20" t="n">
-        <v>23388123.36</v>
+        <v>25785864.81</v>
       </c>
       <c r="G20" t="n">
-        <v>22646930.57</v>
+        <v>25012081.73</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5173831.57</v>
+        <v>5201831.56</v>
       </c>
       <c r="F22" t="n">
-        <v>2157612.25</v>
+        <v>2218577.25</v>
       </c>
       <c r="G22" t="n">
-        <v>2086183.75</v>
+        <v>2153703.15</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>32334136.98</v>
+        <v>36498337.17</v>
       </c>
       <c r="F23" t="n">
-        <v>31982170.73</v>
+        <v>36111682.65</v>
       </c>
       <c r="G23" t="n">
-        <v>30948887.6</v>
+        <v>35069263.25</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>73577264.63</v>
+        <v>75217619.45999999</v>
       </c>
       <c r="F24" t="n">
-        <v>59314256.03</v>
+        <v>60628266.46</v>
       </c>
       <c r="G24" t="n">
-        <v>58181169.43</v>
+        <v>58684656.63</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8324091279.58</v>
+        <v>8824566137.58</v>
       </c>
       <c r="F27" t="n">
-        <v>6187310992.66</v>
+        <v>6706842855.7</v>
       </c>
       <c r="G27" t="n">
-        <v>5823423530.47</v>
+        <v>6498287753.94</v>
       </c>
       <c r="H27" t="n">
-        <v>337639370.08</v>
+        <v>348314152.22</v>
       </c>
       <c r="I27" t="n">
-        <v>433901629.01</v>
+        <v>456191694.34</v>
       </c>
       <c r="J27" t="n">
-        <v>771540999.09</v>
+        <v>804505846.5599999</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20918207.67</v>
+        <v>20944673.57</v>
       </c>
       <c r="F28" t="n">
-        <v>6030068.12</v>
+        <v>6336947.74</v>
       </c>
       <c r="G28" t="n">
-        <v>4240430.78</v>
+        <v>4840838.18</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>30571739.86</v>
+        <v>30575533.78</v>
       </c>
       <c r="J28" t="n">
-        <v>35158509.34</v>
+        <v>35162303.26</v>
       </c>
     </row>
     <row r="29">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>377313.03</v>
+        <v>377600.11</v>
       </c>
       <c r="F29" t="n">
-        <v>112539.5</v>
+        <v>117731.93</v>
       </c>
       <c r="G29" t="n">
-        <v>110792.06</v>
+        <v>116134.11</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7349684527.54</v>
+        <v>8828303225.52</v>
       </c>
       <c r="F30" t="n">
-        <v>7340006868.97</v>
+        <v>8818625566.950001</v>
       </c>
       <c r="G30" t="n">
-        <v>7339879826.73</v>
+        <v>8818498332.280001</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>28034461.35</v>
+        <v>31440662.01</v>
       </c>
       <c r="F31" t="n">
-        <v>24762074.23</v>
+        <v>28792170.19</v>
       </c>
       <c r="G31" t="n">
-        <v>24501695.76</v>
+        <v>28359213.79</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>1890806.7</v>
+        <v>1960334.51</v>
       </c>
       <c r="J31" t="n">
-        <v>1891025.63</v>
+        <v>1960553.44</v>
       </c>
     </row>
     <row r="32">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1145288025.9</v>
+        <v>1289879070.22</v>
       </c>
       <c r="F32" t="n">
-        <v>1007150356.84</v>
+        <v>1168794609.32</v>
       </c>
       <c r="G32" t="n">
-        <v>973388422.97</v>
+        <v>1124118034.73</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>91510279.09</v>
+        <v>91686642.43000001</v>
       </c>
       <c r="J32" t="n">
-        <v>97551410.2</v>
+        <v>97727773.54000001</v>
       </c>
     </row>
     <row r="33">
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>304155.02</v>
+        <v>310478.82</v>
       </c>
       <c r="F33" t="n">
-        <v>293437.71</v>
+        <v>295186.81</v>
       </c>
       <c r="G33" t="n">
-        <v>270420.09</v>
+        <v>272249.19</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>29595866.88</v>
+        <v>34541537.36</v>
       </c>
       <c r="F34" t="n">
-        <v>28084611.42</v>
+        <v>32902758.88</v>
       </c>
       <c r="G34" t="n">
-        <v>27288671.41</v>
+        <v>32305422.73</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
       </c>
       <c r="I34" t="n">
-        <v>1674828.31</v>
+        <v>1678664.04</v>
       </c>
       <c r="J34" t="n">
-        <v>1702516.47</v>
+        <v>1706352.2</v>
       </c>
     </row>
     <row r="35">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1272418.75</v>
+        <v>1383063.6</v>
       </c>
       <c r="F35" t="n">
         <v>1149192</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1103345.57</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1695,10 +1695,10 @@
         <v>432646942.18</v>
       </c>
       <c r="F36" t="n">
-        <v>158944934.25</v>
+        <v>160660901.26</v>
       </c>
       <c r="G36" t="n">
-        <v>145507480.92</v>
+        <v>148272784.6</v>
       </c>
       <c r="H36" t="n">
         <v>53631506.45</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2394612.34</v>
+        <v>2709713.46</v>
       </c>
       <c r="F37" t="n">
-        <v>2251695.48</v>
+        <v>2564258.12</v>
       </c>
       <c r="G37" t="n">
-        <v>2203095.37</v>
+        <v>2515632.69</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220457458.26</v>
+        <v>236626077.9</v>
       </c>
       <c r="F39" t="n">
-        <v>159330668.83</v>
+        <v>171677093.31</v>
       </c>
       <c r="G39" t="n">
-        <v>124523224.48</v>
+        <v>135563992.68</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>133334792.31</v>
+        <v>133337424.34</v>
       </c>
       <c r="J39" t="n">
-        <v>140522065.38</v>
+        <v>140524697.41</v>
       </c>
     </row>
     <row r="40">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>63680777.79</v>
+        <v>64369439.59</v>
       </c>
       <c r="F40" t="n">
-        <v>30258592.25</v>
+        <v>33269291.04</v>
       </c>
       <c r="G40" t="n">
-        <v>28087036.73</v>
+        <v>29837781.14</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>54479019.4</v>
+        <v>55506641.22</v>
       </c>
       <c r="F41" t="n">
-        <v>23962433.01</v>
+        <v>25493362.59</v>
       </c>
       <c r="G41" t="n">
-        <v>22296843.74</v>
+        <v>23322644.12</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3587463351.05</v>
+        <v>3807924827.02</v>
       </c>
       <c r="F42" t="n">
         <v>3370156381.14</v>
       </c>
       <c r="G42" t="n">
-        <v>3107590425.12</v>
+        <v>3322123781.54</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185088909.18</v>
+        <v>201870793.4</v>
       </c>
       <c r="F43" t="n">
-        <v>153430024.78</v>
+        <v>170596137.22</v>
       </c>
       <c r="G43" t="n">
-        <v>148496639.8</v>
+        <v>166440428.9</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>23532405.38</v>
+        <v>23533810.38</v>
       </c>
       <c r="J43" t="n">
-        <v>26880480.66</v>
+        <v>26881885.66</v>
       </c>
     </row>
     <row r="44">
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25633243.89</v>
+        <v>28964520.89</v>
       </c>
       <c r="F44" t="n">
-        <v>13557129</v>
+        <v>17247931.64</v>
       </c>
       <c r="G44" t="n">
-        <v>12992939.42</v>
+        <v>16084636.09</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>18376867.37</v>
+        <v>18861918.75</v>
       </c>
       <c r="J44" t="n">
-        <v>19398654.3</v>
+        <v>19883705.68</v>
       </c>
     </row>
     <row r="45">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>97269212.77</v>
+        <v>105857386.4</v>
       </c>
       <c r="F45" t="n">
-        <v>88914728.12</v>
+        <v>102661981.29</v>
       </c>
       <c r="G45" t="n">
-        <v>83462180.54000001</v>
+        <v>98212839.89</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>7244971.19</v>
+        <v>7272577.03</v>
       </c>
       <c r="J45" t="n">
-        <v>7731503.84</v>
+        <v>7759109.68</v>
       </c>
     </row>
     <row r="46">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>11129530.59</v>
+        <v>12298666.91</v>
       </c>
       <c r="F46" t="n">
-        <v>8499645.289999999</v>
+        <v>9724766.84</v>
       </c>
       <c r="G46" t="n">
-        <v>8027701.49</v>
+        <v>9205375.300000001</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>23897982.9</v>
+        <v>26492216.78</v>
       </c>
       <c r="F47" t="n">
-        <v>21640038.19</v>
+        <v>24238780.59</v>
       </c>
       <c r="G47" t="n">
-        <v>20200947.25</v>
+        <v>22800673.45</v>
       </c>
       <c r="H47" t="n">
         <v>5234428.46</v>
@@ -2124,13 +2124,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>128487296.4</v>
+        <v>152296583.13</v>
       </c>
       <c r="F48" t="n">
-        <v>123301513.8</v>
+        <v>147349684.62</v>
       </c>
       <c r="G48" t="n">
-        <v>122490595.06</v>
+        <v>146327676.79</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>16613890.91</v>
+        <v>18295588.41</v>
       </c>
       <c r="F49" t="n">
-        <v>15785883.87</v>
+        <v>17392617.3</v>
       </c>
       <c r="G49" t="n">
-        <v>15113267.01</v>
+        <v>16721311.53</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1040476951.19</v>
+        <v>1097026982.54</v>
       </c>
       <c r="F50" t="n">
-        <v>723599820.1900001</v>
+        <v>766828388.15</v>
       </c>
       <c r="G50" t="n">
-        <v>704446179.71</v>
+        <v>747877094.64</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>192157498.6</v>
+        <v>192239471</v>
       </c>
       <c r="J50" t="n">
-        <v>192254395.97</v>
+        <v>192336368.37</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1388414457.92</v>
+        <v>1580488081.37</v>
       </c>
       <c r="F51" t="n">
-        <v>1373603272.88</v>
+        <v>1564011752.29</v>
       </c>
       <c r="G51" t="n">
-        <v>1349889895.07</v>
+        <v>1537079491.69</v>
       </c>
       <c r="H51" t="n">
-        <v>19281961</v>
+        <v>19328798.48</v>
       </c>
       <c r="I51" t="n">
-        <v>34443501.76</v>
+        <v>34444083.68</v>
       </c>
       <c r="J51" t="n">
-        <v>53725462.76</v>
+        <v>53772882.16</v>
       </c>
     </row>
     <row r="52">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>18354626.58</v>
+        <v>20446769.11</v>
       </c>
       <c r="F52" t="n">
-        <v>16395825.67</v>
+        <v>18572720.67</v>
       </c>
       <c r="G52" t="n">
-        <v>15457996.49</v>
+        <v>17527883.08</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1464301.66</v>
+        <v>1702938.37</v>
       </c>
       <c r="F53" t="n">
-        <v>1413308.51</v>
+        <v>1663147.47</v>
       </c>
       <c r="G53" t="n">
-        <v>1374125.67</v>
+        <v>1615160.52</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8506542.25</v>
+        <v>10034001.54</v>
       </c>
       <c r="F54" t="n">
-        <v>8001213.25</v>
+        <v>9524085.189999999</v>
       </c>
       <c r="G54" t="n">
-        <v>7938346.35</v>
+        <v>9461345.289999999</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12961302.85</v>
+        <v>12978755.64</v>
       </c>
       <c r="F55" t="n">
-        <v>10403135.16</v>
+        <v>12978755.64</v>
       </c>
       <c r="G55" t="n">
-        <v>10390853.25</v>
+        <v>12978755.64</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1385530752.05</v>
+        <v>1630572693.71</v>
       </c>
       <c r="F56" t="n">
-        <v>1324699618.87</v>
+        <v>1571159754.32</v>
       </c>
       <c r="G56" t="n">
-        <v>1309703145.14</v>
+        <v>1555490264.54</v>
       </c>
       <c r="H56" t="n">
-        <v>6938464.44</v>
+        <v>8940604.800000001</v>
       </c>
       <c r="I56" t="n">
-        <v>30377299.29</v>
+        <v>31169093.34</v>
       </c>
       <c r="J56" t="n">
-        <v>37315763.73</v>
+        <v>40109698.14</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>7309418515.18</v>
+        <v>8707182464.360001</v>
       </c>
       <c r="F57" t="n">
-        <v>7116651535.61</v>
+        <v>8524889908.73</v>
       </c>
       <c r="G57" t="n">
-        <v>7097075559.41</v>
+        <v>8489555011.67</v>
       </c>
       <c r="H57" t="n">
         <v>18529479.85</v>
       </c>
       <c r="I57" t="n">
-        <v>139998246.63</v>
+        <v>143886118.97</v>
       </c>
       <c r="J57" t="n">
-        <v>158527726.48</v>
+        <v>162415598.82</v>
       </c>
     </row>
     <row r="58">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4112809.7</v>
+        <v>4613035.78</v>
       </c>
       <c r="F58" t="n">
-        <v>4054484.47</v>
+        <v>4529798.83</v>
       </c>
       <c r="G58" t="n">
-        <v>3961791.31</v>
+        <v>4437105.67</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>248507880.41</v>
+        <v>303277365.62</v>
       </c>
       <c r="F59" t="n">
-        <v>194043370.19</v>
+        <v>257593836.11</v>
       </c>
       <c r="G59" t="n">
-        <v>192953153.07</v>
+        <v>255964811.56</v>
       </c>
       <c r="H59" t="n">
         <v>6876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>16392015.92</v>
+        <v>16452028.91</v>
       </c>
       <c r="J59" t="n">
-        <v>23268534.08</v>
+        <v>23328547.07</v>
       </c>
     </row>
     <row r="60">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5518280.7</v>
+        <v>6621414.01</v>
       </c>
       <c r="F60" t="n">
-        <v>5339696.41</v>
+        <v>6175346.52</v>
       </c>
       <c r="G60" t="n">
-        <v>5253527.05</v>
+        <v>6089212.98</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>82865181.3</v>
+        <v>84754428.59</v>
       </c>
       <c r="F61" t="n">
-        <v>36368431.49</v>
+        <v>38569432.36</v>
       </c>
       <c r="G61" t="n">
-        <v>34538568.93</v>
+        <v>36415573.37</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>56779446.78</v>
+        <v>56956632.42</v>
       </c>
       <c r="J61" t="n">
-        <v>56839446.88</v>
+        <v>57016632.52</v>
       </c>
     </row>
     <row r="62">
@@ -2622,22 +2622,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103843078.63</v>
+        <v>138392604.49</v>
       </c>
       <c r="F62" t="n">
-        <v>93683920.23</v>
+        <v>127959548.45</v>
       </c>
       <c r="G62" t="n">
-        <v>65553661.76</v>
+        <v>118718974.03</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
       </c>
       <c r="I62" t="n">
-        <v>620274.23</v>
+        <v>634111.73</v>
       </c>
       <c r="J62" t="n">
-        <v>939890.1</v>
+        <v>953727.6</v>
       </c>
     </row>
     <row r="63">
@@ -2658,22 +2658,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>59439299.8</v>
+        <v>75385060.89</v>
       </c>
       <c r="F63" t="n">
-        <v>23889261.09</v>
+        <v>31071725.22</v>
       </c>
       <c r="G63" t="n">
-        <v>22612315.81</v>
+        <v>30097740.89</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>23205532.54</v>
+        <v>31064758.23</v>
       </c>
       <c r="J63" t="n">
-        <v>23205532.54</v>
+        <v>31064758.23</v>
       </c>
     </row>
     <row r="64">
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>79760646.64</v>
+        <v>161155496.82</v>
       </c>
       <c r="F64" t="n">
-        <v>76531903.53</v>
+        <v>154910821.45</v>
       </c>
       <c r="G64" t="n">
-        <v>64806500.18</v>
+        <v>111936465.74</v>
       </c>
       <c r="H64" t="n">
-        <v>11842578.76</v>
+        <v>11942560.14</v>
       </c>
       <c r="I64" t="n">
-        <v>14102752.39</v>
+        <v>14366153</v>
       </c>
       <c r="J64" t="n">
-        <v>25945331.15</v>
+        <v>26308713.14</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8664018022.610001</v>
+        <v>10132639390.55</v>
       </c>
       <c r="F65" t="n">
-        <v>8322194732.45</v>
+        <v>9830740044.219999</v>
       </c>
       <c r="G65" t="n">
-        <v>8239564659.31</v>
+        <v>9758959298.940001</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>132456860.67</v>
+        <v>138191249.17</v>
       </c>
       <c r="J65" t="n">
-        <v>328364287.14</v>
+        <v>334098675.64</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>805041968.35</v>
+        <v>933574214.5</v>
       </c>
       <c r="F66" t="n">
-        <v>725780634.59</v>
+        <v>861406910.42</v>
       </c>
       <c r="G66" t="n">
-        <v>708195519.15</v>
+        <v>838574610.21</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>53836568.43</v>
+        <v>54991278.22</v>
       </c>
       <c r="J66" t="n">
-        <v>61502012.64</v>
+        <v>62656722.43</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>297637267.84</v>
+        <v>341516662.63</v>
       </c>
       <c r="F67" t="n">
-        <v>286218181.32</v>
+        <v>336128273.22</v>
       </c>
       <c r="G67" t="n">
-        <v>243379380.24</v>
+        <v>308181174.55</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>595320093.95</v>
+        <v>815498958.28</v>
       </c>
       <c r="F68" t="n">
-        <v>575373025.97</v>
+        <v>785272706.38</v>
       </c>
       <c r="G68" t="n">
-        <v>501647281.47</v>
+        <v>749636283.3</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>24497708.44</v>
+        <v>24738622.16</v>
       </c>
       <c r="J68" t="n">
-        <v>40341516.21</v>
+        <v>40582429.93</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2198972195.57</v>
+        <v>2435816624.41</v>
       </c>
       <c r="F69" t="n">
-        <v>1939524868.42</v>
+        <v>2191465584.86</v>
       </c>
       <c r="G69" t="n">
-        <v>1912787373.06</v>
+        <v>2158203230.68</v>
       </c>
       <c r="H69" t="n">
         <v>14513945.66</v>
       </c>
       <c r="I69" t="n">
-        <v>123227122.58</v>
+        <v>125978175.75</v>
       </c>
       <c r="J69" t="n">
-        <v>137741068.24</v>
+        <v>140492121.41</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>98201227.43000001</v>
+        <v>120063357.71</v>
       </c>
       <c r="F70" t="n">
-        <v>90223934.06</v>
+        <v>112175567.22</v>
       </c>
       <c r="G70" t="n">
-        <v>87531113.01000001</v>
+        <v>103755494.69</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>347898507.16</v>
+        <v>368097605.23</v>
       </c>
       <c r="F71" t="n">
-        <v>273870857.62</v>
+        <v>294090860.29</v>
       </c>
       <c r="G71" t="n">
-        <v>237837918.39</v>
+        <v>270513568.29</v>
       </c>
       <c r="H71" t="n">
         <v>28757634.3</v>
       </c>
       <c r="I71" t="n">
-        <v>66276910.43</v>
+        <v>66619973.53</v>
       </c>
       <c r="J71" t="n">
-        <v>95034544.73</v>
+        <v>95377607.83</v>
       </c>
     </row>
     <row r="72">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>7248002.09</v>
+        <v>8508089.140000001</v>
       </c>
       <c r="F72" t="n">
-        <v>6783613.16</v>
+        <v>7593127.13</v>
       </c>
       <c r="G72" t="n">
-        <v>5878301.7</v>
+        <v>6657416.11</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>179150781.22</v>
+        <v>216207943.6</v>
       </c>
       <c r="F73" t="n">
-        <v>163123253.36</v>
+        <v>192456407.25</v>
       </c>
       <c r="G73" t="n">
-        <v>159757200.72</v>
+        <v>187399624.09</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
       </c>
       <c r="I73" t="n">
-        <v>18466096.57</v>
+        <v>19670832.81</v>
       </c>
       <c r="J73" t="n">
-        <v>18678507.51</v>
+        <v>19883243.75</v>
       </c>
     </row>
     <row r="74">
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>210294308.69</v>
+        <v>250113890.08</v>
       </c>
       <c r="F74" t="n">
-        <v>195066164.82</v>
+        <v>228620404.29</v>
       </c>
       <c r="G74" t="n">
-        <v>190215982.12</v>
+        <v>224084316.44</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>21692603.48</v>
+        <v>21984509.81</v>
       </c>
       <c r="J74" t="n">
-        <v>21823057.26</v>
+        <v>22114963.59</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3852271.18</v>
+        <v>4073927.92</v>
       </c>
       <c r="F75" t="n">
-        <v>2783906.47</v>
+        <v>3260945.81</v>
       </c>
       <c r="G75" t="n">
-        <v>2584163.88</v>
+        <v>3024040.13</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>617806106.28</v>
+        <v>639898654.39</v>
       </c>
       <c r="F2" t="n">
-        <v>592945182.22</v>
+        <v>599944084.58</v>
       </c>
       <c r="G2" t="n">
-        <v>502096123.26</v>
+        <v>518716242.75</v>
       </c>
       <c r="H2" t="n">
-        <v>214250064.35</v>
+        <v>214279936.92</v>
       </c>
       <c r="I2" t="n">
-        <v>2470511.47</v>
+        <v>2470960.14</v>
       </c>
       <c r="J2" t="n">
-        <v>216720575.82</v>
+        <v>216750897.06</v>
       </c>
     </row>
     <row r="3">
@@ -537,10 +537,10 @@
         <v>3551203.43</v>
       </c>
       <c r="F3" t="n">
-        <v>3409454.44</v>
+        <v>3431157.26</v>
       </c>
       <c r="G3" t="n">
-        <v>3240962.44</v>
+        <v>3268273.21</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4104662.83</v>
+        <v>4115236.42</v>
       </c>
       <c r="F4" t="n">
-        <v>2110495.29</v>
+        <v>2152810.24</v>
       </c>
       <c r="G4" t="n">
-        <v>1797202.17</v>
+        <v>1817080.31</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11612415.15</v>
+        <v>11663287.32</v>
       </c>
       <c r="F5" t="n">
-        <v>10322467.96</v>
+        <v>10373111.82</v>
       </c>
       <c r="G5" t="n">
-        <v>10245394.62</v>
+        <v>10295966</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27794225.72</v>
+        <v>27794584.98</v>
       </c>
       <c r="F6" t="n">
-        <v>18053785.27</v>
+        <v>18072929</v>
       </c>
       <c r="G6" t="n">
-        <v>16508612.73</v>
+        <v>16730039.18</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1040966458.63</v>
+        <v>1046217159.32</v>
       </c>
       <c r="F7" t="n">
-        <v>1006441325.88</v>
+        <v>1015359329.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1004878559.2</v>
+        <v>1011384852</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>32552462.46</v>
+        <v>33859186.28</v>
       </c>
       <c r="J7" t="n">
-        <v>38599266.34</v>
+        <v>39905990.16</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34787350.53</v>
+        <v>34789509.94</v>
       </c>
       <c r="F8" t="n">
-        <v>34621511.95</v>
+        <v>34699365.68</v>
       </c>
       <c r="G8" t="n">
-        <v>34547507.17</v>
+        <v>34550492.72</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1083963872.32</v>
+        <v>1116438285.94</v>
       </c>
       <c r="F9" t="n">
-        <v>582499745.65</v>
+        <v>588993231.53</v>
       </c>
       <c r="G9" t="n">
-        <v>556409451.3</v>
+        <v>567667070.37</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>270507894.5</v>
+        <v>275856201.43</v>
       </c>
       <c r="J9" t="n">
-        <v>283939542.05</v>
+        <v>289287848.98</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48450358.23</v>
+        <v>49284708.23</v>
       </c>
       <c r="F10" t="n">
-        <v>43255573.74</v>
+        <v>43263774.42</v>
       </c>
       <c r="G10" t="n">
-        <v>35221082.21</v>
+        <v>35978168.71</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>509509748.28</v>
+        <v>759509748.28</v>
       </c>
       <c r="F11" t="n">
         <v>444147454.03</v>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>145843538.13</v>
+        <v>180266897.78</v>
       </c>
       <c r="F13" t="n">
-        <v>145843538.13</v>
+        <v>180266897.78</v>
       </c>
       <c r="G13" t="n">
-        <v>145843538.13</v>
+        <v>180266897.78</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12769086.04</v>
+        <v>15493154.83</v>
       </c>
       <c r="F14" t="n">
-        <v>12769086.04</v>
+        <v>15493154.83</v>
       </c>
       <c r="G14" t="n">
-        <v>12769086.04</v>
+        <v>15493154.83</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -948,13 +948,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>57931533.11</v>
+        <v>71727903.56999999</v>
       </c>
       <c r="F15" t="n">
-        <v>57931533.11</v>
+        <v>71727903.56999999</v>
       </c>
       <c r="G15" t="n">
-        <v>57931533.11</v>
+        <v>71727903.56999999</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12812866.45</v>
+        <v>12933171.98</v>
       </c>
       <c r="F16" t="n">
-        <v>11168321.81</v>
+        <v>11449919.15</v>
       </c>
       <c r="G16" t="n">
-        <v>10869424.55</v>
+        <v>10979489.91</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1017,10 +1017,10 @@
         <v>238804</v>
       </c>
       <c r="F17" t="n">
-        <v>151205.25</v>
+        <v>181355.46</v>
       </c>
       <c r="G17" t="n">
-        <v>142902.15</v>
+        <v>171391.74</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2275080.17</v>
+        <v>2360568.08</v>
       </c>
       <c r="F18" t="n">
-        <v>2215164.86</v>
+        <v>2311488.79</v>
       </c>
       <c r="G18" t="n">
-        <v>2134468.54</v>
+        <v>2211788.78</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>306172748.78</v>
+        <v>307557161.82</v>
       </c>
       <c r="F19" t="n">
-        <v>245877095.59</v>
+        <v>253193758.03</v>
       </c>
       <c r="G19" t="n">
-        <v>225832606.4</v>
+        <v>242778399.5</v>
       </c>
       <c r="H19" t="n">
-        <v>3369052.62</v>
+        <v>3369120.12</v>
       </c>
       <c r="I19" t="n">
-        <v>3674484.75</v>
+        <v>3676734.75</v>
       </c>
       <c r="J19" t="n">
-        <v>7043537.37</v>
+        <v>7045854.87</v>
       </c>
     </row>
     <row r="20">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>32017496.6</v>
+        <v>33206450.26</v>
       </c>
       <c r="F20" t="n">
-        <v>25785864.81</v>
+        <v>26243115.76</v>
       </c>
       <c r="G20" t="n">
-        <v>25012081.73</v>
+        <v>25536988.16</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5201831.56</v>
+        <v>5621583.22</v>
       </c>
       <c r="F22" t="n">
-        <v>2218577.25</v>
+        <v>2238836.81</v>
       </c>
       <c r="G22" t="n">
-        <v>2153703.15</v>
+        <v>2217452.5</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>36498337.17</v>
+        <v>38658456.26</v>
       </c>
       <c r="F23" t="n">
-        <v>36111682.65</v>
+        <v>37937563.2</v>
       </c>
       <c r="G23" t="n">
-        <v>35069263.25</v>
+        <v>36385542.73</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>75217619.45999999</v>
+        <v>113032762.61</v>
       </c>
       <c r="F24" t="n">
-        <v>60628266.46</v>
+        <v>65826370.06</v>
       </c>
       <c r="G24" t="n">
-        <v>58684656.63</v>
+        <v>64680362.4</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8824566137.58</v>
+        <v>9105181172.219999</v>
       </c>
       <c r="F27" t="n">
-        <v>6706842855.7</v>
+        <v>7073877623.45</v>
       </c>
       <c r="G27" t="n">
-        <v>6498287753.94</v>
+        <v>6892678352.18</v>
       </c>
       <c r="H27" t="n">
-        <v>348314152.22</v>
+        <v>367754071.26</v>
       </c>
       <c r="I27" t="n">
-        <v>456191694.34</v>
+        <v>484384172.2</v>
       </c>
       <c r="J27" t="n">
-        <v>804505846.5599999</v>
+        <v>852138243.46</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20944673.57</v>
+        <v>22427765.26</v>
       </c>
       <c r="F28" t="n">
-        <v>6336947.74</v>
+        <v>6535693.75</v>
       </c>
       <c r="G28" t="n">
-        <v>4840838.18</v>
+        <v>6114075.6</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>30575533.78</v>
+        <v>30987691.46</v>
       </c>
       <c r="J28" t="n">
-        <v>35162303.26</v>
+        <v>35574460.94</v>
       </c>
     </row>
     <row r="29">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>377600.11</v>
+        <v>392822.81</v>
       </c>
       <c r="F29" t="n">
-        <v>117731.93</v>
+        <v>120089.23</v>
       </c>
       <c r="G29" t="n">
-        <v>116134.11</v>
+        <v>118439.46</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8828303225.52</v>
+        <v>8881091674.26</v>
       </c>
       <c r="F30" t="n">
-        <v>8818625566.950001</v>
+        <v>8876246188.32</v>
       </c>
       <c r="G30" t="n">
-        <v>8818498332.280001</v>
+        <v>8876116628.75</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31440662.01</v>
+        <v>31440318.89</v>
       </c>
       <c r="F31" t="n">
-        <v>28792170.19</v>
+        <v>29001009.85</v>
       </c>
       <c r="G31" t="n">
-        <v>28359213.79</v>
+        <v>28511547.93</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>1960334.51</v>
+        <v>1962831.19</v>
       </c>
       <c r="J31" t="n">
-        <v>1960553.44</v>
+        <v>1963050.12</v>
       </c>
     </row>
     <row r="32">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1289879070.22</v>
+        <v>1309934310.36</v>
       </c>
       <c r="F32" t="n">
-        <v>1168794609.32</v>
+        <v>1201419646.95</v>
       </c>
       <c r="G32" t="n">
-        <v>1124118034.73</v>
+        <v>1138022713.83</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>91686642.43000001</v>
+        <v>92228152.40000001</v>
       </c>
       <c r="J32" t="n">
-        <v>97727773.54000001</v>
+        <v>98269283.51000001</v>
       </c>
     </row>
     <row r="33">
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>310478.82</v>
+        <v>340935.7</v>
       </c>
       <c r="F33" t="n">
-        <v>295186.81</v>
+        <v>325643.69</v>
       </c>
       <c r="G33" t="n">
-        <v>272249.19</v>
+        <v>297998.06</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,13 +1620,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>34541537.36</v>
+        <v>37411143.52</v>
       </c>
       <c r="F34" t="n">
-        <v>32902758.88</v>
+        <v>33230493.71</v>
       </c>
       <c r="G34" t="n">
-        <v>32305422.73</v>
+        <v>32369981.05</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>432646942.18</v>
+        <v>438585972.43</v>
       </c>
       <c r="F36" t="n">
-        <v>160660901.26</v>
+        <v>163432525.09</v>
       </c>
       <c r="G36" t="n">
-        <v>148272784.6</v>
+        <v>150772789.3</v>
       </c>
       <c r="H36" t="n">
         <v>53631506.45</v>
@@ -1731,10 +1731,10 @@
         <v>2709713.46</v>
       </c>
       <c r="F37" t="n">
-        <v>2564258.12</v>
+        <v>2581432.79</v>
       </c>
       <c r="G37" t="n">
-        <v>2515632.69</v>
+        <v>2531118.29</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>63097212.7</v>
+        <v>94331218.25</v>
       </c>
       <c r="F38" t="n">
-        <v>59757125.84</v>
+        <v>59759279.11</v>
       </c>
       <c r="G38" t="n">
-        <v>59734319.6</v>
+        <v>59736472.87</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>236626077.9</v>
+        <v>245468044.22</v>
       </c>
       <c r="F39" t="n">
-        <v>171677093.31</v>
+        <v>182850954.98</v>
       </c>
       <c r="G39" t="n">
-        <v>135563992.68</v>
+        <v>150135142.32</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>133337424.34</v>
+        <v>133390851.22</v>
       </c>
       <c r="J39" t="n">
-        <v>140524697.41</v>
+        <v>140578124.29</v>
       </c>
     </row>
     <row r="40">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>64369439.59</v>
+        <v>65833201.19</v>
       </c>
       <c r="F40" t="n">
-        <v>33269291.04</v>
+        <v>34579263.89</v>
       </c>
       <c r="G40" t="n">
-        <v>29837781.14</v>
+        <v>32838130.02</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>55506641.22</v>
+        <v>56174452.45</v>
       </c>
       <c r="F41" t="n">
-        <v>25493362.59</v>
+        <v>26664537.57</v>
       </c>
       <c r="G41" t="n">
-        <v>23322644.12</v>
+        <v>24116274.2</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3807924827.02</v>
+        <v>5684372611.7</v>
       </c>
       <c r="F42" t="n">
-        <v>3370156381.14</v>
+        <v>5035253969.73</v>
       </c>
       <c r="G42" t="n">
-        <v>3322123781.54</v>
+        <v>4987221370.13</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>201870793.4</v>
+        <v>210678768.72</v>
       </c>
       <c r="F43" t="n">
-        <v>170596137.22</v>
+        <v>177189985.97</v>
       </c>
       <c r="G43" t="n">
-        <v>166440428.9</v>
+        <v>169792057.4</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>23533810.38</v>
+        <v>23600115.01</v>
       </c>
       <c r="J43" t="n">
-        <v>26881885.66</v>
+        <v>26948190.29</v>
       </c>
     </row>
     <row r="44">
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>28964520.89</v>
+        <v>33073921.07</v>
       </c>
       <c r="F44" t="n">
-        <v>17247931.64</v>
+        <v>22333562.32</v>
       </c>
       <c r="G44" t="n">
-        <v>16084636.09</v>
+        <v>21919712.7</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>18861918.75</v>
+        <v>18937966.13</v>
       </c>
       <c r="J44" t="n">
-        <v>19883705.68</v>
+        <v>19959753.06</v>
       </c>
     </row>
     <row r="45">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105857386.4</v>
+        <v>109409013.88</v>
       </c>
       <c r="F45" t="n">
-        <v>102661981.29</v>
+        <v>105620150.9</v>
       </c>
       <c r="G45" t="n">
-        <v>98212839.89</v>
+        <v>99780274.81999999</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>7272577.03</v>
+        <v>7291001.14</v>
       </c>
       <c r="J45" t="n">
-        <v>7759109.68</v>
+        <v>7777533.79</v>
       </c>
     </row>
     <row r="46">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12298666.91</v>
+        <v>12895748.29</v>
       </c>
       <c r="F46" t="n">
-        <v>9724766.84</v>
+        <v>10032185.06</v>
       </c>
       <c r="G46" t="n">
-        <v>9205375.300000001</v>
+        <v>9233670.1</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26492216.78</v>
+        <v>26753552.45</v>
       </c>
       <c r="F47" t="n">
-        <v>24238780.59</v>
+        <v>24571789.73</v>
       </c>
       <c r="G47" t="n">
-        <v>22800673.45</v>
+        <v>22927063.82</v>
       </c>
       <c r="H47" t="n">
         <v>5234428.46</v>
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>152296583.13</v>
+        <v>152873401.13</v>
       </c>
       <c r="F48" t="n">
-        <v>147349684.62</v>
+        <v>148186995.68</v>
       </c>
       <c r="G48" t="n">
-        <v>146327676.79</v>
+        <v>146680754.03</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4718709.47</v>
+        <v>4752371.75</v>
       </c>
       <c r="J48" t="n">
-        <v>5228623.39</v>
+        <v>5262285.67</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>18295588.41</v>
+        <v>18307051.98</v>
       </c>
       <c r="F49" t="n">
-        <v>17392617.3</v>
+        <v>17770685.26</v>
       </c>
       <c r="G49" t="n">
-        <v>16721311.53</v>
+        <v>16990385.93</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1097026982.54</v>
+        <v>1135693300.67</v>
       </c>
       <c r="F50" t="n">
-        <v>766828388.15</v>
+        <v>804141265.5</v>
       </c>
       <c r="G50" t="n">
-        <v>747877094.64</v>
+        <v>782720301.6900001</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>192239471</v>
+        <v>192658636.01</v>
       </c>
       <c r="J50" t="n">
-        <v>192336368.37</v>
+        <v>192755533.38</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1580488081.37</v>
+        <v>1628320841</v>
       </c>
       <c r="F51" t="n">
-        <v>1564011752.29</v>
+        <v>1606673465.53</v>
       </c>
       <c r="G51" t="n">
-        <v>1537079491.69</v>
+        <v>1578909099.25</v>
       </c>
       <c r="H51" t="n">
-        <v>19328798.48</v>
+        <v>19329128.48</v>
       </c>
       <c r="I51" t="n">
-        <v>34444083.68</v>
+        <v>34488062.3</v>
       </c>
       <c r="J51" t="n">
-        <v>53772882.16</v>
+        <v>53817190.78</v>
       </c>
     </row>
     <row r="52">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>20446769.11</v>
+        <v>20683416.51</v>
       </c>
       <c r="F52" t="n">
-        <v>18572720.67</v>
+        <v>18574074.75</v>
       </c>
       <c r="G52" t="n">
-        <v>17527883.08</v>
+        <v>17529098.48</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1702938.37</v>
+        <v>1802865.76</v>
       </c>
       <c r="F53" t="n">
-        <v>1663147.47</v>
+        <v>1671298.28</v>
       </c>
       <c r="G53" t="n">
-        <v>1615160.52</v>
+        <v>1632090.34</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10034001.54</v>
+        <v>10034801.5</v>
       </c>
       <c r="F54" t="n">
-        <v>9524085.189999999</v>
+        <v>9542360.48</v>
       </c>
       <c r="G54" t="n">
-        <v>9461345.289999999</v>
+        <v>9479586.859999999</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1630572693.71</v>
+        <v>1638202970.95</v>
       </c>
       <c r="F56" t="n">
-        <v>1571159754.32</v>
+        <v>1584097186.93</v>
       </c>
       <c r="G56" t="n">
-        <v>1555490264.54</v>
+        <v>1557199832.84</v>
       </c>
       <c r="H56" t="n">
         <v>8940604.800000001</v>
       </c>
       <c r="I56" t="n">
-        <v>31169093.34</v>
+        <v>31217609.18</v>
       </c>
       <c r="J56" t="n">
-        <v>40109698.14</v>
+        <v>40158213.98</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>8707182464.360001</v>
+        <v>8714625943.58</v>
       </c>
       <c r="F57" t="n">
-        <v>8524889908.73</v>
+        <v>8538643866.9</v>
       </c>
       <c r="G57" t="n">
-        <v>8489555011.67</v>
+        <v>8498541403.67</v>
       </c>
       <c r="H57" t="n">
         <v>18529479.85</v>
       </c>
       <c r="I57" t="n">
-        <v>143886118.97</v>
+        <v>146946692.83</v>
       </c>
       <c r="J57" t="n">
-        <v>162415598.82</v>
+        <v>165476172.68</v>
       </c>
     </row>
     <row r="58">
@@ -2478,22 +2478,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4613035.78</v>
+        <v>4643257.47</v>
       </c>
       <c r="F58" t="n">
-        <v>4529798.83</v>
+        <v>4600211.3</v>
       </c>
       <c r="G58" t="n">
-        <v>4437105.67</v>
+        <v>4481722.55</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
       </c>
       <c r="I58" t="n">
-        <v>214364.3</v>
+        <v>217467.44</v>
       </c>
       <c r="J58" t="n">
-        <v>336771.97</v>
+        <v>339875.11</v>
       </c>
     </row>
     <row r="59">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>303277365.62</v>
+        <v>316999632.66</v>
       </c>
       <c r="F59" t="n">
-        <v>257593836.11</v>
+        <v>273498190.52</v>
       </c>
       <c r="G59" t="n">
-        <v>255964811.56</v>
+        <v>272480474.67</v>
       </c>
       <c r="H59" t="n">
         <v>6876518.16</v>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6621414.01</v>
+        <v>6624422.91</v>
       </c>
       <c r="F60" t="n">
-        <v>6175346.52</v>
+        <v>6395494.92</v>
       </c>
       <c r="G60" t="n">
-        <v>6089212.98</v>
+        <v>6257519.39</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>84754428.59</v>
+        <v>84779766.69</v>
       </c>
       <c r="F61" t="n">
-        <v>38569432.36</v>
+        <v>40670376.46</v>
       </c>
       <c r="G61" t="n">
-        <v>36415573.37</v>
+        <v>36788102.07</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>138392604.49</v>
+        <v>154599229.49</v>
       </c>
       <c r="F62" t="n">
-        <v>127959548.45</v>
+        <v>138619272.91</v>
       </c>
       <c r="G62" t="n">
-        <v>118718974.03</v>
+        <v>132327905.32</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,22 +2658,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>75385060.89</v>
+        <v>81613420.84999999</v>
       </c>
       <c r="F63" t="n">
-        <v>31071725.22</v>
+        <v>40114256.65</v>
       </c>
       <c r="G63" t="n">
-        <v>30097740.89</v>
+        <v>38673869.43</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>31064758.23</v>
+        <v>32246052.17</v>
       </c>
       <c r="J63" t="n">
-        <v>31064758.23</v>
+        <v>32246052.17</v>
       </c>
     </row>
     <row r="64">
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>161155496.82</v>
+        <v>171935655.86</v>
       </c>
       <c r="F64" t="n">
-        <v>154910821.45</v>
+        <v>164166608.24</v>
       </c>
       <c r="G64" t="n">
-        <v>111936465.74</v>
+        <v>159565865.31</v>
       </c>
       <c r="H64" t="n">
         <v>11942560.14</v>
       </c>
       <c r="I64" t="n">
-        <v>14366153</v>
+        <v>14614134.23</v>
       </c>
       <c r="J64" t="n">
-        <v>26308713.14</v>
+        <v>26556694.37</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10132639390.55</v>
+        <v>10252545273.01</v>
       </c>
       <c r="F65" t="n">
-        <v>9830740044.219999</v>
+        <v>9901658093.85</v>
       </c>
       <c r="G65" t="n">
-        <v>9758959298.940001</v>
+        <v>9874527790.139999</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>138191249.17</v>
+        <v>140946088.08</v>
       </c>
       <c r="J65" t="n">
-        <v>334098675.64</v>
+        <v>336853514.55</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>933574214.5</v>
+        <v>935634084.47</v>
       </c>
       <c r="F66" t="n">
-        <v>861406910.42</v>
+        <v>864208931.61</v>
       </c>
       <c r="G66" t="n">
-        <v>838574610.21</v>
+        <v>839471201.26</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>54991278.22</v>
+        <v>55087578.96</v>
       </c>
       <c r="J66" t="n">
-        <v>62656722.43</v>
+        <v>62753023.17</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>341516662.63</v>
+        <v>344217236.8</v>
       </c>
       <c r="F67" t="n">
-        <v>336128273.22</v>
+        <v>339010434.3</v>
       </c>
       <c r="G67" t="n">
-        <v>308181174.55</v>
+        <v>326313783.13</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>815498958.28</v>
+        <v>858785508.98</v>
       </c>
       <c r="F68" t="n">
-        <v>785272706.38</v>
+        <v>830056002.9299999</v>
       </c>
       <c r="G68" t="n">
-        <v>749636283.3</v>
+        <v>812248201.61</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>24738622.16</v>
+        <v>25728583.42</v>
       </c>
       <c r="J68" t="n">
-        <v>40582429.93</v>
+        <v>41572391.19</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2435816624.41</v>
+        <v>2493594592.1</v>
       </c>
       <c r="F69" t="n">
-        <v>2191465584.86</v>
+        <v>2254358063.54</v>
       </c>
       <c r="G69" t="n">
-        <v>2158203230.68</v>
+        <v>2213683465.29</v>
       </c>
       <c r="H69" t="n">
         <v>14513945.66</v>
       </c>
       <c r="I69" t="n">
-        <v>125978175.75</v>
+        <v>125983640.31</v>
       </c>
       <c r="J69" t="n">
-        <v>140492121.41</v>
+        <v>140497585.97</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>120063357.71</v>
+        <v>130610616.83</v>
       </c>
       <c r="F70" t="n">
-        <v>112175567.22</v>
+        <v>124091208.63</v>
       </c>
       <c r="G70" t="n">
-        <v>103755494.69</v>
+        <v>117893153.95</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>368097605.23</v>
+        <v>374119117.96</v>
       </c>
       <c r="F71" t="n">
-        <v>294090860.29</v>
+        <v>298693956.04</v>
       </c>
       <c r="G71" t="n">
-        <v>270513568.29</v>
+        <v>271925794.86</v>
       </c>
       <c r="H71" t="n">
-        <v>28757634.3</v>
+        <v>28800758.26</v>
       </c>
       <c r="I71" t="n">
-        <v>66619973.53</v>
+        <v>67522747.98</v>
       </c>
       <c r="J71" t="n">
-        <v>95377607.83</v>
+        <v>96323506.23999999</v>
       </c>
     </row>
     <row r="72">
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8508089.140000001</v>
+        <v>8716530.76</v>
       </c>
       <c r="F72" t="n">
-        <v>7593127.13</v>
+        <v>8071345.76</v>
       </c>
       <c r="G72" t="n">
         <v>6657416.11</v>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>216207943.6</v>
+        <v>222143811.82</v>
       </c>
       <c r="F73" t="n">
-        <v>192456407.25</v>
+        <v>194293939.32</v>
       </c>
       <c r="G73" t="n">
-        <v>187399624.09</v>
+        <v>189172769.51</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>250113890.08</v>
+        <v>252771673.8</v>
       </c>
       <c r="F74" t="n">
-        <v>228620404.29</v>
+        <v>230681689.58</v>
       </c>
       <c r="G74" t="n">
-        <v>224084316.44</v>
+        <v>225940984.11</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>21984509.81</v>
+        <v>22690830.13</v>
       </c>
       <c r="J74" t="n">
-        <v>22114963.59</v>
+        <v>22821283.91</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4073927.92</v>
+        <v>4077619.92</v>
       </c>
       <c r="F75" t="n">
-        <v>3260945.81</v>
+        <v>3341835.49</v>
       </c>
       <c r="G75" t="n">
-        <v>3024040.13</v>
+        <v>3098079.16</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>639898654.39</v>
+        <v>664225686.61</v>
       </c>
       <c r="F2" t="n">
-        <v>599944084.58</v>
+        <v>621603077.8099999</v>
       </c>
       <c r="G2" t="n">
-        <v>518716242.75</v>
+        <v>583798076.1</v>
       </c>
       <c r="H2" t="n">
         <v>214279936.92</v>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3551203.43</v>
+        <v>3891073.69</v>
       </c>
       <c r="F3" t="n">
         <v>3431157.26</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4115236.42</v>
+        <v>4434050.13</v>
       </c>
       <c r="F4" t="n">
-        <v>2152810.24</v>
+        <v>2183336.05</v>
       </c>
       <c r="G4" t="n">
-        <v>1817080.31</v>
+        <v>2013652.17</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11663287.32</v>
+        <v>11898942.6</v>
       </c>
       <c r="F5" t="n">
-        <v>10373111.82</v>
+        <v>10597694.7</v>
       </c>
       <c r="G5" t="n">
-        <v>10295966</v>
+        <v>10508136.32</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27794584.98</v>
+        <v>27796942.11</v>
       </c>
       <c r="F6" t="n">
-        <v>18072929</v>
+        <v>19152097.36</v>
       </c>
       <c r="G6" t="n">
-        <v>16730039.18</v>
+        <v>17646073.63</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1046217159.32</v>
+        <v>1053284927.07</v>
       </c>
       <c r="F7" t="n">
-        <v>1015359329.7</v>
+        <v>1016938571.76</v>
       </c>
       <c r="G7" t="n">
-        <v>1011384852</v>
+        <v>1014168292.87</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>33859186.28</v>
+        <v>34431633.72</v>
       </c>
       <c r="J7" t="n">
-        <v>39905990.16</v>
+        <v>40478437.6</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34789509.94</v>
+        <v>35498949.36</v>
       </c>
       <c r="F8" t="n">
-        <v>34699365.68</v>
+        <v>34777438.78</v>
       </c>
       <c r="G8" t="n">
-        <v>34550492.72</v>
+        <v>34699961.24</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1116438285.94</v>
+        <v>1321347993.38</v>
       </c>
       <c r="F9" t="n">
-        <v>588993231.53</v>
+        <v>650123392.29</v>
       </c>
       <c r="G9" t="n">
-        <v>567667070.37</v>
+        <v>575279533.22</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>275856201.43</v>
+        <v>290140336.64</v>
       </c>
       <c r="J9" t="n">
-        <v>289287848.98</v>
+        <v>303571984.19</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49284708.23</v>
+        <v>49561074.78</v>
       </c>
       <c r="F10" t="n">
-        <v>43263774.42</v>
+        <v>43401052.44</v>
       </c>
       <c r="G10" t="n">
-        <v>35978168.71</v>
+        <v>36115402.58</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>759509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>444147454.03</v>
+        <v>446922752.09</v>
       </c>
       <c r="G11" t="n">
-        <v>444143091.26</v>
+        <v>446918389.32</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90894782.2</v>
+        <v>91642668.67</v>
       </c>
       <c r="F12" t="n">
-        <v>89950646.42</v>
+        <v>89955113.42</v>
       </c>
       <c r="G12" t="n">
-        <v>89758303.68000001</v>
+        <v>89939985.48</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12933171.98</v>
+        <v>12946651.75</v>
       </c>
       <c r="F16" t="n">
-        <v>11449919.15</v>
+        <v>11493581.93</v>
       </c>
       <c r="G16" t="n">
-        <v>10979489.91</v>
+        <v>11154570.59</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>238804</v>
+        <v>314027.26</v>
       </c>
       <c r="F17" t="n">
         <v>181355.46</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2360568.08</v>
+        <v>2426090.62</v>
       </c>
       <c r="F18" t="n">
-        <v>2311488.79</v>
+        <v>2325655.45</v>
       </c>
       <c r="G18" t="n">
-        <v>2211788.78</v>
+        <v>2226951.47</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>307557161.82</v>
+        <v>309326618.52</v>
       </c>
       <c r="F19" t="n">
-        <v>253193758.03</v>
+        <v>253910997.42</v>
       </c>
       <c r="G19" t="n">
-        <v>242778399.5</v>
+        <v>247779452.85</v>
       </c>
       <c r="H19" t="n">
         <v>3369120.12</v>
       </c>
       <c r="I19" t="n">
-        <v>3676734.75</v>
+        <v>3677333.75</v>
       </c>
       <c r="J19" t="n">
-        <v>7045854.87</v>
+        <v>7046453.87</v>
       </c>
     </row>
     <row r="20">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33206450.26</v>
+        <v>33487383.07</v>
       </c>
       <c r="F20" t="n">
-        <v>26243115.76</v>
+        <v>26368357.97</v>
       </c>
       <c r="G20" t="n">
-        <v>25536988.16</v>
+        <v>25607496.63</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1598585.9</v>
+        <v>1611008.66</v>
       </c>
       <c r="J20" t="n">
-        <v>2465519.21</v>
+        <v>2477941.97</v>
       </c>
     </row>
     <row r="21">
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>249016.26</v>
+        <v>293494.49</v>
       </c>
       <c r="J21" t="n">
-        <v>249016.26</v>
+        <v>293494.49</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5621583.22</v>
+        <v>7152793.22</v>
       </c>
       <c r="F22" t="n">
-        <v>2238836.81</v>
+        <v>3749492.92</v>
       </c>
       <c r="G22" t="n">
-        <v>2217452.5</v>
+        <v>3327230.57</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>38658456.26</v>
+        <v>39081655.98</v>
       </c>
       <c r="F23" t="n">
-        <v>37937563.2</v>
+        <v>38618320.62</v>
       </c>
       <c r="G23" t="n">
-        <v>36385542.73</v>
+        <v>36991502.18</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>113032762.61</v>
+        <v>114807683.9</v>
       </c>
       <c r="F24" t="n">
-        <v>65826370.06</v>
+        <v>83732564.72</v>
       </c>
       <c r="G24" t="n">
-        <v>64680362.4</v>
+        <v>81210825.62</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1335,10 +1335,10 @@
         <v>6534927.36</v>
       </c>
       <c r="F26" t="n">
-        <v>6499021.15</v>
+        <v>6534927.36</v>
       </c>
       <c r="G26" t="n">
-        <v>6499021.15</v>
+        <v>6534927.36</v>
       </c>
       <c r="H26" t="n">
         <v>360498.89</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9105181172.219999</v>
+        <v>9117221085.01</v>
       </c>
       <c r="F27" t="n">
-        <v>7073877623.45</v>
+        <v>7179012244.16</v>
       </c>
       <c r="G27" t="n">
-        <v>6892678352.18</v>
+        <v>6986430902.91</v>
       </c>
       <c r="H27" t="n">
-        <v>367754071.26</v>
+        <v>377148754.54</v>
       </c>
       <c r="I27" t="n">
-        <v>484384172.2</v>
+        <v>489173403.46</v>
       </c>
       <c r="J27" t="n">
-        <v>852138243.46</v>
+        <v>866322158</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>22427765.26</v>
+        <v>25369038.48</v>
       </c>
       <c r="F28" t="n">
-        <v>6535693.75</v>
+        <v>7171950.66</v>
       </c>
       <c r="G28" t="n">
-        <v>6114075.6</v>
+        <v>6567187.92</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>30987691.46</v>
+        <v>36213393.49</v>
       </c>
       <c r="J28" t="n">
-        <v>35574460.94</v>
+        <v>40800162.97</v>
       </c>
     </row>
     <row r="29">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392822.81</v>
+        <v>392896.59</v>
       </c>
       <c r="F29" t="n">
-        <v>120089.23</v>
+        <v>140653.38</v>
       </c>
       <c r="G29" t="n">
-        <v>118439.46</v>
+        <v>125104.21</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8881091674.26</v>
+        <v>8881697931.040001</v>
       </c>
       <c r="F30" t="n">
-        <v>8876246188.32</v>
+        <v>8876852452.09</v>
       </c>
       <c r="G30" t="n">
-        <v>8876116628.75</v>
+        <v>8876722243.83</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31440318.89</v>
+        <v>31537614.89</v>
       </c>
       <c r="F31" t="n">
-        <v>29001009.85</v>
+        <v>29135635.4</v>
       </c>
       <c r="G31" t="n">
-        <v>28511547.93</v>
+        <v>28824878.85</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>1962831.19</v>
+        <v>1981440.57</v>
       </c>
       <c r="J31" t="n">
-        <v>1963050.12</v>
+        <v>1981659.5</v>
       </c>
     </row>
     <row r="32">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1309934310.36</v>
+        <v>1330136490.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1201419646.95</v>
+        <v>1220391830.03</v>
       </c>
       <c r="G32" t="n">
-        <v>1138022713.83</v>
+        <v>1179249568.89</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>92228152.40000001</v>
+        <v>92478350.93000001</v>
       </c>
       <c r="J32" t="n">
-        <v>98269283.51000001</v>
+        <v>98519482.04000001</v>
       </c>
     </row>
     <row r="33">
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37411143.52</v>
+        <v>37409116.91</v>
       </c>
       <c r="F34" t="n">
-        <v>33230493.71</v>
+        <v>34039216.49</v>
       </c>
       <c r="G34" t="n">
-        <v>32369981.05</v>
+        <v>32479867.03</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
       </c>
       <c r="I34" t="n">
-        <v>1678664.04</v>
+        <v>1813430.58</v>
       </c>
       <c r="J34" t="n">
-        <v>1706352.2</v>
+        <v>1841118.74</v>
       </c>
     </row>
     <row r="35">
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>330494.88</v>
+        <v>403322.88</v>
       </c>
       <c r="J35" t="n">
-        <v>330494.88</v>
+        <v>403322.88</v>
       </c>
     </row>
     <row r="36">
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>438585972.43</v>
+        <v>524766345.95</v>
       </c>
       <c r="F36" t="n">
-        <v>163432525.09</v>
+        <v>180156295.53</v>
       </c>
       <c r="G36" t="n">
         <v>150772789.3</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2709713.46</v>
+        <v>2709900.62</v>
       </c>
       <c r="F37" t="n">
-        <v>2581432.79</v>
+        <v>2600256.76</v>
       </c>
       <c r="G37" t="n">
-        <v>2531118.29</v>
+        <v>2548490.75</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1764,13 +1764,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>94331218.25</v>
+        <v>94331218.23999999</v>
       </c>
       <c r="F38" t="n">
-        <v>59759279.11</v>
+        <v>75298322.3</v>
       </c>
       <c r="G38" t="n">
-        <v>59736472.87</v>
+        <v>75275516.06</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>245468044.22</v>
+        <v>248755217.7</v>
       </c>
       <c r="F39" t="n">
-        <v>182850954.98</v>
+        <v>184565114.56</v>
       </c>
       <c r="G39" t="n">
-        <v>150135142.32</v>
+        <v>171376744.89</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>133390851.22</v>
+        <v>133678547.85</v>
       </c>
       <c r="J39" t="n">
-        <v>140578124.29</v>
+        <v>140865820.92</v>
       </c>
     </row>
     <row r="40">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>65833201.19</v>
+        <v>66092800.35</v>
       </c>
       <c r="F40" t="n">
-        <v>34579263.89</v>
+        <v>38884604.64</v>
       </c>
       <c r="G40" t="n">
-        <v>32838130.02</v>
+        <v>34513436.66</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,22 +1872,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>56174452.45</v>
+        <v>56045634.5</v>
       </c>
       <c r="F41" t="n">
-        <v>26664537.57</v>
+        <v>28506783.77</v>
       </c>
       <c r="G41" t="n">
-        <v>24116274.2</v>
+        <v>25025633.07</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
       </c>
       <c r="I41" t="n">
-        <v>11291437.22</v>
+        <v>11359008.03</v>
       </c>
       <c r="J41" t="n">
-        <v>13094655.34</v>
+        <v>13162226.15</v>
       </c>
     </row>
     <row r="42">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5684372611.7</v>
+        <v>6496445251.75</v>
       </c>
       <c r="F42" t="n">
-        <v>5035253969.73</v>
+        <v>5295387364.22</v>
       </c>
       <c r="G42" t="n">
-        <v>4987221370.13</v>
+        <v>5021071903.88</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210678768.72</v>
+        <v>211903964.11</v>
       </c>
       <c r="F43" t="n">
-        <v>177189985.97</v>
+        <v>178891955.08</v>
       </c>
       <c r="G43" t="n">
-        <v>169792057.4</v>
+        <v>171288451.4</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>33073921.07</v>
+        <v>34373540.34</v>
       </c>
       <c r="F44" t="n">
-        <v>22333562.32</v>
+        <v>24333444.23</v>
       </c>
       <c r="G44" t="n">
-        <v>21919712.7</v>
+        <v>23896950.11</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>18937966.13</v>
+        <v>19204694.32</v>
       </c>
       <c r="J44" t="n">
-        <v>19959753.06</v>
+        <v>20226481.25</v>
       </c>
     </row>
     <row r="45">
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>109409013.88</v>
+        <v>110324603.22</v>
       </c>
       <c r="F45" t="n">
-        <v>105620150.9</v>
+        <v>107485484.02</v>
       </c>
       <c r="G45" t="n">
-        <v>99780274.81999999</v>
+        <v>101238418.17</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12895748.29</v>
+        <v>12950101.2</v>
       </c>
       <c r="F46" t="n">
-        <v>10032185.06</v>
+        <v>10081233.64</v>
       </c>
       <c r="G46" t="n">
-        <v>9233670.1</v>
+        <v>9755547.960000001</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26753552.45</v>
+        <v>26865020.91</v>
       </c>
       <c r="F47" t="n">
-        <v>24571789.73</v>
+        <v>24726752.88</v>
       </c>
       <c r="G47" t="n">
-        <v>22927063.82</v>
+        <v>23226737.61</v>
       </c>
       <c r="H47" t="n">
-        <v>5234428.46</v>
+        <v>6104162.13</v>
       </c>
       <c r="I47" t="n">
         <v>10971227.93</v>
       </c>
       <c r="J47" t="n">
-        <v>16205656.39</v>
+        <v>17075390.06</v>
       </c>
     </row>
     <row r="48">
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>152873401.13</v>
+        <v>153519167.35</v>
       </c>
       <c r="F48" t="n">
-        <v>148186995.68</v>
+        <v>148999529.44</v>
       </c>
       <c r="G48" t="n">
-        <v>146680754.03</v>
+        <v>148000838.47</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4752371.75</v>
+        <v>4824663.77</v>
       </c>
       <c r="J48" t="n">
-        <v>5262285.67</v>
+        <v>5334577.69</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>18307051.98</v>
+        <v>18345283.91</v>
       </c>
       <c r="F49" t="n">
-        <v>17770685.26</v>
+        <v>17872884.86</v>
       </c>
       <c r="G49" t="n">
-        <v>16990385.93</v>
+        <v>17091783.45</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1135693300.67</v>
+        <v>1159064644.16</v>
       </c>
       <c r="F50" t="n">
-        <v>804141265.5</v>
+        <v>828971698.41</v>
       </c>
       <c r="G50" t="n">
-        <v>782720301.6900001</v>
+        <v>808247938.1</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>192658636.01</v>
+        <v>192923339.47</v>
       </c>
       <c r="J50" t="n">
-        <v>192755533.38</v>
+        <v>193020236.84</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1628320841</v>
+        <v>1644961689.62</v>
       </c>
       <c r="F51" t="n">
-        <v>1606673465.53</v>
+        <v>1614638864.63</v>
       </c>
       <c r="G51" t="n">
-        <v>1578909099.25</v>
+        <v>1589712527.08</v>
       </c>
       <c r="H51" t="n">
-        <v>19329128.48</v>
+        <v>19331338.95</v>
       </c>
       <c r="I51" t="n">
-        <v>34488062.3</v>
+        <v>34491941.89</v>
       </c>
       <c r="J51" t="n">
-        <v>53817190.78</v>
+        <v>53823280.84</v>
       </c>
     </row>
     <row r="52">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>20683416.51</v>
+        <v>22688145.11</v>
       </c>
       <c r="F52" t="n">
-        <v>18574074.75</v>
+        <v>19272108.71</v>
       </c>
       <c r="G52" t="n">
-        <v>17529098.48</v>
+        <v>18008364.46</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1802865.76</v>
+        <v>1802948.19</v>
       </c>
       <c r="F53" t="n">
-        <v>1671298.28</v>
+        <v>1671484.03</v>
       </c>
       <c r="G53" t="n">
-        <v>1632090.34</v>
+        <v>1632274.92</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10034801.5</v>
+        <v>10092999.89</v>
       </c>
       <c r="F54" t="n">
-        <v>9542360.48</v>
+        <v>9694580.74</v>
       </c>
       <c r="G54" t="n">
-        <v>9479586.859999999</v>
+        <v>9619774.23</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12978755.64</v>
+        <v>12979747.5</v>
       </c>
       <c r="F55" t="n">
-        <v>12978755.64</v>
+        <v>12979747.5</v>
       </c>
       <c r="G55" t="n">
         <v>12978755.64</v>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1638202970.95</v>
+        <v>1642559949.72</v>
       </c>
       <c r="F56" t="n">
-        <v>1584097186.93</v>
+        <v>1586713117.37</v>
       </c>
       <c r="G56" t="n">
-        <v>1557199832.84</v>
+        <v>1573272769.25</v>
       </c>
       <c r="H56" t="n">
         <v>8940604.800000001</v>
       </c>
       <c r="I56" t="n">
-        <v>31217609.18</v>
+        <v>31635193.9</v>
       </c>
       <c r="J56" t="n">
-        <v>40158213.98</v>
+        <v>40575798.7</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>8714625943.58</v>
+        <v>8739629305.379999</v>
       </c>
       <c r="F57" t="n">
-        <v>8538643866.9</v>
+        <v>8548037679.96</v>
       </c>
       <c r="G57" t="n">
-        <v>8498541403.67</v>
+        <v>8528023820.54</v>
       </c>
       <c r="H57" t="n">
-        <v>18529479.85</v>
+        <v>18536120.52</v>
       </c>
       <c r="I57" t="n">
-        <v>146946692.83</v>
+        <v>169661861.1</v>
       </c>
       <c r="J57" t="n">
-        <v>165476172.68</v>
+        <v>188197981.62</v>
       </c>
     </row>
     <row r="58">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4643257.47</v>
+        <v>4642757.47</v>
       </c>
       <c r="F58" t="n">
-        <v>4600211.3</v>
+        <v>4608967.31</v>
       </c>
       <c r="G58" t="n">
-        <v>4481722.55</v>
+        <v>4507133.94</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>316999632.66</v>
+        <v>315680365.78</v>
       </c>
       <c r="F59" t="n">
-        <v>273498190.52</v>
+        <v>273800527.16</v>
       </c>
       <c r="G59" t="n">
-        <v>272480474.67</v>
+        <v>272770908.63</v>
       </c>
       <c r="H59" t="n">
         <v>6876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>16452028.91</v>
+        <v>16547905.35</v>
       </c>
       <c r="J59" t="n">
-        <v>23328547.07</v>
+        <v>23424423.51</v>
       </c>
     </row>
     <row r="60">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6624422.91</v>
+        <v>6698868.92</v>
       </c>
       <c r="F60" t="n">
-        <v>6395494.92</v>
+        <v>6422750.9</v>
       </c>
       <c r="G60" t="n">
-        <v>6257519.39</v>
+        <v>6317502.57</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>84779766.69</v>
+        <v>84817942.41</v>
       </c>
       <c r="F61" t="n">
-        <v>40670376.46</v>
+        <v>46940849.61</v>
       </c>
       <c r="G61" t="n">
-        <v>36788102.07</v>
+        <v>38765895.36</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>56956632.42</v>
+        <v>58835415.36</v>
       </c>
       <c r="J61" t="n">
-        <v>57016632.52</v>
+        <v>58895415.46</v>
       </c>
     </row>
     <row r="62">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>154599229.49</v>
+        <v>157507925.6</v>
       </c>
       <c r="F62" t="n">
-        <v>138619272.91</v>
+        <v>150357749.81</v>
       </c>
       <c r="G62" t="n">
-        <v>132327905.32</v>
+        <v>144979947.47</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,22 +2658,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>81613420.84999999</v>
+        <v>280021179.19</v>
       </c>
       <c r="F63" t="n">
-        <v>40114256.65</v>
+        <v>48877359.16</v>
       </c>
       <c r="G63" t="n">
-        <v>38673869.43</v>
+        <v>47544090.14</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>32246052.17</v>
+        <v>32623825.04</v>
       </c>
       <c r="J63" t="n">
-        <v>32246052.17</v>
+        <v>32623825.04</v>
       </c>
     </row>
     <row r="64">
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>171935655.86</v>
+        <v>173142729.59</v>
       </c>
       <c r="F64" t="n">
-        <v>164166608.24</v>
+        <v>164889838.37</v>
       </c>
       <c r="G64" t="n">
-        <v>159565865.31</v>
+        <v>160194242.56</v>
       </c>
       <c r="H64" t="n">
         <v>11942560.14</v>
       </c>
       <c r="I64" t="n">
-        <v>14614134.23</v>
+        <v>14809012.55</v>
       </c>
       <c r="J64" t="n">
-        <v>26556694.37</v>
+        <v>26751572.69</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10252545273.01</v>
+        <v>10521912708.14</v>
       </c>
       <c r="F65" t="n">
-        <v>9901658093.85</v>
+        <v>10059312313.93</v>
       </c>
       <c r="G65" t="n">
-        <v>9874527790.139999</v>
+        <v>9943851547.33</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>140946088.08</v>
+        <v>143083334.23</v>
       </c>
       <c r="J65" t="n">
-        <v>336853514.55</v>
+        <v>338990760.7</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>935634084.47</v>
+        <v>941703954.67</v>
       </c>
       <c r="F66" t="n">
-        <v>864208931.61</v>
+        <v>872673218.6799999</v>
       </c>
       <c r="G66" t="n">
-        <v>839471201.26</v>
+        <v>852444523.0700001</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>55087578.96</v>
+        <v>55298255.33</v>
       </c>
       <c r="J66" t="n">
-        <v>62753023.17</v>
+        <v>62963699.54</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>344217236.8</v>
+        <v>345046152.76</v>
       </c>
       <c r="F67" t="n">
-        <v>339010434.3</v>
+        <v>340430192.75</v>
       </c>
       <c r="G67" t="n">
-        <v>326313783.13</v>
+        <v>328849014.68</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>858785508.98</v>
+        <v>858873959.85</v>
       </c>
       <c r="F68" t="n">
-        <v>830056002.9299999</v>
+        <v>830928001.16</v>
       </c>
       <c r="G68" t="n">
-        <v>812248201.61</v>
+        <v>812796777.73</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>25728583.42</v>
+        <v>25735332.08</v>
       </c>
       <c r="J68" t="n">
-        <v>41572391.19</v>
+        <v>41579139.85</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2493594592.1</v>
+        <v>2628125677.09</v>
       </c>
       <c r="F69" t="n">
-        <v>2254358063.54</v>
+        <v>2331591714.17</v>
       </c>
       <c r="G69" t="n">
-        <v>2213683465.29</v>
+        <v>2231908051.76</v>
       </c>
       <c r="H69" t="n">
-        <v>14513945.66</v>
+        <v>14522878.29</v>
       </c>
       <c r="I69" t="n">
-        <v>125983640.31</v>
+        <v>126994960.55</v>
       </c>
       <c r="J69" t="n">
-        <v>140497585.97</v>
+        <v>141517838.84</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>130610616.83</v>
+        <v>131169926.01</v>
       </c>
       <c r="F70" t="n">
-        <v>124091208.63</v>
+        <v>124505058.53</v>
       </c>
       <c r="G70" t="n">
-        <v>117893153.95</v>
+        <v>120198617.17</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>374119117.96</v>
+        <v>398697528.9</v>
       </c>
       <c r="F71" t="n">
-        <v>298693956.04</v>
+        <v>312023997.99</v>
       </c>
       <c r="G71" t="n">
-        <v>271925794.86</v>
+        <v>278441225.48</v>
       </c>
       <c r="H71" t="n">
         <v>28800758.26</v>
       </c>
       <c r="I71" t="n">
-        <v>67522747.98</v>
+        <v>67658226.64</v>
       </c>
       <c r="J71" t="n">
-        <v>96323506.23999999</v>
+        <v>96458984.90000001</v>
       </c>
     </row>
     <row r="72">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8716530.76</v>
+        <v>8735518.949999999</v>
       </c>
       <c r="F72" t="n">
-        <v>8071345.76</v>
+        <v>8080254.15</v>
       </c>
       <c r="G72" t="n">
-        <v>6657416.11</v>
+        <v>6680478.27</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222143811.82</v>
+        <v>223267623.98</v>
       </c>
       <c r="F73" t="n">
-        <v>194293939.32</v>
+        <v>199775431.69</v>
       </c>
       <c r="G73" t="n">
-        <v>189172769.51</v>
+        <v>194942154.7</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
       </c>
       <c r="I73" t="n">
-        <v>19670832.81</v>
+        <v>19671647.61</v>
       </c>
       <c r="J73" t="n">
-        <v>19883243.75</v>
+        <v>19884058.55</v>
       </c>
     </row>
     <row r="74">
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>252771673.8</v>
+        <v>253867450.72</v>
       </c>
       <c r="F74" t="n">
-        <v>230681689.58</v>
+        <v>234856398.43</v>
       </c>
       <c r="G74" t="n">
-        <v>225940984.11</v>
+        <v>229553737.14</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>22690830.13</v>
+        <v>22805507.51</v>
       </c>
       <c r="J74" t="n">
-        <v>22821283.91</v>
+        <v>22935961.29</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4077619.92</v>
+        <v>4979820.02</v>
       </c>
       <c r="F75" t="n">
-        <v>3341835.49</v>
+        <v>3359325.67</v>
       </c>
       <c r="G75" t="n">
-        <v>3098079.16</v>
+        <v>3112231.11</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>664225686.61</v>
+        <v>667744402.36</v>
       </c>
       <c r="F2" t="n">
-        <v>621603077.8099999</v>
+        <v>633832898.99</v>
       </c>
       <c r="G2" t="n">
-        <v>583798076.1</v>
+        <v>602070567.34</v>
       </c>
       <c r="H2" t="n">
-        <v>214279936.92</v>
+        <v>214399217.64</v>
       </c>
       <c r="I2" t="n">
         <v>2470960.14</v>
       </c>
       <c r="J2" t="n">
-        <v>216750897.06</v>
+        <v>216870177.78</v>
       </c>
     </row>
     <row r="3">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3891073.69</v>
+        <v>3890894.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3431157.26</v>
+        <v>3629480.17</v>
       </c>
       <c r="G3" t="n">
-        <v>3268273.21</v>
+        <v>3436228.04</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4434050.13</v>
+        <v>4477808.8</v>
       </c>
       <c r="F4" t="n">
-        <v>2183336.05</v>
+        <v>2351627.81</v>
       </c>
       <c r="G4" t="n">
-        <v>2013652.17</v>
+        <v>2013857.64</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11898942.6</v>
+        <v>11912956.24</v>
       </c>
       <c r="F5" t="n">
-        <v>10597694.7</v>
+        <v>10753026.21</v>
       </c>
       <c r="G5" t="n">
-        <v>10508136.32</v>
+        <v>10552583.85</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27796942.11</v>
+        <v>28215235.25</v>
       </c>
       <c r="F6" t="n">
-        <v>19152097.36</v>
+        <v>20646326.3</v>
       </c>
       <c r="G6" t="n">
-        <v>17646073.63</v>
+        <v>19064704.44</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1053284927.07</v>
+        <v>1064055591.53</v>
       </c>
       <c r="F7" t="n">
-        <v>1016938571.76</v>
+        <v>1018515541.87</v>
       </c>
       <c r="G7" t="n">
-        <v>1014168292.87</v>
+        <v>1015169274.98</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>34431633.72</v>
+        <v>35772403.17</v>
       </c>
       <c r="J7" t="n">
-        <v>40478437.6</v>
+        <v>41819207.05</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35498949.36</v>
+        <v>35661596.37</v>
       </c>
       <c r="F8" t="n">
-        <v>34777438.78</v>
+        <v>34804342.85</v>
       </c>
       <c r="G8" t="n">
-        <v>34699961.24</v>
+        <v>34732605.12</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1321347993.38</v>
+        <v>1396503727.07</v>
       </c>
       <c r="F9" t="n">
-        <v>650123392.29</v>
+        <v>705048668.53</v>
       </c>
       <c r="G9" t="n">
-        <v>575279533.22</v>
+        <v>580888026.91</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>290140336.64</v>
+        <v>290154539.54</v>
       </c>
       <c r="J9" t="n">
-        <v>303571984.19</v>
+        <v>303586187.09</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49561074.78</v>
+        <v>52614705.01</v>
       </c>
       <c r="F10" t="n">
-        <v>43401052.44</v>
+        <v>46149825.87</v>
       </c>
       <c r="G10" t="n">
-        <v>36115402.58</v>
+        <v>36125534.13</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>759509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>446922752.09</v>
+        <v>448928332.84</v>
       </c>
       <c r="G11" t="n">
-        <v>446918389.32</v>
+        <v>448923970.07</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -978,22 +978,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12946651.75</v>
+        <v>12983969.47</v>
       </c>
       <c r="F16" t="n">
-        <v>11493581.93</v>
+        <v>11655558.21</v>
       </c>
       <c r="G16" t="n">
-        <v>11154570.59</v>
+        <v>11349050.65</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
       </c>
       <c r="I16" t="n">
-        <v>959977.4300000001</v>
+        <v>963707.42</v>
       </c>
       <c r="J16" t="n">
-        <v>1171305.47</v>
+        <v>1175035.46</v>
       </c>
     </row>
     <row r="17">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2426090.62</v>
+        <v>2435918.07</v>
       </c>
       <c r="F18" t="n">
-        <v>2325655.45</v>
+        <v>2346722.57</v>
       </c>
       <c r="G18" t="n">
-        <v>2226951.47</v>
+        <v>2240417.91</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
       </c>
       <c r="I18" t="n">
-        <v>67312.25999999999</v>
+        <v>72457.69</v>
       </c>
       <c r="J18" t="n">
-        <v>113698.45</v>
+        <v>118843.88</v>
       </c>
     </row>
     <row r="19">
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>309326618.52</v>
+        <v>324432515.94</v>
       </c>
       <c r="F19" t="n">
-        <v>253910997.42</v>
+        <v>266151112.67</v>
       </c>
       <c r="G19" t="n">
-        <v>247779452.85</v>
+        <v>259798962.87</v>
       </c>
       <c r="H19" t="n">
         <v>3369120.12</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33487383.07</v>
+        <v>33537035.31</v>
       </c>
       <c r="F20" t="n">
-        <v>26368357.97</v>
+        <v>27261757.06</v>
       </c>
       <c r="G20" t="n">
-        <v>25607496.63</v>
+        <v>26427588.4</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>293494.49</v>
+        <v>331804.68</v>
       </c>
       <c r="J21" t="n">
-        <v>293494.49</v>
+        <v>331804.68</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7152793.22</v>
+        <v>7156693.22</v>
       </c>
       <c r="F22" t="n">
-        <v>3749492.92</v>
+        <v>3997872.71</v>
       </c>
       <c r="G22" t="n">
-        <v>3327230.57</v>
+        <v>3707270.72</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>39081655.98</v>
+        <v>39253678.67</v>
       </c>
       <c r="F23" t="n">
-        <v>38618320.62</v>
+        <v>38865113.68</v>
       </c>
       <c r="G23" t="n">
-        <v>36991502.18</v>
+        <v>37526934.83</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>114807683.9</v>
+        <v>114917294.25</v>
       </c>
       <c r="F24" t="n">
-        <v>83732564.72</v>
+        <v>84267552.54000001</v>
       </c>
       <c r="G24" t="n">
-        <v>81210825.62</v>
+        <v>82746757.91</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9117221085.01</v>
+        <v>9201084668.309999</v>
       </c>
       <c r="F27" t="n">
-        <v>7179012244.16</v>
+        <v>7220485317.15</v>
       </c>
       <c r="G27" t="n">
-        <v>6986430902.91</v>
+        <v>7098979745.43</v>
       </c>
       <c r="H27" t="n">
-        <v>377148754.54</v>
+        <v>404008038.73</v>
       </c>
       <c r="I27" t="n">
-        <v>489173403.46</v>
+        <v>503081728.08</v>
       </c>
       <c r="J27" t="n">
-        <v>866322158</v>
+        <v>907089766.8099999</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>25369038.48</v>
+        <v>26974814.93</v>
       </c>
       <c r="F28" t="n">
-        <v>7171950.66</v>
+        <v>7611917.9</v>
       </c>
       <c r="G28" t="n">
-        <v>6567187.92</v>
+        <v>6929945.94</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>36213393.49</v>
+        <v>36520640.79</v>
       </c>
       <c r="J28" t="n">
-        <v>40800162.97</v>
+        <v>41107410.27</v>
       </c>
     </row>
     <row r="29">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392896.59</v>
+        <v>392534.59</v>
       </c>
       <c r="F29" t="n">
-        <v>140653.38</v>
+        <v>339582.41</v>
       </c>
       <c r="G29" t="n">
-        <v>125104.21</v>
+        <v>326587.69</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8881697931.040001</v>
+        <v>8885986883.15</v>
       </c>
       <c r="F30" t="n">
-        <v>8876852452.09</v>
+        <v>8881141404.200001</v>
       </c>
       <c r="G30" t="n">
-        <v>8876722243.83</v>
+        <v>8881009427.92</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31537614.89</v>
+        <v>32013566.29</v>
       </c>
       <c r="F31" t="n">
-        <v>29135635.4</v>
+        <v>29406086.39</v>
       </c>
       <c r="G31" t="n">
-        <v>28824878.85</v>
+        <v>29051249.18</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>1981440.57</v>
+        <v>2002149.27</v>
       </c>
       <c r="J31" t="n">
-        <v>1981659.5</v>
+        <v>2002368.2</v>
       </c>
     </row>
     <row r="32">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1330136490.5</v>
+        <v>1349381716.13</v>
       </c>
       <c r="F32" t="n">
-        <v>1220391830.03</v>
+        <v>1230804567.27</v>
       </c>
       <c r="G32" t="n">
-        <v>1179249568.89</v>
+        <v>1192974201.58</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>92478350.93000001</v>
+        <v>92659834.86</v>
       </c>
       <c r="J32" t="n">
-        <v>98519482.04000001</v>
+        <v>98700965.97</v>
       </c>
     </row>
     <row r="33">
@@ -1587,10 +1587,10 @@
         <v>340935.7</v>
       </c>
       <c r="F33" t="n">
-        <v>325643.69</v>
+        <v>328993.19</v>
       </c>
       <c r="G33" t="n">
-        <v>297998.06</v>
+        <v>301347.56</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,22 +1620,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37409116.91</v>
+        <v>37417148.04</v>
       </c>
       <c r="F34" t="n">
-        <v>34039216.49</v>
+        <v>34093921.79</v>
       </c>
       <c r="G34" t="n">
-        <v>32479867.03</v>
+        <v>33079777.35</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
       </c>
       <c r="I34" t="n">
-        <v>1813430.58</v>
+        <v>2077147.11</v>
       </c>
       <c r="J34" t="n">
-        <v>1841118.74</v>
+        <v>2104835.27</v>
       </c>
     </row>
     <row r="35">
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>403322.88</v>
+        <v>1064170.39</v>
       </c>
       <c r="J35" t="n">
-        <v>403322.88</v>
+        <v>1064170.39</v>
       </c>
     </row>
     <row r="36">
@@ -1695,10 +1695,10 @@
         <v>524766345.95</v>
       </c>
       <c r="F36" t="n">
-        <v>180156295.53</v>
+        <v>194199797.55</v>
       </c>
       <c r="G36" t="n">
-        <v>150772789.3</v>
+        <v>168332574.74</v>
       </c>
       <c r="H36" t="n">
         <v>53631506.45</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2709900.62</v>
+        <v>2764985.18</v>
       </c>
       <c r="F37" t="n">
-        <v>2600256.76</v>
+        <v>2660557.93</v>
       </c>
       <c r="G37" t="n">
-        <v>2548490.75</v>
+        <v>2579236.65</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1767,10 +1767,10 @@
         <v>94331218.23999999</v>
       </c>
       <c r="F38" t="n">
-        <v>75298322.3</v>
+        <v>75314682.45</v>
       </c>
       <c r="G38" t="n">
-        <v>75275516.06</v>
+        <v>75291807.04000001</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>248755217.7</v>
+        <v>253685609.39</v>
       </c>
       <c r="F39" t="n">
-        <v>184565114.56</v>
+        <v>185927949.91</v>
       </c>
       <c r="G39" t="n">
-        <v>171376744.89</v>
+        <v>172187822.64</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I39" t="n">
-        <v>133678547.85</v>
+        <v>133806987.85</v>
       </c>
       <c r="J39" t="n">
-        <v>140865820.92</v>
+        <v>140994260.92</v>
       </c>
     </row>
     <row r="40">
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>66092800.35</v>
+        <v>67513009.2</v>
       </c>
       <c r="F40" t="n">
-        <v>38884604.64</v>
+        <v>42125922.66</v>
       </c>
       <c r="G40" t="n">
-        <v>34513436.66</v>
+        <v>37970593.88</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>56045634.5</v>
+        <v>56957663.43</v>
       </c>
       <c r="F41" t="n">
-        <v>28506783.77</v>
+        <v>28991175.82</v>
       </c>
       <c r="G41" t="n">
-        <v>25025633.07</v>
+        <v>26751718.98</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
@@ -1914,7 +1914,7 @@
         <v>5295387364.22</v>
       </c>
       <c r="G42" t="n">
-        <v>5021071903.88</v>
+        <v>5131366301.81</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>211903964.11</v>
+        <v>219199321.91</v>
       </c>
       <c r="F43" t="n">
-        <v>178891955.08</v>
+        <v>181635880.8</v>
       </c>
       <c r="G43" t="n">
-        <v>171288451.4</v>
+        <v>175983247.72</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>23600115.01</v>
+        <v>23835934.33</v>
       </c>
       <c r="J43" t="n">
-        <v>26948190.29</v>
+        <v>27184009.61</v>
       </c>
     </row>
     <row r="44">
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>34373540.34</v>
+        <v>34523943.35</v>
       </c>
       <c r="F44" t="n">
-        <v>24333444.23</v>
+        <v>25360721.61</v>
       </c>
       <c r="G44" t="n">
-        <v>23896950.11</v>
+        <v>24528642.18</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>19204694.32</v>
+        <v>19582360.28</v>
       </c>
       <c r="J44" t="n">
-        <v>20226481.25</v>
+        <v>20604147.21</v>
       </c>
     </row>
     <row r="45">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>110324603.22</v>
+        <v>110981157.15</v>
       </c>
       <c r="F45" t="n">
-        <v>107485484.02</v>
+        <v>107970273.37</v>
       </c>
       <c r="G45" t="n">
-        <v>101238418.17</v>
+        <v>102548317.03</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>7291001.14</v>
+        <v>7631059.24</v>
       </c>
       <c r="J45" t="n">
-        <v>7777533.79</v>
+        <v>8117591.89</v>
       </c>
     </row>
     <row r="46">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12950101.2</v>
+        <v>12967106.26</v>
       </c>
       <c r="F46" t="n">
-        <v>10081233.64</v>
+        <v>10127082.56</v>
       </c>
       <c r="G46" t="n">
-        <v>9755547.960000001</v>
+        <v>9801221.939999999</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26865020.91</v>
+        <v>26922130.83</v>
       </c>
       <c r="F47" t="n">
-        <v>24726752.88</v>
+        <v>24825751.46</v>
       </c>
       <c r="G47" t="n">
-        <v>23226737.61</v>
+        <v>23351560</v>
       </c>
       <c r="H47" t="n">
         <v>6104162.13</v>
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>153519167.35</v>
+        <v>155704872.16</v>
       </c>
       <c r="F48" t="n">
-        <v>148999529.44</v>
+        <v>149494369.41</v>
       </c>
       <c r="G48" t="n">
-        <v>148000838.47</v>
+        <v>148678134.61</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4824663.77</v>
+        <v>4940029.35</v>
       </c>
       <c r="J48" t="n">
-        <v>5334577.69</v>
+        <v>5449943.27</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>18345283.91</v>
+        <v>19131671.06</v>
       </c>
       <c r="F49" t="n">
-        <v>17872884.86</v>
+        <v>18520805.27</v>
       </c>
       <c r="G49" t="n">
-        <v>17091783.45</v>
+        <v>17718668.02</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1159064644.16</v>
+        <v>1442852458.53</v>
       </c>
       <c r="F50" t="n">
-        <v>828971698.41</v>
+        <v>858274382.5599999</v>
       </c>
       <c r="G50" t="n">
-        <v>808247938.1</v>
+        <v>837045719.8200001</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>192923339.47</v>
+        <v>193043091.57</v>
       </c>
       <c r="J50" t="n">
-        <v>193020236.84</v>
+        <v>193139988.94</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1644961689.62</v>
+        <v>1727292343.89</v>
       </c>
       <c r="F51" t="n">
-        <v>1614638864.63</v>
+        <v>1695600273.89</v>
       </c>
       <c r="G51" t="n">
-        <v>1589712527.08</v>
+        <v>1672726322.13</v>
       </c>
       <c r="H51" t="n">
         <v>19331338.95</v>
       </c>
       <c r="I51" t="n">
-        <v>34491941.89</v>
+        <v>34494491.99</v>
       </c>
       <c r="J51" t="n">
-        <v>53823280.84</v>
+        <v>53825830.94</v>
       </c>
     </row>
     <row r="52">
@@ -2268,22 +2268,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>22688145.11</v>
+        <v>24621083.72</v>
       </c>
       <c r="F52" t="n">
-        <v>19272108.71</v>
+        <v>19593969.93</v>
       </c>
       <c r="G52" t="n">
-        <v>18008364.46</v>
+        <v>18491429.64</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
       </c>
       <c r="I52" t="n">
-        <v>1859710.27</v>
+        <v>1859956.27</v>
       </c>
       <c r="J52" t="n">
-        <v>2979183.08</v>
+        <v>2979429.08</v>
       </c>
     </row>
     <row r="53">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1802948.19</v>
+        <v>1802870.17</v>
       </c>
       <c r="F53" t="n">
-        <v>1671484.03</v>
+        <v>1761146.22</v>
       </c>
       <c r="G53" t="n">
-        <v>1632274.92</v>
+        <v>1708799.21</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10092999.89</v>
+        <v>10135803.16</v>
       </c>
       <c r="F54" t="n">
-        <v>9694580.74</v>
+        <v>9709878.689999999</v>
       </c>
       <c r="G54" t="n">
-        <v>9619774.23</v>
+        <v>9634732.99</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>12979747.5</v>
       </c>
       <c r="G55" t="n">
-        <v>12978755.64</v>
+        <v>12979747.5</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1642559949.72</v>
+        <v>1649996876.1</v>
       </c>
       <c r="F56" t="n">
-        <v>1586713117.37</v>
+        <v>1594241685.24</v>
       </c>
       <c r="G56" t="n">
-        <v>1573272769.25</v>
+        <v>1576933616.66</v>
       </c>
       <c r="H56" t="n">
         <v>8940604.800000001</v>
       </c>
       <c r="I56" t="n">
-        <v>31635193.9</v>
+        <v>35579039.97</v>
       </c>
       <c r="J56" t="n">
-        <v>40575798.7</v>
+        <v>44519644.77</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>8739629305.379999</v>
+        <v>10205310781.85</v>
       </c>
       <c r="F57" t="n">
-        <v>8548037679.96</v>
+        <v>10023659713.72</v>
       </c>
       <c r="G57" t="n">
-        <v>8528023820.54</v>
+        <v>9995455410.24</v>
       </c>
       <c r="H57" t="n">
         <v>18536120.52</v>
       </c>
       <c r="I57" t="n">
-        <v>169661861.1</v>
+        <v>182554228.38</v>
       </c>
       <c r="J57" t="n">
-        <v>188197981.62</v>
+        <v>201090348.9</v>
       </c>
     </row>
     <row r="58">
@@ -2484,7 +2484,7 @@
         <v>4608967.31</v>
       </c>
       <c r="G58" t="n">
-        <v>4507133.94</v>
+        <v>4512134.38</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>315680365.78</v>
+        <v>315707082.62</v>
       </c>
       <c r="F59" t="n">
-        <v>273800527.16</v>
+        <v>273922481.85</v>
       </c>
       <c r="G59" t="n">
-        <v>272770908.63</v>
+        <v>272879460.16</v>
       </c>
       <c r="H59" t="n">
         <v>6876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>16547905.35</v>
+        <v>16637143.46</v>
       </c>
       <c r="J59" t="n">
-        <v>23424423.51</v>
+        <v>23513661.62</v>
       </c>
     </row>
     <row r="60">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6698868.92</v>
+        <v>6720539.39</v>
       </c>
       <c r="F60" t="n">
-        <v>6422750.9</v>
+        <v>6448658.4</v>
       </c>
       <c r="G60" t="n">
-        <v>6317502.57</v>
+        <v>6325288.62</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>84817942.41</v>
+        <v>85510156.23</v>
       </c>
       <c r="F61" t="n">
-        <v>46940849.61</v>
+        <v>50370077.61</v>
       </c>
       <c r="G61" t="n">
-        <v>38765895.36</v>
+        <v>45306199.03</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>58835415.36</v>
+        <v>60386101.1</v>
       </c>
       <c r="J61" t="n">
-        <v>58895415.46</v>
+        <v>60446101.2</v>
       </c>
     </row>
     <row r="62">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>157507925.6</v>
+        <v>164664087.71</v>
       </c>
       <c r="F62" t="n">
-        <v>150357749.81</v>
+        <v>154666045.36</v>
       </c>
       <c r="G62" t="n">
-        <v>144979947.47</v>
+        <v>150354546.33</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>280021179.19</v>
+        <v>280142285.12</v>
       </c>
       <c r="F63" t="n">
-        <v>48877359.16</v>
+        <v>49381655.07</v>
       </c>
       <c r="G63" t="n">
-        <v>47544090.14</v>
+        <v>47672481.38</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>173142729.59</v>
+        <v>173481996.39</v>
       </c>
       <c r="F64" t="n">
-        <v>164889838.37</v>
+        <v>165103451.04</v>
       </c>
       <c r="G64" t="n">
-        <v>160194242.56</v>
+        <v>161350242.01</v>
       </c>
       <c r="H64" t="n">
         <v>11942560.14</v>
       </c>
       <c r="I64" t="n">
-        <v>14809012.55</v>
+        <v>15562957.29</v>
       </c>
       <c r="J64" t="n">
-        <v>26751572.69</v>
+        <v>27505517.43</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10521912708.14</v>
+        <v>10560044463.95</v>
       </c>
       <c r="F65" t="n">
-        <v>10059312313.93</v>
+        <v>10197232647.86</v>
       </c>
       <c r="G65" t="n">
-        <v>9943851547.33</v>
+        <v>10149137596.27</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>143083334.23</v>
+        <v>142988460.02</v>
       </c>
       <c r="J65" t="n">
-        <v>338990760.7</v>
+        <v>338895886.49</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>941703954.67</v>
+        <v>948186020.91</v>
       </c>
       <c r="F66" t="n">
-        <v>872673218.6799999</v>
+        <v>877873859.88</v>
       </c>
       <c r="G66" t="n">
-        <v>852444523.0700001</v>
+        <v>859961751.16</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>55298255.33</v>
+        <v>55304538.53</v>
       </c>
       <c r="J66" t="n">
-        <v>62963699.54</v>
+        <v>62969982.74</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>345046152.76</v>
+        <v>345308150.55</v>
       </c>
       <c r="F67" t="n">
-        <v>340430192.75</v>
+        <v>341568091.72</v>
       </c>
       <c r="G67" t="n">
-        <v>328849014.68</v>
+        <v>330275405.94</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>858873959.85</v>
+        <v>859795917.75</v>
       </c>
       <c r="F68" t="n">
-        <v>830928001.16</v>
+        <v>831803619</v>
       </c>
       <c r="G68" t="n">
-        <v>812796777.73</v>
+        <v>813706038.3</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>25735332.08</v>
+        <v>25772089.81</v>
       </c>
       <c r="J68" t="n">
-        <v>41579139.85</v>
+        <v>41615897.58</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2628125677.09</v>
+        <v>2632925955.06</v>
       </c>
       <c r="F69" t="n">
-        <v>2331591714.17</v>
+        <v>2381466580.63</v>
       </c>
       <c r="G69" t="n">
-        <v>2231908051.76</v>
+        <v>2289905102.69</v>
       </c>
       <c r="H69" t="n">
-        <v>14522878.29</v>
+        <v>14535120.17</v>
       </c>
       <c r="I69" t="n">
-        <v>126994960.55</v>
+        <v>129003601.11</v>
       </c>
       <c r="J69" t="n">
-        <v>141517838.84</v>
+        <v>143538721.28</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>131169926.01</v>
+        <v>131492739.16</v>
       </c>
       <c r="F70" t="n">
-        <v>124505058.53</v>
+        <v>124637790.26</v>
       </c>
       <c r="G70" t="n">
-        <v>120198617.17</v>
+        <v>120531647.53</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>398697528.9</v>
+        <v>419578806.67</v>
       </c>
       <c r="F71" t="n">
-        <v>312023997.99</v>
+        <v>321451140.85</v>
       </c>
       <c r="G71" t="n">
-        <v>278441225.48</v>
+        <v>295653485.05</v>
       </c>
       <c r="H71" t="n">
         <v>28800758.26</v>
       </c>
       <c r="I71" t="n">
-        <v>67658226.64</v>
+        <v>67789699.34999999</v>
       </c>
       <c r="J71" t="n">
-        <v>96458984.90000001</v>
+        <v>96590457.61</v>
       </c>
     </row>
     <row r="72">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8735518.949999999</v>
+        <v>9305836.390000001</v>
       </c>
       <c r="F72" t="n">
-        <v>8080254.15</v>
+        <v>8239082.85</v>
       </c>
       <c r="G72" t="n">
-        <v>6680478.27</v>
+        <v>6829438.9</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223267623.98</v>
+        <v>225122997.13</v>
       </c>
       <c r="F73" t="n">
-        <v>199775431.69</v>
+        <v>201214010.77</v>
       </c>
       <c r="G73" t="n">
-        <v>194942154.7</v>
+        <v>196320852.55</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
       </c>
       <c r="I73" t="n">
-        <v>19671647.61</v>
+        <v>19688593.21</v>
       </c>
       <c r="J73" t="n">
-        <v>19884058.55</v>
+        <v>19901004.15</v>
       </c>
     </row>
     <row r="74">
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>253867450.72</v>
+        <v>255419234.32</v>
       </c>
       <c r="F74" t="n">
-        <v>234856398.43</v>
+        <v>238275744.14</v>
       </c>
       <c r="G74" t="n">
-        <v>229553737.14</v>
+        <v>231970432.86</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>22805507.51</v>
+        <v>22923582.1</v>
       </c>
       <c r="J74" t="n">
-        <v>22935961.29</v>
+        <v>23054035.88</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4979820.02</v>
+        <v>5047719.58</v>
       </c>
       <c r="F75" t="n">
-        <v>3359325.67</v>
+        <v>3390800.32</v>
       </c>
       <c r="G75" t="n">
-        <v>3112231.11</v>
+        <v>3143651.74</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>667744402.36</v>
+        <v>698472185.63</v>
       </c>
       <c r="F2" t="n">
-        <v>633832898.99</v>
+        <v>668712046.51</v>
       </c>
       <c r="G2" t="n">
-        <v>602070567.34</v>
+        <v>643533910.29</v>
       </c>
       <c r="H2" t="n">
         <v>214399217.64</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3890894.3</v>
+        <v>3891304.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3629480.17</v>
+        <v>3631640.17</v>
       </c>
       <c r="G3" t="n">
-        <v>3436228.04</v>
+        <v>3438388.04</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4477808.8</v>
+        <v>4508127.34</v>
       </c>
       <c r="F4" t="n">
-        <v>2351627.81</v>
+        <v>2365372.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2013857.64</v>
+        <v>2027617.38</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11912956.24</v>
+        <v>11916309.34</v>
       </c>
       <c r="F5" t="n">
-        <v>10753026.21</v>
+        <v>10758484.55</v>
       </c>
       <c r="G5" t="n">
-        <v>10552583.85</v>
+        <v>10557951.71</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>138222.38</v>
+        <v>140322.38</v>
       </c>
       <c r="J5" t="n">
-        <v>146504.18</v>
+        <v>148604.18</v>
       </c>
     </row>
     <row r="6">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28215235.25</v>
+        <v>28257857.57</v>
       </c>
       <c r="F6" t="n">
-        <v>20646326.3</v>
+        <v>20688885.55</v>
       </c>
       <c r="G6" t="n">
-        <v>19064704.44</v>
+        <v>19107263.69</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1064055591.53</v>
+        <v>1066888734.27</v>
       </c>
       <c r="F7" t="n">
-        <v>1018515541.87</v>
+        <v>1019916108.92</v>
       </c>
       <c r="G7" t="n">
-        <v>1015169274.98</v>
+        <v>1017354236.14</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>35772403.17</v>
+        <v>36357487.73</v>
       </c>
       <c r="J7" t="n">
-        <v>41819207.05</v>
+        <v>42404291.61</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35661596.37</v>
+        <v>41249784.78</v>
       </c>
       <c r="F8" t="n">
-        <v>34804342.85</v>
+        <v>40409622.01</v>
       </c>
       <c r="G8" t="n">
-        <v>34732605.12</v>
+        <v>40253484.49</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1396503727.07</v>
+        <v>1404971453.05</v>
       </c>
       <c r="F9" t="n">
-        <v>705048668.53</v>
+        <v>792468985.0700001</v>
       </c>
       <c r="G9" t="n">
-        <v>580888026.91</v>
+        <v>709112775.67</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>290154539.54</v>
+        <v>310017918.73</v>
       </c>
       <c r="J9" t="n">
-        <v>303586187.09</v>
+        <v>323449566.28</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>52614705.01</v>
+        <v>70177676.66</v>
       </c>
       <c r="F10" t="n">
-        <v>46149825.87</v>
+        <v>49834953.04</v>
       </c>
       <c r="G10" t="n">
-        <v>36125534.13</v>
+        <v>37413079.58</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>759509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>448928332.84</v>
+        <v>505938234.49</v>
       </c>
       <c r="G11" t="n">
-        <v>448923970.07</v>
+        <v>505933871.72</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91642668.67</v>
+        <v>106600704.31</v>
       </c>
       <c r="F12" t="n">
-        <v>89955113.42</v>
+        <v>105090948.51</v>
       </c>
       <c r="G12" t="n">
-        <v>89939985.48</v>
+        <v>104898021.12</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12983969.47</v>
+        <v>14584834.63</v>
       </c>
       <c r="F16" t="n">
-        <v>11655558.21</v>
+        <v>13059620.64</v>
       </c>
       <c r="G16" t="n">
-        <v>11349050.65</v>
+        <v>12753523.69</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314027.26</v>
+        <v>358206</v>
       </c>
       <c r="F17" t="n">
         <v>181355.46</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2435918.07</v>
+        <v>2442592.2</v>
       </c>
       <c r="F18" t="n">
-        <v>2346722.57</v>
+        <v>2365873.45</v>
       </c>
       <c r="G18" t="n">
-        <v>2240417.91</v>
+        <v>2266813.54</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>324432515.94</v>
+        <v>349729150.18</v>
       </c>
       <c r="F19" t="n">
-        <v>266151112.67</v>
+        <v>292164146.9</v>
       </c>
       <c r="G19" t="n">
-        <v>259798962.87</v>
+        <v>275282043.53</v>
       </c>
       <c r="H19" t="n">
         <v>3369120.12</v>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33537035.31</v>
+        <v>33639950.8</v>
       </c>
       <c r="F20" t="n">
-        <v>27261757.06</v>
+        <v>27514522.6</v>
       </c>
       <c r="G20" t="n">
-        <v>26427588.4</v>
+        <v>26596545.58</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>331804.68</v>
+        <v>701268.5600000001</v>
       </c>
       <c r="J21" t="n">
-        <v>331804.68</v>
+        <v>701268.5600000001</v>
       </c>
     </row>
     <row r="22">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7156693.22</v>
+        <v>7216023.22</v>
       </c>
       <c r="F22" t="n">
-        <v>3997872.71</v>
+        <v>4010787.06</v>
       </c>
       <c r="G22" t="n">
-        <v>3707270.72</v>
+        <v>3780910.07</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>39253678.67</v>
+        <v>39329311.41</v>
       </c>
       <c r="F23" t="n">
-        <v>38865113.68</v>
+        <v>39019507.86</v>
       </c>
       <c r="G23" t="n">
-        <v>37526934.83</v>
+        <v>37587302.58</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>114917294.25</v>
+        <v>114978130.53</v>
       </c>
       <c r="F24" t="n">
-        <v>84267552.54000001</v>
+        <v>84348733.33</v>
       </c>
       <c r="G24" t="n">
-        <v>82746757.91</v>
+        <v>83244498.19</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6534927.36</v>
+        <v>7835873.39</v>
       </c>
       <c r="F26" t="n">
-        <v>6534927.36</v>
+        <v>7835873.39</v>
       </c>
       <c r="G26" t="n">
-        <v>6534927.36</v>
+        <v>7673251.28</v>
       </c>
       <c r="H26" t="n">
         <v>360498.89</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9201084668.309999</v>
+        <v>9372960647.67</v>
       </c>
       <c r="F27" t="n">
-        <v>7220485317.15</v>
+        <v>7385354657.05</v>
       </c>
       <c r="G27" t="n">
-        <v>7098979745.43</v>
+        <v>7158775244.75</v>
       </c>
       <c r="H27" t="n">
-        <v>404008038.73</v>
+        <v>406187245.49</v>
       </c>
       <c r="I27" t="n">
-        <v>503081728.08</v>
+        <v>512399874.94</v>
       </c>
       <c r="J27" t="n">
-        <v>907089766.8099999</v>
+        <v>918587120.4299999</v>
       </c>
     </row>
     <row r="28">
@@ -1404,13 +1404,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26974814.93</v>
+        <v>28776770.87</v>
       </c>
       <c r="F28" t="n">
-        <v>7611917.9</v>
+        <v>8373552.86</v>
       </c>
       <c r="G28" t="n">
-        <v>6929945.94</v>
+        <v>6985334.7</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392534.59</v>
+        <v>392405.97</v>
       </c>
       <c r="F29" t="n">
-        <v>339582.41</v>
+        <v>355458.13</v>
       </c>
       <c r="G29" t="n">
-        <v>326587.69</v>
+        <v>342002.75</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8885986883.15</v>
+        <v>10329145840.55</v>
       </c>
       <c r="F30" t="n">
-        <v>8881141404.200001</v>
+        <v>10324310310.95</v>
       </c>
       <c r="G30" t="n">
-        <v>8881009427.92</v>
+        <v>10324177342.51</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>32013566.29</v>
+        <v>31837170.64</v>
       </c>
       <c r="F31" t="n">
-        <v>29406086.39</v>
+        <v>29959717.7</v>
       </c>
       <c r="G31" t="n">
-        <v>29051249.18</v>
+        <v>29603380.65</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
       </c>
       <c r="I31" t="n">
-        <v>2002149.27</v>
+        <v>2003431.69</v>
       </c>
       <c r="J31" t="n">
-        <v>2002368.2</v>
+        <v>2003650.62</v>
       </c>
     </row>
     <row r="32">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1349381716.13</v>
+        <v>1359483370.81</v>
       </c>
       <c r="F32" t="n">
-        <v>1230804567.27</v>
+        <v>1245659049.98</v>
       </c>
       <c r="G32" t="n">
-        <v>1192974201.58</v>
+        <v>1207286703.38</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>92659834.86</v>
+        <v>92761447.23</v>
       </c>
       <c r="J32" t="n">
-        <v>98700965.97</v>
+        <v>98802578.34</v>
       </c>
     </row>
     <row r="33">
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>340935.7</v>
+        <v>340941.55</v>
       </c>
       <c r="F33" t="n">
-        <v>328993.19</v>
+        <v>330808.54</v>
       </c>
       <c r="G33" t="n">
-        <v>301347.56</v>
+        <v>303162.91</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,13 +1620,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37417148.04</v>
+        <v>37524674.1</v>
       </c>
       <c r="F34" t="n">
-        <v>34093921.79</v>
+        <v>34243661.36</v>
       </c>
       <c r="G34" t="n">
-        <v>33079777.35</v>
+        <v>33204284.24</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
@@ -1659,7 +1659,7 @@
         <v>1383063.6</v>
       </c>
       <c r="F35" t="n">
-        <v>1149192</v>
+        <v>1259836.85</v>
       </c>
       <c r="G35" t="n">
         <v>1103345.57</v>
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>524766345.95</v>
+        <v>570866345.95</v>
       </c>
       <c r="F36" t="n">
-        <v>194199797.55</v>
+        <v>200928897.65</v>
       </c>
       <c r="G36" t="n">
-        <v>168332574.74</v>
+        <v>185695277.13</v>
       </c>
       <c r="H36" t="n">
         <v>53631506.45</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2764985.18</v>
+        <v>2857947.51</v>
       </c>
       <c r="F37" t="n">
-        <v>2660557.93</v>
+        <v>2720389.66</v>
       </c>
       <c r="G37" t="n">
-        <v>2579236.65</v>
+        <v>2654512.94</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1770,7 +1770,7 @@
         <v>75314682.45</v>
       </c>
       <c r="G38" t="n">
-        <v>75291807.04000001</v>
+        <v>75291876.20999999</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>253685609.39</v>
+        <v>255379776.21</v>
       </c>
       <c r="F39" t="n">
-        <v>185927949.91</v>
+        <v>188752849.12</v>
       </c>
       <c r="G39" t="n">
-        <v>172187822.64</v>
+        <v>180060344.45</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>67513009.2</v>
+        <v>67539746.84999999</v>
       </c>
       <c r="F40" t="n">
-        <v>42125922.66</v>
+        <v>44906520.62</v>
       </c>
       <c r="G40" t="n">
-        <v>37970593.88</v>
+        <v>42656069.04</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>56957663.43</v>
+        <v>58345691.65</v>
       </c>
       <c r="F41" t="n">
-        <v>28991175.82</v>
+        <v>30664108.88</v>
       </c>
       <c r="G41" t="n">
-        <v>26751718.98</v>
+        <v>28658267.93</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
@@ -1911,10 +1911,10 @@
         <v>6496445251.75</v>
       </c>
       <c r="F42" t="n">
-        <v>5295387364.22</v>
+        <v>5441350028.37</v>
       </c>
       <c r="G42" t="n">
-        <v>5131366301.81</v>
+        <v>5277328965.96</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1944,22 +1944,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219199321.91</v>
+        <v>221517557.93</v>
       </c>
       <c r="F43" t="n">
-        <v>181635880.8</v>
+        <v>189911673.04</v>
       </c>
       <c r="G43" t="n">
-        <v>175983247.72</v>
+        <v>178050642.49</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I43" t="n">
-        <v>23835934.33</v>
+        <v>23877480.85</v>
       </c>
       <c r="J43" t="n">
-        <v>27184009.61</v>
+        <v>27225556.13</v>
       </c>
     </row>
     <row r="44">
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>34523943.35</v>
+        <v>34814978.58</v>
       </c>
       <c r="F44" t="n">
-        <v>25360721.61</v>
+        <v>26714756.78</v>
       </c>
       <c r="G44" t="n">
-        <v>24528642.18</v>
+        <v>26113572.58</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>19582360.28</v>
+        <v>20377202.42</v>
       </c>
       <c r="J44" t="n">
-        <v>20604147.21</v>
+        <v>21398989.35</v>
       </c>
     </row>
     <row r="45">
@@ -2016,22 +2016,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>110981157.15</v>
+        <v>115125766.98</v>
       </c>
       <c r="F45" t="n">
-        <v>107970273.37</v>
+        <v>111669058.1</v>
       </c>
       <c r="G45" t="n">
-        <v>102548317.03</v>
+        <v>106090935.32</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
       </c>
       <c r="I45" t="n">
-        <v>7631059.24</v>
+        <v>7674266.39</v>
       </c>
       <c r="J45" t="n">
-        <v>8117591.89</v>
+        <v>8160799.04</v>
       </c>
     </row>
     <row r="46">
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>12967106.26</v>
+        <v>13463147.03</v>
       </c>
       <c r="F46" t="n">
-        <v>10127082.56</v>
+        <v>10166877.42</v>
       </c>
       <c r="G46" t="n">
-        <v>9801221.939999999</v>
+        <v>9841747.189999999</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26922130.83</v>
+        <v>26935081.97</v>
       </c>
       <c r="F47" t="n">
-        <v>24825751.46</v>
+        <v>24826168.44</v>
       </c>
       <c r="G47" t="n">
-        <v>23351560</v>
+        <v>23351976.98</v>
       </c>
       <c r="H47" t="n">
         <v>6104162.13</v>
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>155704872.16</v>
+        <v>156917563.02</v>
       </c>
       <c r="F48" t="n">
-        <v>149494369.41</v>
+        <v>149949724.16</v>
       </c>
       <c r="G48" t="n">
-        <v>148678134.61</v>
+        <v>148881208.46</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>4940029.35</v>
+        <v>5026583.5</v>
       </c>
       <c r="J48" t="n">
-        <v>5449943.27</v>
+        <v>5536497.42</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19131671.06</v>
+        <v>19562496.14</v>
       </c>
       <c r="F49" t="n">
-        <v>18520805.27</v>
+        <v>18884902.81</v>
       </c>
       <c r="G49" t="n">
-        <v>17718668.02</v>
+        <v>18063939.12</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1442852458.53</v>
+        <v>1476438760.64</v>
       </c>
       <c r="F50" t="n">
-        <v>858274382.5599999</v>
+        <v>898012855.08</v>
       </c>
       <c r="G50" t="n">
-        <v>837045719.8200001</v>
+        <v>874334694.3200001</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>193043091.57</v>
+        <v>193362565.5</v>
       </c>
       <c r="J50" t="n">
-        <v>193139988.94</v>
+        <v>193459462.87</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1727292343.89</v>
+        <v>1902801706.06</v>
       </c>
       <c r="F51" t="n">
-        <v>1695600273.89</v>
+        <v>1872778384.57</v>
       </c>
       <c r="G51" t="n">
-        <v>1672726322.13</v>
+        <v>1850238265.92</v>
       </c>
       <c r="H51" t="n">
         <v>19331338.95</v>
       </c>
       <c r="I51" t="n">
-        <v>34494491.99</v>
+        <v>34502524.19</v>
       </c>
       <c r="J51" t="n">
-        <v>53825830.94</v>
+        <v>53833863.14</v>
       </c>
     </row>
     <row r="52">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>24621083.72</v>
+        <v>24678041.58</v>
       </c>
       <c r="F52" t="n">
-        <v>19593969.93</v>
+        <v>19756223.84</v>
       </c>
       <c r="G52" t="n">
-        <v>18491429.64</v>
+        <v>18601510.17</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1802870.17</v>
+        <v>1803231.71</v>
       </c>
       <c r="F53" t="n">
-        <v>1761146.22</v>
+        <v>1761311.37</v>
       </c>
       <c r="G53" t="n">
-        <v>1708799.21</v>
+        <v>1708959.65</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10135803.16</v>
+        <v>11640712.8</v>
       </c>
       <c r="F54" t="n">
-        <v>9709878.689999999</v>
+        <v>11214108.93</v>
       </c>
       <c r="G54" t="n">
-        <v>9634732.99</v>
+        <v>11138946.92</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1649996876.1</v>
+        <v>1904204621.85</v>
       </c>
       <c r="F56" t="n">
-        <v>1594241685.24</v>
+        <v>1831182133.48</v>
       </c>
       <c r="G56" t="n">
-        <v>1576933616.66</v>
+        <v>1812857886.18</v>
       </c>
       <c r="H56" t="n">
         <v>8940604.800000001</v>
       </c>
       <c r="I56" t="n">
-        <v>35579039.97</v>
+        <v>35846119.36</v>
       </c>
       <c r="J56" t="n">
-        <v>44519644.77</v>
+        <v>44786724.16</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10205310781.85</v>
+        <v>10215818685.23</v>
       </c>
       <c r="F57" t="n">
-        <v>10023659713.72</v>
+        <v>10034683852.61</v>
       </c>
       <c r="G57" t="n">
-        <v>9995455410.24</v>
+        <v>9998806847.16</v>
       </c>
       <c r="H57" t="n">
         <v>18536120.52</v>
       </c>
       <c r="I57" t="n">
-        <v>182554228.38</v>
+        <v>184163665.08</v>
       </c>
       <c r="J57" t="n">
-        <v>201090348.9</v>
+        <v>202699785.6</v>
       </c>
     </row>
     <row r="58">
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4642757.47</v>
+        <v>5166816.35</v>
       </c>
       <c r="F58" t="n">
-        <v>4608967.31</v>
+        <v>5068530.91</v>
       </c>
       <c r="G58" t="n">
-        <v>4512134.38</v>
+        <v>4971697.98</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>315707082.62</v>
+        <v>319271156.5</v>
       </c>
       <c r="F59" t="n">
-        <v>273922481.85</v>
+        <v>305606490.75</v>
       </c>
       <c r="G59" t="n">
-        <v>272879460.16</v>
+        <v>275148610.68</v>
       </c>
       <c r="H59" t="n">
         <v>6876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>16637143.46</v>
+        <v>16650954.35</v>
       </c>
       <c r="J59" t="n">
-        <v>23513661.62</v>
+        <v>23527472.51</v>
       </c>
     </row>
     <row r="60">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6720539.39</v>
+        <v>7707942.03</v>
       </c>
       <c r="F60" t="n">
-        <v>6448658.4</v>
+        <v>7300544.46</v>
       </c>
       <c r="G60" t="n">
-        <v>6325288.62</v>
+        <v>7196284.14</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>85510156.23</v>
+        <v>86605230.43000001</v>
       </c>
       <c r="F61" t="n">
-        <v>50370077.61</v>
+        <v>57527202.94</v>
       </c>
       <c r="G61" t="n">
-        <v>45306199.03</v>
+        <v>54076317.12</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>60386101.1</v>
+        <v>61192657.95</v>
       </c>
       <c r="J61" t="n">
-        <v>60446101.2</v>
+        <v>61252658.05</v>
       </c>
     </row>
     <row r="62">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>164664087.71</v>
+        <v>167280942.72</v>
       </c>
       <c r="F62" t="n">
-        <v>154666045.36</v>
+        <v>157899664.44</v>
       </c>
       <c r="G62" t="n">
-        <v>150354546.33</v>
+        <v>154699165.06</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>280142285.12</v>
+        <v>282292111.25</v>
       </c>
       <c r="F63" t="n">
-        <v>49381655.07</v>
+        <v>51529310.9</v>
       </c>
       <c r="G63" t="n">
-        <v>47672481.38</v>
+        <v>49820129.5</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>173481996.39</v>
+        <v>181956584.99</v>
       </c>
       <c r="F64" t="n">
-        <v>165103451.04</v>
+        <v>173646367.46</v>
       </c>
       <c r="G64" t="n">
-        <v>161350242.01</v>
+        <v>169309402.23</v>
       </c>
       <c r="H64" t="n">
         <v>11942560.14</v>
       </c>
       <c r="I64" t="n">
-        <v>15562957.29</v>
+        <v>15874226.69</v>
       </c>
       <c r="J64" t="n">
-        <v>27505517.43</v>
+        <v>27816786.83</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10560044463.95</v>
+        <v>11691692996.34</v>
       </c>
       <c r="F65" t="n">
-        <v>10197232647.86</v>
+        <v>11355099701.74</v>
       </c>
       <c r="G65" t="n">
-        <v>10149137596.27</v>
+        <v>11313229954.19</v>
       </c>
       <c r="H65" t="n">
         <v>195907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>142988460.02</v>
+        <v>145259508.87</v>
       </c>
       <c r="J65" t="n">
-        <v>338895886.49</v>
+        <v>341166935.34</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>948186020.91</v>
+        <v>1072329289.23</v>
       </c>
       <c r="F66" t="n">
-        <v>877873859.88</v>
+        <v>1005543994.17</v>
       </c>
       <c r="G66" t="n">
-        <v>859961751.16</v>
+        <v>985113016.9400001</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>55304538.53</v>
+        <v>57004241.74</v>
       </c>
       <c r="J66" t="n">
-        <v>62969982.74</v>
+        <v>64669685.95</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>345308150.55</v>
+        <v>350790715.07</v>
       </c>
       <c r="F67" t="n">
-        <v>341568091.72</v>
+        <v>346172575.96</v>
       </c>
       <c r="G67" t="n">
-        <v>330275405.94</v>
+        <v>337664758.88</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>859795917.75</v>
+        <v>865353339.1900001</v>
       </c>
       <c r="F68" t="n">
-        <v>831803619</v>
+        <v>837083896.9299999</v>
       </c>
       <c r="G68" t="n">
-        <v>813706038.3</v>
+        <v>819491797.84</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>25772089.81</v>
+        <v>27314237.08</v>
       </c>
       <c r="J68" t="n">
-        <v>41615897.58</v>
+        <v>43158044.85</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2632925955.06</v>
+        <v>2955841101.24</v>
       </c>
       <c r="F69" t="n">
-        <v>2381466580.63</v>
+        <v>2707042244.82</v>
       </c>
       <c r="G69" t="n">
-        <v>2289905102.69</v>
+        <v>2627406532.03</v>
       </c>
       <c r="H69" t="n">
         <v>14535120.17</v>
       </c>
       <c r="I69" t="n">
-        <v>129003601.11</v>
+        <v>129416960.69</v>
       </c>
       <c r="J69" t="n">
-        <v>143538721.28</v>
+        <v>143952080.86</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>131492739.16</v>
+        <v>144812981.62</v>
       </c>
       <c r="F70" t="n">
-        <v>124637790.26</v>
+        <v>135625135.64</v>
       </c>
       <c r="G70" t="n">
-        <v>120531647.53</v>
+        <v>131120630.99</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>419578806.67</v>
+        <v>437609833.89</v>
       </c>
       <c r="F71" t="n">
-        <v>321451140.85</v>
+        <v>342417078.8</v>
       </c>
       <c r="G71" t="n">
-        <v>295653485.05</v>
+        <v>318687055.43</v>
       </c>
       <c r="H71" t="n">
         <v>28800758.26</v>
       </c>
       <c r="I71" t="n">
-        <v>67789699.34999999</v>
+        <v>69410912.92</v>
       </c>
       <c r="J71" t="n">
-        <v>96590457.61</v>
+        <v>98211671.18000001</v>
       </c>
     </row>
     <row r="72">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9305836.390000001</v>
+        <v>9350838.26</v>
       </c>
       <c r="F72" t="n">
-        <v>8239082.85</v>
+        <v>8289866.47</v>
       </c>
       <c r="G72" t="n">
-        <v>6829438.9</v>
+        <v>7240498.85</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>225122997.13</v>
+        <v>226695771.8</v>
       </c>
       <c r="F73" t="n">
-        <v>201214010.77</v>
+        <v>202557350.13</v>
       </c>
       <c r="G73" t="n">
-        <v>196320852.55</v>
+        <v>197700458.34</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>255419234.32</v>
+        <v>259913057.16</v>
       </c>
       <c r="F74" t="n">
-        <v>238275744.14</v>
+        <v>240969367.81</v>
       </c>
       <c r="G74" t="n">
-        <v>231970432.86</v>
+        <v>235264887.32</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>22923582.1</v>
+        <v>23079091.14</v>
       </c>
       <c r="J74" t="n">
-        <v>23054035.88</v>
+        <v>23209544.92</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5047719.58</v>
+        <v>5051015.97</v>
       </c>
       <c r="F75" t="n">
-        <v>3390800.32</v>
+        <v>3713708.09</v>
       </c>
       <c r="G75" t="n">
-        <v>3143651.74</v>
+        <v>3430254.5</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>698472185.63</v>
+        <v>705305578.87</v>
       </c>
       <c r="F2" t="n">
-        <v>668712046.51</v>
+        <v>673373318.87</v>
       </c>
       <c r="G2" t="n">
-        <v>643533910.29</v>
+        <v>648151485.51</v>
       </c>
       <c r="H2" t="n">
         <v>214399217.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2470960.14</v>
+        <v>2507327.52</v>
       </c>
       <c r="J2" t="n">
-        <v>216870177.78</v>
+        <v>216906545.16</v>
       </c>
     </row>
     <row r="3">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3891304.3</v>
+        <v>4405901.79</v>
       </c>
       <c r="F3" t="n">
-        <v>3631640.17</v>
+        <v>3979411.44</v>
       </c>
       <c r="G3" t="n">
-        <v>3438388.04</v>
+        <v>3786153.58</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4508127.34</v>
+        <v>4654598.08</v>
       </c>
       <c r="F4" t="n">
-        <v>2365372.08</v>
+        <v>2520939.62</v>
       </c>
       <c r="G4" t="n">
-        <v>2027617.38</v>
+        <v>2320997.32</v>
       </c>
       <c r="H4" t="n">
         <v>17304.09</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>11916309.34</v>
+        <v>13680200.2</v>
       </c>
       <c r="F5" t="n">
-        <v>10758484.55</v>
+        <v>12398534.71</v>
       </c>
       <c r="G5" t="n">
-        <v>10557951.71</v>
+        <v>12196695.8</v>
       </c>
       <c r="H5" t="n">
         <v>8281.799999999999</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28257857.57</v>
+        <v>29649444.35</v>
       </c>
       <c r="F6" t="n">
-        <v>20688885.55</v>
+        <v>22760805.1</v>
       </c>
       <c r="G6" t="n">
-        <v>19107263.69</v>
+        <v>21006749.43</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1066888734.27</v>
+        <v>1243569630.82</v>
       </c>
       <c r="F7" t="n">
-        <v>1019916108.92</v>
+        <v>1195486695.43</v>
       </c>
       <c r="G7" t="n">
-        <v>1017354236.14</v>
+        <v>1188372471.46</v>
       </c>
       <c r="H7" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I7" t="n">
-        <v>36357487.73</v>
+        <v>36365738.63</v>
       </c>
       <c r="J7" t="n">
-        <v>42404291.61</v>
+        <v>42412542.51</v>
       </c>
     </row>
     <row r="8">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>41249784.78</v>
+        <v>41249511.59</v>
       </c>
       <c r="F8" t="n">
-        <v>40409622.01</v>
+        <v>40413325.31</v>
       </c>
       <c r="G8" t="n">
-        <v>40253484.49</v>
+        <v>40327275.65</v>
       </c>
       <c r="H8" t="n">
         <v>5062</v>
@@ -750,22 +750,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1404971453.05</v>
+        <v>1488306881.88</v>
       </c>
       <c r="F9" t="n">
-        <v>792468985.0700001</v>
+        <v>824289427.47</v>
       </c>
       <c r="G9" t="n">
-        <v>709112775.67</v>
+        <v>756139093.33</v>
       </c>
       <c r="H9" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I9" t="n">
-        <v>310017918.73</v>
+        <v>315282883.59</v>
       </c>
       <c r="J9" t="n">
-        <v>323449566.28</v>
+        <v>328714531.14</v>
       </c>
     </row>
     <row r="10">
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70177676.66</v>
+        <v>88908413.98</v>
       </c>
       <c r="F10" t="n">
-        <v>49834953.04</v>
+        <v>58636790.31</v>
       </c>
       <c r="G10" t="n">
-        <v>37413079.58</v>
+        <v>55512577.41</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -819,10 +819,10 @@
         <v>759509748.28</v>
       </c>
       <c r="F11" t="n">
-        <v>505938234.49</v>
+        <v>509322862.97</v>
       </c>
       <c r="G11" t="n">
-        <v>505933871.72</v>
+        <v>509318500.2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106600704.31</v>
+        <v>106602145</v>
       </c>
       <c r="F12" t="n">
-        <v>105090948.51</v>
+        <v>105092389.2</v>
       </c>
       <c r="G12" t="n">
-        <v>104898021.12</v>
+        <v>104899461.81</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14584834.63</v>
+        <v>14680022.46</v>
       </c>
       <c r="F16" t="n">
-        <v>13059620.64</v>
+        <v>13255919.53</v>
       </c>
       <c r="G16" t="n">
-        <v>12753523.69</v>
+        <v>12902203.09</v>
       </c>
       <c r="H16" t="n">
         <v>211328.04</v>
@@ -1017,10 +1017,10 @@
         <v>358206</v>
       </c>
       <c r="F17" t="n">
-        <v>181355.46</v>
+        <v>192075.83</v>
       </c>
       <c r="G17" t="n">
-        <v>171391.74</v>
+        <v>182112.11</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2442592.2</v>
+        <v>2825008.42</v>
       </c>
       <c r="F18" t="n">
-        <v>2365873.45</v>
+        <v>2647073.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2266813.54</v>
+        <v>2547852.14</v>
       </c>
       <c r="H18" t="n">
         <v>46386.19</v>
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>349729150.18</v>
+        <v>362918768.99</v>
       </c>
       <c r="F19" t="n">
-        <v>292164146.9</v>
+        <v>316675197.92</v>
       </c>
       <c r="G19" t="n">
-        <v>275282043.53</v>
+        <v>305801580.9</v>
       </c>
       <c r="H19" t="n">
         <v>3369120.12</v>
       </c>
       <c r="I19" t="n">
-        <v>3677333.75</v>
+        <v>3679583.75</v>
       </c>
       <c r="J19" t="n">
-        <v>7046453.87</v>
+        <v>7048703.87</v>
       </c>
     </row>
     <row r="20">
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33639950.8</v>
+        <v>36878711.88</v>
       </c>
       <c r="F20" t="n">
-        <v>27514522.6</v>
+        <v>32629875.34</v>
       </c>
       <c r="G20" t="n">
-        <v>26596545.58</v>
+        <v>31794765.58</v>
       </c>
       <c r="H20" t="n">
         <v>866933.3100000001</v>
@@ -1197,10 +1197,10 @@
         <v>7216023.22</v>
       </c>
       <c r="F22" t="n">
-        <v>4010787.06</v>
+        <v>4012990.61</v>
       </c>
       <c r="G22" t="n">
-        <v>3780910.07</v>
+        <v>3808512.62</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>39329311.41</v>
+        <v>44998379.87</v>
       </c>
       <c r="F23" t="n">
-        <v>39019507.86</v>
+        <v>44496088.07</v>
       </c>
       <c r="G23" t="n">
-        <v>37587302.58</v>
+        <v>43015841.03</v>
       </c>
       <c r="H23" t="n">
         <v>8.359999999999999</v>
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>114978130.53</v>
+        <v>115196251.11</v>
       </c>
       <c r="F24" t="n">
-        <v>84348733.33</v>
+        <v>85090467.48999999</v>
       </c>
       <c r="G24" t="n">
-        <v>83244498.19</v>
+        <v>83979017.12</v>
       </c>
       <c r="H24" t="n">
         <v>594553.05</v>
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9372960647.67</v>
+        <v>9572245232.959999</v>
       </c>
       <c r="F27" t="n">
-        <v>7385354657.05</v>
+        <v>7701251147.17</v>
       </c>
       <c r="G27" t="n">
-        <v>7158775244.75</v>
+        <v>7412373093.92</v>
       </c>
       <c r="H27" t="n">
-        <v>406187245.49</v>
+        <v>406056474.84</v>
       </c>
       <c r="I27" t="n">
-        <v>512399874.94</v>
+        <v>523896154.11</v>
       </c>
       <c r="J27" t="n">
-        <v>918587120.4299999</v>
+        <v>929952628.95</v>
       </c>
     </row>
     <row r="28">
@@ -1404,22 +1404,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>28776770.87</v>
+        <v>34206115.73</v>
       </c>
       <c r="F28" t="n">
-        <v>8373552.86</v>
+        <v>8968874.51</v>
       </c>
       <c r="G28" t="n">
-        <v>6985334.7</v>
+        <v>7739343.23</v>
       </c>
       <c r="H28" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I28" t="n">
-        <v>36520640.79</v>
+        <v>37399974.31</v>
       </c>
       <c r="J28" t="n">
-        <v>41107410.27</v>
+        <v>41986743.79</v>
       </c>
     </row>
     <row r="29">
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392405.97</v>
+        <v>392555.97</v>
       </c>
       <c r="F29" t="n">
-        <v>355458.13</v>
+        <v>356664.88</v>
       </c>
       <c r="G29" t="n">
-        <v>342002.75</v>
+        <v>343209.5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10329145840.55</v>
+        <v>10355598525.01</v>
       </c>
       <c r="F30" t="n">
-        <v>10324310310.95</v>
+        <v>10353866334.27</v>
       </c>
       <c r="G30" t="n">
-        <v>10324177342.51</v>
+        <v>10353727456.5</v>
       </c>
       <c r="H30" t="n">
         <v>57945.89</v>
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31837170.64</v>
+        <v>36086163.78</v>
       </c>
       <c r="F31" t="n">
-        <v>29959717.7</v>
+        <v>33620279.41</v>
       </c>
       <c r="G31" t="n">
-        <v>29603380.65</v>
+        <v>33274997.49</v>
       </c>
       <c r="H31" t="n">
         <v>218.93</v>
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1359483370.81</v>
+        <v>1512215059.36</v>
       </c>
       <c r="F32" t="n">
-        <v>1245659049.98</v>
+        <v>1408043649.18</v>
       </c>
       <c r="G32" t="n">
-        <v>1207286703.38</v>
+        <v>1351808321.49</v>
       </c>
       <c r="H32" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I32" t="n">
-        <v>92761447.23</v>
+        <v>92917136.89</v>
       </c>
       <c r="J32" t="n">
-        <v>98802578.34</v>
+        <v>98958268</v>
       </c>
     </row>
     <row r="33">
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>340941.55</v>
+        <v>383516.53</v>
       </c>
       <c r="F33" t="n">
-        <v>330808.54</v>
+        <v>362529.62</v>
       </c>
       <c r="G33" t="n">
-        <v>303162.91</v>
+        <v>309609.01</v>
       </c>
       <c r="H33" t="n">
         <v>68494.85000000001</v>
@@ -1620,13 +1620,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37524674.1</v>
+        <v>42165711.88</v>
       </c>
       <c r="F34" t="n">
-        <v>34243661.36</v>
+        <v>38895755.04</v>
       </c>
       <c r="G34" t="n">
-        <v>33204284.24</v>
+        <v>38074348.02</v>
       </c>
       <c r="H34" t="n">
         <v>27688.16</v>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2857947.51</v>
+        <v>3318606.77</v>
       </c>
       <c r="F37" t="n">
-        <v>2720389.66</v>
+        <v>3148932.61</v>
       </c>
       <c r="G37" t="n">
-        <v>2654512.94</v>
+        <v>3076449.56</v>
       </c>
       <c r="H37" t="n">
         <v>23147.54</v>
@@ -1800,13 +1800,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>255379776.21</v>
+        <v>272689211.85</v>
       </c>
       <c r="F39" t="n">
-        <v>188752849.12</v>
+        <v>202777298.67</v>
       </c>
       <c r="G39" t="n">
-        <v>180060344.45</v>
+        <v>191371189.07</v>
       </c>
       <c r="H39" t="n">
         <v>7187273.07</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>67539746.84999999</v>
+        <v>68075254.52</v>
       </c>
       <c r="F40" t="n">
-        <v>44906520.62</v>
+        <v>46511366.19</v>
       </c>
       <c r="G40" t="n">
-        <v>42656069.04</v>
+        <v>42909975.91</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1872,13 +1872,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>58345691.65</v>
+        <v>60009688.08</v>
       </c>
       <c r="F41" t="n">
-        <v>30664108.88</v>
+        <v>32726369.24</v>
       </c>
       <c r="G41" t="n">
-        <v>28658267.93</v>
+        <v>29967519.44</v>
       </c>
       <c r="H41" t="n">
         <v>1803218.12</v>
@@ -1908,22 +1908,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6496445251.75</v>
+        <v>6470084509.41</v>
       </c>
       <c r="F42" t="n">
-        <v>5441350028.37</v>
+        <v>5443212798.51</v>
       </c>
       <c r="G42" t="n">
-        <v>5277328965.96</v>
+        <v>5386862798.93</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>43587892.37</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>43587892.37</v>
       </c>
     </row>
     <row r="43">
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221517557.93</v>
+        <v>245473804.92</v>
       </c>
       <c r="F43" t="n">
-        <v>189911673.04</v>
+        <v>207990821.07</v>
       </c>
       <c r="G43" t="n">
-        <v>178050642.49</v>
+        <v>199832067.02</v>
       </c>
       <c r="H43" t="n">
         <v>3348075.28</v>
@@ -1980,22 +1980,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>34814978.58</v>
+        <v>35730381.97</v>
       </c>
       <c r="F44" t="n">
-        <v>26714756.78</v>
+        <v>29019562.4</v>
       </c>
       <c r="G44" t="n">
-        <v>26113572.58</v>
+        <v>28501124.23</v>
       </c>
       <c r="H44" t="n">
         <v>1021786.93</v>
       </c>
       <c r="I44" t="n">
-        <v>20377202.42</v>
+        <v>20421491.42</v>
       </c>
       <c r="J44" t="n">
-        <v>21398989.35</v>
+        <v>21443278.35</v>
       </c>
     </row>
     <row r="45">
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>115125766.98</v>
+        <v>130617071.83</v>
       </c>
       <c r="F45" t="n">
-        <v>111669058.1</v>
+        <v>126385709.85</v>
       </c>
       <c r="G45" t="n">
-        <v>106090935.32</v>
+        <v>119886840.37</v>
       </c>
       <c r="H45" t="n">
         <v>486532.65</v>
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>13463147.03</v>
+        <v>14518366.59</v>
       </c>
       <c r="F46" t="n">
-        <v>10166877.42</v>
+        <v>11279029.75</v>
       </c>
       <c r="G46" t="n">
-        <v>9841747.189999999</v>
+        <v>10947151.26</v>
       </c>
       <c r="H46" t="n">
         <v>702452.89</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>26935081.97</v>
+        <v>29791099.67</v>
       </c>
       <c r="F47" t="n">
-        <v>24826168.44</v>
+        <v>27447571.53</v>
       </c>
       <c r="G47" t="n">
-        <v>23351976.98</v>
+        <v>25969243.31</v>
       </c>
       <c r="H47" t="n">
         <v>6104162.13</v>
@@ -2124,22 +2124,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>156917563.02</v>
+        <v>172333235.8</v>
       </c>
       <c r="F48" t="n">
-        <v>149949724.16</v>
+        <v>165153183.18</v>
       </c>
       <c r="G48" t="n">
-        <v>148881208.46</v>
+        <v>164340471.78</v>
       </c>
       <c r="H48" t="n">
         <v>509913.92</v>
       </c>
       <c r="I48" t="n">
-        <v>5026583.5</v>
+        <v>5029043.27</v>
       </c>
       <c r="J48" t="n">
-        <v>5536497.42</v>
+        <v>5538957.19</v>
       </c>
     </row>
     <row r="49">
@@ -2160,13 +2160,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19562496.14</v>
+        <v>22285384.65</v>
       </c>
       <c r="F49" t="n">
-        <v>18884902.81</v>
+        <v>21735282.25</v>
       </c>
       <c r="G49" t="n">
-        <v>18063939.12</v>
+        <v>20800435.26</v>
       </c>
       <c r="H49" t="n">
         <v>6330.51</v>
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1476438760.64</v>
+        <v>1510617602.41</v>
       </c>
       <c r="F50" t="n">
-        <v>898012855.08</v>
+        <v>1003106612.23</v>
       </c>
       <c r="G50" t="n">
-        <v>874334694.3200001</v>
+        <v>950269130.99</v>
       </c>
       <c r="H50" t="n">
         <v>96897.37</v>
       </c>
       <c r="I50" t="n">
-        <v>193362565.5</v>
+        <v>193463880.41</v>
       </c>
       <c r="J50" t="n">
-        <v>193459462.87</v>
+        <v>193560777.78</v>
       </c>
     </row>
     <row r="51">
@@ -2232,22 +2232,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1902801706.06</v>
+        <v>1916521928.92</v>
       </c>
       <c r="F51" t="n">
-        <v>1872778384.57</v>
+        <v>1881474307.27</v>
       </c>
       <c r="G51" t="n">
-        <v>1850238265.92</v>
+        <v>1857816477.1</v>
       </c>
       <c r="H51" t="n">
         <v>19331338.95</v>
       </c>
       <c r="I51" t="n">
-        <v>34502524.19</v>
+        <v>34533549.39</v>
       </c>
       <c r="J51" t="n">
-        <v>53833863.14</v>
+        <v>53864888.34</v>
       </c>
     </row>
     <row r="52">
@@ -2268,22 +2268,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>24678041.58</v>
+        <v>26542686.76</v>
       </c>
       <c r="F52" t="n">
-        <v>19756223.84</v>
+        <v>21681770.69</v>
       </c>
       <c r="G52" t="n">
-        <v>18601510.17</v>
+        <v>21034312.38</v>
       </c>
       <c r="H52" t="n">
         <v>1119472.81</v>
       </c>
       <c r="I52" t="n">
-        <v>1859956.27</v>
+        <v>1861547.75</v>
       </c>
       <c r="J52" t="n">
-        <v>2979429.08</v>
+        <v>2981020.56</v>
       </c>
     </row>
     <row r="53">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1803231.71</v>
+        <v>2063938.86</v>
       </c>
       <c r="F53" t="n">
-        <v>1761311.37</v>
+        <v>2025539.08</v>
       </c>
       <c r="G53" t="n">
-        <v>1708959.65</v>
+        <v>1971796.92</v>
       </c>
       <c r="H53" t="n">
         <v>1692.39</v>
@@ -2340,13 +2340,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>11640712.8</v>
+        <v>11643712.8</v>
       </c>
       <c r="F54" t="n">
-        <v>11214108.93</v>
+        <v>11227925.73</v>
       </c>
       <c r="G54" t="n">
-        <v>11138946.92</v>
+        <v>11152763.72</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12979747.5</v>
+        <v>15557346.18</v>
       </c>
       <c r="F55" t="n">
-        <v>12979747.5</v>
+        <v>15557346.18</v>
       </c>
       <c r="G55" t="n">
-        <v>12979747.5</v>
+        <v>15557346.18</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1904204621.85</v>
+        <v>1909800259.32</v>
       </c>
       <c r="F56" t="n">
-        <v>1831182133.48</v>
+        <v>1832674350.96</v>
       </c>
       <c r="G56" t="n">
-        <v>1812857886.18</v>
+        <v>1814546561.13</v>
       </c>
       <c r="H56" t="n">
         <v>8940604.800000001</v>
       </c>
       <c r="I56" t="n">
-        <v>35846119.36</v>
+        <v>36021559.01</v>
       </c>
       <c r="J56" t="n">
-        <v>44786724.16</v>
+        <v>44962163.81</v>
       </c>
     </row>
     <row r="57">
@@ -2442,22 +2442,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10215818685.23</v>
+        <v>10229705360.79</v>
       </c>
       <c r="F57" t="n">
-        <v>10034683852.61</v>
+        <v>10048900771.98</v>
       </c>
       <c r="G57" t="n">
-        <v>9998806847.16</v>
+        <v>10012131466.37</v>
       </c>
       <c r="H57" t="n">
         <v>18536120.52</v>
       </c>
       <c r="I57" t="n">
-        <v>184163665.08</v>
+        <v>184554944.79</v>
       </c>
       <c r="J57" t="n">
-        <v>202699785.6</v>
+        <v>203091065.31</v>
       </c>
     </row>
     <row r="58">
@@ -2481,10 +2481,10 @@
         <v>5166816.35</v>
       </c>
       <c r="F58" t="n">
-        <v>5068530.91</v>
+        <v>5127499.31</v>
       </c>
       <c r="G58" t="n">
-        <v>4971697.98</v>
+        <v>5021643.12</v>
       </c>
       <c r="H58" t="n">
         <v>122407.67</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>319271156.5</v>
+        <v>319445806.3</v>
       </c>
       <c r="F59" t="n">
-        <v>305606490.75</v>
+        <v>305967651</v>
       </c>
       <c r="G59" t="n">
-        <v>275148610.68</v>
+        <v>275359973.62</v>
       </c>
       <c r="H59" t="n">
         <v>6876518.16</v>
       </c>
       <c r="I59" t="n">
-        <v>16650954.35</v>
+        <v>16804739.31</v>
       </c>
       <c r="J59" t="n">
-        <v>23527472.51</v>
+        <v>23681257.47</v>
       </c>
     </row>
     <row r="60">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7707942.03</v>
+        <v>7737352.03</v>
       </c>
       <c r="F60" t="n">
-        <v>7300544.46</v>
+        <v>7537027.82</v>
       </c>
       <c r="G60" t="n">
-        <v>7196284.14</v>
+        <v>7394721.15</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>86605230.43000001</v>
+        <v>86708274.93000001</v>
       </c>
       <c r="F61" t="n">
-        <v>57527202.94</v>
+        <v>60570990.74</v>
       </c>
       <c r="G61" t="n">
-        <v>54076317.12</v>
+        <v>55465404.97</v>
       </c>
       <c r="H61" t="n">
         <v>60000.1</v>
       </c>
       <c r="I61" t="n">
-        <v>61192657.95</v>
+        <v>61241610.36</v>
       </c>
       <c r="J61" t="n">
-        <v>61252658.05</v>
+        <v>61301610.46</v>
       </c>
     </row>
     <row r="62">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>167280942.72</v>
+        <v>171946421.45</v>
       </c>
       <c r="F62" t="n">
-        <v>157899664.44</v>
+        <v>163173008.95</v>
       </c>
       <c r="G62" t="n">
-        <v>154699165.06</v>
+        <v>160722457.03</v>
       </c>
       <c r="H62" t="n">
         <v>319615.87</v>
@@ -2658,22 +2658,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>282292111.25</v>
+        <v>282599912.71</v>
       </c>
       <c r="F63" t="n">
-        <v>51529310.9</v>
+        <v>51726050.15</v>
       </c>
       <c r="G63" t="n">
-        <v>49820129.5</v>
+        <v>50358956.45</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>32623825.04</v>
+        <v>40005821.35</v>
       </c>
       <c r="J63" t="n">
-        <v>32623825.04</v>
+        <v>40005821.35</v>
       </c>
     </row>
     <row r="64">
@@ -2694,22 +2694,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>181956584.99</v>
+        <v>185763137.58</v>
       </c>
       <c r="F64" t="n">
-        <v>173646367.46</v>
+        <v>177086446.63</v>
       </c>
       <c r="G64" t="n">
-        <v>169309402.23</v>
+        <v>171228970.49</v>
       </c>
       <c r="H64" t="n">
         <v>11942560.14</v>
       </c>
       <c r="I64" t="n">
-        <v>15874226.69</v>
+        <v>15956888.74</v>
       </c>
       <c r="J64" t="n">
-        <v>27816786.83</v>
+        <v>27899448.88</v>
       </c>
     </row>
     <row r="65">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11691692996.34</v>
+        <v>11847866748.19</v>
       </c>
       <c r="F65" t="n">
-        <v>11355099701.74</v>
+        <v>11539239278.88</v>
       </c>
       <c r="G65" t="n">
-        <v>11313229954.19</v>
+        <v>11479554726</v>
       </c>
       <c r="H65" t="n">
-        <v>195907426.47</v>
+        <v>199907426.47</v>
       </c>
       <c r="I65" t="n">
-        <v>145259508.87</v>
+        <v>145442522.43</v>
       </c>
       <c r="J65" t="n">
-        <v>341166935.34</v>
+        <v>345349948.9</v>
       </c>
     </row>
     <row r="66">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1072329289.23</v>
+        <v>1082262047.26</v>
       </c>
       <c r="F66" t="n">
-        <v>1005543994.17</v>
+        <v>1008327889.53</v>
       </c>
       <c r="G66" t="n">
-        <v>985113016.9400001</v>
+        <v>988016215.05</v>
       </c>
       <c r="H66" t="n">
         <v>7665444.21</v>
       </c>
       <c r="I66" t="n">
-        <v>57004241.74</v>
+        <v>57085162.85</v>
       </c>
       <c r="J66" t="n">
-        <v>64669685.95</v>
+        <v>64750607.06</v>
       </c>
     </row>
     <row r="67">
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>350790715.07</v>
+        <v>351184899.99</v>
       </c>
       <c r="F67" t="n">
-        <v>346172575.96</v>
+        <v>347948057.18</v>
       </c>
       <c r="G67" t="n">
-        <v>337664758.88</v>
+        <v>337732397.04</v>
       </c>
       <c r="H67" t="n">
         <v>11209003.04</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>865353339.1900001</v>
+        <v>865638559.39</v>
       </c>
       <c r="F68" t="n">
-        <v>837083896.9299999</v>
+        <v>837411428.96</v>
       </c>
       <c r="G68" t="n">
-        <v>819491797.84</v>
+        <v>819600630.51</v>
       </c>
       <c r="H68" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I68" t="n">
-        <v>27314237.08</v>
+        <v>27922531.5</v>
       </c>
       <c r="J68" t="n">
-        <v>43158044.85</v>
+        <v>43766339.27</v>
       </c>
     </row>
     <row r="69">
@@ -2874,22 +2874,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2955841101.24</v>
+        <v>2958737418.95</v>
       </c>
       <c r="F69" t="n">
-        <v>2707042244.82</v>
+        <v>2711201183.7</v>
       </c>
       <c r="G69" t="n">
-        <v>2627406532.03</v>
+        <v>2673739249.78</v>
       </c>
       <c r="H69" t="n">
-        <v>14535120.17</v>
+        <v>14535917.67</v>
       </c>
       <c r="I69" t="n">
-        <v>129416960.69</v>
+        <v>130140512.22</v>
       </c>
       <c r="J69" t="n">
-        <v>143952080.86</v>
+        <v>144676429.89</v>
       </c>
     </row>
     <row r="70">
@@ -2910,13 +2910,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>144812981.62</v>
+        <v>145811257.97</v>
       </c>
       <c r="F70" t="n">
-        <v>135625135.64</v>
+        <v>138984415.08</v>
       </c>
       <c r="G70" t="n">
-        <v>131120630.99</v>
+        <v>131450357.12</v>
       </c>
       <c r="H70" t="n">
         <v>3823909.86</v>
@@ -2946,13 +2946,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>437609833.89</v>
+        <v>441219355.07</v>
       </c>
       <c r="F71" t="n">
-        <v>342417078.8</v>
+        <v>348809039.55</v>
       </c>
       <c r="G71" t="n">
-        <v>318687055.43</v>
+        <v>320539285.53</v>
       </c>
       <c r="H71" t="n">
         <v>28800758.26</v>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9350838.26</v>
+        <v>10515457.61</v>
       </c>
       <c r="F72" t="n">
-        <v>8289866.47</v>
+        <v>9043950.67</v>
       </c>
       <c r="G72" t="n">
-        <v>7240498.85</v>
+        <v>7994583.05</v>
       </c>
       <c r="H72" t="n">
         <v>32410.16</v>
@@ -3018,22 +3018,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>226695771.8</v>
+        <v>255250384.35</v>
       </c>
       <c r="F73" t="n">
-        <v>202557350.13</v>
+        <v>229976545.51</v>
       </c>
       <c r="G73" t="n">
-        <v>197700458.34</v>
+        <v>224976211.13</v>
       </c>
       <c r="H73" t="n">
         <v>212410.94</v>
       </c>
       <c r="I73" t="n">
-        <v>19688593.21</v>
+        <v>19719523.6</v>
       </c>
       <c r="J73" t="n">
-        <v>19901004.15</v>
+        <v>19931934.54</v>
       </c>
     </row>
     <row r="74">
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>259913057.16</v>
+        <v>296171203.29</v>
       </c>
       <c r="F74" t="n">
-        <v>240969367.81</v>
+        <v>276426814.07</v>
       </c>
       <c r="G74" t="n">
-        <v>235264887.32</v>
+        <v>270176853.43</v>
       </c>
       <c r="H74" t="n">
         <v>130453.78</v>
       </c>
       <c r="I74" t="n">
-        <v>23079091.14</v>
+        <v>23179037.58</v>
       </c>
       <c r="J74" t="n">
-        <v>23209544.92</v>
+        <v>23309491.36</v>
       </c>
     </row>
     <row r="75">
@@ -3090,13 +3090,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5051015.97</v>
+        <v>4664247.3</v>
       </c>
       <c r="F75" t="n">
-        <v>3713708.09</v>
+        <v>3969132.75</v>
       </c>
       <c r="G75" t="n">
-        <v>3430254.5</v>
+        <v>3680268.15</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>705305578.87</v>
+        <v>734562549.8200001</v>
       </c>
       <c r="F2" t="n">
-        <v>673373318.87</v>
+        <v>673615234.83</v>
       </c>
       <c r="G2" t="n">
-        <v>648151485.51</v>
+        <v>648458870.17</v>
       </c>
       <c r="H2" t="n">
         <v>214399217.64</v>
@@ -558,34 +558,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARMVA</t>
+          <t>ALMG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2461</v>
+        <v>1011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4654598.08</v>
+        <v>1244613639.61</v>
       </c>
       <c r="F4" t="n">
-        <v>2520939.62</v>
+        <v>1160969633.41</v>
       </c>
       <c r="G4" t="n">
-        <v>2320997.32</v>
+        <v>1148721705.64</v>
       </c>
       <c r="H4" t="n">
-        <v>17304.09</v>
+        <v>6630.3</v>
       </c>
       <c r="I4" t="n">
-        <v>667892.4</v>
+        <v>32317228.61</v>
       </c>
       <c r="J4" t="n">
-        <v>685196.49</v>
+        <v>32323858.91</v>
       </c>
     </row>
     <row r="5">
@@ -594,34 +594,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARSAE -MG</t>
+          <t>ARMVA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2441</v>
+        <v>2461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13680200.2</v>
+        <v>4653416.51</v>
       </c>
       <c r="F5" t="n">
-        <v>12398534.71</v>
+        <v>2520939.62</v>
       </c>
       <c r="G5" t="n">
-        <v>12196695.8</v>
+        <v>2320997.32</v>
       </c>
       <c r="H5" t="n">
-        <v>8281.799999999999</v>
+        <v>17304.09</v>
       </c>
       <c r="I5" t="n">
-        <v>140322.38</v>
+        <v>667892.4</v>
       </c>
       <c r="J5" t="n">
-        <v>148604.18</v>
+        <v>685196.49</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARTEMIG</t>
+          <t>ARSAE -MG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2471</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>29649444.35</v>
+        <v>13680200.2</v>
       </c>
       <c r="F6" t="n">
-        <v>22760805.1</v>
+        <v>12437440.66</v>
       </c>
       <c r="G6" t="n">
-        <v>21006749.43</v>
+        <v>12196695.8</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>8281.799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>2159796.82</v>
+        <v>140322.38</v>
       </c>
       <c r="J6" t="n">
-        <v>2159796.82</v>
+        <v>148604.18</v>
       </c>
     </row>
     <row r="7">
@@ -666,34 +666,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CBMMG</t>
+          <t>ARTEMIG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1401</v>
+        <v>2471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE TRANSPORTES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1243569630.82</v>
+        <v>29681444.35</v>
       </c>
       <c r="F7" t="n">
-        <v>1195486695.43</v>
+        <v>22779913.34</v>
       </c>
       <c r="G7" t="n">
-        <v>1188372471.46</v>
+        <v>21009823.44</v>
       </c>
       <c r="H7" t="n">
-        <v>6046803.88</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>36365738.63</v>
+        <v>2159796.82</v>
       </c>
       <c r="J7" t="n">
-        <v>42412542.51</v>
+        <v>2159796.82</v>
       </c>
     </row>
     <row r="8">
@@ -702,34 +702,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CGE</t>
+          <t>CBMMG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1521</v>
+        <v>1401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CONTROLADORIA-GERAL DO ESTADO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>41249511.59</v>
+        <v>1243690975.8</v>
       </c>
       <c r="F8" t="n">
-        <v>40413325.31</v>
+        <v>1195761025.63</v>
       </c>
       <c r="G8" t="n">
-        <v>40327275.65</v>
+        <v>1188465677.96</v>
       </c>
       <c r="H8" t="n">
-        <v>5062</v>
+        <v>6046803.88</v>
       </c>
       <c r="I8" t="n">
-        <v>1311388.02</v>
+        <v>36365738.63</v>
       </c>
       <c r="J8" t="n">
-        <v>1316450.02</v>
+        <v>42412542.51</v>
       </c>
     </row>
     <row r="9">
@@ -738,34 +738,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DER-MG</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2301</v>
+        <v>1521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>CONTROLADORIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1488306881.88</v>
+        <v>41248498.52</v>
       </c>
       <c r="F9" t="n">
-        <v>824289427.47</v>
+        <v>40416316.16</v>
       </c>
       <c r="G9" t="n">
-        <v>756139093.33</v>
+        <v>40327275.65</v>
       </c>
       <c r="H9" t="n">
-        <v>13431647.55</v>
+        <v>5062</v>
       </c>
       <c r="I9" t="n">
-        <v>315282883.59</v>
+        <v>1311388.02</v>
       </c>
       <c r="J9" t="n">
-        <v>328714531.14</v>
+        <v>1316450.02</v>
       </c>
     </row>
     <row r="10">
@@ -774,29 +774,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DETRAN/MG</t>
+          <t>DEF PUB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2481</v>
+        <v>1441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO ESTADUAL DE TRANSITO DE MINAS GERAIS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>88908413.98</v>
+        <v>651992053.26</v>
       </c>
       <c r="F10" t="n">
-        <v>58636790.31</v>
+        <v>645656844.39</v>
       </c>
       <c r="G10" t="n">
-        <v>55512577.41</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>633038463.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7410</v>
+      </c>
+      <c r="I10" t="n">
+        <v>13720685.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13728095.95</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -804,34 +810,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EGE - SEF</t>
+          <t>DER-MG</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1911</v>
+        <v>2301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>759509748.28</v>
+        <v>1499682431.17</v>
       </c>
       <c r="F11" t="n">
-        <v>509322862.97</v>
+        <v>824355792.11</v>
       </c>
       <c r="G11" t="n">
-        <v>509318500.2</v>
+        <v>756256401.0599999</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>13431647.55</v>
       </c>
       <c r="I11" t="n">
-        <v>73808566.59999999</v>
+        <v>315282883.59</v>
       </c>
       <c r="J11" t="n">
-        <v>73808566.59999999</v>
+        <v>328714531.14</v>
       </c>
     </row>
     <row r="12">
@@ -840,35 +846,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EGE-SEPLAG</t>
+          <t>DETRAN/MG</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1941</v>
+        <v>2481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>DEPARTAMENTO ESTADUAL DE TRANSITO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106602145</v>
+        <v>90330686.45</v>
       </c>
       <c r="F12" t="n">
-        <v>105092389.2</v>
+        <v>60068361.36</v>
       </c>
       <c r="G12" t="n">
-        <v>104899461.81</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>893022.58</v>
-      </c>
-      <c r="J12" t="n">
-        <v>893022.58</v>
-      </c>
+        <v>55512577.41</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -876,29 +876,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>EGE - SEF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3041</v>
+        <v>1911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>180266897.78</v>
+        <v>759509748.28</v>
       </c>
       <c r="F13" t="n">
-        <v>180266897.78</v>
+        <v>509322862.97</v>
       </c>
       <c r="G13" t="n">
-        <v>180266897.78</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>509318500.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>73808566.59999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>73808566.59999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -906,29 +912,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>EGE-SEPLAG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3151</v>
+        <v>1941</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15493154.83</v>
+        <v>106602145</v>
       </c>
       <c r="F14" t="n">
-        <v>15493154.83</v>
+        <v>105092389.2</v>
       </c>
       <c r="G14" t="n">
-        <v>15493154.83</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+        <v>104899461.81</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>893022.58</v>
+      </c>
+      <c r="J14" t="n">
+        <v>893022.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -936,25 +948,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3051</v>
+        <v>3041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71727903.56999999</v>
+        <v>180266897.78</v>
       </c>
       <c r="F15" t="n">
-        <v>71727903.56999999</v>
+        <v>180266897.78</v>
       </c>
       <c r="G15" t="n">
-        <v>71727903.56999999</v>
+        <v>180266897.78</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -966,35 +978,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1541</v>
+        <v>3151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14680022.46</v>
+        <v>15493154.83</v>
       </c>
       <c r="F16" t="n">
-        <v>13255919.53</v>
+        <v>15493154.83</v>
       </c>
       <c r="G16" t="n">
-        <v>12902203.09</v>
-      </c>
-      <c r="H16" t="n">
-        <v>211328.04</v>
-      </c>
-      <c r="I16" t="n">
-        <v>963707.42</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1175035.46</v>
-      </c>
+        <v>15493154.83</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1002,35 +1008,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4541</v>
+        <v>3051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>358206</v>
+        <v>71727903.56999999</v>
       </c>
       <c r="F17" t="n">
-        <v>192075.83</v>
+        <v>71727903.56999999</v>
       </c>
       <c r="G17" t="n">
-        <v>182112.11</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>28664.16</v>
-      </c>
-      <c r="J17" t="n">
-        <v>28664.16</v>
-      </c>
+        <v>71727903.56999999</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1038,34 +1038,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2171</v>
+        <v>1541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2825008.42</v>
+        <v>14680022.46</v>
       </c>
       <c r="F18" t="n">
-        <v>2647073.2</v>
+        <v>13256094.73</v>
       </c>
       <c r="G18" t="n">
-        <v>2547852.14</v>
+        <v>12914678.02</v>
       </c>
       <c r="H18" t="n">
-        <v>46386.19</v>
+        <v>211328.04</v>
       </c>
       <c r="I18" t="n">
-        <v>72457.69</v>
+        <v>963707.42</v>
       </c>
       <c r="J18" t="n">
-        <v>118843.88</v>
+        <v>1175035.46</v>
       </c>
     </row>
     <row r="19">
@@ -1074,34 +1074,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2071</v>
+        <v>4541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>362918768.99</v>
+        <v>358206</v>
       </c>
       <c r="F19" t="n">
-        <v>316675197.92</v>
+        <v>192075.83</v>
       </c>
       <c r="G19" t="n">
-        <v>305801580.9</v>
+        <v>182112.11</v>
       </c>
       <c r="H19" t="n">
-        <v>3369120.12</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3679583.75</v>
+        <v>28664.16</v>
       </c>
       <c r="J19" t="n">
-        <v>7048703.87</v>
+        <v>28664.16</v>
       </c>
     </row>
     <row r="20">
@@ -1110,34 +1110,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36878711.88</v>
+        <v>2825008.42</v>
       </c>
       <c r="F20" t="n">
-        <v>32629875.34</v>
+        <v>2728137.02</v>
       </c>
       <c r="G20" t="n">
-        <v>31794765.58</v>
+        <v>2547852.14</v>
       </c>
       <c r="H20" t="n">
-        <v>866933.3100000001</v>
+        <v>46386.19</v>
       </c>
       <c r="I20" t="n">
-        <v>1611008.66</v>
+        <v>72457.69</v>
       </c>
       <c r="J20" t="n">
-        <v>2477941.97</v>
+        <v>118843.88</v>
       </c>
     </row>
     <row r="21">
@@ -1146,34 +1146,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4331</v>
+        <v>2071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2643527.87</v>
+        <v>363117260.53</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>316837626.35</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>306284470.66</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3369120.12</v>
       </c>
       <c r="I21" t="n">
-        <v>701268.5600000001</v>
+        <v>3679583.75</v>
       </c>
       <c r="J21" t="n">
-        <v>701268.5600000001</v>
+        <v>7048703.87</v>
       </c>
     </row>
     <row r="22">
@@ -1182,29 +1182,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEAGE</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4751</v>
+        <v>2181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DA ADVOCACIA-GERAL DO ESTADO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7216023.22</v>
+        <v>36900786.26</v>
       </c>
       <c r="F22" t="n">
-        <v>4012990.61</v>
+        <v>32634752.56</v>
       </c>
       <c r="G22" t="n">
-        <v>3808512.62</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+        <v>31802748.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>866933.3100000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1611008.66</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2477941.97</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1212,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>44998379.87</v>
+        <v>2643527.87</v>
       </c>
       <c r="F23" t="n">
-        <v>44496088.07</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>43015841.03</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>8.359999999999999</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1012611.59</v>
+        <v>701268.5600000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1012619.95</v>
+        <v>701268.5600000001</v>
       </c>
     </row>
     <row r="24">
@@ -1248,35 +1254,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FDMP</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4251</v>
+        <v>4731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDO DE DESENVOLVIMENTO DO MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>115196251.11</v>
+        <v>38411334.17</v>
       </c>
       <c r="F24" t="n">
-        <v>85090467.48999999</v>
+        <v>2961334.17</v>
       </c>
       <c r="G24" t="n">
-        <v>83979017.12</v>
-      </c>
-      <c r="H24" t="n">
-        <v>594553.05</v>
-      </c>
-      <c r="I24" t="n">
-        <v>942023.0699999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1536576.12</v>
-      </c>
+        <v>2961334.17</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1284,35 +1284,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAGE</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4491</v>
+        <v>4751</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESPECIAL DA ADVOCACIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>11214.34</v>
+        <v>7267875.22</v>
       </c>
       <c r="F25" t="n">
-        <v>11214.34</v>
+        <v>4014535.36</v>
       </c>
       <c r="G25" t="n">
-        <v>11214.34</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>134615.38</v>
-      </c>
-      <c r="J25" t="n">
-        <v>134615.38</v>
-      </c>
+        <v>3810057.37</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1320,34 +1314,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4101</v>
+        <v>2091</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7835873.39</v>
+        <v>45271913.72</v>
       </c>
       <c r="F26" t="n">
-        <v>7835873.39</v>
+        <v>44627922.64</v>
       </c>
       <c r="G26" t="n">
-        <v>7673251.28</v>
+        <v>43017537.48</v>
       </c>
       <c r="H26" t="n">
-        <v>360498.89</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1012611.59</v>
       </c>
       <c r="J26" t="n">
-        <v>360498.89</v>
+        <v>1012619.95</v>
       </c>
     </row>
     <row r="27">
@@ -1356,34 +1350,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4291</v>
+        <v>4251</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9572245232.959999</v>
+        <v>115195927.68</v>
       </c>
       <c r="F27" t="n">
-        <v>7701251147.17</v>
+        <v>85163012.51000001</v>
       </c>
       <c r="G27" t="n">
-        <v>7412373093.92</v>
+        <v>83983409.91</v>
       </c>
       <c r="H27" t="n">
-        <v>406056474.84</v>
+        <v>594553.05</v>
       </c>
       <c r="I27" t="n">
-        <v>523896154.11</v>
+        <v>942023.0699999999</v>
       </c>
       <c r="J27" t="n">
-        <v>929952628.95</v>
+        <v>1536576.12</v>
       </c>
     </row>
     <row r="28">
@@ -1392,34 +1386,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4691</v>
+        <v>4491</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>34206115.73</v>
+        <v>11214.34</v>
       </c>
       <c r="F28" t="n">
-        <v>8968874.51</v>
+        <v>11214.34</v>
       </c>
       <c r="G28" t="n">
-        <v>7739343.23</v>
+        <v>11214.34</v>
       </c>
       <c r="H28" t="n">
-        <v>4586769.48</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>37399974.31</v>
+        <v>134615.38</v>
       </c>
       <c r="J28" t="n">
-        <v>41986743.79</v>
+        <v>134615.38</v>
       </c>
     </row>
     <row r="29">
@@ -1428,35 +1422,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FEGAJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4701</v>
+        <v>4741</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DE GARANTIA DE ACESSO A JUSTICA</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>392555.97</v>
+        <v>2415176.35</v>
       </c>
       <c r="F29" t="n">
-        <v>356664.88</v>
+        <v>35048</v>
       </c>
       <c r="G29" t="n">
-        <v>343209.5</v>
-      </c>
-      <c r="H29" t="n">
         <v>0</v>
       </c>
-      <c r="I29" t="n">
-        <v>1235436.62</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1235436.62</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1464,34 +1452,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4711</v>
+        <v>4101</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10355598525.01</v>
+        <v>7835873.39</v>
       </c>
       <c r="F30" t="n">
-        <v>10353866334.27</v>
+        <v>7835873.39</v>
       </c>
       <c r="G30" t="n">
-        <v>10353727456.5</v>
+        <v>7673251.28</v>
       </c>
       <c r="H30" t="n">
-        <v>57945.89</v>
+        <v>360498.89</v>
       </c>
       <c r="I30" t="n">
-        <v>759396.5699999999</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>817342.46</v>
+        <v>360498.89</v>
       </c>
     </row>
     <row r="31">
@@ -1500,34 +1488,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2151</v>
+        <v>4451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>36086163.78</v>
+        <v>32344430.46</v>
       </c>
       <c r="F31" t="n">
-        <v>33620279.41</v>
+        <v>26351673.32</v>
       </c>
       <c r="G31" t="n">
-        <v>33274997.49</v>
+        <v>25400808.53</v>
       </c>
       <c r="H31" t="n">
-        <v>218.93</v>
+        <v>64602.55</v>
       </c>
       <c r="I31" t="n">
-        <v>2003431.69</v>
+        <v>32256686.46</v>
       </c>
       <c r="J31" t="n">
-        <v>2003650.62</v>
+        <v>32321289.01</v>
       </c>
     </row>
     <row r="32">
@@ -1536,34 +1524,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2271</v>
+        <v>4031</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1512215059.36</v>
+        <v>1800564605.8</v>
       </c>
       <c r="F32" t="n">
-        <v>1408043649.18</v>
+        <v>1469098929.94</v>
       </c>
       <c r="G32" t="n">
-        <v>1351808321.49</v>
+        <v>1337370766.8</v>
       </c>
       <c r="H32" t="n">
-        <v>6041131.11</v>
+        <v>3735749.68</v>
       </c>
       <c r="I32" t="n">
-        <v>92917136.89</v>
+        <v>241718406.93</v>
       </c>
       <c r="J32" t="n">
-        <v>98958268</v>
+        <v>245454156.61</v>
       </c>
     </row>
     <row r="33">
@@ -1572,34 +1560,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4341</v>
+        <v>4291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>383516.53</v>
+        <v>9564422316.52</v>
       </c>
       <c r="F33" t="n">
-        <v>362529.62</v>
+        <v>7700657244.4</v>
       </c>
       <c r="G33" t="n">
-        <v>309609.01</v>
+        <v>7421469637.08</v>
       </c>
       <c r="H33" t="n">
-        <v>68494.85000000001</v>
+        <v>406056474.84</v>
       </c>
       <c r="I33" t="n">
-        <v>284844.95</v>
+        <v>525046753.85</v>
       </c>
       <c r="J33" t="n">
-        <v>353339.8</v>
+        <v>931103228.6900001</v>
       </c>
     </row>
     <row r="34">
@@ -1608,34 +1596,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2061</v>
+        <v>4691</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>42165711.88</v>
+        <v>34206115.73</v>
       </c>
       <c r="F34" t="n">
-        <v>38895755.04</v>
+        <v>8996184.449999999</v>
       </c>
       <c r="G34" t="n">
-        <v>38074348.02</v>
+        <v>7824565.3</v>
       </c>
       <c r="H34" t="n">
-        <v>27688.16</v>
+        <v>4586769.48</v>
       </c>
       <c r="I34" t="n">
-        <v>2077147.11</v>
+        <v>37399974.31</v>
       </c>
       <c r="J34" t="n">
-        <v>2104835.27</v>
+        <v>41986743.79</v>
       </c>
     </row>
     <row r="35">
@@ -1644,34 +1632,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4141</v>
+        <v>4701</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1383063.6</v>
+        <v>392849.77</v>
       </c>
       <c r="F35" t="n">
-        <v>1259836.85</v>
+        <v>356958.68</v>
       </c>
       <c r="G35" t="n">
-        <v>1103345.57</v>
+        <v>343503.3</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1064170.39</v>
+        <v>1235436.62</v>
       </c>
       <c r="J35" t="n">
-        <v>1064170.39</v>
+        <v>1235436.62</v>
       </c>
     </row>
     <row r="36">
@@ -1680,34 +1668,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4631</v>
+        <v>4711</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>570866345.95</v>
+        <v>10355634203.75</v>
       </c>
       <c r="F36" t="n">
-        <v>200928897.65</v>
+        <v>10353902013.01</v>
       </c>
       <c r="G36" t="n">
-        <v>185695277.13</v>
+        <v>10353755475</v>
       </c>
       <c r="H36" t="n">
-        <v>53631506.45</v>
+        <v>57945.89</v>
       </c>
       <c r="I36" t="n">
-        <v>35431658.61</v>
+        <v>759396.5699999999</v>
       </c>
       <c r="J36" t="n">
-        <v>89063165.06</v>
+        <v>817342.46</v>
       </c>
     </row>
     <row r="37">
@@ -1716,34 +1704,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2161</v>
+        <v>2151</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3318606.77</v>
+        <v>38872052.79</v>
       </c>
       <c r="F37" t="n">
-        <v>3148932.61</v>
+        <v>36426665.12</v>
       </c>
       <c r="G37" t="n">
-        <v>3076449.56</v>
+        <v>33278182.31</v>
       </c>
       <c r="H37" t="n">
-        <v>23147.54</v>
+        <v>218.93</v>
       </c>
       <c r="I37" t="n">
-        <v>154559.3</v>
+        <v>2003431.69</v>
       </c>
       <c r="J37" t="n">
-        <v>177706.84</v>
+        <v>2003650.62</v>
       </c>
     </row>
     <row r="38">
@@ -1752,34 +1740,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4551</v>
+        <v>2271</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>94331218.23999999</v>
+        <v>1513081780.18</v>
       </c>
       <c r="F38" t="n">
-        <v>75314682.45</v>
+        <v>1411677686.81</v>
       </c>
       <c r="G38" t="n">
-        <v>75291876.20999999</v>
+        <v>1352052415.96</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>6041131.11</v>
       </c>
       <c r="I38" t="n">
-        <v>486647</v>
+        <v>92917136.89</v>
       </c>
       <c r="J38" t="n">
-        <v>486647</v>
+        <v>98958268</v>
       </c>
     </row>
     <row r="39">
@@ -1788,34 +1776,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2261</v>
+        <v>4341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>272689211.85</v>
+        <v>383516.53</v>
       </c>
       <c r="F39" t="n">
-        <v>202777298.67</v>
+        <v>362529.62</v>
       </c>
       <c r="G39" t="n">
-        <v>191371189.07</v>
+        <v>318608.61</v>
       </c>
       <c r="H39" t="n">
-        <v>7187273.07</v>
+        <v>68494.85000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>133806987.85</v>
+        <v>284844.95</v>
       </c>
       <c r="J39" t="n">
-        <v>140994260.92</v>
+        <v>353339.8</v>
       </c>
     </row>
     <row r="40">
@@ -1824,34 +1812,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4381</v>
+        <v>2061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>68075254.52</v>
+        <v>42192150.72</v>
       </c>
       <c r="F40" t="n">
-        <v>46511366.19</v>
+        <v>38908453.03</v>
       </c>
       <c r="G40" t="n">
-        <v>42909975.91</v>
+        <v>38083738.2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>27688.16</v>
       </c>
       <c r="I40" t="n">
-        <v>17655143.4</v>
+        <v>2077147.11</v>
       </c>
       <c r="J40" t="n">
-        <v>17655143.4</v>
+        <v>2104835.27</v>
       </c>
     </row>
     <row r="41">
@@ -1860,34 +1848,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1071</v>
+        <v>4141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>60009688.08</v>
+        <v>7383063.6</v>
       </c>
       <c r="F41" t="n">
-        <v>32726369.24</v>
+        <v>1259836.85</v>
       </c>
       <c r="G41" t="n">
-        <v>29967519.44</v>
+        <v>1103345.57</v>
       </c>
       <c r="H41" t="n">
-        <v>1803218.12</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>11359008.03</v>
+        <v>1064170.39</v>
       </c>
       <c r="J41" t="n">
-        <v>13162226.15</v>
+        <v>1064170.39</v>
       </c>
     </row>
     <row r="42">
@@ -1896,34 +1884,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1916</v>
+        <v>4631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6470084509.41</v>
+        <v>570866345.95</v>
       </c>
       <c r="F42" t="n">
-        <v>5443212798.51</v>
+        <v>200928897.65</v>
       </c>
       <c r="G42" t="n">
-        <v>5386862798.93</v>
+        <v>185695277.13</v>
       </c>
       <c r="H42" t="n">
-        <v>43587892.37</v>
+        <v>53631506.45</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>35431658.61</v>
       </c>
       <c r="J42" t="n">
-        <v>43587892.37</v>
+        <v>89063165.06</v>
       </c>
     </row>
     <row r="43">
@@ -1932,34 +1920,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2321</v>
+        <v>2161</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>245473804.92</v>
+        <v>3321006.77</v>
       </c>
       <c r="F43" t="n">
-        <v>207990821.07</v>
+        <v>3150272.27</v>
       </c>
       <c r="G43" t="n">
-        <v>199832067.02</v>
+        <v>3077724.92</v>
       </c>
       <c r="H43" t="n">
-        <v>3348075.28</v>
+        <v>23147.54</v>
       </c>
       <c r="I43" t="n">
-        <v>23877480.85</v>
+        <v>154559.3</v>
       </c>
       <c r="J43" t="n">
-        <v>27225556.13</v>
+        <v>177706.84</v>
       </c>
     </row>
     <row r="44">
@@ -1968,34 +1956,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2421</v>
+        <v>4551</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>35730381.97</v>
+        <v>94331218.23999999</v>
       </c>
       <c r="F44" t="n">
-        <v>29019562.4</v>
+        <v>75314682.45</v>
       </c>
       <c r="G44" t="n">
-        <v>28501124.23</v>
+        <v>75291876.20999999</v>
       </c>
       <c r="H44" t="n">
-        <v>1021786.93</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>20421491.42</v>
+        <v>486647</v>
       </c>
       <c r="J44" t="n">
-        <v>21443278.35</v>
+        <v>486647</v>
       </c>
     </row>
     <row r="45">
@@ -2004,34 +1992,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FUNDALEMG</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2101</v>
+        <v>4121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDO ESPECIAL DA ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>130617071.83</v>
+        <v>5133755.67</v>
       </c>
       <c r="F45" t="n">
-        <v>126385709.85</v>
+        <v>5133755.67</v>
       </c>
       <c r="G45" t="n">
-        <v>119886840.37</v>
+        <v>4473014.43</v>
       </c>
       <c r="H45" t="n">
-        <v>486532.65</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>7674266.39</v>
+        <v>1486024.48</v>
       </c>
       <c r="J45" t="n">
-        <v>8160799.04</v>
+        <v>1486024.48</v>
       </c>
     </row>
     <row r="46">
@@ -2040,34 +2028,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2201</v>
+        <v>2261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>14518366.59</v>
+        <v>273395004.72</v>
       </c>
       <c r="F46" t="n">
-        <v>11279029.75</v>
+        <v>204373813.87</v>
       </c>
       <c r="G46" t="n">
-        <v>10947151.26</v>
+        <v>192212399.44</v>
       </c>
       <c r="H46" t="n">
-        <v>702452.89</v>
+        <v>7187273.07</v>
       </c>
       <c r="I46" t="n">
-        <v>447256.9</v>
+        <v>133806987.85</v>
       </c>
       <c r="J46" t="n">
-        <v>1149709.79</v>
+        <v>140994260.92</v>
       </c>
     </row>
     <row r="47">
@@ -2076,34 +2064,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2241</v>
+        <v>4441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>29791099.67</v>
+        <v>34398168.14</v>
       </c>
       <c r="F47" t="n">
-        <v>27447571.53</v>
+        <v>18389215.75</v>
       </c>
       <c r="G47" t="n">
-        <v>25969243.31</v>
+        <v>17921475.94</v>
       </c>
       <c r="H47" t="n">
-        <v>6104162.13</v>
+        <v>1618421.95</v>
       </c>
       <c r="I47" t="n">
-        <v>10971227.93</v>
+        <v>11762363.92</v>
       </c>
       <c r="J47" t="n">
-        <v>17075390.06</v>
+        <v>13380785.87</v>
       </c>
     </row>
     <row r="48">
@@ -2112,34 +2100,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2371</v>
+        <v>4381</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>172333235.8</v>
+        <v>68075254.52</v>
       </c>
       <c r="F48" t="n">
-        <v>165153183.18</v>
+        <v>46512604.69</v>
       </c>
       <c r="G48" t="n">
-        <v>164340471.78</v>
+        <v>42909975.91</v>
       </c>
       <c r="H48" t="n">
-        <v>509913.92</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>5029043.27</v>
+        <v>17655143.4</v>
       </c>
       <c r="J48" t="n">
-        <v>5538957.19</v>
+        <v>17655143.4</v>
       </c>
     </row>
     <row r="49">
@@ -2148,34 +2136,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2331</v>
+        <v>1071</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22285384.65</v>
+        <v>60175510.81</v>
       </c>
       <c r="F49" t="n">
-        <v>21735282.25</v>
+        <v>32968252.5</v>
       </c>
       <c r="G49" t="n">
-        <v>20800435.26</v>
+        <v>29974186.74</v>
       </c>
       <c r="H49" t="n">
-        <v>6330.51</v>
+        <v>1803218.12</v>
       </c>
       <c r="I49" t="n">
-        <v>1187624.4</v>
+        <v>11359008.03</v>
       </c>
       <c r="J49" t="n">
-        <v>1193954.91</v>
+        <v>13162226.15</v>
       </c>
     </row>
     <row r="50">
@@ -2184,34 +2172,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2011</v>
+        <v>1916</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1510617602.41</v>
+        <v>6470084509.41</v>
       </c>
       <c r="F50" t="n">
-        <v>1003106612.23</v>
+        <v>5443212798.51</v>
       </c>
       <c r="G50" t="n">
-        <v>950269130.99</v>
+        <v>5388725569.07</v>
       </c>
       <c r="H50" t="n">
-        <v>96897.37</v>
+        <v>43587892.37</v>
       </c>
       <c r="I50" t="n">
-        <v>193463880.41</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>193560777.78</v>
+        <v>43587892.37</v>
       </c>
     </row>
     <row r="51">
@@ -2220,34 +2208,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2121</v>
+        <v>2321</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1916521928.92</v>
+        <v>248896482.9</v>
       </c>
       <c r="F51" t="n">
-        <v>1881474307.27</v>
+        <v>208296338.8</v>
       </c>
       <c r="G51" t="n">
-        <v>1857816477.1</v>
+        <v>200326812.84</v>
       </c>
       <c r="H51" t="n">
-        <v>19331338.95</v>
+        <v>3348075.28</v>
       </c>
       <c r="I51" t="n">
-        <v>34533549.39</v>
+        <v>23877918.23</v>
       </c>
       <c r="J51" t="n">
-        <v>53864888.34</v>
+        <v>27225993.51</v>
       </c>
     </row>
     <row r="52">
@@ -2256,34 +2244,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2251</v>
+        <v>2421</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>26542686.76</v>
+        <v>35730381.97</v>
       </c>
       <c r="F52" t="n">
-        <v>21681770.69</v>
+        <v>29079575.92</v>
       </c>
       <c r="G52" t="n">
-        <v>21034312.38</v>
+        <v>28501124.23</v>
       </c>
       <c r="H52" t="n">
-        <v>1119472.81</v>
+        <v>1021786.93</v>
       </c>
       <c r="I52" t="n">
-        <v>1861547.75</v>
+        <v>20447586.11</v>
       </c>
       <c r="J52" t="n">
-        <v>2981020.56</v>
+        <v>21469373.04</v>
       </c>
     </row>
     <row r="53">
@@ -2292,34 +2280,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2041</v>
+        <v>2101</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2063938.86</v>
+        <v>133148923.52</v>
       </c>
       <c r="F53" t="n">
-        <v>2025539.08</v>
+        <v>126737956.12</v>
       </c>
       <c r="G53" t="n">
-        <v>1971796.92</v>
+        <v>120131611.74</v>
       </c>
       <c r="H53" t="n">
-        <v>1692.39</v>
+        <v>486532.65</v>
       </c>
       <c r="I53" t="n">
-        <v>32310.94</v>
+        <v>7674266.39</v>
       </c>
       <c r="J53" t="n">
-        <v>34003.33</v>
+        <v>8160799.04</v>
       </c>
     </row>
     <row r="54">
@@ -2328,34 +2316,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1101</v>
+        <v>2201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>11643712.8</v>
+        <v>14531480</v>
       </c>
       <c r="F54" t="n">
-        <v>11227925.73</v>
+        <v>11574104.99</v>
       </c>
       <c r="G54" t="n">
-        <v>11152763.72</v>
+        <v>10948638.61</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>702452.89</v>
       </c>
       <c r="I54" t="n">
-        <v>93457.72</v>
+        <v>447256.9</v>
       </c>
       <c r="J54" t="n">
-        <v>93457.72</v>
+        <v>1149709.79</v>
       </c>
     </row>
     <row r="55">
@@ -2364,29 +2352,35 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1915</v>
+        <v>2241</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>15557346.18</v>
+        <v>29791490.1</v>
       </c>
       <c r="F55" t="n">
-        <v>15557346.18</v>
+        <v>27486465.87</v>
       </c>
       <c r="G55" t="n">
-        <v>15557346.18</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+        <v>25975564.51</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6104162.13</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10971227.93</v>
+      </c>
+      <c r="J55" t="n">
+        <v>17075390.06</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2394,34 +2388,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1511</v>
+        <v>2371</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1909800259.32</v>
+        <v>172577200.5</v>
       </c>
       <c r="F56" t="n">
-        <v>1832674350.96</v>
+        <v>165329766.34</v>
       </c>
       <c r="G56" t="n">
-        <v>1814546561.13</v>
+        <v>164359930.33</v>
       </c>
       <c r="H56" t="n">
-        <v>8940604.800000001</v>
+        <v>509913.92</v>
       </c>
       <c r="I56" t="n">
-        <v>36021559.01</v>
+        <v>5029043.27</v>
       </c>
       <c r="J56" t="n">
-        <v>44962163.81</v>
+        <v>5538957.19</v>
       </c>
     </row>
     <row r="57">
@@ -2430,34 +2424,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1251</v>
+        <v>2331</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10229705360.79</v>
+        <v>22285384.65</v>
       </c>
       <c r="F57" t="n">
-        <v>10048900771.98</v>
+        <v>21748928.28</v>
       </c>
       <c r="G57" t="n">
-        <v>10012131466.37</v>
+        <v>20813533.99</v>
       </c>
       <c r="H57" t="n">
-        <v>18536120.52</v>
+        <v>6330.51</v>
       </c>
       <c r="I57" t="n">
-        <v>184554944.79</v>
+        <v>1187624.4</v>
       </c>
       <c r="J57" t="n">
-        <v>203091065.31</v>
+        <v>1193954.91</v>
       </c>
     </row>
     <row r="58">
@@ -2466,35 +2460,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1721</v>
+        <v>2361</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5166816.35</v>
+        <v>36674575.01</v>
       </c>
       <c r="F58" t="n">
-        <v>5127499.31</v>
+        <v>36674575.01</v>
       </c>
       <c r="G58" t="n">
-        <v>5021643.12</v>
-      </c>
-      <c r="H58" t="n">
-        <v>122407.67</v>
-      </c>
-      <c r="I58" t="n">
-        <v>217467.44</v>
-      </c>
-      <c r="J58" t="n">
-        <v>339875.11</v>
-      </c>
+        <v>36674575.01</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2502,34 +2490,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1231</v>
+        <v>2011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>319445806.3</v>
+        <v>1513247571.25</v>
       </c>
       <c r="F59" t="n">
-        <v>305967651</v>
+        <v>1004683126.95</v>
       </c>
       <c r="G59" t="n">
-        <v>275359973.62</v>
+        <v>952754443.16</v>
       </c>
       <c r="H59" t="n">
-        <v>6876518.16</v>
+        <v>96897.37</v>
       </c>
       <c r="I59" t="n">
-        <v>16804739.31</v>
+        <v>193463880.41</v>
       </c>
       <c r="J59" t="n">
-        <v>23681257.47</v>
+        <v>193560777.78</v>
       </c>
     </row>
     <row r="60">
@@ -2538,34 +2526,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1631</v>
+        <v>2121</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>7737352.03</v>
+        <v>1918711351.38</v>
       </c>
       <c r="F60" t="n">
-        <v>7537027.82</v>
+        <v>1887098328.34</v>
       </c>
       <c r="G60" t="n">
-        <v>7394721.15</v>
+        <v>1858230852.83</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>19331338.95</v>
       </c>
       <c r="I60" t="n">
-        <v>34378.25</v>
+        <v>34533549.39</v>
       </c>
       <c r="J60" t="n">
-        <v>34378.25</v>
+        <v>53864888.34</v>
       </c>
     </row>
     <row r="61">
@@ -2574,34 +2562,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1711</v>
+        <v>2251</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>86708274.93000001</v>
+        <v>26542686.76</v>
       </c>
       <c r="F61" t="n">
-        <v>60570990.74</v>
+        <v>21681770.69</v>
       </c>
       <c r="G61" t="n">
-        <v>55465404.97</v>
+        <v>21034312.38</v>
       </c>
       <c r="H61" t="n">
-        <v>60000.1</v>
+        <v>1119472.81</v>
       </c>
       <c r="I61" t="n">
-        <v>61241610.36</v>
+        <v>1861547.75</v>
       </c>
       <c r="J61" t="n">
-        <v>61301610.46</v>
+        <v>2981020.56</v>
       </c>
     </row>
     <row r="62">
@@ -2610,34 +2598,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1271</v>
+        <v>2041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>171946421.45</v>
+        <v>2136180.21</v>
       </c>
       <c r="F62" t="n">
-        <v>163173008.95</v>
+        <v>2110765.51</v>
       </c>
       <c r="G62" t="n">
-        <v>160722457.03</v>
+        <v>1977687.36</v>
       </c>
       <c r="H62" t="n">
-        <v>319615.87</v>
+        <v>1692.39</v>
       </c>
       <c r="I62" t="n">
-        <v>634111.73</v>
+        <v>32310.94</v>
       </c>
       <c r="J62" t="n">
-        <v>953727.6</v>
+        <v>34003.33</v>
       </c>
     </row>
     <row r="63">
@@ -2646,34 +2634,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1221</v>
+        <v>1101</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>282599912.71</v>
+        <v>11520444.05</v>
       </c>
       <c r="F63" t="n">
-        <v>51726050.15</v>
+        <v>11227925.73</v>
       </c>
       <c r="G63" t="n">
-        <v>50358956.45</v>
+        <v>11152763.72</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>40005821.35</v>
+        <v>93457.72</v>
       </c>
       <c r="J63" t="n">
-        <v>40005821.35</v>
+        <v>93457.72</v>
       </c>
     </row>
     <row r="64">
@@ -2682,35 +2670,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1481</v>
+        <v>1915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185763137.58</v>
+        <v>15557346.18</v>
       </c>
       <c r="F64" t="n">
-        <v>177086446.63</v>
+        <v>15557346.18</v>
       </c>
       <c r="G64" t="n">
-        <v>171228970.49</v>
-      </c>
-      <c r="H64" t="n">
-        <v>11942560.14</v>
-      </c>
-      <c r="I64" t="n">
-        <v>15956888.74</v>
-      </c>
-      <c r="J64" t="n">
-        <v>27899448.88</v>
-      </c>
+        <v>15557346.18</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2718,34 +2700,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1261</v>
+        <v>1511</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11847866748.19</v>
+        <v>1910507138.58</v>
       </c>
       <c r="F65" t="n">
-        <v>11539239278.88</v>
+        <v>1833143041.67</v>
       </c>
       <c r="G65" t="n">
-        <v>11479554726</v>
+        <v>1814834020.61</v>
       </c>
       <c r="H65" t="n">
-        <v>199907426.47</v>
+        <v>8940604.800000001</v>
       </c>
       <c r="I65" t="n">
-        <v>145442522.43</v>
+        <v>36021559.01</v>
       </c>
       <c r="J65" t="n">
-        <v>345349948.9</v>
+        <v>44962163.81</v>
       </c>
     </row>
     <row r="66">
@@ -2754,34 +2736,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1191</v>
+        <v>1091</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1082262047.26</v>
+        <v>2637829103.12</v>
       </c>
       <c r="F66" t="n">
-        <v>1008327889.53</v>
+        <v>2553293170.6</v>
       </c>
       <c r="G66" t="n">
-        <v>988016215.05</v>
+        <v>2530864251.23</v>
       </c>
       <c r="H66" t="n">
-        <v>7665444.21</v>
+        <v>2903668.96</v>
       </c>
       <c r="I66" t="n">
-        <v>57085162.85</v>
+        <v>73908144.37</v>
       </c>
       <c r="J66" t="n">
-        <v>64750607.06</v>
+        <v>76811813.33</v>
       </c>
     </row>
     <row r="67">
@@ -2790,34 +2772,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1491</v>
+        <v>1251</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>351184899.99</v>
+        <v>10231147240.12</v>
       </c>
       <c r="F67" t="n">
-        <v>347948057.18</v>
+        <v>10050555132.43</v>
       </c>
       <c r="G67" t="n">
-        <v>337732397.04</v>
+        <v>10012559337.12</v>
       </c>
       <c r="H67" t="n">
-        <v>11209003.04</v>
+        <v>18536120.52</v>
       </c>
       <c r="I67" t="n">
-        <v>4958053</v>
+        <v>184651886.79</v>
       </c>
       <c r="J67" t="n">
-        <v>16167056.04</v>
+        <v>203188007.31</v>
       </c>
     </row>
     <row r="68">
@@ -2826,34 +2808,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1301</v>
+        <v>1721</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>865638559.39</v>
+        <v>5161215.86</v>
       </c>
       <c r="F68" t="n">
-        <v>837411428.96</v>
+        <v>5127499.31</v>
       </c>
       <c r="G68" t="n">
-        <v>819600630.51</v>
+        <v>5021643.12</v>
       </c>
       <c r="H68" t="n">
-        <v>15843807.77</v>
+        <v>122407.67</v>
       </c>
       <c r="I68" t="n">
-        <v>27922531.5</v>
+        <v>217467.44</v>
       </c>
       <c r="J68" t="n">
-        <v>43766339.27</v>
+        <v>339875.11</v>
       </c>
     </row>
     <row r="69">
@@ -2862,34 +2844,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1451</v>
+        <v>1231</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2958737418.95</v>
+        <v>319509205.02</v>
       </c>
       <c r="F69" t="n">
-        <v>2711201183.7</v>
+        <v>306034091.73</v>
       </c>
       <c r="G69" t="n">
-        <v>2673739249.78</v>
+        <v>275422362.56</v>
       </c>
       <c r="H69" t="n">
-        <v>14535917.67</v>
+        <v>6876518.16</v>
       </c>
       <c r="I69" t="n">
-        <v>130140512.22</v>
+        <v>16804739.31</v>
       </c>
       <c r="J69" t="n">
-        <v>144676429.89</v>
+        <v>23681257.47</v>
       </c>
     </row>
     <row r="70">
@@ -2898,34 +2880,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1371</v>
+        <v>1631</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>145811257.97</v>
+        <v>7737352.03</v>
       </c>
       <c r="F70" t="n">
-        <v>138984415.08</v>
+        <v>7554354.88</v>
       </c>
       <c r="G70" t="n">
-        <v>131450357.12</v>
+        <v>7411645.49</v>
       </c>
       <c r="H70" t="n">
-        <v>3823909.86</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>4333968.61</v>
+        <v>34378.25</v>
       </c>
       <c r="J70" t="n">
-        <v>8157878.47</v>
+        <v>34378.25</v>
       </c>
     </row>
     <row r="71">
@@ -2934,34 +2916,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1501</v>
+        <v>1711</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>441219355.07</v>
+        <v>86682191.59999999</v>
       </c>
       <c r="F71" t="n">
-        <v>348809039.55</v>
+        <v>60571203.34</v>
       </c>
       <c r="G71" t="n">
-        <v>320539285.53</v>
+        <v>55465404.97</v>
       </c>
       <c r="H71" t="n">
-        <v>28800758.26</v>
+        <v>60000.1</v>
       </c>
       <c r="I71" t="n">
-        <v>69410912.92</v>
+        <v>61241610.36</v>
       </c>
       <c r="J71" t="n">
-        <v>98211671.18000001</v>
+        <v>61301610.46</v>
       </c>
     </row>
     <row r="72">
@@ -2970,34 +2952,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2211</v>
+        <v>1271</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>10515457.61</v>
+        <v>176742218.09</v>
       </c>
       <c r="F72" t="n">
-        <v>9043950.67</v>
+        <v>169163951.83</v>
       </c>
       <c r="G72" t="n">
-        <v>7994583.05</v>
+        <v>163258370.69</v>
       </c>
       <c r="H72" t="n">
-        <v>32410.16</v>
+        <v>319615.87</v>
       </c>
       <c r="I72" t="n">
-        <v>560777.9399999999</v>
+        <v>634111.73</v>
       </c>
       <c r="J72" t="n">
-        <v>593188.1</v>
+        <v>953727.6</v>
       </c>
     </row>
     <row r="73">
@@ -3006,34 +2988,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2351</v>
+        <v>1221</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>255250384.35</v>
+        <v>283519775.75</v>
       </c>
       <c r="F73" t="n">
-        <v>229976545.51</v>
+        <v>51727436.9</v>
       </c>
       <c r="G73" t="n">
-        <v>224976211.13</v>
+        <v>50360343.2</v>
       </c>
       <c r="H73" t="n">
-        <v>212410.94</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>19719523.6</v>
+        <v>40005821.35</v>
       </c>
       <c r="J73" t="n">
-        <v>19931934.54</v>
+        <v>40005821.35</v>
       </c>
     </row>
     <row r="74">
@@ -3042,34 +3024,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2311</v>
+        <v>1481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>296171203.29</v>
+        <v>185979084.28</v>
       </c>
       <c r="F74" t="n">
-        <v>276426814.07</v>
+        <v>177119519.28</v>
       </c>
       <c r="G74" t="n">
-        <v>270176853.43</v>
+        <v>171258028.77</v>
       </c>
       <c r="H74" t="n">
-        <v>130453.78</v>
+        <v>11942560.14</v>
       </c>
       <c r="I74" t="n">
-        <v>23179037.58</v>
+        <v>15956888.74</v>
       </c>
       <c r="J74" t="n">
-        <v>23309491.36</v>
+        <v>27899448.88</v>
       </c>
     </row>
     <row r="75">
@@ -3078,33 +3060,495 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>SEE</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1261</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>11846392492.2</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11542638818.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11486519267.89</v>
+      </c>
+      <c r="H75" t="n">
+        <v>199907426.47</v>
+      </c>
+      <c r="I75" t="n">
+        <v>145442522.43</v>
+      </c>
+      <c r="J75" t="n">
+        <v>345349948.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SEF</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1082661286.8</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1008422011.43</v>
+      </c>
+      <c r="G76" t="n">
+        <v>988655821.9400001</v>
+      </c>
+      <c r="H76" t="n">
+        <v>7665444.21</v>
+      </c>
+      <c r="I76" t="n">
+        <v>57313606.16</v>
+      </c>
+      <c r="J76" t="n">
+        <v>64979050.37</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SEGOV</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>350985602.7</v>
+      </c>
+      <c r="F77" t="n">
+        <v>347966423.03</v>
+      </c>
+      <c r="G77" t="n">
+        <v>337738726.89</v>
+      </c>
+      <c r="H77" t="n">
+        <v>11209003.04</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4958053</v>
+      </c>
+      <c r="J77" t="n">
+        <v>16167056.04</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SEINFRA</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>865679188.52</v>
+      </c>
+      <c r="F78" t="n">
+        <v>837414298.98</v>
+      </c>
+      <c r="G78" t="n">
+        <v>819603491.0700001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>15843807.77</v>
+      </c>
+      <c r="I78" t="n">
+        <v>27922531.5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>43766339.27</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SEJUSP</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2959474355.82</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2712544550.98</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2679434073.03</v>
+      </c>
+      <c r="H79" t="n">
+        <v>14535917.67</v>
+      </c>
+      <c r="I79" t="n">
+        <v>130178221.01</v>
+      </c>
+      <c r="J79" t="n">
+        <v>144714138.68</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>146097347.08</v>
+      </c>
+      <c r="F80" t="n">
+        <v>139031345.51</v>
+      </c>
+      <c r="G80" t="n">
+        <v>131468065.97</v>
+      </c>
+      <c r="H80" t="n">
+        <v>3823909.86</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4333968.61</v>
+      </c>
+      <c r="J80" t="n">
+        <v>8157878.47</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SEPLAG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>441263403.72</v>
+      </c>
+      <c r="F81" t="n">
+        <v>351154976.53</v>
+      </c>
+      <c r="G81" t="n">
+        <v>320559279.24</v>
+      </c>
+      <c r="H81" t="n">
+        <v>28800758.26</v>
+      </c>
+      <c r="I81" t="n">
+        <v>69410912.92</v>
+      </c>
+      <c r="J81" t="n">
+        <v>98211671.18000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TCEMG</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>824377961.83</v>
+      </c>
+      <c r="F82" t="n">
+        <v>799349646.21</v>
+      </c>
+      <c r="G82" t="n">
+        <v>792055697.61</v>
+      </c>
+      <c r="H82" t="n">
+        <v>6831.37</v>
+      </c>
+      <c r="I82" t="n">
+        <v>29944186.06</v>
+      </c>
+      <c r="J82" t="n">
+        <v>29951017.43</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TJMG</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5960601163.36</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5960601163.36</v>
+      </c>
+      <c r="G83" t="n">
+        <v>5960644580.03</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TJMMG</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>87210085.23999999</v>
+      </c>
+      <c r="F84" t="n">
+        <v>85960968.77</v>
+      </c>
+      <c r="G84" t="n">
+        <v>85141554.3</v>
+      </c>
+      <c r="H84" t="n">
+        <v>117516.51</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4472955.56</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4590472.07</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TV MINAS</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2211</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>10515847.61</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9044340.67</v>
+      </c>
+      <c r="G85" t="n">
+        <v>7994973.05</v>
+      </c>
+      <c r="H85" t="n">
+        <v>32410.16</v>
+      </c>
+      <c r="I85" t="n">
+        <v>560777.9399999999</v>
+      </c>
+      <c r="J85" t="n">
+        <v>593188.1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>255447900.37</v>
+      </c>
+      <c r="F86" t="n">
+        <v>230025078.9</v>
+      </c>
+      <c r="G86" t="n">
+        <v>225045062.42</v>
+      </c>
+      <c r="H86" t="n">
+        <v>212410.94</v>
+      </c>
+      <c r="I86" t="n">
+        <v>19719523.6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>19931934.54</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>296290218.31</v>
+      </c>
+      <c r="F87" t="n">
+        <v>276603827.46</v>
+      </c>
+      <c r="G87" t="n">
+        <v>270329239.33</v>
+      </c>
+      <c r="H87" t="n">
+        <v>130453.78</v>
+      </c>
+      <c r="I87" t="n">
+        <v>23270028.37</v>
+      </c>
+      <c r="J87" t="n">
+        <v>23400482.15</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="C88" t="n">
         <v>2281</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E75" t="n">
-        <v>4664247.3</v>
-      </c>
-      <c r="F75" t="n">
-        <v>3969132.75</v>
-      </c>
-      <c r="G75" t="n">
-        <v>3680268.15</v>
-      </c>
-      <c r="H75" t="n">
+      <c r="E88" t="n">
+        <v>4909061.97</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3983532.7</v>
+      </c>
+      <c r="G88" t="n">
+        <v>3694387.47</v>
+      </c>
+      <c r="H88" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I88" t="n">
         <v>263905.44</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J88" t="n">
         <v>263905.44</v>
       </c>
     </row>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>734562549.8200001</v>
+        <v>752620692.3099999</v>
       </c>
       <c r="F2" t="n">
-        <v>673615234.83</v>
+        <v>685518619.83</v>
       </c>
       <c r="G2" t="n">
-        <v>648458870.17</v>
+        <v>652284398.86</v>
       </c>
       <c r="H2" t="n">
         <v>214399217.64</v>
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4405901.79</v>
+        <v>4405900.79</v>
       </c>
       <c r="F3" t="n">
-        <v>3979411.44</v>
+        <v>4165467.73</v>
       </c>
       <c r="G3" t="n">
-        <v>3786153.58</v>
+        <v>3826097.61</v>
       </c>
       <c r="H3" t="n">
         <v>167935.23</v>
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1244613639.61</v>
+        <v>1248859971.37</v>
       </c>
       <c r="F4" t="n">
-        <v>1160969633.41</v>
+        <v>1166909784.09</v>
       </c>
       <c r="G4" t="n">
-        <v>1148721705.64</v>
+        <v>1154194510.58</v>
       </c>
       <c r="H4" t="n">
         <v>6630.3</v>
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4653416.51</v>
+        <v>4017822.78</v>
       </c>
       <c r="F5" t="n">
-        <v>2520939.62</v>
+        <v>2543460.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2320997.32</v>
+        <v>2343161.52</v>
       </c>
       <c r="H5" t="n">
         <v>17304.09</v>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13680200.2</v>
+        <v>13682629.31</v>
       </c>
       <c r="F6" t="n">
-        <v>12437440.66</v>
+        <v>12444322.72</v>
       </c>
       <c r="G6" t="n">
-        <v>12196695.8</v>
+        <v>12310886.47</v>
       </c>
       <c r="H6" t="n">
         <v>8281.799999999999</v>
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29681444.35</v>
+        <v>30182211.42</v>
       </c>
       <c r="F7" t="n">
-        <v>22779913.34</v>
+        <v>22815850.85</v>
       </c>
       <c r="G7" t="n">
-        <v>21009823.44</v>
+        <v>21025702.68</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1243690975.8</v>
+        <v>1244230747.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1195761025.63</v>
+        <v>1196726966.24</v>
       </c>
       <c r="G8" t="n">
-        <v>1188465677.96</v>
+        <v>1188684859.92</v>
       </c>
       <c r="H8" t="n">
         <v>6046803.88</v>
       </c>
       <c r="I8" t="n">
-        <v>36365738.63</v>
+        <v>40120083.83</v>
       </c>
       <c r="J8" t="n">
-        <v>42412542.51</v>
+        <v>46166887.71</v>
       </c>
     </row>
     <row r="9">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>41248498.52</v>
+        <v>41248674.64</v>
       </c>
       <c r="F9" t="n">
-        <v>40416316.16</v>
+        <v>40616933.29</v>
       </c>
       <c r="G9" t="n">
         <v>40327275.65</v>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>651992053.26</v>
+        <v>657745380.83</v>
       </c>
       <c r="F10" t="n">
-        <v>645656844.39</v>
+        <v>647654106.23</v>
       </c>
       <c r="G10" t="n">
-        <v>633038463.35</v>
+        <v>635557692.46</v>
       </c>
       <c r="H10" t="n">
         <v>7410</v>
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1499682431.17</v>
+        <v>1521501436.26</v>
       </c>
       <c r="F11" t="n">
-        <v>824355792.11</v>
+        <v>842228728.8200001</v>
       </c>
       <c r="G11" t="n">
-        <v>756256401.0599999</v>
+        <v>770351970.6900001</v>
       </c>
       <c r="H11" t="n">
         <v>13431647.55</v>
       </c>
       <c r="I11" t="n">
-        <v>315282883.59</v>
+        <v>315352398.37</v>
       </c>
       <c r="J11" t="n">
-        <v>328714531.14</v>
+        <v>328784045.92</v>
       </c>
     </row>
     <row r="12">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>90330686.45</v>
+        <v>91741567.73</v>
       </c>
       <c r="F12" t="n">
-        <v>60068361.36</v>
+        <v>61684923.03</v>
       </c>
       <c r="G12" t="n">
-        <v>55512577.41</v>
+        <v>55914234.61</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>759509748.28</v>
+        <v>901530417.48</v>
       </c>
       <c r="F13" t="n">
-        <v>509322862.97</v>
+        <v>656760506.6799999</v>
       </c>
       <c r="G13" t="n">
-        <v>509318500.2</v>
+        <v>656756143.91</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -924,22 +924,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106602145</v>
+        <v>106613604.26</v>
       </c>
       <c r="F14" t="n">
-        <v>105092389.2</v>
+        <v>105103848.46</v>
       </c>
       <c r="G14" t="n">
-        <v>104899461.81</v>
+        <v>104910921.07</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>893022.58</v>
+        <v>895934.49</v>
       </c>
       <c r="J14" t="n">
-        <v>893022.58</v>
+        <v>895934.49</v>
       </c>
     </row>
     <row r="15">
@@ -960,13 +960,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>180266897.78</v>
+        <v>210407094.06</v>
       </c>
       <c r="F15" t="n">
-        <v>180266897.78</v>
+        <v>210407094.06</v>
       </c>
       <c r="G15" t="n">
-        <v>180266897.78</v>
+        <v>210407094.06</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>15493154.83</v>
+        <v>17658291.2</v>
       </c>
       <c r="F16" t="n">
-        <v>15493154.83</v>
+        <v>17658291.2</v>
       </c>
       <c r="G16" t="n">
-        <v>15493154.83</v>
+        <v>17658291.2</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71727903.56999999</v>
+        <v>85431443.5</v>
       </c>
       <c r="F17" t="n">
-        <v>71727903.56999999</v>
+        <v>85431443.5</v>
       </c>
       <c r="G17" t="n">
-        <v>71727903.56999999</v>
+        <v>85431443.5</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1050,13 +1050,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14680022.46</v>
+        <v>17847575.25</v>
       </c>
       <c r="F18" t="n">
-        <v>13256094.73</v>
+        <v>13503523.05</v>
       </c>
       <c r="G18" t="n">
-        <v>12914678.02</v>
+        <v>12938907.78</v>
       </c>
       <c r="H18" t="n">
         <v>211328.04</v>
@@ -1125,10 +1125,10 @@
         <v>2825008.42</v>
       </c>
       <c r="F20" t="n">
-        <v>2728137.02</v>
+        <v>2732511.68</v>
       </c>
       <c r="G20" t="n">
-        <v>2547852.14</v>
+        <v>2617470.23</v>
       </c>
       <c r="H20" t="n">
         <v>46386.19</v>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>363117260.53</v>
+        <v>367149212.36</v>
       </c>
       <c r="F21" t="n">
-        <v>316837626.35</v>
+        <v>321440796.32</v>
       </c>
       <c r="G21" t="n">
-        <v>306284470.66</v>
+        <v>312430080.13</v>
       </c>
       <c r="H21" t="n">
         <v>3369120.12</v>
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36900786.26</v>
+        <v>36940378.21</v>
       </c>
       <c r="F22" t="n">
-        <v>32634752.56</v>
+        <v>33587303.97</v>
       </c>
       <c r="G22" t="n">
-        <v>31802748.5</v>
+        <v>31836868.88</v>
       </c>
       <c r="H22" t="n">
         <v>866933.3100000001</v>
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7267875.22</v>
+        <v>7600917.52</v>
       </c>
       <c r="F25" t="n">
-        <v>4014535.36</v>
+        <v>4017134.11</v>
       </c>
       <c r="G25" t="n">
-        <v>3810057.37</v>
+        <v>3812656.12</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>45271913.72</v>
+        <v>45458888.15</v>
       </c>
       <c r="F26" t="n">
-        <v>44627922.64</v>
+        <v>45039164.29</v>
       </c>
       <c r="G26" t="n">
-        <v>43017537.48</v>
+        <v>43021886.33</v>
       </c>
       <c r="H26" t="n">
         <v>8.359999999999999</v>
@@ -1362,22 +1362,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>115195927.68</v>
+        <v>115639161.6</v>
       </c>
       <c r="F27" t="n">
-        <v>85163012.51000001</v>
+        <v>95054425.70999999</v>
       </c>
       <c r="G27" t="n">
-        <v>83983409.91</v>
+        <v>84043290.43000001</v>
       </c>
       <c r="H27" t="n">
         <v>594553.05</v>
       </c>
       <c r="I27" t="n">
-        <v>942023.0699999999</v>
+        <v>1398403.07</v>
       </c>
       <c r="J27" t="n">
-        <v>1536576.12</v>
+        <v>1992956.12</v>
       </c>
     </row>
     <row r="28">
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2415176.35</v>
+        <v>5461576.35</v>
       </c>
       <c r="F29" t="n">
-        <v>35048</v>
+        <v>1251642</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1500,22 +1500,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>32344430.46</v>
+        <v>33273206.74</v>
       </c>
       <c r="F31" t="n">
-        <v>26351673.32</v>
+        <v>28444078.41</v>
       </c>
       <c r="G31" t="n">
-        <v>25400808.53</v>
+        <v>27195758.83</v>
       </c>
       <c r="H31" t="n">
         <v>64602.55</v>
       </c>
       <c r="I31" t="n">
-        <v>32256686.46</v>
+        <v>32257156.6</v>
       </c>
       <c r="J31" t="n">
-        <v>32321289.01</v>
+        <v>32321759.15</v>
       </c>
     </row>
     <row r="32">
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1800564605.8</v>
+        <v>1852742918.43</v>
       </c>
       <c r="F32" t="n">
-        <v>1469098929.94</v>
+        <v>1522709918.95</v>
       </c>
       <c r="G32" t="n">
-        <v>1337370766.8</v>
+        <v>1388743960.9</v>
       </c>
       <c r="H32" t="n">
         <v>3735749.68</v>
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>9564422316.52</v>
+        <v>9627898259.98</v>
       </c>
       <c r="F33" t="n">
-        <v>7700657244.4</v>
+        <v>7764261566.23</v>
       </c>
       <c r="G33" t="n">
-        <v>7421469637.08</v>
+        <v>7651508079.78</v>
       </c>
       <c r="H33" t="n">
-        <v>406056474.84</v>
+        <v>408368777.38</v>
       </c>
       <c r="I33" t="n">
-        <v>525046753.85</v>
+        <v>526147048.92</v>
       </c>
       <c r="J33" t="n">
-        <v>931103228.6900001</v>
+        <v>934515826.3</v>
       </c>
     </row>
     <row r="34">
@@ -1608,22 +1608,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>34206115.73</v>
+        <v>38263914.83</v>
       </c>
       <c r="F34" t="n">
-        <v>8996184.449999999</v>
+        <v>9519790.93</v>
       </c>
       <c r="G34" t="n">
-        <v>7824565.3</v>
+        <v>7940338.83</v>
       </c>
       <c r="H34" t="n">
         <v>4586769.48</v>
       </c>
       <c r="I34" t="n">
-        <v>37399974.31</v>
+        <v>38121054.54</v>
       </c>
       <c r="J34" t="n">
-        <v>41986743.79</v>
+        <v>42707824.02</v>
       </c>
     </row>
     <row r="35">
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>392849.77</v>
+        <v>447503.2</v>
       </c>
       <c r="F35" t="n">
-        <v>356958.68</v>
+        <v>370161.07</v>
       </c>
       <c r="G35" t="n">
-        <v>343503.3</v>
+        <v>356194.78</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10355634203.75</v>
+        <v>10356563942.37</v>
       </c>
       <c r="F36" t="n">
-        <v>10353902013.01</v>
+        <v>10354839342.48</v>
       </c>
       <c r="G36" t="n">
-        <v>10353755475</v>
+        <v>10354690898.05</v>
       </c>
       <c r="H36" t="n">
         <v>57945.89</v>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>38872052.79</v>
+        <v>38933328.21</v>
       </c>
       <c r="F37" t="n">
-        <v>36426665.12</v>
+        <v>36543528.65</v>
       </c>
       <c r="G37" t="n">
-        <v>33278182.31</v>
+        <v>33302605.77</v>
       </c>
       <c r="H37" t="n">
         <v>218.93</v>
@@ -1752,22 +1752,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1513081780.18</v>
+        <v>1528867657.2</v>
       </c>
       <c r="F38" t="n">
-        <v>1411677686.81</v>
+        <v>1428384594.3</v>
       </c>
       <c r="G38" t="n">
-        <v>1352052415.96</v>
+        <v>1371087704.36</v>
       </c>
       <c r="H38" t="n">
         <v>6041131.11</v>
       </c>
       <c r="I38" t="n">
-        <v>92917136.89</v>
+        <v>93465890.20999999</v>
       </c>
       <c r="J38" t="n">
-        <v>98958268</v>
+        <v>99507021.31999999</v>
       </c>
     </row>
     <row r="39">
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>383516.53</v>
+        <v>383813.38</v>
       </c>
       <c r="F39" t="n">
-        <v>362529.62</v>
+        <v>362826.47</v>
       </c>
       <c r="G39" t="n">
-        <v>318608.61</v>
+        <v>318905.46</v>
       </c>
       <c r="H39" t="n">
         <v>68494.85000000001</v>
@@ -1824,22 +1824,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>42192150.72</v>
+        <v>41957443.38</v>
       </c>
       <c r="F40" t="n">
-        <v>38908453.03</v>
+        <v>39711853.3</v>
       </c>
       <c r="G40" t="n">
-        <v>38083738.2</v>
+        <v>38200190.08</v>
       </c>
       <c r="H40" t="n">
         <v>27688.16</v>
       </c>
       <c r="I40" t="n">
-        <v>2077147.11</v>
+        <v>2223889.93</v>
       </c>
       <c r="J40" t="n">
-        <v>2104835.27</v>
+        <v>2251578.09</v>
       </c>
     </row>
     <row r="41">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>570866345.95</v>
+        <v>583177905.95</v>
       </c>
       <c r="F42" t="n">
         <v>200928897.65</v>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3321006.77</v>
+        <v>3723996.76</v>
       </c>
       <c r="F43" t="n">
-        <v>3150272.27</v>
+        <v>3152508.98</v>
       </c>
       <c r="G43" t="n">
-        <v>3077724.92</v>
+        <v>3079960.16</v>
       </c>
       <c r="H43" t="n">
         <v>23147.54</v>
@@ -1971,10 +1971,10 @@
         <v>94331218.23999999</v>
       </c>
       <c r="F44" t="n">
-        <v>75314682.45</v>
+        <v>82432650.7</v>
       </c>
       <c r="G44" t="n">
-        <v>75291876.20999999</v>
+        <v>82409844.45999999</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5133755.67</v>
+        <v>5537566.67</v>
       </c>
       <c r="F45" t="n">
-        <v>5133755.67</v>
+        <v>5537566.67</v>
       </c>
       <c r="G45" t="n">
         <v>4473014.43</v>
@@ -2040,22 +2040,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>273395004.72</v>
+        <v>275300839.68</v>
       </c>
       <c r="F46" t="n">
-        <v>204373813.87</v>
+        <v>206479814.85</v>
       </c>
       <c r="G46" t="n">
-        <v>192212399.44</v>
+        <v>194134841.11</v>
       </c>
       <c r="H46" t="n">
         <v>7187273.07</v>
       </c>
       <c r="I46" t="n">
-        <v>133806987.85</v>
+        <v>133812063.31</v>
       </c>
       <c r="J46" t="n">
-        <v>140994260.92</v>
+        <v>140999336.38</v>
       </c>
     </row>
     <row r="47">
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>34398168.14</v>
+        <v>34559002.14</v>
       </c>
       <c r="F47" t="n">
-        <v>18389215.75</v>
+        <v>18438504.52</v>
       </c>
       <c r="G47" t="n">
-        <v>17921475.94</v>
+        <v>17964206.49</v>
       </c>
       <c r="H47" t="n">
         <v>1618421.95</v>
       </c>
       <c r="I47" t="n">
-        <v>11762363.92</v>
+        <v>11763907.67</v>
       </c>
       <c r="J47" t="n">
-        <v>13380785.87</v>
+        <v>13382329.62</v>
       </c>
     </row>
     <row r="48">
@@ -2112,13 +2112,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>68075254.52</v>
+        <v>76668649.38</v>
       </c>
       <c r="F48" t="n">
-        <v>46512604.69</v>
+        <v>48517242.95</v>
       </c>
       <c r="G48" t="n">
-        <v>42909975.91</v>
+        <v>44958428.11</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2148,22 +2148,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60175510.81</v>
+        <v>60776001.68</v>
       </c>
       <c r="F49" t="n">
-        <v>32968252.5</v>
+        <v>33509841.88</v>
       </c>
       <c r="G49" t="n">
-        <v>29974186.74</v>
+        <v>31353476.52</v>
       </c>
       <c r="H49" t="n">
         <v>1803218.12</v>
       </c>
       <c r="I49" t="n">
-        <v>11359008.03</v>
+        <v>12201363.74</v>
       </c>
       <c r="J49" t="n">
-        <v>13162226.15</v>
+        <v>14004581.86</v>
       </c>
     </row>
     <row r="50">
@@ -2187,10 +2187,10 @@
         <v>6470084509.41</v>
       </c>
       <c r="F50" t="n">
-        <v>5443212798.51</v>
+        <v>5505007532.43</v>
       </c>
       <c r="G50" t="n">
-        <v>5388725569.07</v>
+        <v>5442367303.33</v>
       </c>
       <c r="H50" t="n">
         <v>43587892.37</v>
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>248896482.9</v>
+        <v>251376332.38</v>
       </c>
       <c r="F51" t="n">
-        <v>208296338.8</v>
+        <v>208814598.75</v>
       </c>
       <c r="G51" t="n">
-        <v>200326812.84</v>
+        <v>202069398.31</v>
       </c>
       <c r="H51" t="n">
         <v>3348075.28</v>
       </c>
       <c r="I51" t="n">
-        <v>23877918.23</v>
+        <v>23920129.79</v>
       </c>
       <c r="J51" t="n">
-        <v>27225993.51</v>
+        <v>27268205.07</v>
       </c>
     </row>
     <row r="52">
@@ -2256,13 +2256,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>35730381.97</v>
+        <v>36310404.77</v>
       </c>
       <c r="F52" t="n">
-        <v>29079575.92</v>
+        <v>29151316.95</v>
       </c>
       <c r="G52" t="n">
-        <v>28501124.23</v>
+        <v>28632877.04</v>
       </c>
       <c r="H52" t="n">
         <v>1021786.93</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>133148923.52</v>
+        <v>137598925.81</v>
       </c>
       <c r="F53" t="n">
-        <v>126737956.12</v>
+        <v>128151768.74</v>
       </c>
       <c r="G53" t="n">
-        <v>120131611.74</v>
+        <v>121237551.33</v>
       </c>
       <c r="H53" t="n">
         <v>486532.65</v>
@@ -2328,22 +2328,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14531480</v>
+        <v>12479577.8</v>
       </c>
       <c r="F54" t="n">
-        <v>11574104.99</v>
+        <v>11627274.98</v>
       </c>
       <c r="G54" t="n">
-        <v>10948638.61</v>
+        <v>11251810.86</v>
       </c>
       <c r="H54" t="n">
         <v>702452.89</v>
       </c>
       <c r="I54" t="n">
-        <v>447256.9</v>
+        <v>500171.63</v>
       </c>
       <c r="J54" t="n">
-        <v>1149709.79</v>
+        <v>1202624.52</v>
       </c>
     </row>
     <row r="55">
@@ -2364,22 +2364,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29791490.1</v>
+        <v>29985122.69</v>
       </c>
       <c r="F55" t="n">
-        <v>27486465.87</v>
+        <v>27678111.92</v>
       </c>
       <c r="G55" t="n">
-        <v>25975564.51</v>
+        <v>26171362.46</v>
       </c>
       <c r="H55" t="n">
-        <v>6104162.13</v>
+        <v>6973895.8</v>
       </c>
       <c r="I55" t="n">
         <v>10971227.93</v>
       </c>
       <c r="J55" t="n">
-        <v>17075390.06</v>
+        <v>17945123.73</v>
       </c>
     </row>
     <row r="56">
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>172577200.5</v>
+        <v>173222482.14</v>
       </c>
       <c r="F56" t="n">
-        <v>165329766.34</v>
+        <v>166797609.45</v>
       </c>
       <c r="G56" t="n">
-        <v>164359930.33</v>
+        <v>165883790.64</v>
       </c>
       <c r="H56" t="n">
         <v>509913.92</v>
@@ -2436,13 +2436,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>22285384.65</v>
+        <v>22705305.12</v>
       </c>
       <c r="F57" t="n">
-        <v>21748928.28</v>
+        <v>22045437.89</v>
       </c>
       <c r="G57" t="n">
-        <v>20813533.99</v>
+        <v>21113915.31</v>
       </c>
       <c r="H57" t="n">
         <v>6330.51</v>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>36674575.01</v>
+        <v>42043986.36</v>
       </c>
       <c r="F58" t="n">
-        <v>36674575.01</v>
+        <v>42043986.36</v>
       </c>
       <c r="G58" t="n">
-        <v>36674575.01</v>
+        <v>42043986.36</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2502,22 +2502,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1513247571.25</v>
+        <v>1520682290.54</v>
       </c>
       <c r="F59" t="n">
-        <v>1004683126.95</v>
+        <v>1030557799.8</v>
       </c>
       <c r="G59" t="n">
-        <v>952754443.16</v>
+        <v>1004987048.91</v>
       </c>
       <c r="H59" t="n">
         <v>96897.37</v>
       </c>
       <c r="I59" t="n">
-        <v>193463880.41</v>
+        <v>193539528.62</v>
       </c>
       <c r="J59" t="n">
-        <v>193560777.78</v>
+        <v>193636425.99</v>
       </c>
     </row>
     <row r="60">
@@ -2538,22 +2538,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1918711351.38</v>
+        <v>1919344634.1</v>
       </c>
       <c r="F60" t="n">
-        <v>1887098328.34</v>
+        <v>1889756958.13</v>
       </c>
       <c r="G60" t="n">
-        <v>1858230852.83</v>
+        <v>1868659071.76</v>
       </c>
       <c r="H60" t="n">
         <v>19331338.95</v>
       </c>
       <c r="I60" t="n">
-        <v>34533549.39</v>
+        <v>34541276.63</v>
       </c>
       <c r="J60" t="n">
-        <v>53864888.34</v>
+        <v>53872615.58</v>
       </c>
     </row>
     <row r="61">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>26542686.76</v>
+        <v>26632542.48</v>
       </c>
       <c r="F61" t="n">
-        <v>21681770.69</v>
+        <v>21829892.67</v>
       </c>
       <c r="G61" t="n">
-        <v>21034312.38</v>
+        <v>21035034.88</v>
       </c>
       <c r="H61" t="n">
         <v>1119472.81</v>
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2136180.21</v>
+        <v>2131579.3</v>
       </c>
       <c r="F62" t="n">
-        <v>2110765.51</v>
+        <v>2110865.59</v>
       </c>
       <c r="G62" t="n">
-        <v>1977687.36</v>
+        <v>1977787.44</v>
       </c>
       <c r="H62" t="n">
         <v>1692.39</v>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11520444.05</v>
+        <v>11646897.13</v>
       </c>
       <c r="F63" t="n">
-        <v>11227925.73</v>
+        <v>11306723.26</v>
       </c>
       <c r="G63" t="n">
-        <v>11152763.72</v>
+        <v>11220887.32</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2712,22 +2712,22 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1910507138.58</v>
+        <v>1916710631.48</v>
       </c>
       <c r="F65" t="n">
-        <v>1833143041.67</v>
+        <v>1840619128.35</v>
       </c>
       <c r="G65" t="n">
-        <v>1814834020.61</v>
+        <v>1816682778.43</v>
       </c>
       <c r="H65" t="n">
         <v>8940604.800000001</v>
       </c>
       <c r="I65" t="n">
-        <v>36021559.01</v>
+        <v>36346355.92</v>
       </c>
       <c r="J65" t="n">
-        <v>44962163.81</v>
+        <v>45286960.72</v>
       </c>
     </row>
     <row r="66">
@@ -2748,22 +2748,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2637829103.12</v>
+        <v>2647726417.79</v>
       </c>
       <c r="F66" t="n">
-        <v>2553293170.6</v>
+        <v>2562940668.11</v>
       </c>
       <c r="G66" t="n">
-        <v>2530864251.23</v>
+        <v>2540196416.99</v>
       </c>
       <c r="H66" t="n">
         <v>2903668.96</v>
       </c>
       <c r="I66" t="n">
-        <v>73908144.37</v>
+        <v>74129286.09999999</v>
       </c>
       <c r="J66" t="n">
-        <v>76811813.33</v>
+        <v>77032955.06</v>
       </c>
     </row>
     <row r="67">
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10231147240.12</v>
+        <v>10239585264.17</v>
       </c>
       <c r="F67" t="n">
-        <v>10050555132.43</v>
+        <v>10056512792.79</v>
       </c>
       <c r="G67" t="n">
-        <v>10012559337.12</v>
+        <v>10019574022.91</v>
       </c>
       <c r="H67" t="n">
         <v>18536120.52</v>
       </c>
       <c r="I67" t="n">
-        <v>184651886.79</v>
+        <v>185087240.89</v>
       </c>
       <c r="J67" t="n">
-        <v>203188007.31</v>
+        <v>203623361.41</v>
       </c>
     </row>
     <row r="68">
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5161215.86</v>
+        <v>5205500.86</v>
       </c>
       <c r="F68" t="n">
         <v>5127499.31</v>
@@ -2856,22 +2856,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>319509205.02</v>
+        <v>319681569.34</v>
       </c>
       <c r="F69" t="n">
-        <v>306034091.73</v>
+        <v>306249879.72</v>
       </c>
       <c r="G69" t="n">
-        <v>275422362.56</v>
+        <v>281025856.32</v>
       </c>
       <c r="H69" t="n">
         <v>6876518.16</v>
       </c>
       <c r="I69" t="n">
-        <v>16804739.31</v>
+        <v>17066235.64</v>
       </c>
       <c r="J69" t="n">
-        <v>23681257.47</v>
+        <v>23942753.8</v>
       </c>
     </row>
     <row r="70">
@@ -2892,13 +2892,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7737352.03</v>
+        <v>7830450.35</v>
       </c>
       <c r="F70" t="n">
-        <v>7554354.88</v>
+        <v>7573268.49</v>
       </c>
       <c r="G70" t="n">
-        <v>7411645.49</v>
+        <v>7430514.43</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2928,22 +2928,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>86682191.59999999</v>
+        <v>86863535.37</v>
       </c>
       <c r="F71" t="n">
-        <v>60571203.34</v>
+        <v>63750813.94</v>
       </c>
       <c r="G71" t="n">
-        <v>55465404.97</v>
+        <v>57695523.18</v>
       </c>
       <c r="H71" t="n">
         <v>60000.1</v>
       </c>
       <c r="I71" t="n">
-        <v>61241610.36</v>
+        <v>61968141.74</v>
       </c>
       <c r="J71" t="n">
-        <v>61301610.46</v>
+        <v>62028141.84</v>
       </c>
     </row>
     <row r="72">
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>176742218.09</v>
+        <v>182752516.09</v>
       </c>
       <c r="F72" t="n">
-        <v>169163951.83</v>
+        <v>173919446.19</v>
       </c>
       <c r="G72" t="n">
-        <v>163258370.69</v>
+        <v>170753192.37</v>
       </c>
       <c r="H72" t="n">
         <v>319615.87</v>
@@ -3000,13 +3000,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>283519775.75</v>
+        <v>283612179.46</v>
       </c>
       <c r="F73" t="n">
-        <v>51727436.9</v>
+        <v>52731378.7</v>
       </c>
       <c r="G73" t="n">
-        <v>50360343.2</v>
+        <v>51209783.63</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3036,22 +3036,22 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185979084.28</v>
+        <v>186619675.22</v>
       </c>
       <c r="F74" t="n">
-        <v>177119519.28</v>
+        <v>177193783.89</v>
       </c>
       <c r="G74" t="n">
-        <v>171258028.77</v>
+        <v>171575931.03</v>
       </c>
       <c r="H74" t="n">
         <v>11942560.14</v>
       </c>
       <c r="I74" t="n">
-        <v>15956888.74</v>
+        <v>16037031.82</v>
       </c>
       <c r="J74" t="n">
-        <v>27899448.88</v>
+        <v>27979591.96</v>
       </c>
     </row>
     <row r="75">
@@ -3072,22 +3072,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>11846392492.2</v>
+        <v>11879343269.82</v>
       </c>
       <c r="F75" t="n">
-        <v>11542638818.21</v>
+        <v>11555326866.6</v>
       </c>
       <c r="G75" t="n">
-        <v>11486519267.89</v>
+        <v>11516623306.1</v>
       </c>
       <c r="H75" t="n">
         <v>199907426.47</v>
       </c>
       <c r="I75" t="n">
-        <v>145442522.43</v>
+        <v>145444134.85</v>
       </c>
       <c r="J75" t="n">
-        <v>345349948.9</v>
+        <v>345351561.32</v>
       </c>
     </row>
     <row r="76">
@@ -3108,13 +3108,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1082661286.8</v>
+        <v>1092450835.95</v>
       </c>
       <c r="F76" t="n">
-        <v>1008422011.43</v>
+        <v>1012056912.62</v>
       </c>
       <c r="G76" t="n">
-        <v>988655821.9400001</v>
+        <v>993851496.4</v>
       </c>
       <c r="H76" t="n">
         <v>7665444.21</v>
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>350985602.7</v>
+        <v>351020515.67</v>
       </c>
       <c r="F77" t="n">
-        <v>347966423.03</v>
+        <v>348153288.83</v>
       </c>
       <c r="G77" t="n">
-        <v>337738726.89</v>
+        <v>338165674.71</v>
       </c>
       <c r="H77" t="n">
         <v>11209003.04</v>
@@ -3180,22 +3180,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>865679188.52</v>
+        <v>865698344.35</v>
       </c>
       <c r="F78" t="n">
-        <v>837414298.98</v>
+        <v>837569561.85</v>
       </c>
       <c r="G78" t="n">
-        <v>819603491.0700001</v>
+        <v>819945622.47</v>
       </c>
       <c r="H78" t="n">
         <v>15843807.77</v>
       </c>
       <c r="I78" t="n">
-        <v>27922531.5</v>
+        <v>29097751.57</v>
       </c>
       <c r="J78" t="n">
-        <v>43766339.27</v>
+        <v>44941559.34</v>
       </c>
     </row>
     <row r="79">
@@ -3216,22 +3216,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2959474355.82</v>
+        <v>2970711458.04</v>
       </c>
       <c r="F79" t="n">
-        <v>2712544550.98</v>
+        <v>2737401767.01</v>
       </c>
       <c r="G79" t="n">
-        <v>2679434073.03</v>
+        <v>2682018405.3</v>
       </c>
       <c r="H79" t="n">
         <v>14535917.67</v>
       </c>
       <c r="I79" t="n">
-        <v>130178221.01</v>
+        <v>130184006.95</v>
       </c>
       <c r="J79" t="n">
-        <v>144714138.68</v>
+        <v>144719924.62</v>
       </c>
     </row>
     <row r="80">
@@ -3252,22 +3252,22 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>146097347.08</v>
+        <v>146679345.08</v>
       </c>
       <c r="F80" t="n">
-        <v>139031345.51</v>
+        <v>139914269.33</v>
       </c>
       <c r="G80" t="n">
-        <v>131468065.97</v>
+        <v>133856016.92</v>
       </c>
       <c r="H80" t="n">
         <v>3823909.86</v>
       </c>
       <c r="I80" t="n">
-        <v>4333968.61</v>
+        <v>4463529.39</v>
       </c>
       <c r="J80" t="n">
-        <v>8157878.47</v>
+        <v>8287439.25</v>
       </c>
     </row>
     <row r="81">
@@ -3288,22 +3288,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>441263403.72</v>
+        <v>442042309.26</v>
       </c>
       <c r="F81" t="n">
-        <v>351154976.53</v>
+        <v>358079671.15</v>
       </c>
       <c r="G81" t="n">
-        <v>320559279.24</v>
+        <v>321457214.02</v>
       </c>
       <c r="H81" t="n">
         <v>28800758.26</v>
       </c>
       <c r="I81" t="n">
-        <v>69410912.92</v>
+        <v>69436004.42</v>
       </c>
       <c r="J81" t="n">
-        <v>98211671.18000001</v>
+        <v>98236762.68000001</v>
       </c>
     </row>
     <row r="82">
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>824377961.83</v>
+        <v>833316160.41</v>
       </c>
       <c r="F82" t="n">
-        <v>799349646.21</v>
+        <v>800085427.9400001</v>
       </c>
       <c r="G82" t="n">
-        <v>792055697.61</v>
+        <v>792496641.89</v>
       </c>
       <c r="H82" t="n">
         <v>6831.37</v>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>87210085.23999999</v>
+        <v>90064035.56</v>
       </c>
       <c r="F84" t="n">
-        <v>85960968.77</v>
+        <v>88847435.34</v>
       </c>
       <c r="G84" t="n">
-        <v>85141554.3</v>
+        <v>88117671.34999999</v>
       </c>
       <c r="H84" t="n">
         <v>117516.51</v>
@@ -3426,13 +3426,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10515847.61</v>
+        <v>10508218.48</v>
       </c>
       <c r="F85" t="n">
-        <v>9044340.67</v>
+        <v>9459221.02</v>
       </c>
       <c r="G85" t="n">
-        <v>7994973.05</v>
+        <v>8003358.15</v>
       </c>
       <c r="H85" t="n">
         <v>32410.16</v>
@@ -3462,13 +3462,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>255447900.37</v>
+        <v>260781459.53</v>
       </c>
       <c r="F86" t="n">
-        <v>230025078.9</v>
+        <v>233661495.89</v>
       </c>
       <c r="G86" t="n">
-        <v>225045062.42</v>
+        <v>227966534.48</v>
       </c>
       <c r="H86" t="n">
         <v>212410.94</v>
@@ -3498,22 +3498,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>296290218.31</v>
+        <v>297629666.56</v>
       </c>
       <c r="F87" t="n">
-        <v>276603827.46</v>
+        <v>277073687.64</v>
       </c>
       <c r="G87" t="n">
-        <v>270329239.33</v>
+        <v>271011446.04</v>
       </c>
       <c r="H87" t="n">
         <v>130453.78</v>
       </c>
       <c r="I87" t="n">
-        <v>23270028.37</v>
+        <v>23271481.62</v>
       </c>
       <c r="J87" t="n">
-        <v>23400482.15</v>
+        <v>23401935.4</v>
       </c>
     </row>
     <row r="88">
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4909061.97</v>
+        <v>4901061.97</v>
       </c>
       <c r="F88" t="n">
-        <v>3983532.7</v>
+        <v>3997408.85</v>
       </c>
       <c r="G88" t="n">
-        <v>3694387.47</v>
+        <v>3707744.41</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:I90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,10 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Valor Pago Processado</t>
+          <t>Valor Liquidado RP</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Pago Não Processado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Pago RP</t>
         </is>
@@ -498,21 +493,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>752620692.3099999</v>
+        <v>22332270.08</v>
       </c>
       <c r="F2" t="n">
-        <v>685518619.83</v>
+        <v>14963862.11</v>
       </c>
       <c r="G2" t="n">
-        <v>652284398.86</v>
+        <v>12525010.25</v>
       </c>
       <c r="H2" t="n">
-        <v>214399217.64</v>
+        <v>2688406.55</v>
       </c>
       <c r="I2" t="n">
-        <v>2507327.52</v>
-      </c>
-      <c r="J2" t="n">
         <v>216906545.16</v>
       </c>
     </row>
@@ -534,21 +526,18 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4405900.79</v>
+        <v>1758306.07</v>
       </c>
       <c r="F3" t="n">
-        <v>4165467.73</v>
+        <v>1592927.63</v>
       </c>
       <c r="G3" t="n">
-        <v>3826097.61</v>
+        <v>1371061.21</v>
       </c>
       <c r="H3" t="n">
-        <v>167935.23</v>
+        <v>60903.67</v>
       </c>
       <c r="I3" t="n">
-        <v>59221.61</v>
-      </c>
-      <c r="J3" t="n">
         <v>227156.84</v>
       </c>
     </row>
@@ -570,21 +559,18 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1248859971.37</v>
+        <v>175908589.19</v>
       </c>
       <c r="F4" t="n">
-        <v>1166909784.09</v>
+        <v>103664078.48</v>
       </c>
       <c r="G4" t="n">
-        <v>1154194510.58</v>
+        <v>84345643.25</v>
       </c>
       <c r="H4" t="n">
-        <v>6630.3</v>
+        <v>35254649.02</v>
       </c>
       <c r="I4" t="n">
-        <v>32317228.61</v>
-      </c>
-      <c r="J4" t="n">
         <v>32323858.91</v>
       </c>
     </row>
@@ -606,21 +592,18 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4017822.78</v>
+        <v>2861674.28</v>
       </c>
       <c r="F5" t="n">
-        <v>2543460.28</v>
+        <v>1504062.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2343161.52</v>
+        <v>1299309.81</v>
       </c>
       <c r="H5" t="n">
-        <v>17304.09</v>
+        <v>706301.5699999999</v>
       </c>
       <c r="I5" t="n">
-        <v>667892.4</v>
-      </c>
-      <c r="J5" t="n">
         <v>685196.49</v>
       </c>
     </row>
@@ -642,21 +625,18 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13682629.31</v>
+        <v>2359721.72</v>
       </c>
       <c r="F6" t="n">
-        <v>12444322.72</v>
+        <v>1218942.41</v>
       </c>
       <c r="G6" t="n">
-        <v>12310886.47</v>
+        <v>1144455.74</v>
       </c>
       <c r="H6" t="n">
-        <v>8281.799999999999</v>
+        <v>154017.57</v>
       </c>
       <c r="I6" t="n">
-        <v>140322.38</v>
-      </c>
-      <c r="J6" t="n">
         <v>148604.18</v>
       </c>
     </row>
@@ -678,23 +658,20 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30182211.42</v>
+        <v>24188305.35</v>
       </c>
       <c r="F7" t="n">
-        <v>22815850.85</v>
+        <v>17266417.88</v>
       </c>
       <c r="G7" t="n">
-        <v>21025702.68</v>
+        <v>15512207.22</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2353030.07</v>
       </c>
       <c r="I7" t="n">
         <v>2159796.82</v>
       </c>
-      <c r="J7" t="n">
-        <v>2159796.82</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -714,22 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1244230747.9</v>
+        <v>73568060.63</v>
       </c>
       <c r="F8" t="n">
-        <v>1196726966.24</v>
+        <v>27127933.86</v>
       </c>
       <c r="G8" t="n">
-        <v>1188684859.92</v>
+        <v>24041195.1</v>
       </c>
       <c r="H8" t="n">
-        <v>6046803.88</v>
+        <v>41641504.94</v>
       </c>
       <c r="I8" t="n">
-        <v>40120083.83</v>
-      </c>
-      <c r="J8" t="n">
-        <v>46166887.71</v>
+        <v>46287655.7</v>
       </c>
     </row>
     <row r="9">
@@ -750,21 +724,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>41248674.64</v>
+        <v>2868271.45</v>
       </c>
       <c r="F9" t="n">
-        <v>40616933.29</v>
+        <v>2239688.5</v>
       </c>
       <c r="G9" t="n">
-        <v>40327275.65</v>
+        <v>1940984.01</v>
       </c>
       <c r="H9" t="n">
-        <v>5062</v>
+        <v>1345976.77</v>
       </c>
       <c r="I9" t="n">
-        <v>1311388.02</v>
-      </c>
-      <c r="J9" t="n">
         <v>1316450.02</v>
       </c>
     </row>
@@ -786,21 +757,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>657745380.83</v>
+        <v>75914900.18000001</v>
       </c>
       <c r="F10" t="n">
-        <v>647654106.23</v>
+        <v>68849244.65000001</v>
       </c>
       <c r="G10" t="n">
-        <v>635557692.46</v>
+        <v>56783708.35</v>
       </c>
       <c r="H10" t="n">
-        <v>7410</v>
+        <v>14753073.98</v>
       </c>
       <c r="I10" t="n">
-        <v>13720685.95</v>
-      </c>
-      <c r="J10" t="n">
         <v>13728095.95</v>
       </c>
     </row>
@@ -822,22 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1521501436.26</v>
+        <v>1320835946.4</v>
       </c>
       <c r="F11" t="n">
-        <v>842228728.8200001</v>
+        <v>661065907.65</v>
       </c>
       <c r="G11" t="n">
-        <v>770351970.6900001</v>
+        <v>635451644.1799999</v>
       </c>
       <c r="H11" t="n">
-        <v>13431647.55</v>
+        <v>321436487.85</v>
       </c>
       <c r="I11" t="n">
-        <v>315352398.37</v>
-      </c>
-      <c r="J11" t="n">
-        <v>328784045.92</v>
+        <v>328784183.12</v>
       </c>
     </row>
     <row r="12">
@@ -858,17 +823,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91741567.73</v>
+        <v>33713880.02</v>
       </c>
       <c r="F12" t="n">
-        <v>61684923.03</v>
+        <v>6624846.95</v>
       </c>
       <c r="G12" t="n">
-        <v>55914234.61</v>
+        <v>3648128.78</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -888,23 +852,20 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>901530417.48</v>
+        <v>5089748.28</v>
       </c>
       <c r="F13" t="n">
-        <v>656760506.6799999</v>
+        <v>3949462.01</v>
       </c>
       <c r="G13" t="n">
-        <v>656756143.91</v>
+        <v>3945099.24</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>73808566.59999999</v>
       </c>
       <c r="I13" t="n">
         <v>73808566.59999999</v>
       </c>
-      <c r="J13" t="n">
-        <v>73808566.59999999</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -924,23 +885,20 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106613604.26</v>
+        <v>2193789.5</v>
       </c>
       <c r="F14" t="n">
-        <v>105103848.46</v>
+        <v>684033.7</v>
       </c>
       <c r="G14" t="n">
-        <v>104910921.07</v>
+        <v>653535.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>932410.0600000001</v>
       </c>
       <c r="I14" t="n">
         <v>895934.49</v>
       </c>
-      <c r="J14" t="n">
-        <v>895934.49</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -970,7 +928,6 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1000,7 +957,6 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1008,29 +964,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMG - ADM. DIRETA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3051</v>
+        <v>9999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>85431443.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>85431443.5</v>
-      </c>
-      <c r="G17" t="n">
-        <v>85431443.5</v>
-      </c>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1038,35 +987,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>17847575.25</v>
+        <v>85431443.5</v>
       </c>
       <c r="F18" t="n">
-        <v>13503523.05</v>
+        <v>85431443.5</v>
       </c>
       <c r="G18" t="n">
-        <v>12938907.78</v>
-      </c>
-      <c r="H18" t="n">
-        <v>211328.04</v>
-      </c>
-      <c r="I18" t="n">
-        <v>963707.42</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1175035.46</v>
-      </c>
+        <v>85431443.5</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1074,34 +1016,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>358206</v>
+        <v>8271435.92</v>
       </c>
       <c r="F19" t="n">
-        <v>192075.83</v>
+        <v>3994770.02</v>
       </c>
       <c r="G19" t="n">
-        <v>182112.11</v>
+        <v>3628433.41</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1040158.72</v>
       </c>
       <c r="I19" t="n">
-        <v>28664.16</v>
-      </c>
-      <c r="J19" t="n">
-        <v>28664.16</v>
+        <v>1175035.46</v>
       </c>
     </row>
     <row r="20">
@@ -1110,34 +1049,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2825008.42</v>
+        <v>358206</v>
       </c>
       <c r="F20" t="n">
-        <v>2732511.68</v>
+        <v>192075.83</v>
       </c>
       <c r="G20" t="n">
-        <v>2617470.23</v>
+        <v>182112.11</v>
       </c>
       <c r="H20" t="n">
-        <v>46386.19</v>
+        <v>30324.78</v>
       </c>
       <c r="I20" t="n">
-        <v>72457.69</v>
-      </c>
-      <c r="J20" t="n">
-        <v>118843.88</v>
+        <v>28664.16</v>
       </c>
     </row>
     <row r="21">
@@ -1146,34 +1082,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>367149212.36</v>
+        <v>796643.42</v>
       </c>
       <c r="F21" t="n">
-        <v>321440796.32</v>
+        <v>722195.38</v>
       </c>
       <c r="G21" t="n">
-        <v>312430080.13</v>
+        <v>608014.02</v>
       </c>
       <c r="H21" t="n">
-        <v>3369120.12</v>
+        <v>97349.38</v>
       </c>
       <c r="I21" t="n">
-        <v>3679583.75</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7048703.87</v>
+        <v>118843.88</v>
       </c>
     </row>
     <row r="22">
@@ -1182,34 +1115,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36940378.21</v>
+        <v>17313298.71</v>
       </c>
       <c r="F22" t="n">
-        <v>33587303.97</v>
+        <v>14272953.56</v>
       </c>
       <c r="G22" t="n">
-        <v>31836868.88</v>
+        <v>12717987.08</v>
       </c>
       <c r="H22" t="n">
-        <v>866933.3100000001</v>
+        <v>4320776.84</v>
       </c>
       <c r="I22" t="n">
-        <v>1611008.66</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2477941.97</v>
+        <v>7048703.87</v>
       </c>
     </row>
     <row r="23">
@@ -1218,34 +1148,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2643527.87</v>
+        <v>8660090.779999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>7784018.21</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>6072957.69</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1737322.76</v>
       </c>
       <c r="I23" t="n">
-        <v>701268.5600000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>701268.5600000001</v>
+        <v>2477941.97</v>
       </c>
     </row>
     <row r="24">
@@ -1254,29 +1181,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FDMP</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4731</v>
+        <v>4331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO DO MINISTERIO PUBLICO</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38411334.17</v>
+        <v>2643527.87</v>
       </c>
       <c r="F24" t="n">
-        <v>2961334.17</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2961334.17</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1177918.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>701268.5600000001</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1284,29 +1214,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEAGE</t>
+          <t>FDMP</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4751</v>
+        <v>4731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DA ADVOCACIA-GERAL DO ESTADO</t>
+          <t>FUNDO DE DESENVOLVIMENTO DO MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7600917.52</v>
+        <v>35450000</v>
       </c>
       <c r="F25" t="n">
-        <v>4017134.11</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3812656.12</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1314,35 +1243,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FEAGE</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2091</v>
+        <v>4751</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO ESPECIAL DA ADVOCACIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>45458888.15</v>
+        <v>7530917.52</v>
       </c>
       <c r="F26" t="n">
-        <v>45039164.29</v>
+        <v>3958854.96</v>
       </c>
       <c r="G26" t="n">
-        <v>43021886.33</v>
-      </c>
-      <c r="H26" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1012611.59</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1012619.95</v>
-      </c>
+        <v>3913832.76</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1350,34 +1272,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>115639161.6</v>
+        <v>8959436.140000001</v>
       </c>
       <c r="F27" t="n">
-        <v>95054425.70999999</v>
+        <v>8571826.949999999</v>
       </c>
       <c r="G27" t="n">
-        <v>84043290.43000001</v>
+        <v>7082950.29</v>
       </c>
       <c r="H27" t="n">
-        <v>594553.05</v>
+        <v>1102595.36</v>
       </c>
       <c r="I27" t="n">
-        <v>1398403.07</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1992956.12</v>
+        <v>1012619.95</v>
       </c>
     </row>
     <row r="28">
@@ -1386,34 +1305,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>11214.34</v>
+        <v>6941514.09</v>
       </c>
       <c r="F28" t="n">
-        <v>11214.34</v>
+        <v>6124129.84</v>
       </c>
       <c r="G28" t="n">
-        <v>11214.34</v>
+        <v>5445537.53</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1499694.06</v>
       </c>
       <c r="I28" t="n">
-        <v>134615.38</v>
-      </c>
-      <c r="J28" t="n">
-        <v>134615.38</v>
+        <v>1992956.12</v>
       </c>
     </row>
     <row r="29">
@@ -1422,29 +1338,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FEGAJ</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4741</v>
+        <v>4491</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DE GARANTIA DE ACESSO A JUSTICA</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>5461576.35</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1251642</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>134615.38</v>
+      </c>
+      <c r="I29" t="n">
+        <v>134615.38</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1452,35 +1365,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEGAJ</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4101</v>
+        <v>4741</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESPECIAL DE GARANTIA DE ACESSO A JUSTICA</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7835873.39</v>
+        <v>2415176.35</v>
       </c>
       <c r="F30" t="n">
-        <v>7835873.39</v>
+        <v>1251642</v>
       </c>
       <c r="G30" t="n">
-        <v>7673251.28</v>
-      </c>
-      <c r="H30" t="n">
-        <v>360498.89</v>
-      </c>
-      <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="n">
-        <v>360498.89</v>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1488,34 +1394,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4451</v>
+        <v>4101</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>33273206.74</v>
-      </c>
-      <c r="F31" t="n">
-        <v>28444078.41</v>
-      </c>
-      <c r="G31" t="n">
-        <v>27195758.83</v>
-      </c>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>64602.55</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>32257156.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>32321759.15</v>
+        <v>360498.89</v>
       </c>
     </row>
     <row r="32">
@@ -1524,34 +1421,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FEPJ</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4031</v>
+        <v>4601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>1852742918.43</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1522709918.95</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1388743960.9</v>
-      </c>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>3735749.68</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>241718406.93</v>
-      </c>
-      <c r="J32" t="n">
-        <v>245454156.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1560,34 +1448,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4291</v>
+        <v>4451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>9627898259.98</v>
+        <v>13984104.86</v>
       </c>
       <c r="F33" t="n">
-        <v>7764261566.23</v>
+        <v>9733154.15</v>
       </c>
       <c r="G33" t="n">
-        <v>7651508079.78</v>
+        <v>8478140.82</v>
       </c>
       <c r="H33" t="n">
-        <v>408368777.38</v>
+        <v>33147977.58</v>
       </c>
       <c r="I33" t="n">
-        <v>526147048.92</v>
-      </c>
-      <c r="J33" t="n">
-        <v>934515826.3</v>
+        <v>32321759.15</v>
       </c>
     </row>
     <row r="34">
@@ -1596,34 +1481,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4691</v>
+        <v>4031</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>38263914.83</v>
+        <v>1259110476.93</v>
       </c>
       <c r="F34" t="n">
-        <v>9519790.93</v>
+        <v>953681419.8200001</v>
       </c>
       <c r="G34" t="n">
-        <v>7940338.83</v>
+        <v>822854435.47</v>
       </c>
       <c r="H34" t="n">
-        <v>4586769.48</v>
+        <v>264050297.93</v>
       </c>
       <c r="I34" t="n">
-        <v>38121054.54</v>
-      </c>
-      <c r="J34" t="n">
-        <v>42707824.02</v>
+        <v>245454156.61</v>
       </c>
     </row>
     <row r="35">
@@ -1632,34 +1514,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4701</v>
+        <v>4291</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>447503.2</v>
+        <v>865769985.91</v>
       </c>
       <c r="F35" t="n">
-        <v>370161.07</v>
+        <v>496694973.75</v>
       </c>
       <c r="G35" t="n">
-        <v>356194.78</v>
+        <v>440348829.06</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>539018285.77</v>
       </c>
       <c r="I35" t="n">
-        <v>1235436.62</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1235436.62</v>
+        <v>934515826.3</v>
       </c>
     </row>
     <row r="36">
@@ -1668,34 +1547,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4711</v>
+        <v>4691</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10356563942.37</v>
+        <v>38219202.33</v>
       </c>
       <c r="F36" t="n">
-        <v>10354839342.48</v>
+        <v>10023153.41</v>
       </c>
       <c r="G36" t="n">
-        <v>10354690898.05</v>
+        <v>7897246.33</v>
       </c>
       <c r="H36" t="n">
-        <v>57945.89</v>
+        <v>36680361.59</v>
       </c>
       <c r="I36" t="n">
-        <v>759396.5699999999</v>
-      </c>
-      <c r="J36" t="n">
-        <v>817342.46</v>
+        <v>43106562.02</v>
       </c>
     </row>
     <row r="37">
@@ -1704,34 +1580,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2151</v>
+        <v>4701</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>38933328.21</v>
+        <v>354347.75</v>
       </c>
       <c r="F37" t="n">
-        <v>36543528.65</v>
+        <v>284657.75</v>
       </c>
       <c r="G37" t="n">
-        <v>33302605.77</v>
+        <v>269666.03</v>
       </c>
       <c r="H37" t="n">
-        <v>218.93</v>
+        <v>1251438.8</v>
       </c>
       <c r="I37" t="n">
-        <v>2003431.69</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2003650.62</v>
+        <v>1235436.62</v>
       </c>
     </row>
     <row r="38">
@@ -1740,34 +1613,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2271</v>
+        <v>4711</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>1528867657.2</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1428384594.3</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1371087704.36</v>
-      </c>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>6041131.11</v>
+        <v>759396.5699999999</v>
       </c>
       <c r="I38" t="n">
-        <v>93465890.20999999</v>
-      </c>
-      <c r="J38" t="n">
-        <v>99507021.31999999</v>
+        <v>817342.46</v>
       </c>
     </row>
     <row r="39">
@@ -1776,34 +1640,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4341</v>
+        <v>2151</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>383813.38</v>
+        <v>11720838.18</v>
       </c>
       <c r="F39" t="n">
-        <v>362826.47</v>
+        <v>7860769.97</v>
       </c>
       <c r="G39" t="n">
-        <v>318905.46</v>
+        <v>7504361.78</v>
       </c>
       <c r="H39" t="n">
-        <v>68494.85000000001</v>
+        <v>2106224.16</v>
       </c>
       <c r="I39" t="n">
-        <v>284844.95</v>
-      </c>
-      <c r="J39" t="n">
-        <v>353339.8</v>
+        <v>2035954.51</v>
       </c>
     </row>
     <row r="40">
@@ -1812,34 +1673,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2061</v>
+        <v>2271</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>41957443.38</v>
+        <v>442707849.29</v>
       </c>
       <c r="F40" t="n">
-        <v>39711853.3</v>
+        <v>349127070.67</v>
       </c>
       <c r="G40" t="n">
-        <v>38200190.08</v>
+        <v>306017252.17</v>
       </c>
       <c r="H40" t="n">
-        <v>27688.16</v>
+        <v>98967527.22</v>
       </c>
       <c r="I40" t="n">
-        <v>2223889.93</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2251578.09</v>
+        <v>99500096.98</v>
       </c>
     </row>
     <row r="41">
@@ -1848,34 +1706,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4141</v>
+        <v>4341</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>7383063.6</v>
+        <v>181001.31</v>
       </c>
       <c r="F41" t="n">
-        <v>1259836.85</v>
+        <v>181001.31</v>
       </c>
       <c r="G41" t="n">
-        <v>1103345.57</v>
+        <v>150124.23</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>842769.0699999999</v>
       </c>
       <c r="I41" t="n">
-        <v>1064170.39</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1064170.39</v>
+        <v>353339.8</v>
       </c>
     </row>
     <row r="42">
@@ -1884,34 +1739,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4631</v>
+        <v>4091</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>583177905.95</v>
-      </c>
-      <c r="F42" t="n">
-        <v>200928897.65</v>
-      </c>
-      <c r="G42" t="n">
-        <v>185695277.13</v>
-      </c>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>53631506.45</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>35431658.61</v>
-      </c>
-      <c r="J42" t="n">
-        <v>89063165.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1920,34 +1766,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2161</v>
+        <v>2061</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3723996.76</v>
+        <v>7933514.44</v>
       </c>
       <c r="F43" t="n">
-        <v>3152508.98</v>
+        <v>6072301.82</v>
       </c>
       <c r="G43" t="n">
-        <v>3079960.16</v>
+        <v>5274987.41</v>
       </c>
       <c r="H43" t="n">
-        <v>23147.54</v>
+        <v>2401848.01</v>
       </c>
       <c r="I43" t="n">
-        <v>154559.3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>177706.84</v>
+        <v>2251578.09</v>
       </c>
     </row>
     <row r="44">
@@ -1956,34 +1799,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4551</v>
+        <v>4141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>94331218.23999999</v>
+        <v>6123226.75</v>
       </c>
       <c r="F44" t="n">
-        <v>82432650.7</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>82409844.45999999</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2205946.03</v>
       </c>
       <c r="I44" t="n">
-        <v>486647</v>
-      </c>
-      <c r="J44" t="n">
-        <v>486647</v>
+        <v>1064170.39</v>
       </c>
     </row>
     <row r="45">
@@ -1992,34 +1832,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FUNDALEMG</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4121</v>
+        <v>4631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DA ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5537566.67</v>
+        <v>583177905.95</v>
       </c>
       <c r="F45" t="n">
-        <v>5537566.67</v>
+        <v>213240454.3</v>
       </c>
       <c r="G45" t="n">
-        <v>4473014.43</v>
+        <v>185695277.13</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>38776739.66</v>
       </c>
       <c r="I45" t="n">
-        <v>1486024.48</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1486024.48</v>
+        <v>89063165.06</v>
       </c>
     </row>
     <row r="46">
@@ -2028,34 +1865,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2261</v>
+        <v>2161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>275300839.68</v>
+        <v>1260115.53</v>
       </c>
       <c r="F46" t="n">
-        <v>206479814.85</v>
+        <v>709860.47</v>
       </c>
       <c r="G46" t="n">
-        <v>194134841.11</v>
+        <v>656798.0600000001</v>
       </c>
       <c r="H46" t="n">
-        <v>7187273.07</v>
+        <v>178281.27</v>
       </c>
       <c r="I46" t="n">
-        <v>133812063.31</v>
-      </c>
-      <c r="J46" t="n">
-        <v>140999336.38</v>
+        <v>177706.84</v>
       </c>
     </row>
     <row r="47">
@@ -2064,34 +1898,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FUNEMP</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4441</v>
+        <v>4551</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>34559002.14</v>
-      </c>
-      <c r="F47" t="n">
-        <v>18438504.52</v>
-      </c>
-      <c r="G47" t="n">
-        <v>17964206.49</v>
-      </c>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>1618421.95</v>
+        <v>486647</v>
       </c>
       <c r="I47" t="n">
-        <v>11763907.67</v>
-      </c>
-      <c r="J47" t="n">
-        <v>13382329.62</v>
+        <v>486647</v>
       </c>
     </row>
     <row r="48">
@@ -2100,34 +1925,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNDALEMG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4381</v>
+        <v>4121</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>76668649.38</v>
-      </c>
-      <c r="F48" t="n">
-        <v>48517242.95</v>
-      </c>
-      <c r="G48" t="n">
-        <v>44958428.11</v>
-      </c>
+          <t>FUNDO ESPECIAL DA ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1615244</v>
       </c>
       <c r="I48" t="n">
-        <v>17655143.4</v>
-      </c>
-      <c r="J48" t="n">
-        <v>17655143.4</v>
+        <v>1486024.48</v>
       </c>
     </row>
     <row r="49">
@@ -2136,34 +1952,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1071</v>
+        <v>2261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>60776001.68</v>
+        <v>203091260.55</v>
       </c>
       <c r="F49" t="n">
-        <v>33509841.88</v>
+        <v>134588846.01</v>
       </c>
       <c r="G49" t="n">
-        <v>31353476.52</v>
+        <v>123674100.82</v>
       </c>
       <c r="H49" t="n">
-        <v>1803218.12</v>
+        <v>135331229.29</v>
       </c>
       <c r="I49" t="n">
-        <v>12201363.74</v>
-      </c>
-      <c r="J49" t="n">
-        <v>14004581.86</v>
+        <v>140999336.38</v>
       </c>
     </row>
     <row r="50">
@@ -2172,34 +1985,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1916</v>
+        <v>4441</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6470084509.41</v>
+        <v>15777879.91</v>
       </c>
       <c r="F50" t="n">
-        <v>5505007532.43</v>
+        <v>1120119.09</v>
       </c>
       <c r="G50" t="n">
-        <v>5442367303.33</v>
+        <v>841094.1899999999</v>
       </c>
       <c r="H50" t="n">
-        <v>43587892.37</v>
+        <v>19799154.85</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>43587892.37</v>
+        <v>21143662.17</v>
       </c>
     </row>
     <row r="51">
@@ -2208,34 +2018,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2321</v>
+        <v>4381</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>251376332.38</v>
+        <v>76655093.98</v>
       </c>
       <c r="F51" t="n">
-        <v>208814598.75</v>
+        <v>48874672.05</v>
       </c>
       <c r="G51" t="n">
-        <v>202069398.31</v>
+        <v>45781012.24</v>
       </c>
       <c r="H51" t="n">
-        <v>3348075.28</v>
+        <v>18617499.53</v>
       </c>
       <c r="I51" t="n">
-        <v>23920129.79</v>
-      </c>
-      <c r="J51" t="n">
-        <v>27268205.07</v>
+        <v>17655143.4</v>
       </c>
     </row>
     <row r="52">
@@ -2244,34 +2051,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2421</v>
+        <v>1071</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>36310404.77</v>
+        <v>46957600.37</v>
       </c>
       <c r="F52" t="n">
-        <v>29151316.95</v>
+        <v>19849796.26</v>
       </c>
       <c r="G52" t="n">
-        <v>28632877.04</v>
+        <v>17599040.31</v>
       </c>
       <c r="H52" t="n">
-        <v>1021786.93</v>
+        <v>12470050.72</v>
       </c>
       <c r="I52" t="n">
-        <v>20447586.11</v>
-      </c>
-      <c r="J52" t="n">
-        <v>21469373.04</v>
+        <v>14004581.86</v>
       </c>
     </row>
     <row r="53">
@@ -2280,34 +2084,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2101</v>
+        <v>1916</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>137598925.81</v>
-      </c>
-      <c r="F53" t="n">
-        <v>128151768.74</v>
-      </c>
-      <c r="G53" t="n">
-        <v>121237551.33</v>
-      </c>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>486532.65</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>7674266.39</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8160799.04</v>
+        <v>43587892.37</v>
       </c>
     </row>
     <row r="54">
@@ -2316,34 +2111,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2201</v>
+        <v>2321</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12479577.8</v>
+        <v>136593727.07</v>
       </c>
       <c r="F54" t="n">
-        <v>11627274.98</v>
+        <v>94543258.69</v>
       </c>
       <c r="G54" t="n">
-        <v>11251810.86</v>
+        <v>87916385.39</v>
       </c>
       <c r="H54" t="n">
-        <v>702452.89</v>
+        <v>24455509.03</v>
       </c>
       <c r="I54" t="n">
-        <v>500171.63</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1202624.52</v>
+        <v>27268205.07</v>
       </c>
     </row>
     <row r="55">
@@ -2352,34 +2144,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2241</v>
+        <v>2421</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29985122.69</v>
+        <v>26052758.59</v>
       </c>
       <c r="F55" t="n">
-        <v>27678111.92</v>
+        <v>19557176.99</v>
       </c>
       <c r="G55" t="n">
-        <v>26171362.46</v>
+        <v>19025155.92</v>
       </c>
       <c r="H55" t="n">
-        <v>6973895.8</v>
+        <v>20861772.58</v>
       </c>
       <c r="I55" t="n">
-        <v>10971227.93</v>
-      </c>
-      <c r="J55" t="n">
-        <v>17945123.73</v>
+        <v>21615782.78</v>
       </c>
     </row>
     <row r="56">
@@ -2388,34 +2177,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2371</v>
+        <v>2101</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>173222482.14</v>
+        <v>40017961.48</v>
       </c>
       <c r="F56" t="n">
-        <v>166797609.45</v>
+        <v>34158517.22</v>
       </c>
       <c r="G56" t="n">
-        <v>165883790.64</v>
+        <v>27733529.11</v>
       </c>
       <c r="H56" t="n">
-        <v>509913.92</v>
+        <v>8592422.24</v>
       </c>
       <c r="I56" t="n">
-        <v>5029043.27</v>
-      </c>
-      <c r="J56" t="n">
-        <v>5538957.19</v>
+        <v>8160799.04</v>
       </c>
     </row>
     <row r="57">
@@ -2424,34 +2210,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2331</v>
+        <v>2201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>22705305.12</v>
+        <v>4212207.96</v>
       </c>
       <c r="F57" t="n">
-        <v>22045437.89</v>
+        <v>3469459.48</v>
       </c>
       <c r="G57" t="n">
-        <v>21113915.31</v>
+        <v>3102900.18</v>
       </c>
       <c r="H57" t="n">
-        <v>6330.51</v>
+        <v>532120.09</v>
       </c>
       <c r="I57" t="n">
-        <v>1187624.4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1193954.91</v>
+        <v>1202624.52</v>
       </c>
     </row>
     <row r="58">
@@ -2460,29 +2243,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IPLEMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2361</v>
+        <v>2241</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>42043986.36</v>
+        <v>6557705.33</v>
       </c>
       <c r="F58" t="n">
-        <v>42043986.36</v>
+        <v>4497227.14</v>
       </c>
       <c r="G58" t="n">
-        <v>42043986.36</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+        <v>4221263.02</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11011249.85</v>
+      </c>
+      <c r="I58" t="n">
+        <v>17945123.73</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2490,34 +2276,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2011</v>
+        <v>2371</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1520682290.54</v>
+        <v>14304815.5</v>
       </c>
       <c r="F59" t="n">
-        <v>1030557799.8</v>
+        <v>7644448.44</v>
       </c>
       <c r="G59" t="n">
-        <v>1004987048.91</v>
+        <v>7202343.03</v>
       </c>
       <c r="H59" t="n">
-        <v>96897.37</v>
+        <v>5237570.34</v>
       </c>
       <c r="I59" t="n">
-        <v>193539528.62</v>
-      </c>
-      <c r="J59" t="n">
-        <v>193636425.99</v>
+        <v>5538957.19</v>
       </c>
     </row>
     <row r="60">
@@ -2526,34 +2309,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2121</v>
+        <v>2331</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1919344634.1</v>
+        <v>8867547.23</v>
       </c>
       <c r="F60" t="n">
-        <v>1889756958.13</v>
+        <v>8546850.76</v>
       </c>
       <c r="G60" t="n">
-        <v>1868659071.76</v>
+        <v>7567139.22</v>
       </c>
       <c r="H60" t="n">
-        <v>19331338.95</v>
+        <v>1332496.42</v>
       </c>
       <c r="I60" t="n">
-        <v>34541276.63</v>
-      </c>
-      <c r="J60" t="n">
-        <v>53872615.58</v>
+        <v>1193954.91</v>
       </c>
     </row>
     <row r="61">
@@ -2562,35 +2342,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2251</v>
+        <v>2361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>26632542.48</v>
+        <v>42043986.36</v>
       </c>
       <c r="F61" t="n">
-        <v>21829892.67</v>
+        <v>42043986.36</v>
       </c>
       <c r="G61" t="n">
-        <v>21035034.88</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1119472.81</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1861547.75</v>
-      </c>
-      <c r="J61" t="n">
-        <v>2981020.56</v>
-      </c>
+        <v>42043986.36</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2598,34 +2371,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2041</v>
+        <v>2011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2131579.3</v>
+        <v>227138263.38</v>
       </c>
       <c r="F62" t="n">
-        <v>2110865.59</v>
+        <v>169180339.58</v>
       </c>
       <c r="G62" t="n">
-        <v>1977787.44</v>
+        <v>156996648.22</v>
       </c>
       <c r="H62" t="n">
-        <v>1692.39</v>
+        <v>198295027.06</v>
       </c>
       <c r="I62" t="n">
-        <v>32310.94</v>
-      </c>
-      <c r="J62" t="n">
-        <v>34003.33</v>
+        <v>193636425.99</v>
       </c>
     </row>
     <row r="63">
@@ -2634,34 +2404,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1101</v>
+        <v>2121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11646897.13</v>
+        <v>63110059.27</v>
       </c>
       <c r="F63" t="n">
-        <v>11306723.26</v>
+        <v>46209020.36</v>
       </c>
       <c r="G63" t="n">
-        <v>11220887.32</v>
+        <v>41906440.55</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>35329981.08</v>
       </c>
       <c r="I63" t="n">
-        <v>93457.72</v>
-      </c>
-      <c r="J63" t="n">
-        <v>93457.72</v>
+        <v>53872615.58</v>
       </c>
     </row>
     <row r="64">
@@ -2670,29 +2437,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1915</v>
+        <v>2251</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>15557346.18</v>
+        <v>11572164.77</v>
       </c>
       <c r="F64" t="n">
-        <v>15557346.18</v>
+        <v>7083738.39</v>
       </c>
       <c r="G64" t="n">
-        <v>15557346.18</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+        <v>6390028.46</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1960878.57</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2981020.56</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2700,34 +2470,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1511</v>
+        <v>2041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1916710631.48</v>
+        <v>481714.72</v>
       </c>
       <c r="F65" t="n">
-        <v>1840619128.35</v>
+        <v>462032.79</v>
       </c>
       <c r="G65" t="n">
-        <v>1816682778.43</v>
+        <v>331062.84</v>
       </c>
       <c r="H65" t="n">
-        <v>8940604.800000001</v>
+        <v>34744.58</v>
       </c>
       <c r="I65" t="n">
-        <v>36346355.92</v>
-      </c>
-      <c r="J65" t="n">
-        <v>45286960.72</v>
+        <v>34003.33</v>
       </c>
     </row>
     <row r="66">
@@ -2736,34 +2503,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PGJ</t>
+          <t>MG INVESTE</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1091</v>
+        <v>4621</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTICA</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>2647726417.79</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2562940668.11</v>
-      </c>
-      <c r="G66" t="n">
-        <v>2540196416.99</v>
-      </c>
+          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>2903668.96</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>74129286.09999999</v>
-      </c>
-      <c r="J66" t="n">
-        <v>77032955.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2772,34 +2530,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1251</v>
+        <v>1101</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10239585264.17</v>
+        <v>1470240.61</v>
       </c>
       <c r="F67" t="n">
-        <v>10056512792.79</v>
+        <v>1131809.2</v>
       </c>
       <c r="G67" t="n">
-        <v>10019574022.91</v>
+        <v>1042985.95</v>
       </c>
       <c r="H67" t="n">
-        <v>18536120.52</v>
+        <v>94459.97</v>
       </c>
       <c r="I67" t="n">
-        <v>185087240.89</v>
-      </c>
-      <c r="J67" t="n">
-        <v>203623361.41</v>
+        <v>93457.72</v>
       </c>
     </row>
     <row r="68">
@@ -2808,34 +2563,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SCC</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1721</v>
+        <v>1511</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5205500.86</v>
+        <v>226954370.45</v>
       </c>
       <c r="F68" t="n">
-        <v>5127499.31</v>
+        <v>153442055.14</v>
       </c>
       <c r="G68" t="n">
-        <v>5021643.12</v>
+        <v>134493290.51</v>
       </c>
       <c r="H68" t="n">
-        <v>122407.67</v>
+        <v>46159550.39</v>
       </c>
       <c r="I68" t="n">
-        <v>217467.44</v>
-      </c>
-      <c r="J68" t="n">
-        <v>339875.11</v>
+        <v>45340823.45</v>
       </c>
     </row>
     <row r="69">
@@ -2844,34 +2596,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1231</v>
+        <v>1091</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>319681569.34</v>
+        <v>245949036.95</v>
       </c>
       <c r="F69" t="n">
-        <v>306249879.72</v>
+        <v>168515401.94</v>
       </c>
       <c r="G69" t="n">
-        <v>281025856.32</v>
+        <v>145602310.93</v>
       </c>
       <c r="H69" t="n">
-        <v>6876518.16</v>
+        <v>84616730.2</v>
       </c>
       <c r="I69" t="n">
-        <v>17066235.64</v>
-      </c>
-      <c r="J69" t="n">
-        <v>23942753.8</v>
+        <v>81649603.02</v>
       </c>
     </row>
     <row r="70">
@@ -2880,34 +2629,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1631</v>
+        <v>1251</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7830450.35</v>
+        <v>458973670.53</v>
       </c>
       <c r="F70" t="n">
-        <v>7573268.49</v>
+        <v>276455074.86</v>
       </c>
       <c r="G70" t="n">
-        <v>7430514.43</v>
+        <v>243663513.09</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>226049252.01</v>
       </c>
       <c r="I70" t="n">
-        <v>34378.25</v>
-      </c>
-      <c r="J70" t="n">
-        <v>34378.25</v>
+        <v>203624020.05</v>
       </c>
     </row>
     <row r="71">
@@ -2916,34 +2662,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SECOM</t>
+          <t>SCC</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1711</v>
+        <v>1721</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DA CASA CIVIL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>86863535.37</v>
+        <v>1053263.69</v>
       </c>
       <c r="F71" t="n">
-        <v>63750813.94</v>
+        <v>986509.17</v>
       </c>
       <c r="G71" t="n">
-        <v>57695523.18</v>
+        <v>879915.6</v>
       </c>
       <c r="H71" t="n">
-        <v>60000.1</v>
+        <v>225243.01</v>
       </c>
       <c r="I71" t="n">
-        <v>61968141.74</v>
-      </c>
-      <c r="J71" t="n">
-        <v>62028141.84</v>
+        <v>339875.11</v>
       </c>
     </row>
     <row r="72">
@@ -2952,34 +2695,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1271</v>
+        <v>1231</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>182752516.09</v>
+        <v>48498942.56</v>
       </c>
       <c r="F72" t="n">
-        <v>173919446.19</v>
+        <v>36804835.06</v>
       </c>
       <c r="G72" t="n">
-        <v>170753192.37</v>
+        <v>11801540.42</v>
       </c>
       <c r="H72" t="n">
-        <v>319615.87</v>
+        <v>17353879.26</v>
       </c>
       <c r="I72" t="n">
-        <v>634111.73</v>
-      </c>
-      <c r="J72" t="n">
-        <v>953727.6</v>
+        <v>23942753.8</v>
       </c>
     </row>
     <row r="73">
@@ -2988,34 +2728,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1221</v>
+        <v>1631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>283612179.46</v>
+        <v>1526990.65</v>
       </c>
       <c r="F73" t="n">
-        <v>52731378.7</v>
+        <v>1339082.66</v>
       </c>
       <c r="G73" t="n">
-        <v>51209783.63</v>
+        <v>1174246.18</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>34378.25</v>
       </c>
       <c r="I73" t="n">
-        <v>40005821.35</v>
-      </c>
-      <c r="J73" t="n">
-        <v>40005821.35</v>
+        <v>34378.25</v>
       </c>
     </row>
     <row r="74">
@@ -3024,34 +2761,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SECOM</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1481</v>
+        <v>1711</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE COMUNICACAO SOCIAL</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>186619675.22</v>
+        <v>79039406.66</v>
       </c>
       <c r="F74" t="n">
-        <v>177193783.89</v>
+        <v>56809019.63</v>
       </c>
       <c r="G74" t="n">
-        <v>171575931.03</v>
+        <v>53392542.67</v>
       </c>
       <c r="H74" t="n">
-        <v>11942560.14</v>
+        <v>65508646.19</v>
       </c>
       <c r="I74" t="n">
-        <v>16037031.82</v>
-      </c>
-      <c r="J74" t="n">
-        <v>27979591.96</v>
+        <v>62223029.11</v>
       </c>
     </row>
     <row r="75">
@@ -3060,34 +2794,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>11879343269.82</v>
+        <v>18077966.74</v>
       </c>
       <c r="F75" t="n">
-        <v>11555326866.6</v>
+        <v>13763481.07</v>
       </c>
       <c r="G75" t="n">
-        <v>11516623306.1</v>
+        <v>11380159.75</v>
       </c>
       <c r="H75" t="n">
-        <v>199907426.47</v>
+        <v>674995.91</v>
       </c>
       <c r="I75" t="n">
-        <v>145444134.85</v>
-      </c>
-      <c r="J75" t="n">
-        <v>345351561.32</v>
+        <v>953727.6</v>
       </c>
     </row>
     <row r="76">
@@ -3096,34 +2827,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1191</v>
+        <v>1221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1092450835.95</v>
+        <v>241707987.83</v>
       </c>
       <c r="F76" t="n">
-        <v>1012056912.62</v>
+        <v>11099931.64</v>
       </c>
       <c r="G76" t="n">
-        <v>993851496.4</v>
+        <v>9687859.9</v>
       </c>
       <c r="H76" t="n">
-        <v>7665444.21</v>
+        <v>42747070.03</v>
       </c>
       <c r="I76" t="n">
-        <v>57313606.16</v>
-      </c>
-      <c r="J76" t="n">
-        <v>64979050.37</v>
+        <v>40416079.35</v>
       </c>
     </row>
     <row r="77">
@@ -3132,34 +2860,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1491</v>
+        <v>1481</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>351020515.67</v>
+        <v>24419328.71</v>
       </c>
       <c r="F77" t="n">
-        <v>348153288.83</v>
+        <v>16909368.65</v>
       </c>
       <c r="G77" t="n">
-        <v>338165674.71</v>
+        <v>15069584.69</v>
       </c>
       <c r="H77" t="n">
-        <v>11209003.04</v>
+        <v>16778618.73</v>
       </c>
       <c r="I77" t="n">
-        <v>4958053</v>
-      </c>
-      <c r="J77" t="n">
-        <v>16167056.04</v>
+        <v>27979591.96</v>
       </c>
     </row>
     <row r="78">
@@ -3168,34 +2893,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>865698344.35</v>
+        <v>870225269.95</v>
       </c>
       <c r="F78" t="n">
-        <v>837569561.85</v>
+        <v>602978934.95</v>
       </c>
       <c r="G78" t="n">
-        <v>819945622.47</v>
+        <v>580075324.86</v>
       </c>
       <c r="H78" t="n">
-        <v>15843807.77</v>
+        <v>149645419.54</v>
       </c>
       <c r="I78" t="n">
-        <v>29097751.57</v>
-      </c>
-      <c r="J78" t="n">
-        <v>44941559.34</v>
+        <v>345351561.32</v>
       </c>
     </row>
     <row r="79">
@@ -3204,34 +2926,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1451</v>
+        <v>1191</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2970711458.04</v>
+        <v>174721509.56</v>
       </c>
       <c r="F79" t="n">
-        <v>2737401767.01</v>
+        <v>112455280.54</v>
       </c>
       <c r="G79" t="n">
-        <v>2682018405.3</v>
+        <v>99237145.54000001</v>
       </c>
       <c r="H79" t="n">
-        <v>14535917.67</v>
+        <v>60953895.09</v>
       </c>
       <c r="I79" t="n">
-        <v>130184006.95</v>
-      </c>
-      <c r="J79" t="n">
-        <v>144719924.62</v>
+        <v>65319782.01</v>
       </c>
     </row>
     <row r="80">
@@ -3240,34 +2959,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1371</v>
+        <v>1491</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>146679345.08</v>
+        <v>28662423.54</v>
       </c>
       <c r="F80" t="n">
-        <v>139914269.33</v>
+        <v>25822817.24</v>
       </c>
       <c r="G80" t="n">
-        <v>133856016.92</v>
+        <v>23829303.77</v>
       </c>
       <c r="H80" t="n">
-        <v>3823909.86</v>
+        <v>4983225.57</v>
       </c>
       <c r="I80" t="n">
-        <v>4463529.39</v>
-      </c>
-      <c r="J80" t="n">
-        <v>8287439.25</v>
+        <v>16167056.04</v>
       </c>
     </row>
     <row r="81">
@@ -3276,34 +2992,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1501</v>
+        <v>1301</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA, MOBILIDADE E PARCERIAS</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>442042309.26</v>
+        <v>51026750.03</v>
       </c>
       <c r="F81" t="n">
-        <v>358079671.15</v>
+        <v>24468347.3</v>
       </c>
       <c r="G81" t="n">
-        <v>321457214.02</v>
+        <v>22822424.37</v>
       </c>
       <c r="H81" t="n">
-        <v>28800758.26</v>
+        <v>30104506.35</v>
       </c>
       <c r="I81" t="n">
-        <v>69436004.42</v>
-      </c>
-      <c r="J81" t="n">
-        <v>98236762.68000001</v>
+        <v>87096685.52</v>
       </c>
     </row>
     <row r="82">
@@ -3312,34 +3025,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TCEMG</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1021</v>
+        <v>1451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>833316160.41</v>
+        <v>550094829.24</v>
       </c>
       <c r="F82" t="n">
-        <v>800085427.9400001</v>
+        <v>396444506.4</v>
       </c>
       <c r="G82" t="n">
-        <v>792496641.89</v>
+        <v>356312093.82</v>
       </c>
       <c r="H82" t="n">
-        <v>6831.37</v>
+        <v>136681460.34</v>
       </c>
       <c r="I82" t="n">
-        <v>29944186.06</v>
-      </c>
-      <c r="J82" t="n">
-        <v>29951017.43</v>
+        <v>145341889.84</v>
       </c>
     </row>
     <row r="83">
@@ -3348,29 +3058,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TJMG</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1031</v>
+        <v>1371</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5960601163.36</v>
+        <v>26452591.22</v>
       </c>
       <c r="F83" t="n">
-        <v>5960601163.36</v>
+        <v>22724587.04</v>
       </c>
       <c r="G83" t="n">
-        <v>5960644580.03</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+        <v>19995868.94</v>
+      </c>
+      <c r="H83" t="n">
+        <v>4788552.39</v>
+      </c>
+      <c r="I83" t="n">
+        <v>8287439.25</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3378,34 +3091,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TJMMG</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1051</v>
+        <v>1501</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>90064035.56</v>
+        <v>273940981.93</v>
       </c>
       <c r="F84" t="n">
-        <v>88847435.34</v>
+        <v>193449615.41</v>
       </c>
       <c r="G84" t="n">
-        <v>88117671.34999999</v>
+        <v>155034383.58</v>
       </c>
       <c r="H84" t="n">
-        <v>117516.51</v>
+        <v>72342416.15000001</v>
       </c>
       <c r="I84" t="n">
-        <v>4472955.56</v>
-      </c>
-      <c r="J84" t="n">
-        <v>4590472.07</v>
+        <v>98263630.39</v>
       </c>
     </row>
     <row r="85">
@@ -3414,34 +3124,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>TCEMG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2211</v>
+        <v>1021</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10508218.48</v>
+        <v>91071087.23999999</v>
       </c>
       <c r="F85" t="n">
-        <v>9459221.02</v>
+        <v>60504456.53</v>
       </c>
       <c r="G85" t="n">
-        <v>8003358.15</v>
+        <v>49581539.49</v>
       </c>
       <c r="H85" t="n">
-        <v>32410.16</v>
+        <v>34224558.14</v>
       </c>
       <c r="I85" t="n">
-        <v>560777.9399999999</v>
-      </c>
-      <c r="J85" t="n">
-        <v>593188.1</v>
+        <v>29951017.43</v>
       </c>
     </row>
     <row r="86">
@@ -3450,34 +3157,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>TJMMG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2351</v>
+        <v>1051</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>260781459.53</v>
+        <v>8452916.49</v>
       </c>
       <c r="F86" t="n">
-        <v>233661495.89</v>
+        <v>7335299.34</v>
       </c>
       <c r="G86" t="n">
-        <v>227966534.48</v>
+        <v>6598053.82</v>
       </c>
       <c r="H86" t="n">
-        <v>212410.94</v>
+        <v>5299396.31</v>
       </c>
       <c r="I86" t="n">
-        <v>19719523.6</v>
-      </c>
-      <c r="J86" t="n">
-        <v>19931934.54</v>
+        <v>4752168.36</v>
       </c>
     </row>
     <row r="87">
@@ -3486,34 +3190,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2311</v>
+        <v>2211</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>297629666.56</v>
+        <v>4888035.82</v>
       </c>
       <c r="F87" t="n">
-        <v>277073687.64</v>
+        <v>3982311.19</v>
       </c>
       <c r="G87" t="n">
-        <v>271011446.04</v>
+        <v>2519462.66</v>
       </c>
       <c r="H87" t="n">
-        <v>130453.78</v>
+        <v>624962.6800000001</v>
       </c>
       <c r="I87" t="n">
-        <v>23271481.62</v>
-      </c>
-      <c r="J87" t="n">
-        <v>23401935.4</v>
+        <v>593188.1</v>
       </c>
     </row>
     <row r="88">
@@ -3522,33 +3223,96 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>61086660.48</v>
+      </c>
+      <c r="F88" t="n">
+        <v>43325400.12</v>
+      </c>
+      <c r="G88" t="n">
+        <v>38513703.44</v>
+      </c>
+      <c r="H88" t="n">
+        <v>20763045.19</v>
+      </c>
+      <c r="I88" t="n">
+        <v>19931934.54</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>48773484.5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>34982676.96</v>
+      </c>
+      <c r="G89" t="n">
+        <v>31249596.56</v>
+      </c>
+      <c r="H89" t="n">
+        <v>25413074.72</v>
+      </c>
+      <c r="I89" t="n">
+        <v>23423795.69</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="C90" t="n">
         <v>2281</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E88" t="n">
-        <v>4901061.97</v>
-      </c>
-      <c r="F88" t="n">
-        <v>3997408.85</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3707744.41</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>263905.44</v>
-      </c>
-      <c r="J88" t="n">
+      <c r="E90" t="n">
+        <v>2343525.26</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1823888.79</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1603823.2</v>
+      </c>
+      <c r="H90" t="n">
+        <v>294468.9</v>
+      </c>
+      <c r="I90" t="n">
         <v>263905.44</v>
       </c>
     </row>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -493,13 +493,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22332270.08</v>
+        <v>22412731.08</v>
       </c>
       <c r="F2" t="n">
-        <v>14963862.11</v>
+        <v>16039235.06</v>
       </c>
       <c r="G2" t="n">
-        <v>12525010.25</v>
+        <v>14066345.68</v>
       </c>
       <c r="H2" t="n">
         <v>2688406.55</v>
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>175908589.19</v>
+        <v>175948863.65</v>
       </c>
       <c r="F4" t="n">
-        <v>103664078.48</v>
+        <v>106017806.99</v>
       </c>
       <c r="G4" t="n">
-        <v>84345643.25</v>
+        <v>85902072.34999999</v>
       </c>
       <c r="H4" t="n">
         <v>35254649.02</v>
       </c>
       <c r="I4" t="n">
-        <v>32323858.91</v>
+        <v>32694704.95</v>
       </c>
     </row>
     <row r="5">
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2861674.28</v>
+        <v>2872182.23</v>
       </c>
       <c r="F5" t="n">
-        <v>1504062.82</v>
+        <v>1504523.2</v>
       </c>
       <c r="G5" t="n">
-        <v>1299309.81</v>
+        <v>1299770.19</v>
       </c>
       <c r="H5" t="n">
         <v>706301.5699999999</v>
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2359721.72</v>
+        <v>2442953.43</v>
       </c>
       <c r="F6" t="n">
-        <v>1218942.41</v>
+        <v>1410608.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1144455.74</v>
+        <v>1185185.46</v>
       </c>
       <c r="H6" t="n">
-        <v>154017.57</v>
+        <v>154717.57</v>
       </c>
       <c r="I6" t="n">
         <v>148604.18</v>
@@ -661,7 +661,7 @@
         <v>24188305.35</v>
       </c>
       <c r="F7" t="n">
-        <v>17266417.88</v>
+        <v>17269584.22</v>
       </c>
       <c r="G7" t="n">
         <v>15512207.22</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73568060.63</v>
+        <v>75370726.47</v>
       </c>
       <c r="F8" t="n">
-        <v>27127933.86</v>
+        <v>28114937.7</v>
       </c>
       <c r="G8" t="n">
-        <v>24041195.1</v>
+        <v>24487872.3</v>
       </c>
       <c r="H8" t="n">
-        <v>41641504.94</v>
+        <v>42530538.57</v>
       </c>
       <c r="I8" t="n">
-        <v>46287655.7</v>
+        <v>46545225.95</v>
       </c>
     </row>
     <row r="9">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2868271.45</v>
+        <v>3402906.48</v>
       </c>
       <c r="F9" t="n">
-        <v>2239688.5</v>
+        <v>2255652.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1940984.01</v>
+        <v>2074019.78</v>
       </c>
       <c r="H9" t="n">
         <v>1345976.77</v>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75914900.18000001</v>
+        <v>76885034.73999999</v>
       </c>
       <c r="F10" t="n">
-        <v>68849244.65000001</v>
+        <v>69558603.72</v>
       </c>
       <c r="G10" t="n">
-        <v>56783708.35</v>
+        <v>62241413.7</v>
       </c>
       <c r="H10" t="n">
         <v>14753073.98</v>
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1320835946.4</v>
+        <v>1374404682.84</v>
       </c>
       <c r="F11" t="n">
-        <v>661065907.65</v>
+        <v>681123520.74</v>
       </c>
       <c r="G11" t="n">
-        <v>635451644.1799999</v>
+        <v>636990790.46</v>
       </c>
       <c r="H11" t="n">
-        <v>321436487.85</v>
+        <v>328950376.63</v>
       </c>
       <c r="I11" t="n">
-        <v>328784183.12</v>
+        <v>330388180.83</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33713880.02</v>
+        <v>33838025.62</v>
       </c>
       <c r="F12" t="n">
-        <v>6624846.95</v>
+        <v>9884312.93</v>
       </c>
       <c r="G12" t="n">
-        <v>3648128.78</v>
+        <v>9218013.07</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -891,7 +891,7 @@
         <v>684033.7</v>
       </c>
       <c r="G14" t="n">
-        <v>653535.02</v>
+        <v>663142.76</v>
       </c>
       <c r="H14" t="n">
         <v>932410.0600000001</v>
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8271435.92</v>
+        <v>8593524.810000001</v>
       </c>
       <c r="F19" t="n">
-        <v>3994770.02</v>
+        <v>4072897.29</v>
       </c>
       <c r="G19" t="n">
-        <v>3628433.41</v>
+        <v>3715615.72</v>
       </c>
       <c r="H19" t="n">
         <v>1040158.72</v>
       </c>
       <c r="I19" t="n">
-        <v>1175035.46</v>
+        <v>1179226.69</v>
       </c>
     </row>
     <row r="20">
@@ -1064,10 +1064,10 @@
         <v>358206</v>
       </c>
       <c r="F20" t="n">
-        <v>192075.83</v>
+        <v>212512.09</v>
       </c>
       <c r="G20" t="n">
-        <v>182112.11</v>
+        <v>200780.62</v>
       </c>
       <c r="H20" t="n">
         <v>30324.78</v>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>796643.42</v>
+        <v>818965.1899999999</v>
       </c>
       <c r="F21" t="n">
         <v>722195.38</v>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17313298.71</v>
+        <v>17323726.25</v>
       </c>
       <c r="F22" t="n">
-        <v>14272953.56</v>
+        <v>14303331.52</v>
       </c>
       <c r="G22" t="n">
-        <v>12717987.08</v>
+        <v>12745345.47</v>
       </c>
       <c r="H22" t="n">
-        <v>4320776.84</v>
+        <v>4321576.84</v>
       </c>
       <c r="I22" t="n">
-        <v>7048703.87</v>
+        <v>7049503.87</v>
       </c>
     </row>
     <row r="23">
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8660090.779999999</v>
+        <v>8663290.779999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7784018.21</v>
+        <v>7787150.01</v>
       </c>
       <c r="G23" t="n">
-        <v>6072957.69</v>
+        <v>6074757.99</v>
       </c>
       <c r="H23" t="n">
         <v>1737322.76</v>
@@ -1205,7 +1205,7 @@
         <v>1177918.8</v>
       </c>
       <c r="I24" t="n">
-        <v>701268.5600000001</v>
+        <v>1121378.69</v>
       </c>
     </row>
     <row r="25">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7530917.52</v>
+        <v>7576003.15</v>
       </c>
       <c r="F26" t="n">
-        <v>3958854.96</v>
+        <v>4337156.29</v>
       </c>
       <c r="G26" t="n">
-        <v>3913832.76</v>
+        <v>4292134.09</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8959436.140000001</v>
+        <v>9221269.369999999</v>
       </c>
       <c r="F27" t="n">
-        <v>8571826.949999999</v>
+        <v>9019641.609999999</v>
       </c>
       <c r="G27" t="n">
-        <v>7082950.29</v>
+        <v>7441583.67</v>
       </c>
       <c r="H27" t="n">
         <v>1102595.36</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6941514.09</v>
+        <v>8205858.68</v>
       </c>
       <c r="F28" t="n">
-        <v>6124129.84</v>
+        <v>6450033.55</v>
       </c>
       <c r="G28" t="n">
-        <v>5445537.53</v>
+        <v>5450786.01</v>
       </c>
       <c r="H28" t="n">
         <v>1499694.06</v>
@@ -1380,10 +1380,10 @@
         <v>2415176.35</v>
       </c>
       <c r="F30" t="n">
-        <v>1251642</v>
+        <v>1804899.24</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>34627.42</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13984104.86</v>
+        <v>13986432.26</v>
       </c>
       <c r="F33" t="n">
         <v>9733154.15</v>
       </c>
       <c r="G33" t="n">
-        <v>8478140.82</v>
+        <v>8479931.08</v>
       </c>
       <c r="H33" t="n">
         <v>33147977.58</v>
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1259110476.93</v>
+        <v>1288503179.98</v>
       </c>
       <c r="F34" t="n">
-        <v>953681419.8200001</v>
+        <v>997122781.77</v>
       </c>
       <c r="G34" t="n">
-        <v>822854435.47</v>
+        <v>856232492.72</v>
       </c>
       <c r="H34" t="n">
-        <v>264050297.93</v>
+        <v>264051724.65</v>
       </c>
       <c r="I34" t="n">
-        <v>245454156.61</v>
+        <v>245455286.57</v>
       </c>
     </row>
     <row r="35">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>865769985.91</v>
+        <v>884189532.87</v>
       </c>
       <c r="F35" t="n">
-        <v>496694973.75</v>
+        <v>505519003.17</v>
       </c>
       <c r="G35" t="n">
-        <v>440348829.06</v>
+        <v>467531744.28</v>
       </c>
       <c r="H35" t="n">
-        <v>539018285.77</v>
+        <v>539794567.3200001</v>
       </c>
       <c r="I35" t="n">
-        <v>934515826.3</v>
+        <v>934656094.6799999</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>38219202.33</v>
+        <v>39561420.3</v>
       </c>
       <c r="F36" t="n">
-        <v>10023153.41</v>
+        <v>11502807.41</v>
       </c>
       <c r="G36" t="n">
-        <v>7897246.33</v>
+        <v>8646920.73</v>
       </c>
       <c r="H36" t="n">
-        <v>36680361.59</v>
+        <v>38432869.59</v>
       </c>
       <c r="I36" t="n">
-        <v>43106562.02</v>
+        <v>43363887.15</v>
       </c>
     </row>
     <row r="37">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>354347.75</v>
+        <v>389537.41</v>
       </c>
       <c r="F37" t="n">
-        <v>284657.75</v>
+        <v>325505.69</v>
       </c>
       <c r="G37" t="n">
-        <v>269666.03</v>
+        <v>274188.35</v>
       </c>
       <c r="H37" t="n">
         <v>1251438.8</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>11720838.18</v>
+        <v>11977050.69</v>
       </c>
       <c r="F39" t="n">
-        <v>7860769.97</v>
+        <v>8199305.95</v>
       </c>
       <c r="G39" t="n">
-        <v>7504361.78</v>
+        <v>7811326.38</v>
       </c>
       <c r="H39" t="n">
-        <v>2106224.16</v>
+        <v>2136220.73</v>
       </c>
       <c r="I39" t="n">
-        <v>2035954.51</v>
+        <v>2071088.15</v>
       </c>
     </row>
     <row r="40">
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>442707849.29</v>
+        <v>453958673.98</v>
       </c>
       <c r="F40" t="n">
-        <v>349127070.67</v>
+        <v>357173823.59</v>
       </c>
       <c r="G40" t="n">
-        <v>306017252.17</v>
+        <v>321593349.51</v>
       </c>
       <c r="H40" t="n">
-        <v>98967527.22</v>
+        <v>99018631.92</v>
       </c>
       <c r="I40" t="n">
-        <v>99500096.98</v>
+        <v>99977781.26000001</v>
       </c>
     </row>
     <row r="41">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>181001.31</v>
+        <v>195711.57</v>
       </c>
       <c r="F41" t="n">
         <v>181001.31</v>
@@ -1778,16 +1778,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7933514.44</v>
+        <v>7982964.44</v>
       </c>
       <c r="F43" t="n">
-        <v>6072301.82</v>
+        <v>6078441.04</v>
       </c>
       <c r="G43" t="n">
-        <v>5274987.41</v>
+        <v>5281340.55</v>
       </c>
       <c r="H43" t="n">
-        <v>2401848.01</v>
+        <v>2415047.86</v>
       </c>
       <c r="I43" t="n">
         <v>2251578.09</v>
@@ -1847,10 +1847,10 @@
         <v>583177905.95</v>
       </c>
       <c r="F45" t="n">
-        <v>213240454.3</v>
+        <v>230647259.75</v>
       </c>
       <c r="G45" t="n">
-        <v>185695277.13</v>
+        <v>198917304.39</v>
       </c>
       <c r="H45" t="n">
         <v>38776739.66</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1260115.53</v>
+        <v>1282516.16</v>
       </c>
       <c r="F46" t="n">
-        <v>709860.47</v>
+        <v>913259.33</v>
       </c>
       <c r="G46" t="n">
-        <v>656798.0600000001</v>
+        <v>661064.99</v>
       </c>
       <c r="H46" t="n">
         <v>178281.27</v>
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>203091260.55</v>
+        <v>203562393.23</v>
       </c>
       <c r="F49" t="n">
-        <v>134588846.01</v>
+        <v>134990035.77</v>
       </c>
       <c r="G49" t="n">
-        <v>123674100.82</v>
+        <v>124602742.86</v>
       </c>
       <c r="H49" t="n">
         <v>135331229.29</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>15777879.91</v>
+        <v>15780207.31</v>
       </c>
       <c r="F50" t="n">
         <v>1120119.09</v>
@@ -2006,10 +2006,10 @@
         <v>841094.1899999999</v>
       </c>
       <c r="H50" t="n">
-        <v>19799154.85</v>
+        <v>19800702.57</v>
       </c>
       <c r="I50" t="n">
-        <v>21143662.17</v>
+        <v>21144761.45</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>76655093.98</v>
+        <v>91394367.87</v>
       </c>
       <c r="F51" t="n">
-        <v>48874672.05</v>
+        <v>51271421.53</v>
       </c>
       <c r="G51" t="n">
-        <v>45781012.24</v>
+        <v>46938424.92</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>46957600.37</v>
+        <v>47145626.75</v>
       </c>
       <c r="F52" t="n">
-        <v>19849796.26</v>
+        <v>20139064</v>
       </c>
       <c r="G52" t="n">
-        <v>17599040.31</v>
+        <v>17706034.74</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>136593727.07</v>
+        <v>137404637.51</v>
       </c>
       <c r="F54" t="n">
-        <v>94543258.69</v>
+        <v>94890927.59999999</v>
       </c>
       <c r="G54" t="n">
-        <v>87916385.39</v>
+        <v>88319532.31</v>
       </c>
       <c r="H54" t="n">
         <v>24455509.03</v>
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>26052758.59</v>
+        <v>27812758.55</v>
       </c>
       <c r="F55" t="n">
-        <v>19557176.99</v>
+        <v>19669657.2</v>
       </c>
       <c r="G55" t="n">
-        <v>19025155.92</v>
+        <v>19137627.05</v>
       </c>
       <c r="H55" t="n">
-        <v>20861772.58</v>
+        <v>21150847.58</v>
       </c>
       <c r="I55" t="n">
-        <v>21615782.78</v>
+        <v>21905115.99</v>
       </c>
     </row>
     <row r="56">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>40017961.48</v>
+        <v>40420854.02</v>
       </c>
       <c r="F56" t="n">
-        <v>34158517.22</v>
+        <v>35584331.5</v>
       </c>
       <c r="G56" t="n">
-        <v>27733529.11</v>
+        <v>28103759.37</v>
       </c>
       <c r="H56" t="n">
         <v>8592422.24</v>
       </c>
       <c r="I56" t="n">
-        <v>8160799.04</v>
+        <v>8337240.75</v>
       </c>
     </row>
     <row r="57">
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4212207.96</v>
+        <v>4206124.77</v>
       </c>
       <c r="F57" t="n">
-        <v>3469459.48</v>
+        <v>3525940.32</v>
       </c>
       <c r="G57" t="n">
-        <v>3102900.18</v>
+        <v>3152209.8</v>
       </c>
       <c r="H57" t="n">
         <v>532120.09</v>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6557705.33</v>
+        <v>6559605.33</v>
       </c>
       <c r="F58" t="n">
-        <v>4497227.14</v>
+        <v>4565695.55</v>
       </c>
       <c r="G58" t="n">
-        <v>4221263.02</v>
+        <v>4235970.48</v>
       </c>
       <c r="H58" t="n">
         <v>11011249.85</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14304815.5</v>
+        <v>14339820.06</v>
       </c>
       <c r="F59" t="n">
-        <v>7644448.44</v>
+        <v>7737759.2</v>
       </c>
       <c r="G59" t="n">
-        <v>7202343.03</v>
+        <v>7306423.62</v>
       </c>
       <c r="H59" t="n">
         <v>5237570.34</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8867547.23</v>
+        <v>8870211.75</v>
       </c>
       <c r="F60" t="n">
-        <v>8546850.76</v>
+        <v>8551148.310000001</v>
       </c>
       <c r="G60" t="n">
-        <v>7567139.22</v>
+        <v>7571737.4</v>
       </c>
       <c r="H60" t="n">
         <v>1332496.42</v>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>227138263.38</v>
+        <v>229407727.32</v>
       </c>
       <c r="F62" t="n">
-        <v>169180339.58</v>
+        <v>173199844.32</v>
       </c>
       <c r="G62" t="n">
-        <v>156996648.22</v>
+        <v>161406123.57</v>
       </c>
       <c r="H62" t="n">
-        <v>198295027.06</v>
+        <v>198348641.97</v>
       </c>
       <c r="I62" t="n">
-        <v>193636425.99</v>
+        <v>193690036.4</v>
       </c>
     </row>
     <row r="63">
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>63110059.27</v>
+        <v>63418572.43</v>
       </c>
       <c r="F63" t="n">
-        <v>46209020.36</v>
+        <v>46431485.6</v>
       </c>
       <c r="G63" t="n">
-        <v>41906440.55</v>
+        <v>42215465.03</v>
       </c>
       <c r="H63" t="n">
         <v>35329981.08</v>
       </c>
       <c r="I63" t="n">
-        <v>53872615.58</v>
+        <v>53872540.51</v>
       </c>
     </row>
     <row r="64">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11572164.77</v>
+        <v>11486138.54</v>
       </c>
       <c r="F64" t="n">
-        <v>7083738.39</v>
+        <v>7878882.72</v>
       </c>
       <c r="G64" t="n">
-        <v>6390028.46</v>
+        <v>6744641.91</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>481714.72</v>
+        <v>487714.72</v>
       </c>
       <c r="F65" t="n">
-        <v>462032.79</v>
+        <v>465927.16</v>
       </c>
       <c r="G65" t="n">
-        <v>331062.84</v>
+        <v>403385.91</v>
       </c>
       <c r="H65" t="n">
         <v>34744.58</v>
@@ -2545,10 +2545,10 @@
         <v>1470240.61</v>
       </c>
       <c r="F67" t="n">
-        <v>1131809.2</v>
+        <v>1148501.48</v>
       </c>
       <c r="G67" t="n">
-        <v>1042985.95</v>
+        <v>1059661.92</v>
       </c>
       <c r="H67" t="n">
         <v>94459.97</v>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>226954370.45</v>
+        <v>227713631.65</v>
       </c>
       <c r="F68" t="n">
-        <v>153442055.14</v>
+        <v>159821101.08</v>
       </c>
       <c r="G68" t="n">
-        <v>134493290.51</v>
+        <v>140370459.82</v>
       </c>
       <c r="H68" t="n">
-        <v>46159550.39</v>
+        <v>46213714.52</v>
       </c>
       <c r="I68" t="n">
-        <v>45340823.45</v>
+        <v>45618269.72</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>245949036.95</v>
+        <v>247769511.9</v>
       </c>
       <c r="F69" t="n">
-        <v>168515401.94</v>
+        <v>171583086.64</v>
       </c>
       <c r="G69" t="n">
-        <v>145602310.93</v>
+        <v>148455072.82</v>
       </c>
       <c r="H69" t="n">
-        <v>84616730.2</v>
+        <v>84705341.81999999</v>
       </c>
       <c r="I69" t="n">
-        <v>81649603.02</v>
+        <v>81649718.54000001</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>458973670.53</v>
+        <v>470859807.6</v>
       </c>
       <c r="F70" t="n">
-        <v>276455074.86</v>
+        <v>286806136.12</v>
       </c>
       <c r="G70" t="n">
-        <v>243663513.09</v>
+        <v>247481339.89</v>
       </c>
       <c r="H70" t="n">
-        <v>226049252.01</v>
+        <v>233046073.43</v>
       </c>
       <c r="I70" t="n">
-        <v>203624020.05</v>
+        <v>203759986.58</v>
       </c>
     </row>
     <row r="71">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>48498942.56</v>
+        <v>48769714.39</v>
       </c>
       <c r="F72" t="n">
-        <v>36804835.06</v>
+        <v>37321659.27</v>
       </c>
       <c r="G72" t="n">
-        <v>11801540.42</v>
+        <v>12315550.05</v>
       </c>
       <c r="H72" t="n">
-        <v>17353879.26</v>
+        <v>17418729.6</v>
       </c>
       <c r="I72" t="n">
-        <v>23942753.8</v>
+        <v>24007604.14</v>
       </c>
     </row>
     <row r="73">
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1526990.65</v>
+        <v>1531035.25</v>
       </c>
       <c r="F73" t="n">
-        <v>1339082.66</v>
+        <v>1339534.3</v>
       </c>
       <c r="G73" t="n">
-        <v>1174246.18</v>
+        <v>1174697.82</v>
       </c>
       <c r="H73" t="n">
         <v>34378.25</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>79039406.66</v>
+        <v>79240117.42</v>
       </c>
       <c r="F74" t="n">
-        <v>56809019.63</v>
+        <v>61207825.05</v>
       </c>
       <c r="G74" t="n">
-        <v>53392542.67</v>
+        <v>56330153.4</v>
       </c>
       <c r="H74" t="n">
-        <v>65508646.19</v>
+        <v>65829586.85</v>
       </c>
       <c r="I74" t="n">
-        <v>62223029.11</v>
+        <v>62325560.87</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>18077966.74</v>
+        <v>18157837.9</v>
       </c>
       <c r="F75" t="n">
-        <v>13763481.07</v>
+        <v>13805343.64</v>
       </c>
       <c r="G75" t="n">
-        <v>11380159.75</v>
+        <v>11462805.51</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>241707987.83</v>
+        <v>241829996.88</v>
       </c>
       <c r="F76" t="n">
-        <v>11099931.64</v>
+        <v>11296169.21</v>
       </c>
       <c r="G76" t="n">
-        <v>9687859.9</v>
+        <v>10020087.47</v>
       </c>
       <c r="H76" t="n">
-        <v>42747070.03</v>
+        <v>43678750.03</v>
       </c>
       <c r="I76" t="n">
-        <v>40416079.35</v>
+        <v>41347759.35</v>
       </c>
     </row>
     <row r="77">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>24419328.71</v>
+        <v>24492913</v>
       </c>
       <c r="F77" t="n">
-        <v>16909368.65</v>
+        <v>17979986.08</v>
       </c>
       <c r="G77" t="n">
-        <v>15069584.69</v>
+        <v>15354718.98</v>
       </c>
       <c r="H77" t="n">
-        <v>16778618.73</v>
+        <v>17124490.42</v>
       </c>
       <c r="I77" t="n">
-        <v>27979591.96</v>
+        <v>28232024.37</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>870225269.95</v>
+        <v>901624442.5599999</v>
       </c>
       <c r="F78" t="n">
-        <v>602978934.95</v>
+        <v>624890374.8</v>
       </c>
       <c r="G78" t="n">
-        <v>580075324.86</v>
+        <v>602694192.4</v>
       </c>
       <c r="H78" t="n">
-        <v>149645419.54</v>
+        <v>149702930.39</v>
       </c>
       <c r="I78" t="n">
-        <v>345351561.32</v>
+        <v>345403493.61</v>
       </c>
     </row>
     <row r="79">
@@ -2938,13 +2938,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>174721509.56</v>
+        <v>176598655.34</v>
       </c>
       <c r="F79" t="n">
-        <v>112455280.54</v>
+        <v>117102002.37</v>
       </c>
       <c r="G79" t="n">
-        <v>99237145.54000001</v>
+        <v>101884928.43</v>
       </c>
       <c r="H79" t="n">
         <v>60953895.09</v>
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>28662423.54</v>
+        <v>28747378.64</v>
       </c>
       <c r="F80" t="n">
-        <v>25822817.24</v>
+        <v>26089575.55</v>
       </c>
       <c r="G80" t="n">
-        <v>23829303.77</v>
+        <v>24103573.63</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,13 +3004,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>51026750.03</v>
+        <v>51214047.71</v>
       </c>
       <c r="F81" t="n">
-        <v>24468347.3</v>
+        <v>26261364.04</v>
       </c>
       <c r="G81" t="n">
-        <v>22822424.37</v>
+        <v>23008300.5</v>
       </c>
       <c r="H81" t="n">
         <v>30104506.35</v>
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>550094829.24</v>
+        <v>563893084.78</v>
       </c>
       <c r="F82" t="n">
-        <v>396444506.4</v>
+        <v>409768610.58</v>
       </c>
       <c r="G82" t="n">
-        <v>356312093.82</v>
+        <v>379489706.4</v>
       </c>
       <c r="H82" t="n">
-        <v>136681460.34</v>
+        <v>137517834.24</v>
       </c>
       <c r="I82" t="n">
-        <v>145341889.84</v>
+        <v>146091676.13</v>
       </c>
     </row>
     <row r="83">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>26452591.22</v>
+        <v>26620317.74</v>
       </c>
       <c r="F83" t="n">
-        <v>22724587.04</v>
+        <v>22886494.79</v>
       </c>
       <c r="G83" t="n">
-        <v>19995868.94</v>
+        <v>20335492.82</v>
       </c>
       <c r="H83" t="n">
         <v>4788552.39</v>
       </c>
       <c r="I83" t="n">
-        <v>8287439.25</v>
+        <v>8286832.28</v>
       </c>
     </row>
     <row r="84">
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>273940981.93</v>
+        <v>278128293.35</v>
       </c>
       <c r="F84" t="n">
-        <v>193449615.41</v>
+        <v>197675101.7</v>
       </c>
       <c r="G84" t="n">
-        <v>155034383.58</v>
+        <v>177613043.12</v>
       </c>
       <c r="H84" t="n">
-        <v>72342416.15000001</v>
+        <v>72384710.87</v>
       </c>
       <c r="I84" t="n">
         <v>98263630.39</v>
@@ -3136,19 +3136,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>91071087.23999999</v>
+        <v>92197802.11</v>
       </c>
       <c r="F85" t="n">
-        <v>60504456.53</v>
+        <v>67308724.47</v>
       </c>
       <c r="G85" t="n">
-        <v>49581539.49</v>
+        <v>50448377.81</v>
       </c>
       <c r="H85" t="n">
-        <v>34224558.14</v>
+        <v>34226175.48</v>
       </c>
       <c r="I85" t="n">
-        <v>29951017.43</v>
+        <v>29952557.14</v>
       </c>
     </row>
     <row r="86">
@@ -3169,19 +3169,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>8452916.49</v>
+        <v>8608111.039999999</v>
       </c>
       <c r="F86" t="n">
-        <v>7335299.34</v>
+        <v>7468721.44</v>
       </c>
       <c r="G86" t="n">
-        <v>6598053.82</v>
+        <v>6663973.57</v>
       </c>
       <c r="H86" t="n">
-        <v>5299396.31</v>
+        <v>5330446.31</v>
       </c>
       <c r="I86" t="n">
-        <v>4752168.36</v>
+        <v>4783218.36</v>
       </c>
     </row>
     <row r="87">
@@ -3205,10 +3205,10 @@
         <v>4888035.82</v>
       </c>
       <c r="F87" t="n">
-        <v>3982311.19</v>
+        <v>4155155.28</v>
       </c>
       <c r="G87" t="n">
-        <v>2519462.66</v>
+        <v>2664310.36</v>
       </c>
       <c r="H87" t="n">
         <v>624962.6800000001</v>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>61086660.48</v>
+        <v>61473058.69</v>
       </c>
       <c r="F88" t="n">
-        <v>43325400.12</v>
+        <v>44586552.67</v>
       </c>
       <c r="G88" t="n">
-        <v>38513703.44</v>
+        <v>39824524.81</v>
       </c>
       <c r="H88" t="n">
-        <v>20763045.19</v>
+        <v>20764040.49</v>
       </c>
       <c r="I88" t="n">
-        <v>19931934.54</v>
+        <v>19975106.13</v>
       </c>
     </row>
     <row r="89">
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>48773484.5</v>
+        <v>50207924.64</v>
       </c>
       <c r="F89" t="n">
-        <v>34982676.96</v>
+        <v>35984399.94</v>
       </c>
       <c r="G89" t="n">
-        <v>31249596.56</v>
+        <v>32175332.83</v>
       </c>
       <c r="H89" t="n">
-        <v>25413074.72</v>
+        <v>25448738.58</v>
       </c>
       <c r="I89" t="n">
-        <v>23423795.69</v>
+        <v>23458625.39</v>
       </c>
     </row>
     <row r="90">
@@ -3304,10 +3304,10 @@
         <v>2343525.26</v>
       </c>
       <c r="F90" t="n">
-        <v>1823888.79</v>
+        <v>1826706.26</v>
       </c>
       <c r="G90" t="n">
-        <v>1603823.2</v>
+        <v>1606511.41</v>
       </c>
       <c r="H90" t="n">
         <v>294468.9</v>

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -496,16 +496,16 @@
         <v>22412731.08</v>
       </c>
       <c r="F2" t="n">
-        <v>16039235.06</v>
+        <v>16057982.45</v>
       </c>
       <c r="G2" t="n">
-        <v>14066345.68</v>
+        <v>14770969.04</v>
       </c>
       <c r="H2" t="n">
-        <v>2688406.55</v>
+        <v>2727880.95</v>
       </c>
       <c r="I2" t="n">
-        <v>216906545.16</v>
+        <v>216907109.31</v>
       </c>
     </row>
     <row r="3">
@@ -529,10 +529,10 @@
         <v>1758306.07</v>
       </c>
       <c r="F3" t="n">
-        <v>1592927.63</v>
+        <v>1595087.63</v>
       </c>
       <c r="G3" t="n">
-        <v>1371061.21</v>
+        <v>1373221.21</v>
       </c>
       <c r="H3" t="n">
         <v>60903.67</v>
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>175948863.65</v>
+        <v>178862721.16</v>
       </c>
       <c r="F4" t="n">
-        <v>106017806.99</v>
+        <v>106511593.66</v>
       </c>
       <c r="G4" t="n">
-        <v>85902072.34999999</v>
+        <v>95725374.52</v>
       </c>
       <c r="H4" t="n">
-        <v>35254649.02</v>
+        <v>35281888.26</v>
       </c>
       <c r="I4" t="n">
         <v>32694704.95</v>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2872182.23</v>
+        <v>2860809.88</v>
       </c>
       <c r="F5" t="n">
-        <v>1504523.2</v>
+        <v>1698394.62</v>
       </c>
       <c r="G5" t="n">
-        <v>1299770.19</v>
+        <v>1306085.67</v>
       </c>
       <c r="H5" t="n">
         <v>706301.5699999999</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2442953.43</v>
+        <v>2450833.21</v>
       </c>
       <c r="F6" t="n">
-        <v>1410608.42</v>
+        <v>1415667.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1185185.46</v>
+        <v>1326508.19</v>
       </c>
       <c r="H6" t="n">
         <v>154717.57</v>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24188305.35</v>
+        <v>24788305.35</v>
       </c>
       <c r="F7" t="n">
-        <v>17269584.22</v>
+        <v>18364673.28</v>
       </c>
       <c r="G7" t="n">
-        <v>15512207.22</v>
+        <v>16557822.36</v>
       </c>
       <c r="H7" t="n">
         <v>2353030.07</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75370726.47</v>
+        <v>76766769.73</v>
       </c>
       <c r="F8" t="n">
-        <v>28114937.7</v>
+        <v>29980302.65</v>
       </c>
       <c r="G8" t="n">
-        <v>24487872.3</v>
+        <v>25683712.12</v>
       </c>
       <c r="H8" t="n">
-        <v>42530538.57</v>
+        <v>43592820.58</v>
       </c>
       <c r="I8" t="n">
-        <v>46545225.95</v>
+        <v>46581282.35</v>
       </c>
     </row>
     <row r="9">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3402906.48</v>
+        <v>3484649.64</v>
       </c>
       <c r="F9" t="n">
-        <v>2255652.7</v>
+        <v>2604939.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2074019.78</v>
+        <v>2524184.66</v>
       </c>
       <c r="H9" t="n">
         <v>1345976.77</v>
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76885034.73999999</v>
+        <v>77524765.95999999</v>
       </c>
       <c r="F10" t="n">
-        <v>69558603.72</v>
+        <v>70456275.34</v>
       </c>
       <c r="G10" t="n">
-        <v>62241413.7</v>
+        <v>62718785.61</v>
       </c>
       <c r="H10" t="n">
-        <v>14753073.98</v>
+        <v>14910668.98</v>
       </c>
       <c r="I10" t="n">
-        <v>13728095.95</v>
+        <v>13874186.51</v>
       </c>
     </row>
     <row r="11">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1374404682.84</v>
+        <v>1406417218.49</v>
       </c>
       <c r="F11" t="n">
-        <v>681123520.74</v>
+        <v>776397871</v>
       </c>
       <c r="G11" t="n">
-        <v>636990790.46</v>
+        <v>728049748.01</v>
       </c>
       <c r="H11" t="n">
-        <v>328950376.63</v>
+        <v>331700666.42</v>
       </c>
       <c r="I11" t="n">
-        <v>330388180.83</v>
+        <v>333354226.91</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33838025.62</v>
+        <v>33875719.45</v>
       </c>
       <c r="F12" t="n">
-        <v>9884312.93</v>
+        <v>10009051.83</v>
       </c>
       <c r="G12" t="n">
-        <v>9218013.07</v>
+        <v>9220782.57</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8593524.810000001</v>
+        <v>8621219.689999999</v>
       </c>
       <c r="F19" t="n">
-        <v>4072897.29</v>
+        <v>4348467.24</v>
       </c>
       <c r="G19" t="n">
-        <v>3715615.72</v>
+        <v>3970983.82</v>
       </c>
       <c r="H19" t="n">
         <v>1040158.72</v>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>818965.1899999999</v>
+        <v>915987.11</v>
       </c>
       <c r="F21" t="n">
-        <v>722195.38</v>
+        <v>749130.83</v>
       </c>
       <c r="G21" t="n">
-        <v>608014.02</v>
+        <v>620996.6899999999</v>
       </c>
       <c r="H21" t="n">
         <v>97349.38</v>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17323726.25</v>
+        <v>19066904.3</v>
       </c>
       <c r="F22" t="n">
-        <v>14303331.52</v>
+        <v>14346757.57</v>
       </c>
       <c r="G22" t="n">
-        <v>12745345.47</v>
+        <v>12797776.93</v>
       </c>
       <c r="H22" t="n">
-        <v>4321576.84</v>
+        <v>4345882.84</v>
       </c>
       <c r="I22" t="n">
-        <v>7049503.87</v>
+        <v>7072643.18</v>
       </c>
     </row>
     <row r="23">
@@ -1160,19 +1160,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8663290.779999999</v>
+        <v>8711290.779999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7787150.01</v>
+        <v>7861769.57</v>
       </c>
       <c r="G23" t="n">
-        <v>6074757.99</v>
+        <v>6923683.74</v>
       </c>
       <c r="H23" t="n">
-        <v>1737322.76</v>
+        <v>1741057.76</v>
       </c>
       <c r="I23" t="n">
-        <v>2477941.97</v>
+        <v>2481676.97</v>
       </c>
     </row>
     <row r="24">
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1177918.8</v>
+        <v>1695831.09</v>
       </c>
       <c r="I24" t="n">
         <v>1121378.69</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7576003.15</v>
+        <v>7584853.16</v>
       </c>
       <c r="F26" t="n">
-        <v>4337156.29</v>
+        <v>4397596.11</v>
       </c>
       <c r="G26" t="n">
         <v>4292134.09</v>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9221269.369999999</v>
+        <v>9236011.470000001</v>
       </c>
       <c r="F27" t="n">
-        <v>9019641.609999999</v>
+        <v>9048838.939999999</v>
       </c>
       <c r="G27" t="n">
-        <v>7441583.67</v>
+        <v>7557958.08</v>
       </c>
       <c r="H27" t="n">
         <v>1102595.36</v>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8205858.68</v>
+        <v>8299596.68</v>
       </c>
       <c r="F28" t="n">
-        <v>6450033.55</v>
+        <v>6974020.75</v>
       </c>
       <c r="G28" t="n">
-        <v>5450786.01</v>
+        <v>5677756.42</v>
       </c>
       <c r="H28" t="n">
         <v>1499694.06</v>
       </c>
       <c r="I28" t="n">
-        <v>1992956.12</v>
+        <v>1993885.76</v>
       </c>
     </row>
     <row r="29">
@@ -1380,10 +1380,10 @@
         <v>2415176.35</v>
       </c>
       <c r="F30" t="n">
-        <v>1804899.24</v>
+        <v>1943303.29</v>
       </c>
       <c r="G30" t="n">
-        <v>34627.42</v>
+        <v>144022.42</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1460,19 +1460,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13986432.26</v>
+        <v>13989349.97</v>
       </c>
       <c r="F33" t="n">
-        <v>9733154.15</v>
+        <v>9734642.720000001</v>
       </c>
       <c r="G33" t="n">
-        <v>8479931.08</v>
+        <v>8766726.93</v>
       </c>
       <c r="H33" t="n">
-        <v>33147977.58</v>
+        <v>33176516.48</v>
       </c>
       <c r="I33" t="n">
-        <v>32321759.15</v>
+        <v>32348214.72</v>
       </c>
     </row>
     <row r="34">
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1288503179.98</v>
+        <v>1368878692.33</v>
       </c>
       <c r="F34" t="n">
-        <v>997122781.77</v>
+        <v>1081029455.44</v>
       </c>
       <c r="G34" t="n">
-        <v>856232492.72</v>
+        <v>929716283.46</v>
       </c>
       <c r="H34" t="n">
-        <v>264051724.65</v>
+        <v>264059957.04</v>
       </c>
       <c r="I34" t="n">
-        <v>245455286.57</v>
+        <v>245461699.95</v>
       </c>
     </row>
     <row r="35">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>884189532.87</v>
+        <v>912946025.0700001</v>
       </c>
       <c r="F35" t="n">
-        <v>505519003.17</v>
+        <v>522966788.5</v>
       </c>
       <c r="G35" t="n">
-        <v>467531744.28</v>
+        <v>473923459.27</v>
       </c>
       <c r="H35" t="n">
-        <v>539794567.3200001</v>
+        <v>560557281.83</v>
       </c>
       <c r="I35" t="n">
-        <v>934656094.6799999</v>
+        <v>1003989453.26</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>39561420.3</v>
+        <v>40742651.83</v>
       </c>
       <c r="F36" t="n">
-        <v>11502807.41</v>
+        <v>11803169.43</v>
       </c>
       <c r="G36" t="n">
-        <v>8646920.73</v>
+        <v>9579574.91</v>
       </c>
       <c r="H36" t="n">
         <v>38432869.59</v>
       </c>
       <c r="I36" t="n">
-        <v>43363887.15</v>
+        <v>45095365.05</v>
       </c>
     </row>
     <row r="37">
@@ -1598,7 +1598,7 @@
         <v>325505.69</v>
       </c>
       <c r="G37" t="n">
-        <v>274188.35</v>
+        <v>304680.58</v>
       </c>
       <c r="H37" t="n">
         <v>1251438.8</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>11977050.69</v>
+        <v>16360171.89</v>
       </c>
       <c r="F39" t="n">
-        <v>8199305.95</v>
+        <v>8293594.11</v>
       </c>
       <c r="G39" t="n">
-        <v>7811326.38</v>
+        <v>7886597.65</v>
       </c>
       <c r="H39" t="n">
-        <v>2136220.73</v>
+        <v>2138620.73</v>
       </c>
       <c r="I39" t="n">
-        <v>2071088.15</v>
+        <v>2100863.37</v>
       </c>
     </row>
     <row r="40">
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>453958673.98</v>
+        <v>468676689.38</v>
       </c>
       <c r="F40" t="n">
-        <v>357173823.59</v>
+        <v>371400371.77</v>
       </c>
       <c r="G40" t="n">
-        <v>321593349.51</v>
+        <v>333901396.41</v>
       </c>
       <c r="H40" t="n">
-        <v>99018631.92</v>
+        <v>99227455.22</v>
       </c>
       <c r="I40" t="n">
-        <v>99977781.26000001</v>
+        <v>100040710.36</v>
       </c>
     </row>
     <row r="41">
@@ -1721,10 +1721,10 @@
         <v>195711.57</v>
       </c>
       <c r="F41" t="n">
-        <v>181001.31</v>
+        <v>195711.57</v>
       </c>
       <c r="G41" t="n">
-        <v>150124.23</v>
+        <v>164479.93</v>
       </c>
       <c r="H41" t="n">
         <v>842769.0699999999</v>
@@ -1778,19 +1778,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7982964.44</v>
+        <v>8184057.84</v>
       </c>
       <c r="F43" t="n">
-        <v>6078441.04</v>
+        <v>6198574.37</v>
       </c>
       <c r="G43" t="n">
-        <v>5281340.55</v>
+        <v>5339962.51</v>
       </c>
       <c r="H43" t="n">
         <v>2415047.86</v>
       </c>
       <c r="I43" t="n">
-        <v>2251578.09</v>
+        <v>2264144.35</v>
       </c>
     </row>
     <row r="44">
@@ -1814,7 +1814,7 @@
         <v>6123226.75</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>23226.75</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>230647259.75</v>
       </c>
       <c r="G45" t="n">
-        <v>198917304.39</v>
+        <v>213416651.16</v>
       </c>
       <c r="H45" t="n">
         <v>38776739.66</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1282516.16</v>
+        <v>1468123.42</v>
       </c>
       <c r="F46" t="n">
-        <v>913259.33</v>
+        <v>932754.92</v>
       </c>
       <c r="G46" t="n">
-        <v>661064.99</v>
+        <v>847464.86</v>
       </c>
       <c r="H46" t="n">
         <v>178281.27</v>
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>203562393.23</v>
+        <v>208960267.02</v>
       </c>
       <c r="F49" t="n">
-        <v>134990035.77</v>
+        <v>142335784.14</v>
       </c>
       <c r="G49" t="n">
-        <v>124602742.86</v>
+        <v>126998862.51</v>
       </c>
       <c r="H49" t="n">
         <v>135331229.29</v>
@@ -2000,16 +2000,16 @@
         <v>15780207.31</v>
       </c>
       <c r="F50" t="n">
-        <v>1120119.09</v>
+        <v>14595939.09</v>
       </c>
       <c r="G50" t="n">
-        <v>841094.1899999999</v>
+        <v>14147972.19</v>
       </c>
       <c r="H50" t="n">
-        <v>19800702.57</v>
+        <v>19804561.95</v>
       </c>
       <c r="I50" t="n">
-        <v>21144761.45</v>
+        <v>21153997.41</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>91394367.87</v>
+        <v>94040664.15000001</v>
       </c>
       <c r="F51" t="n">
-        <v>51271421.53</v>
+        <v>56449925.57</v>
       </c>
       <c r="G51" t="n">
-        <v>46938424.92</v>
+        <v>51678950.23</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>47145626.75</v>
+        <v>48357328.44</v>
       </c>
       <c r="F52" t="n">
-        <v>20139064</v>
+        <v>20373193.2</v>
       </c>
       <c r="G52" t="n">
-        <v>17706034.74</v>
+        <v>18282605.72</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,19 +2123,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>137404637.51</v>
+        <v>137766768.19</v>
       </c>
       <c r="F54" t="n">
-        <v>94890927.59999999</v>
+        <v>96435617.27</v>
       </c>
       <c r="G54" t="n">
-        <v>88319532.31</v>
+        <v>89496212.75</v>
       </c>
       <c r="H54" t="n">
-        <v>24455509.03</v>
+        <v>24470386.01</v>
       </c>
       <c r="I54" t="n">
-        <v>27268205.07</v>
+        <v>27283227.41</v>
       </c>
     </row>
     <row r="55">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>27812758.55</v>
+        <v>29254510.7</v>
       </c>
       <c r="F55" t="n">
-        <v>19669657.2</v>
+        <v>20771691.61</v>
       </c>
       <c r="G55" t="n">
-        <v>19137627.05</v>
+        <v>19743619.63</v>
       </c>
       <c r="H55" t="n">
-        <v>21150847.58</v>
+        <v>21499979.92</v>
       </c>
       <c r="I55" t="n">
-        <v>21905115.99</v>
+        <v>22250624.42</v>
       </c>
     </row>
     <row r="56">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>40420854.02</v>
+        <v>41361879.17</v>
       </c>
       <c r="F56" t="n">
-        <v>35584331.5</v>
+        <v>36339524.55</v>
       </c>
       <c r="G56" t="n">
-        <v>28103759.37</v>
+        <v>29599680.49</v>
       </c>
       <c r="H56" t="n">
-        <v>8592422.24</v>
+        <v>8597872.24</v>
       </c>
       <c r="I56" t="n">
-        <v>8337240.75</v>
+        <v>8342429.15</v>
       </c>
     </row>
     <row r="57">
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4206124.77</v>
+        <v>4244454.26</v>
       </c>
       <c r="F57" t="n">
-        <v>3525940.32</v>
+        <v>3534012.21</v>
       </c>
       <c r="G57" t="n">
-        <v>3152209.8</v>
+        <v>3160217.84</v>
       </c>
       <c r="H57" t="n">
         <v>532120.09</v>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6559605.33</v>
+        <v>6626347.31</v>
       </c>
       <c r="F58" t="n">
-        <v>4565695.55</v>
+        <v>4593000.53</v>
       </c>
       <c r="G58" t="n">
-        <v>4235970.48</v>
+        <v>4316141.87</v>
       </c>
       <c r="H58" t="n">
         <v>11011249.85</v>
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14339820.06</v>
+        <v>14889268.38</v>
       </c>
       <c r="F59" t="n">
-        <v>7737759.2</v>
+        <v>8354338.78</v>
       </c>
       <c r="G59" t="n">
-        <v>7306423.62</v>
+        <v>7359850.01</v>
       </c>
       <c r="H59" t="n">
         <v>5237570.34</v>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229407727.32</v>
+        <v>232647798.65</v>
       </c>
       <c r="F62" t="n">
-        <v>173199844.32</v>
+        <v>179474140.36</v>
       </c>
       <c r="G62" t="n">
-        <v>161406123.57</v>
+        <v>164044033.02</v>
       </c>
       <c r="H62" t="n">
-        <v>198348641.97</v>
+        <v>198702746.56</v>
       </c>
       <c r="I62" t="n">
-        <v>193690036.4</v>
+        <v>194038222.76</v>
       </c>
     </row>
     <row r="63">
@@ -2416,16 +2416,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>63418572.43</v>
+        <v>64982945.34</v>
       </c>
       <c r="F63" t="n">
-        <v>46431485.6</v>
+        <v>48313652.61</v>
       </c>
       <c r="G63" t="n">
-        <v>42215465.03</v>
+        <v>43878050.8</v>
       </c>
       <c r="H63" t="n">
-        <v>35329981.08</v>
+        <v>35355654.72</v>
       </c>
       <c r="I63" t="n">
         <v>53872540.51</v>
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11486138.54</v>
+        <v>11535411.37</v>
       </c>
       <c r="F64" t="n">
-        <v>7878882.72</v>
+        <v>7897255.89</v>
       </c>
       <c r="G64" t="n">
-        <v>6744641.91</v>
+        <v>6923006.51</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>487714.72</v>
+        <v>490482.72</v>
       </c>
       <c r="F65" t="n">
         <v>465927.16</v>
@@ -2545,10 +2545,10 @@
         <v>1470240.61</v>
       </c>
       <c r="F67" t="n">
-        <v>1148501.48</v>
+        <v>1193299.64</v>
       </c>
       <c r="G67" t="n">
-        <v>1059661.92</v>
+        <v>1103997.51</v>
       </c>
       <c r="H67" t="n">
         <v>94459.97</v>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>227713631.65</v>
+        <v>232479853.5</v>
       </c>
       <c r="F68" t="n">
-        <v>159821101.08</v>
+        <v>165094113.05</v>
       </c>
       <c r="G68" t="n">
-        <v>140370459.82</v>
+        <v>150161761.81</v>
       </c>
       <c r="H68" t="n">
-        <v>46213714.52</v>
+        <v>49043143.94</v>
       </c>
       <c r="I68" t="n">
-        <v>45618269.72</v>
+        <v>45905990.09</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>247769511.9</v>
+        <v>256970178.73</v>
       </c>
       <c r="F69" t="n">
-        <v>171583086.64</v>
+        <v>177934179.72</v>
       </c>
       <c r="G69" t="n">
-        <v>148455072.82</v>
+        <v>150765256.24</v>
       </c>
       <c r="H69" t="n">
-        <v>84705341.81999999</v>
+        <v>86361197.8</v>
       </c>
       <c r="I69" t="n">
-        <v>81649718.54000001</v>
+        <v>83315396.78</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>470859807.6</v>
+        <v>477380618.71</v>
       </c>
       <c r="F70" t="n">
-        <v>286806136.12</v>
+        <v>295919113.56</v>
       </c>
       <c r="G70" t="n">
-        <v>247481339.89</v>
+        <v>262226888.12</v>
       </c>
       <c r="H70" t="n">
-        <v>233046073.43</v>
+        <v>235470551.76</v>
       </c>
       <c r="I70" t="n">
-        <v>203759986.58</v>
+        <v>204464861.28</v>
       </c>
     </row>
     <row r="71">
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>48769714.39</v>
+        <v>58626232.99</v>
       </c>
       <c r="F72" t="n">
-        <v>37321659.27</v>
+        <v>37350954.11</v>
       </c>
       <c r="G72" t="n">
-        <v>12315550.05</v>
+        <v>31648987.72</v>
       </c>
       <c r="H72" t="n">
-        <v>17418729.6</v>
+        <v>19183311.44</v>
       </c>
       <c r="I72" t="n">
-        <v>24007604.14</v>
+        <v>25744326.97</v>
       </c>
     </row>
     <row r="73">
@@ -2743,10 +2743,10 @@
         <v>1531035.25</v>
       </c>
       <c r="F73" t="n">
-        <v>1339534.3</v>
+        <v>1384147.9</v>
       </c>
       <c r="G73" t="n">
-        <v>1174697.82</v>
+        <v>1219226.89</v>
       </c>
       <c r="H73" t="n">
         <v>34378.25</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>79240117.42</v>
+        <v>79379683.33</v>
       </c>
       <c r="F74" t="n">
-        <v>61207825.05</v>
+        <v>62738119.71</v>
       </c>
       <c r="G74" t="n">
-        <v>56330153.4</v>
+        <v>58459714.89</v>
       </c>
       <c r="H74" t="n">
-        <v>65829586.85</v>
+        <v>65766547.38</v>
       </c>
       <c r="I74" t="n">
-        <v>62325560.87</v>
+        <v>62463232.6</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>18157837.9</v>
+        <v>18137837.9</v>
       </c>
       <c r="F75" t="n">
-        <v>13805343.64</v>
+        <v>13840440.2</v>
       </c>
       <c r="G75" t="n">
-        <v>11462805.51</v>
+        <v>11527200.15</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>241829996.88</v>
+        <v>241856312.98</v>
       </c>
       <c r="F76" t="n">
-        <v>11296169.21</v>
+        <v>11691118.77</v>
       </c>
       <c r="G76" t="n">
-        <v>10020087.47</v>
+        <v>10079518.92</v>
       </c>
       <c r="H76" t="n">
-        <v>43678750.03</v>
+        <v>49648869.32</v>
       </c>
       <c r="I76" t="n">
-        <v>41347759.35</v>
+        <v>41421517.35</v>
       </c>
     </row>
     <row r="77">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>24492913</v>
+        <v>25478388.46</v>
       </c>
       <c r="F77" t="n">
-        <v>17979986.08</v>
+        <v>19445201.81</v>
       </c>
       <c r="G77" t="n">
-        <v>15354718.98</v>
+        <v>17692331.93</v>
       </c>
       <c r="H77" t="n">
-        <v>17124490.42</v>
+        <v>17779414.2</v>
       </c>
       <c r="I77" t="n">
-        <v>28232024.37</v>
+        <v>28935408.97</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>901624442.5599999</v>
+        <v>918607465.41</v>
       </c>
       <c r="F78" t="n">
-        <v>624890374.8</v>
+        <v>683082086.26</v>
       </c>
       <c r="G78" t="n">
-        <v>602694192.4</v>
+        <v>629183941.86</v>
       </c>
       <c r="H78" t="n">
-        <v>149702930.39</v>
+        <v>149884628.2</v>
       </c>
       <c r="I78" t="n">
-        <v>345403493.61</v>
+        <v>345411113.7</v>
       </c>
     </row>
     <row r="79">
@@ -2938,19 +2938,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>176598655.34</v>
+        <v>182248930.28</v>
       </c>
       <c r="F79" t="n">
-        <v>117102002.37</v>
+        <v>128846454.85</v>
       </c>
       <c r="G79" t="n">
-        <v>101884928.43</v>
+        <v>103961641</v>
       </c>
       <c r="H79" t="n">
-        <v>60953895.09</v>
+        <v>61968308.03</v>
       </c>
       <c r="I79" t="n">
-        <v>65319782.01</v>
+        <v>65639495.09</v>
       </c>
     </row>
     <row r="80">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>28747378.64</v>
+        <v>28771347.44</v>
       </c>
       <c r="F80" t="n">
-        <v>26089575.55</v>
+        <v>26615604.56</v>
       </c>
       <c r="G80" t="n">
-        <v>24103573.63</v>
+        <v>24626636.26</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>51214047.71</v>
+        <v>52242879.13</v>
       </c>
       <c r="F81" t="n">
-        <v>26261364.04</v>
+        <v>26869439.93</v>
       </c>
       <c r="G81" t="n">
-        <v>23008300.5</v>
+        <v>25286014.99</v>
       </c>
       <c r="H81" t="n">
-        <v>30104506.35</v>
+        <v>30633300.39</v>
       </c>
       <c r="I81" t="n">
-        <v>87096685.52</v>
+        <v>87570361.79000001</v>
       </c>
     </row>
     <row r="82">
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>563893084.78</v>
+        <v>576611011.3099999</v>
       </c>
       <c r="F82" t="n">
-        <v>409768610.58</v>
+        <v>433250971.97</v>
       </c>
       <c r="G82" t="n">
-        <v>379489706.4</v>
+        <v>409841865.09</v>
       </c>
       <c r="H82" t="n">
-        <v>137517834.24</v>
+        <v>144385399.99</v>
       </c>
       <c r="I82" t="n">
-        <v>146091676.13</v>
+        <v>151021272.44</v>
       </c>
     </row>
     <row r="83">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>26620317.74</v>
+        <v>28109491.97</v>
       </c>
       <c r="F83" t="n">
-        <v>22886494.79</v>
+        <v>23468009.08</v>
       </c>
       <c r="G83" t="n">
-        <v>20335492.82</v>
+        <v>20509308.77</v>
       </c>
       <c r="H83" t="n">
         <v>4788552.39</v>
       </c>
       <c r="I83" t="n">
-        <v>8286832.28</v>
+        <v>8287439.25</v>
       </c>
     </row>
     <row r="84">
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>278128293.35</v>
+        <v>281326512.47</v>
       </c>
       <c r="F84" t="n">
-        <v>197675101.7</v>
+        <v>202083921.6</v>
       </c>
       <c r="G84" t="n">
-        <v>177613043.12</v>
+        <v>180073109.26</v>
       </c>
       <c r="H84" t="n">
-        <v>72384710.87</v>
+        <v>74964907.94</v>
       </c>
       <c r="I84" t="n">
-        <v>98263630.39</v>
+        <v>100438151.39</v>
       </c>
     </row>
     <row r="85">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>92197802.11</v>
+        <v>94052205.27</v>
       </c>
       <c r="F85" t="n">
-        <v>67308724.47</v>
+        <v>68597084.84999999</v>
       </c>
       <c r="G85" t="n">
-        <v>50448377.81</v>
+        <v>52778478.87</v>
       </c>
       <c r="H85" t="n">
         <v>34226175.48</v>
@@ -3169,13 +3169,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>8608111.039999999</v>
+        <v>9702048.869999999</v>
       </c>
       <c r="F86" t="n">
-        <v>7468721.44</v>
+        <v>7864300.11</v>
       </c>
       <c r="G86" t="n">
-        <v>6663973.57</v>
+        <v>7063747.7</v>
       </c>
       <c r="H86" t="n">
         <v>5330446.31</v>
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4888035.82</v>
+        <v>4891050.94</v>
       </c>
       <c r="F87" t="n">
-        <v>4155155.28</v>
+        <v>4217438.36</v>
       </c>
       <c r="G87" t="n">
-        <v>2664310.36</v>
+        <v>2841737.61</v>
       </c>
       <c r="H87" t="n">
         <v>624962.6800000001</v>
@@ -3235,13 +3235,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>61473058.69</v>
+        <v>63159552.52</v>
       </c>
       <c r="F88" t="n">
-        <v>44586552.67</v>
+        <v>45039666.55</v>
       </c>
       <c r="G88" t="n">
-        <v>39824524.81</v>
+        <v>40270413.78</v>
       </c>
       <c r="H88" t="n">
         <v>20764040.49</v>
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>50207924.64</v>
+        <v>50915235.12</v>
       </c>
       <c r="F89" t="n">
-        <v>35984399.94</v>
+        <v>37016404.21</v>
       </c>
       <c r="G89" t="n">
-        <v>32175332.83</v>
+        <v>33146742.84</v>
       </c>
       <c r="H89" t="n">
-        <v>25448738.58</v>
+        <v>25474026.17</v>
       </c>
       <c r="I89" t="n">
-        <v>23458625.39</v>
+        <v>23478659.79</v>
       </c>
     </row>
     <row r="90">

--- a/upload/orgao2026.xlsx
+++ b/upload/orgao2026.xlsx
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22412731.08</v>
+        <v>22415131.08</v>
       </c>
       <c r="F2" t="n">
-        <v>16057982.45</v>
+        <v>16221742.57</v>
       </c>
       <c r="G2" t="n">
-        <v>14770969.04</v>
+        <v>14787594.36</v>
       </c>
       <c r="H2" t="n">
         <v>2727880.95</v>
       </c>
       <c r="I2" t="n">
-        <v>216907109.31</v>
+        <v>216944688.94</v>
       </c>
     </row>
     <row r="3">
@@ -529,10 +529,10 @@
         <v>1758306.07</v>
       </c>
       <c r="F3" t="n">
-        <v>1595087.63</v>
+        <v>1601588.54</v>
       </c>
       <c r="G3" t="n">
-        <v>1373221.21</v>
+        <v>1379722.12</v>
       </c>
       <c r="H3" t="n">
         <v>60903.67</v>
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>178862721.16</v>
+        <v>178896103.47</v>
       </c>
       <c r="F4" t="n">
-        <v>106511593.66</v>
+        <v>109545332.47</v>
       </c>
       <c r="G4" t="n">
-        <v>95725374.52</v>
+        <v>98750058.11</v>
       </c>
       <c r="H4" t="n">
-        <v>35281888.26</v>
+        <v>35391637.95</v>
       </c>
       <c r="I4" t="n">
-        <v>32694704.95</v>
+        <v>32828534.51</v>
       </c>
     </row>
     <row r="5">
@@ -595,10 +595,10 @@
         <v>2860809.88</v>
       </c>
       <c r="F5" t="n">
-        <v>1698394.62</v>
+        <v>1710660.75</v>
       </c>
       <c r="G5" t="n">
-        <v>1306085.67</v>
+        <v>1473770.81</v>
       </c>
       <c r="H5" t="n">
         <v>706301.5699999999</v>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2450833.21</v>
+        <v>2497227.64</v>
       </c>
       <c r="F6" t="n">
-        <v>1415667.52</v>
+        <v>1451380.33</v>
       </c>
       <c r="G6" t="n">
-        <v>1326508.19</v>
+        <v>1362028.33</v>
       </c>
       <c r="H6" t="n">
         <v>154717.57</v>
@@ -658,13 +658,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>24788305.35</v>
+        <v>24811305.35</v>
       </c>
       <c r="F7" t="n">
-        <v>18364673.28</v>
+        <v>18556561.21</v>
       </c>
       <c r="G7" t="n">
-        <v>16557822.36</v>
+        <v>16731304.3</v>
       </c>
       <c r="H7" t="n">
         <v>2353030.07</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76766769.73</v>
+        <v>77772291.09</v>
       </c>
       <c r="F8" t="n">
-        <v>29980302.65</v>
+        <v>30773321.07</v>
       </c>
       <c r="G8" t="n">
-        <v>25683712.12</v>
+        <v>27854296.19</v>
       </c>
       <c r="H8" t="n">
-        <v>43592820.58</v>
+        <v>45834152.39</v>
       </c>
       <c r="I8" t="n">
-        <v>46581282.35</v>
+        <v>47131914.41</v>
       </c>
     </row>
     <row r="9">
@@ -727,10 +727,10 @@
         <v>3484649.64</v>
       </c>
       <c r="F9" t="n">
-        <v>2604939.7</v>
+        <v>2695846.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2524184.66</v>
+        <v>2602959.85</v>
       </c>
       <c r="H9" t="n">
         <v>1345976.77</v>
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>77524765.95999999</v>
+        <v>81849575.48999999</v>
       </c>
       <c r="F10" t="n">
-        <v>70456275.34</v>
+        <v>72661047.7</v>
       </c>
       <c r="G10" t="n">
-        <v>62718785.61</v>
+        <v>63546344.13</v>
       </c>
       <c r="H10" t="n">
-        <v>14910668.98</v>
+        <v>14925708.98</v>
       </c>
       <c r="I10" t="n">
-        <v>13874186.51</v>
+        <v>13881706.51</v>
       </c>
     </row>
     <row r="11">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1406417218.49</v>
+        <v>1561236884.63</v>
       </c>
       <c r="F11" t="n">
-        <v>776397871</v>
+        <v>824490142.15</v>
       </c>
       <c r="G11" t="n">
-        <v>728049748.01</v>
+        <v>797316689.8200001</v>
       </c>
       <c r="H11" t="n">
-        <v>331700666.42</v>
+        <v>334598887.77</v>
       </c>
       <c r="I11" t="n">
-        <v>333354226.91</v>
+        <v>340409119.02</v>
       </c>
     </row>
     <row r="12">
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33875719.45</v>
+        <v>33881959.45</v>
       </c>
       <c r="F12" t="n">
-        <v>10009051.83</v>
+        <v>10198029.11</v>
       </c>
       <c r="G12" t="n">
-        <v>9220782.57</v>
+        <v>9409144.609999999</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -888,7 +888,7 @@
         <v>2193789.5</v>
       </c>
       <c r="F14" t="n">
-        <v>684033.7</v>
+        <v>789994.92</v>
       </c>
       <c r="G14" t="n">
         <v>663142.76</v>
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8621219.689999999</v>
+        <v>8645474.49</v>
       </c>
       <c r="F19" t="n">
-        <v>4348467.24</v>
+        <v>4390380.98</v>
       </c>
       <c r="G19" t="n">
-        <v>3970983.82</v>
+        <v>4020702.75</v>
       </c>
       <c r="H19" t="n">
         <v>1040158.72</v>
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>915987.11</v>
+        <v>918523.89</v>
       </c>
       <c r="F21" t="n">
-        <v>749130.83</v>
+        <v>749432.03</v>
       </c>
       <c r="G21" t="n">
-        <v>620996.6899999999</v>
+        <v>621295.3</v>
       </c>
       <c r="H21" t="n">
         <v>97349.38</v>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19066904.3</v>
+        <v>19082553.74</v>
       </c>
       <c r="F22" t="n">
-        <v>14346757.57</v>
+        <v>16420623.95</v>
       </c>
       <c r="G22" t="n">
-        <v>12797776.93</v>
+        <v>14435895.25</v>
       </c>
       <c r="H22" t="n">
         <v>4345882.84</v>
       </c>
       <c r="I22" t="n">
-        <v>7072643.18</v>
+        <v>7074260.62</v>
       </c>
     </row>
     <row r="23">
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8711290.779999999</v>
+        <v>8853290.779999999</v>
       </c>
       <c r="F23" t="n">
-        <v>7861769.57</v>
+        <v>7943980.07</v>
       </c>
       <c r="G23" t="n">
-        <v>6923683.74</v>
+        <v>6994334.95</v>
       </c>
       <c r="H23" t="n">
         <v>1741057.76</v>
@@ -1202,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1695831.09</v>
+        <v>1921024.46</v>
       </c>
       <c r="I24" t="n">
-        <v>1121378.69</v>
+        <v>1828815.27</v>
       </c>
     </row>
     <row r="25">
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7584853.16</v>
+        <v>11010371.13</v>
       </c>
       <c r="F26" t="n">
-        <v>4397596.11</v>
+        <v>4402545.3</v>
       </c>
       <c r="G26" t="n">
-        <v>4292134.09</v>
+        <v>4352573.91</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9236011.470000001</v>
+        <v>9417855.18</v>
       </c>
       <c r="F27" t="n">
-        <v>9048838.939999999</v>
+        <v>9060070.529999999</v>
       </c>
       <c r="G27" t="n">
-        <v>7557958.08</v>
+        <v>7626121.2</v>
       </c>
       <c r="H27" t="n">
         <v>1102595.36</v>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8299596.68</v>
+        <v>8382802.49</v>
       </c>
       <c r="F28" t="n">
-        <v>6974020.75</v>
+        <v>7013936.1</v>
       </c>
       <c r="G28" t="n">
-        <v>5677756.42</v>
+        <v>6297041.02</v>
       </c>
       <c r="H28" t="n">
         <v>1499694.06</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2415176.35</v>
+        <v>2719324.85</v>
       </c>
       <c r="F30" t="n">
         <v>1943303.29</v>
       </c>
       <c r="G30" t="n">
-        <v>144022.42</v>
+        <v>1346017.29</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13989349.97</v>
+        <v>14088679.2</v>
       </c>
       <c r="F33" t="n">
-        <v>9734642.720000001</v>
+        <v>10150334.06</v>
       </c>
       <c r="G33" t="n">
-        <v>8766726.93</v>
+        <v>9109782.140000001</v>
       </c>
       <c r="H33" t="n">
         <v>33176516.48</v>
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1368878692.33</v>
+        <v>1435771676.37</v>
       </c>
       <c r="F34" t="n">
-        <v>1081029455.44</v>
+        <v>1092570706.34</v>
       </c>
       <c r="G34" t="n">
-        <v>929716283.46</v>
+        <v>940775249.28</v>
       </c>
       <c r="H34" t="n">
-        <v>264059957.04</v>
+        <v>264060155.38</v>
       </c>
       <c r="I34" t="n">
-        <v>245461699.95</v>
+        <v>245461898.29</v>
       </c>
     </row>
     <row r="35">
@@ -1526,19 +1526,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>912946025.0700001</v>
+        <v>929143919.91</v>
       </c>
       <c r="F35" t="n">
-        <v>522966788.5</v>
+        <v>564219521.16</v>
       </c>
       <c r="G35" t="n">
-        <v>473923459.27</v>
+        <v>486997835.23</v>
       </c>
       <c r="H35" t="n">
-        <v>560557281.83</v>
+        <v>567287208.3099999</v>
       </c>
       <c r="I35" t="n">
-        <v>1003989453.26</v>
+        <v>1012471891.58</v>
       </c>
     </row>
     <row r="36">
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>40742651.83</v>
+        <v>42544902.07</v>
       </c>
       <c r="F36" t="n">
-        <v>11803169.43</v>
+        <v>12997497.91</v>
       </c>
       <c r="G36" t="n">
-        <v>9579574.91</v>
+        <v>10966232.21</v>
       </c>
       <c r="H36" t="n">
-        <v>38432869.59</v>
+        <v>38712818.59</v>
       </c>
       <c r="I36" t="n">
-        <v>45095365.05</v>
+        <v>43751685.05</v>
       </c>
     </row>
     <row r="37">
@@ -1628,10 +1628,10 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>759396.5699999999</v>
+        <v>774290.05</v>
       </c>
       <c r="I38" t="n">
-        <v>817342.46</v>
+        <v>832235.9399999999</v>
       </c>
     </row>
     <row r="39">
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>16360171.89</v>
+        <v>16375111.89</v>
       </c>
       <c r="F39" t="n">
-        <v>8293594.11</v>
+        <v>10834096.17</v>
       </c>
       <c r="G39" t="n">
-        <v>7886597.65</v>
+        <v>10372955.07</v>
       </c>
       <c r="H39" t="n">
-        <v>2138620.73</v>
+        <v>2161550.53</v>
       </c>
       <c r="I39" t="n">
-        <v>2100863.37</v>
+        <v>2125889.21</v>
       </c>
     </row>
     <row r="40">
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>468676689.38</v>
+        <v>478341486.01</v>
       </c>
       <c r="F40" t="n">
-        <v>371400371.77</v>
+        <v>381087576.67</v>
       </c>
       <c r="G40" t="n">
-        <v>333901396.41</v>
+        <v>342890753.62</v>
       </c>
       <c r="H40" t="n">
-        <v>99227455.22</v>
+        <v>99508258.3</v>
       </c>
       <c r="I40" t="n">
-        <v>100040710.36</v>
+        <v>100084193.41</v>
       </c>
     </row>
     <row r="41">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>195711.57</v>
+        <v>222775.76</v>
       </c>
       <c r="F41" t="n">
         <v>195711.57</v>
@@ -1778,19 +1778,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8184057.84</v>
+        <v>8163868.5</v>
       </c>
       <c r="F43" t="n">
-        <v>6198574.37</v>
+        <v>6300081.39</v>
       </c>
       <c r="G43" t="n">
-        <v>5339962.51</v>
+        <v>5457103.79</v>
       </c>
       <c r="H43" t="n">
-        <v>2415047.86</v>
+        <v>2576363.8</v>
       </c>
       <c r="I43" t="n">
-        <v>2264144.35</v>
+        <v>2281047.66</v>
       </c>
     </row>
     <row r="44">
@@ -1817,13 +1817,13 @@
         <v>23226.75</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>22948.03</v>
       </c>
       <c r="H44" t="n">
         <v>2205946.03</v>
       </c>
       <c r="I44" t="n">
-        <v>1064170.39</v>
+        <v>2170730.39</v>
       </c>
     </row>
     <row r="45">
@@ -1847,7 +1847,7 @@
         <v>583177905.95</v>
       </c>
       <c r="F45" t="n">
-        <v>230647259.75</v>
+        <v>235304145.23</v>
       </c>
       <c r="G45" t="n">
         <v>213416651.16</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1468123.42</v>
+        <v>1480644.25</v>
       </c>
       <c r="F46" t="n">
-        <v>932754.92</v>
+        <v>967430.05</v>
       </c>
       <c r="G46" t="n">
-        <v>847464.86</v>
+        <v>874286.28</v>
       </c>
       <c r="H46" t="n">
         <v>178281.27</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>208960267.02</v>
+        <v>211040578.99</v>
       </c>
       <c r="F49" t="n">
-        <v>142335784.14</v>
+        <v>146406584.76</v>
       </c>
       <c r="G49" t="n">
-        <v>126998862.51</v>
+        <v>129579455.13</v>
       </c>
       <c r="H49" t="n">
         <v>135331229.29</v>
       </c>
       <c r="I49" t="n">
-        <v>140999336.38</v>
+        <v>141000459.38</v>
       </c>
     </row>
     <row r="50">
@@ -2000,16 +2000,16 @@
         <v>15780207.31</v>
       </c>
       <c r="F50" t="n">
-        <v>14595939.09</v>
+        <v>14607689.09</v>
       </c>
       <c r="G50" t="n">
-        <v>14147972.19</v>
+        <v>14173841.97</v>
       </c>
       <c r="H50" t="n">
-        <v>19804561.95</v>
+        <v>19810018.83</v>
       </c>
       <c r="I50" t="n">
-        <v>21153997.41</v>
+        <v>21159454.29</v>
       </c>
     </row>
     <row r="51">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>94040664.15000001</v>
+        <v>94044732.23</v>
       </c>
       <c r="F51" t="n">
-        <v>56449925.57</v>
+        <v>57882497.43</v>
       </c>
       <c r="G51" t="n">
-        <v>51678950.23</v>
+        <v>54816106.12</v>
       </c>
       <c r="H51" t="n">
         <v>18617499.53</v>
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>48357328.44</v>
+        <v>48405402.56</v>
       </c>
       <c r="F52" t="n">
-        <v>20373193.2</v>
+        <v>21206390.26</v>
       </c>
       <c r="G52" t="n">
-        <v>18282605.72</v>
+        <v>18506076.14</v>
       </c>
       <c r="H52" t="n">
         <v>12470050.72</v>
@@ -2123,19 +2123,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>137766768.19</v>
+        <v>142871780.64</v>
       </c>
       <c r="F54" t="n">
-        <v>96435617.27</v>
+        <v>109643004.49</v>
       </c>
       <c r="G54" t="n">
-        <v>89496212.75</v>
+        <v>98165742.48</v>
       </c>
       <c r="H54" t="n">
-        <v>24470386.01</v>
+        <v>24490691.01</v>
       </c>
       <c r="I54" t="n">
-        <v>27283227.41</v>
+        <v>27303259.79</v>
       </c>
     </row>
     <row r="55">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29254510.7</v>
+        <v>29409821.91</v>
       </c>
       <c r="F55" t="n">
-        <v>20771691.61</v>
+        <v>21545152.47</v>
       </c>
       <c r="G55" t="n">
-        <v>19743619.63</v>
+        <v>20722017.78</v>
       </c>
       <c r="H55" t="n">
-        <v>21499979.92</v>
+        <v>22118707.18</v>
       </c>
       <c r="I55" t="n">
-        <v>22250624.42</v>
+        <v>22868744.96</v>
       </c>
     </row>
     <row r="56">
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>41361879.17</v>
+        <v>44031959.61</v>
       </c>
       <c r="F56" t="n">
-        <v>36339524.55</v>
+        <v>36904199.49</v>
       </c>
       <c r="G56" t="n">
-        <v>29599680.49</v>
+        <v>31023491.7</v>
       </c>
       <c r="H56" t="n">
-        <v>8597872.24</v>
+        <v>8627975.140000001</v>
       </c>
       <c r="I56" t="n">
-        <v>8342429.15</v>
+        <v>8371087.11</v>
       </c>
     </row>
     <row r="57">
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4244454.26</v>
+        <v>4266882.26</v>
       </c>
       <c r="F57" t="n">
-        <v>3534012.21</v>
+        <v>3546927.07</v>
       </c>
       <c r="G57" t="n">
-        <v>3160217.84</v>
+        <v>3173108.8</v>
       </c>
       <c r="H57" t="n">
         <v>532120.09</v>
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6626347.31</v>
+        <v>6719534.81</v>
       </c>
       <c r="F58" t="n">
-        <v>4593000.53</v>
+        <v>4597087.66</v>
       </c>
       <c r="G58" t="n">
-        <v>4316141.87</v>
+        <v>4320007.08</v>
       </c>
       <c r="H58" t="n">
-        <v>11011249.85</v>
+        <v>11029049.85</v>
       </c>
       <c r="I58" t="n">
-        <v>17945123.73</v>
+        <v>17962923.73</v>
       </c>
     </row>
     <row r="59">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14889268.38</v>
+        <v>14861291.68</v>
       </c>
       <c r="F59" t="n">
-        <v>8354338.78</v>
+        <v>8433425.58</v>
       </c>
       <c r="G59" t="n">
-        <v>7359850.01</v>
+        <v>7571977.46</v>
       </c>
       <c r="H59" t="n">
         <v>5237570.34</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8870211.75</v>
+        <v>9262595.25</v>
       </c>
       <c r="F60" t="n">
-        <v>8551148.310000001</v>
+        <v>9017803.58</v>
       </c>
       <c r="G60" t="n">
-        <v>7571737.4</v>
+        <v>7916640.25</v>
       </c>
       <c r="H60" t="n">
         <v>1332496.42</v>
@@ -2383,19 +2383,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>232647798.65</v>
+        <v>236204307.71</v>
       </c>
       <c r="F62" t="n">
-        <v>179474140.36</v>
+        <v>184849969.63</v>
       </c>
       <c r="G62" t="n">
-        <v>164044033.02</v>
+        <v>170020318.08</v>
       </c>
       <c r="H62" t="n">
-        <v>198702746.56</v>
+        <v>198983832.99</v>
       </c>
       <c r="I62" t="n">
-        <v>194038222.76</v>
+        <v>194272748.12</v>
       </c>
     </row>
     <row r="63">
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>64982945.34</v>
+        <v>67828383.36</v>
       </c>
       <c r="F63" t="n">
-        <v>48313652.61</v>
+        <v>48384727.31</v>
       </c>
       <c r="G63" t="n">
-        <v>43878050.8</v>
+        <v>43905078.36</v>
       </c>
       <c r="H63" t="n">
-        <v>35355654.72</v>
+        <v>35392114.99</v>
       </c>
       <c r="I63" t="n">
-        <v>53872540.51</v>
+        <v>53898519.67</v>
       </c>
     </row>
     <row r="64">
@@ -2449,13 +2449,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11535411.37</v>
+        <v>11541979.66</v>
       </c>
       <c r="F64" t="n">
-        <v>7897255.89</v>
+        <v>8064558.63</v>
       </c>
       <c r="G64" t="n">
-        <v>6923006.51</v>
+        <v>6925082.61</v>
       </c>
       <c r="H64" t="n">
         <v>1960878.57</v>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>490482.72</v>
+        <v>584746.91</v>
       </c>
       <c r="F65" t="n">
-        <v>465927.16</v>
+        <v>468155.48</v>
       </c>
       <c r="G65" t="n">
-        <v>403385.91</v>
+        <v>405609.52</v>
       </c>
       <c r="H65" t="n">
         <v>34744.58</v>
@@ -2575,19 +2575,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>232479853.5</v>
+        <v>234786515.26</v>
       </c>
       <c r="F68" t="n">
-        <v>165094113.05</v>
+        <v>171889919.57</v>
       </c>
       <c r="G68" t="n">
-        <v>150161761.81</v>
+        <v>151772993.4</v>
       </c>
       <c r="H68" t="n">
-        <v>49043143.94</v>
+        <v>49463492.27</v>
       </c>
       <c r="I68" t="n">
-        <v>45905990.09</v>
+        <v>48253127.95</v>
       </c>
     </row>
     <row r="69">
@@ -2608,19 +2608,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>256970178.73</v>
+        <v>260710928.02</v>
       </c>
       <c r="F69" t="n">
-        <v>177934179.72</v>
+        <v>194028271.69</v>
       </c>
       <c r="G69" t="n">
-        <v>150765256.24</v>
+        <v>166810496.62</v>
       </c>
       <c r="H69" t="n">
-        <v>86361197.8</v>
+        <v>88100410.09</v>
       </c>
       <c r="I69" t="n">
-        <v>83315396.78</v>
+        <v>84956671.15000001</v>
       </c>
     </row>
     <row r="70">
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>477380618.71</v>
+        <v>485810309.21</v>
       </c>
       <c r="F70" t="n">
-        <v>295919113.56</v>
+        <v>303996284.61</v>
       </c>
       <c r="G70" t="n">
-        <v>262226888.12</v>
+        <v>267816295.82</v>
       </c>
       <c r="H70" t="n">
-        <v>235470551.76</v>
+        <v>235557840.68</v>
       </c>
       <c r="I70" t="n">
-        <v>204464861.28</v>
+        <v>205152026.49</v>
       </c>
     </row>
     <row r="71">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1053263.69</v>
+        <v>1086537.57</v>
       </c>
       <c r="F71" t="n">
-        <v>986509.17</v>
+        <v>986783.6800000001</v>
       </c>
       <c r="G71" t="n">
-        <v>879915.6</v>
+        <v>880176.9300000001</v>
       </c>
       <c r="H71" t="n">
         <v>225243.01</v>
@@ -2707,19 +2707,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>58626232.99</v>
+        <v>58978647.59</v>
       </c>
       <c r="F72" t="n">
-        <v>37350954.11</v>
+        <v>38585801.96</v>
       </c>
       <c r="G72" t="n">
-        <v>31648987.72</v>
+        <v>37118035.4</v>
       </c>
       <c r="H72" t="n">
-        <v>19183311.44</v>
+        <v>19489131.64</v>
       </c>
       <c r="I72" t="n">
-        <v>25744326.97</v>
+        <v>26030133.64</v>
       </c>
     </row>
     <row r="73">
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1531035.25</v>
+        <v>1732099.9</v>
       </c>
       <c r="F73" t="n">
-        <v>1384147.9</v>
+        <v>1398181.53</v>
       </c>
       <c r="G73" t="n">
-        <v>1219226.89</v>
+        <v>1233215.85</v>
       </c>
       <c r="H73" t="n">
         <v>34378.25</v>
@@ -2773,19 +2773,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>79379683.33</v>
+        <v>79403938.59</v>
       </c>
       <c r="F74" t="n">
-        <v>62738119.71</v>
+        <v>64175278.12</v>
       </c>
       <c r="G74" t="n">
-        <v>58459714.89</v>
+        <v>60217584.82</v>
       </c>
       <c r="H74" t="n">
-        <v>65766547.38</v>
+        <v>66007855.09</v>
       </c>
       <c r="I74" t="n">
-        <v>62463232.6</v>
+        <v>62689623.1</v>
       </c>
     </row>
     <row r="75">
@@ -2806,13 +2806,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>18137837.9</v>
+        <v>19256664.18</v>
       </c>
       <c r="F75" t="n">
-        <v>13840440.2</v>
+        <v>15178006.27</v>
       </c>
       <c r="G75" t="n">
-        <v>11527200.15</v>
+        <v>12006129.05</v>
       </c>
       <c r="H75" t="n">
         <v>674995.91</v>
@@ -2839,19 +2839,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>241856312.98</v>
+        <v>242899915.51</v>
       </c>
       <c r="F76" t="n">
-        <v>11691118.77</v>
+        <v>11725453.81</v>
       </c>
       <c r="G76" t="n">
-        <v>10079518.92</v>
+        <v>10427477.65</v>
       </c>
       <c r="H76" t="n">
-        <v>49648869.32</v>
+        <v>50036034.12</v>
       </c>
       <c r="I76" t="n">
-        <v>41421517.35</v>
+        <v>47319399.62</v>
       </c>
     </row>
     <row r="77">
@@ -2872,19 +2872,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>25478388.46</v>
+        <v>26313213.94</v>
       </c>
       <c r="F77" t="n">
-        <v>19445201.81</v>
+        <v>21575294.77</v>
       </c>
       <c r="G77" t="n">
-        <v>17692331.93</v>
+        <v>17870272.12</v>
       </c>
       <c r="H77" t="n">
-        <v>17779414.2</v>
+        <v>18126905.4</v>
       </c>
       <c r="I77" t="n">
-        <v>28935408.97</v>
+        <v>29279133.49</v>
       </c>
     </row>
     <row r="78">
@@ -2905,19 +2905,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>918607465.41</v>
+        <v>953992229.74</v>
       </c>
       <c r="F78" t="n">
-        <v>683082086.26</v>
+        <v>723891311.2</v>
       </c>
       <c r="G78" t="n">
-        <v>629183941.86</v>
+        <v>698450457.41</v>
       </c>
       <c r="H78" t="n">
-        <v>149884628.2</v>
+        <v>155884404.2</v>
       </c>
       <c r="I78" t="n">
-        <v>345411113.7</v>
+        <v>351009889.12</v>
       </c>
     </row>
     <row r="79">
@@ -2938,19 +2938,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>182248930.28</v>
+        <v>182912408.42</v>
       </c>
       <c r="F79" t="n">
-        <v>128846454.85</v>
+        <v>134834701.28</v>
       </c>
       <c r="G79" t="n">
-        <v>103961641</v>
+        <v>107583959.85</v>
       </c>
       <c r="H79" t="n">
-        <v>61968308.03</v>
+        <v>62673101.03</v>
       </c>
       <c r="I79" t="n">
-        <v>65639495.09</v>
+        <v>66670976.86</v>
       </c>
     </row>
     <row r="80">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>28771347.44</v>
+        <v>30538470.74</v>
       </c>
       <c r="F80" t="n">
-        <v>26615604.56</v>
+        <v>26673915.73</v>
       </c>
       <c r="G80" t="n">
-        <v>24626636.26</v>
+        <v>24684840.67</v>
       </c>
       <c r="H80" t="n">
         <v>4983225.57</v>
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>52242879.13</v>
+        <v>53609808.85</v>
       </c>
       <c r="F81" t="n">
-        <v>26869439.93</v>
+        <v>29669424.88</v>
       </c>
       <c r="G81" t="n">
-        <v>25286014.99</v>
+        <v>26613915.68</v>
       </c>
       <c r="H81" t="n">
-        <v>30633300.39</v>
+        <v>92783753.01000001</v>
       </c>
       <c r="I81" t="n">
-        <v>87570361.79000001</v>
+        <v>149841879.2</v>
       </c>
     </row>
     <row r="82">
@@ -3037,19 +3037,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>576611011.3099999</v>
+        <v>606278842.4400001</v>
       </c>
       <c r="F82" t="n">
-        <v>433250971.97</v>
+        <v>446204838.77</v>
       </c>
       <c r="G82" t="n">
-        <v>409841865.09</v>
+        <v>422722271.24</v>
       </c>
       <c r="H82" t="n">
-        <v>144385399.99</v>
+        <v>144895064.91</v>
       </c>
       <c r="I82" t="n">
-        <v>151021272.44</v>
+        <v>152004702.77</v>
       </c>
     </row>
     <row r="83">
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>28109491.97</v>
+        <v>31512844.84</v>
       </c>
       <c r="F83" t="n">
-        <v>23468009.08</v>
+        <v>26993582.24</v>
       </c>
       <c r="G83" t="n">
-        <v>20509308.77</v>
+        <v>20987360.64</v>
       </c>
       <c r="H83" t="n">
         <v>4788552.39</v>
@@ -3103,13 +3103,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>281326512.47</v>
+        <v>284016956.71</v>
       </c>
       <c r="F84" t="n">
-        <v>202083921.6</v>
+        <v>207719080.21</v>
       </c>
       <c r="G84" t="n">
-        <v>180073109.26</v>
+        <v>186399379.79</v>
       </c>
       <c r="H84" t="n">
         <v>74964907.94</v>
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>94052205.27</v>
+        <v>94483925.47</v>
       </c>
       <c r="F85" t="n">
-        <v>68597084.84999999</v>
+        <v>69372102.87</v>
       </c>
       <c r="G85" t="n">
-        <v>52778478.87</v>
+        <v>58646143.53</v>
       </c>
       <c r="H85" t="n">
         <v>34226175.48</v>
@@ -3169,19 +3169,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>9702048.869999999</v>
+        <v>9992152.27</v>
       </c>
       <c r="F86" t="n">
-        <v>7864300.11</v>
+        <v>8249961.66</v>
       </c>
       <c r="G86" t="n">
-        <v>7063747.7</v>
+        <v>7420904.84</v>
       </c>
       <c r="H86" t="n">
-        <v>5330446.31</v>
+        <v>5342633.4</v>
       </c>
       <c r="I86" t="n">
-        <v>4783218.36</v>
+        <v>4795259.2</v>
       </c>
     </row>
     <row r="87">
@@ -3202,13 +3202,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4891050.94</v>
+        <v>5543851.35</v>
       </c>
       <c r="F87" t="n">
-        <v>4217438.36</v>
+        <v>4292556.54</v>
       </c>
       <c r="G87" t="n">
-        <v>2841737.61</v>
+        <v>3036744.6</v>
       </c>
       <c r="H87" t="n">
         <v>624962.6800000001</v>
@@ -3235,19 +3235,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>63159552.52</v>
+        <v>66762770.06</v>
       </c>
       <c r="F88" t="n">
-        <v>45039666.55</v>
+        <v>48062788.92</v>
       </c>
       <c r="G88" t="n">
-        <v>40270413.78</v>
+        <v>42846124.83</v>
       </c>
       <c r="H88" t="n">
-        <v>20764040.49</v>
+        <v>20790290.67</v>
       </c>
       <c r="I88" t="n">
-        <v>19975106.13</v>
+        <v>19991976.69</v>
       </c>
     </row>
     <row r="89">
@@ -3268,19 +3268,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>50915235.12</v>
+        <v>57160466.52</v>
       </c>
       <c r="F89" t="n">
-        <v>37016404.21</v>
+        <v>38069320.72</v>
       </c>
       <c r="G89" t="n">
-        <v>33146742.84</v>
+        <v>34126736.11</v>
       </c>
       <c r="H89" t="n">
-        <v>25474026.17</v>
+        <v>25670879.72</v>
       </c>
       <c r="I89" t="n">
-        <v>23478659.79</v>
+        <v>23665823.26</v>
       </c>
     </row>
     <row r="90">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2343525.26</v>
+        <v>2321177.78</v>
       </c>
       <c r="F90" t="n">
-        <v>1826706.26</v>
+        <v>2069207.73</v>
       </c>
       <c r="G90" t="n">
-        <v>1606511.41</v>
+        <v>1815836.86</v>
       </c>
       <c r="H90" t="n">
         <v>294468.9</v>
